--- a/appliances_wtp.xlsx
+++ b/appliances_wtp.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26502"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianadanilenko/Desktop/appliances_analysis/wtp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dand\Documents\GitHub\appliances_interventions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{23E2E8BA-67E3-0F4D-9CCD-93A102C0E96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78FA6AC0-C4F6-4F2E-AA4A-9CB58F9D6BE7}"/>
   <bookViews>
-    <workbookView xWindow="-4480" yWindow="-21600" windowWidth="38400" windowHeight="21600" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4470" yWindow="-21600" windowWidth="38400" windowHeight="21600" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -22,9 +21,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Appliances!$AR$1:$AR$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Usage!$A$1:$BN$53</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="29566" r:id="rId5"/>
+    <pivotCache cacheId="20" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,35 +45,62 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={73C2226C-6106-4DC2-88CF-9C0A06F48311}</author>
     <author>tc={CEE78422-255C-40DC-AFED-5AA185CC03E1}</author>
     <author>tc={C7CEED71-5EFE-4791-84D8-7010C40A69F0}</author>
   </authors>
   <commentList>
-    <comment ref="AQ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="AQ1" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     is this supposed to capture mean difference between control and treatment or ?</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="AZ1" authorId="1" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     daily kWh</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AQ22" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="AQ22" authorId="2" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     in kWh</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -82,26 +108,44 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={1DD52412-77C6-1E43-B8CC-07AD562D2C6E}</author>
     <author>tc={52E723F4-9A55-1E46-88F7-D2164B4696BA}</author>
   </authors>
   <commentList>
-    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="AA1" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     check label studies from srmt for label type</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AR15" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
+    <comment ref="AR15" authorId="1" shapeId="0">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     can we code them as relative WTP? </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -109,19 +153,28 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={CF36070F-7893-4948-8AB8-1CADF6EBBFD9}</author>
   </authors>
   <commentList>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="D6" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     a bit confused as of where it’s correlation and where - quasi-experimental
 Reply:
     the way i reassessed this was - market statistics - correlation, whereas hypothetical choice - quasi-experimental</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -129,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4112" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4109" uniqueCount="650">
   <si>
     <t>Coder</t>
   </si>
@@ -2518,11 +2571,17 @@
   <si>
     <t>Informing Versus Nudging in Environmental Policy</t>
   </si>
+  <si>
+    <t>3,15</t>
+  </si>
+  <si>
+    <t>1,83</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
@@ -2534,7 +2593,7 @@
     <numFmt numFmtId="171" formatCode="0.0000"/>
     <numFmt numFmtId="172" formatCode="0.0000;[Red]0.0000"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="41">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2773,6 +2832,19 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -3004,7 +3076,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3155,12 +3227,30 @@
     <xf numFmtId="2" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3192,7 +3282,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334" xr:uid="{D639B32B-9019-CA48-8E24-1BEF7DE87CE6}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:CD1048576" sheet="Appliances"/>
   </cacheSource>
@@ -34989,7 +35079,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E95B189-0291-5F4C-AF42-581998D9F62B}" name="PivotTable2" cacheId="29566" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -35844,9 +35934,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BP53"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="4" max="4" width="20.625" customWidth="1"/>
     <col min="5" max="5" width="14.125" customWidth="1"/>
@@ -35894,7 +35984,7 @@
     <col min="67" max="67" width="25.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="48">
+    <row r="1" spans="1:68" ht="45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -43692,7 +43782,7 @@
         <v>6.7567567567567571E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:66" s="41" customFormat="1" ht="17.100000000000001">
+    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A39" s="45" t="s">
         <v>68</v>
       </c>
@@ -43897,7 +43987,7 @@
       </c>
       <c r="BN39" s="43"/>
     </row>
-    <row r="40" spans="1:66" s="41" customFormat="1" ht="17.100000000000001">
+    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A40" s="45" t="s">
         <v>68</v>
       </c>
@@ -44102,7 +44192,7 @@
       </c>
       <c r="BN40" s="43"/>
     </row>
-    <row r="41" spans="1:66" s="41" customFormat="1" ht="17.100000000000001">
+    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A41" s="45" t="s">
         <v>68</v>
       </c>
@@ -44311,7 +44401,7 @@
         <v>2.0421052631578922</v>
       </c>
     </row>
-    <row r="42" spans="1:66" s="41" customFormat="1" ht="17.100000000000001">
+    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A42" s="45" t="s">
         <v>68</v>
       </c>
@@ -46708,34 +46798,34 @@
   </sheetData>
   <dataConsolidate/>
   <dataValidations count="10">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12">
       <formula1>$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12">
       <formula1>$D$2:$D$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51">
       <formula1>$D$2:$D$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51">
       <formula1>$F$2:$F$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -46744,43 +46834,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>BC23:BC28 BC54:BC1048576 BC33:BC38 BC1:BC12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$9</xm:f>
           </x14:formula1>
           <xm:sqref>J54:J1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>AS43:AX51 AS54:AX1048576 AS23:AX38 AS2:AX12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$10</xm:f>
           </x14:formula1>
           <xm:sqref>J38</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$E$2:$E$4</xm:f>
           </x14:formula1>
           <xm:sqref>AO43:AO51</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$6</xm:f>
           </x14:formula1>
           <xm:sqref>K54:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$7</xm:f>
           </x14:formula1>
@@ -46793,9 +46883,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CH76"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="5" max="5" width="24.625" customWidth="1"/>
     <col min="6" max="6" width="17.625" customWidth="1"/>
@@ -47337,19 +47427,19 @@
         <v>0</v>
       </c>
       <c r="BX2" s="30">
-        <f>((AZ2^2)/(AZ2^2+BI2))^(1/2)</f>
+        <f t="shared" ref="BX2:BX33" si="0">((AZ2^2)/(AZ2^2+BI2))^(1/2)</f>
         <v>0.15374448735583945</v>
       </c>
       <c r="BY2" s="30">
-        <f>0.5*LN((1+BX2)/(1-BX2))</f>
+        <f t="shared" ref="BY2:BY33" si="1">0.5*LN((1+BX2)/(1-BX2))</f>
         <v>0.15497333468721167</v>
       </c>
       <c r="BZ2" s="30">
-        <f>((1-(BY2^2)^2)/(BI2-1))</f>
+        <f t="shared" ref="BZ2:BZ33" si="2">((1-(BY2^2)^2)/(BI2-1))</f>
         <v>1.4806269577269365E-3</v>
       </c>
       <c r="CA2" s="30">
-        <f>1/(BI2-3)</f>
+        <f t="shared" ref="CA2:CA33" si="3">1/(BI2-3)</f>
         <v>1.4858841010401188E-3</v>
       </c>
       <c r="CC2">
@@ -47596,19 +47686,19 @@
         <v>1</v>
       </c>
       <c r="BX3" s="30">
-        <f>((AZ3^2)/(AZ3^2+BI3))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>1.3921746511164878E-2</v>
       </c>
       <c r="BY3" s="30">
-        <f>0.5*LN((1+BX3)/(1-BX3))</f>
+        <f t="shared" si="1"/>
         <v>1.3922646030325031E-2</v>
       </c>
       <c r="BZ3" s="30">
-        <f>((1-(BY3^2)^2)/(BI3-1))</f>
+        <f t="shared" si="2"/>
         <v>4.1000408463551713E-4</v>
       </c>
       <c r="CA3" s="30">
-        <f>1/(BI3-3)</f>
+        <f t="shared" si="3"/>
         <v>4.103405826836274E-4</v>
       </c>
       <c r="CC3">
@@ -47616,19 +47706,19 @@
         <v>2438</v>
       </c>
       <c r="CE3" s="30">
-        <f t="shared" ref="CE3:CE62" si="0">((AZ3^2)/(AZ3^2+BJ3))^(1/2)</f>
+        <f t="shared" ref="CE3:CE62" si="4">((AZ3^2)/(AZ3^2+BJ3))^(1/2)</f>
         <v>8.0630640330570883E-3</v>
       </c>
       <c r="CF3" s="30">
-        <f t="shared" ref="CF3:CF62" si="1">0.5*LN((1+CE3)/(1-CE3))</f>
+        <f t="shared" ref="CF3:CF62" si="5">0.5*LN((1+CE3)/(1-CE3))</f>
         <v>8.0632387745383748E-3</v>
       </c>
       <c r="CG3" s="30">
-        <f t="shared" ref="CG3:CG62" si="2">((1-(CF3^2)^2)/(BJ3-1))</f>
+        <f t="shared" ref="CG3:CG62" si="6">((1-(CF3^2)^2)/(BJ3-1))</f>
         <v>1.374759411290821E-4</v>
       </c>
       <c r="CH3" s="30">
-        <f t="shared" ref="CH3:CH62" si="3">1/(BJ3-3)</f>
+        <f t="shared" ref="CH3:CH62" si="7">1/(BJ3-3)</f>
         <v>1.3751375137513751E-4</v>
       </c>
     </row>
@@ -47856,19 +47946,19 @@
         <v>1</v>
       </c>
       <c r="BX4" s="104">
-        <f>((AZ4^2)/(AZ4^2+BI4))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>2.4066942415906588E-2</v>
       </c>
       <c r="BY4" s="104">
-        <f>0.5*LN((1+BX4)/(1-BX4))</f>
+        <f t="shared" si="1"/>
         <v>2.4071590697916326E-2</v>
       </c>
       <c r="BZ4" s="104">
-        <f>((1-(BY4^2)^2)/(BI4-1))</f>
+        <f t="shared" si="2"/>
         <v>2.9940109708011158E-3</v>
       </c>
       <c r="CA4" s="95">
-        <f>1/(BI4-3)</f>
+        <f t="shared" si="3"/>
         <v>3.0120481927710845E-3</v>
       </c>
       <c r="CC4">
@@ -47876,19 +47966,19 @@
         <v>333</v>
       </c>
       <c r="CE4" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.4066942415906588E-2</v>
       </c>
       <c r="CF4" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.4071590697916326E-2</v>
       </c>
       <c r="CG4" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>2.9940109708011158E-3</v>
       </c>
       <c r="CH4" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.0120481927710845E-3</v>
       </c>
     </row>
@@ -48117,19 +48207,19 @@
         <v>1</v>
       </c>
       <c r="BX5" s="104">
-        <f>((AZ5^2)/(AZ5^2+BI5))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.18088754235543161</v>
       </c>
       <c r="BY5" s="104">
-        <f>0.5*LN((1+BX5)/(1-BX5))</f>
+        <f t="shared" si="1"/>
         <v>0.18290010196181533</v>
       </c>
       <c r="BZ5" s="104">
-        <f>((1-(BY5^2)^2)/(BI5-1))</f>
+        <f t="shared" si="2"/>
         <v>2.2753552022091081E-3</v>
       </c>
       <c r="CA5" s="95">
-        <f>1/(BI5-3)</f>
+        <f t="shared" si="3"/>
         <v>2.2883295194508009E-3</v>
       </c>
       <c r="CB5"/>
@@ -48139,19 +48229,19 @@
       </c>
       <c r="CD5"/>
       <c r="CE5" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0.18088754235543161</v>
       </c>
       <c r="CF5" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.18290010196181533</v>
       </c>
       <c r="CG5" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>2.2753552022091081E-3</v>
       </c>
       <c r="CH5" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2.2883295194508009E-3</v>
       </c>
     </row>
@@ -48378,19 +48468,19 @@
         <v>1</v>
       </c>
       <c r="BX6" s="104">
-        <f>((AZ6^2)/(AZ6^2+BI6))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.47242735990047685</v>
       </c>
       <c r="BY6" s="104">
-        <f>0.5*LN((1+BX6)/(1-BX6))</f>
+        <f t="shared" si="1"/>
         <v>0.51319051047617226</v>
       </c>
       <c r="BZ6" s="104">
-        <f>((1-(BY6^2)^2)/(BI6-1))</f>
+        <f t="shared" si="2"/>
         <v>6.6760340037102519E-4</v>
       </c>
       <c r="CA6" s="104">
-        <f>1/(BI6-3)</f>
+        <f t="shared" si="3"/>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CC6">
@@ -48398,19 +48488,19 @@
         <v>1394</v>
       </c>
       <c r="CE6" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0.47242735990047685</v>
       </c>
       <c r="CF6" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.51319051047617226</v>
       </c>
       <c r="CG6" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>6.6760340037102519E-4</v>
       </c>
       <c r="CH6" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
@@ -48638,19 +48728,19 @@
         <v>1</v>
       </c>
       <c r="BX7" s="104">
-        <f>((AZ7^2)/(AZ7^2+BI7))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.29473516954008327</v>
       </c>
       <c r="BY7" s="104">
-        <f>0.5*LN((1+BX7)/(1-BX7))</f>
+        <f t="shared" si="1"/>
         <v>0.3037440363085756</v>
       </c>
       <c r="BZ7" s="104">
-        <f>((1-(BY7^2)^2)/(BI7-1))</f>
+        <f t="shared" si="2"/>
         <v>7.1125395357683058E-4</v>
       </c>
       <c r="CA7" s="104">
-        <f>1/(BI7-3)</f>
+        <f t="shared" si="3"/>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB7"/>
@@ -48660,19 +48750,19 @@
       </c>
       <c r="CD7"/>
       <c r="CE7" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0.29473516954008327</v>
       </c>
       <c r="CF7" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.3037440363085756</v>
       </c>
       <c r="CG7" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>7.1125395357683058E-4</v>
       </c>
       <c r="CH7" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
@@ -48899,41 +48989,41 @@
         <v>0</v>
       </c>
       <c r="BX8" s="104">
-        <f>((AZ8^2)/(AZ8^2+BI8))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.32021801928313393</v>
       </c>
       <c r="BY8" s="104">
-        <f>0.5*LN((1+BX8)/(1-BX8))</f>
+        <f t="shared" si="1"/>
         <v>0.33189001894838011</v>
       </c>
       <c r="BZ8" s="104">
-        <f>((1-(BY8^2)^2)/(BI8-1))</f>
+        <f t="shared" si="2"/>
         <v>2.822476458784471E-2</v>
       </c>
       <c r="CA8" s="104">
-        <f>1/(BI8-3)</f>
+        <f t="shared" si="3"/>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="CB8"/>
       <c r="CC8">
-        <f>BI8-2</f>
+        <f t="shared" ref="CC8:CC36" si="8">BI8-2</f>
         <v>34</v>
       </c>
       <c r="CD8"/>
       <c r="CE8" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.1459137182263048E-2</v>
       </c>
       <c r="CF8" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.1462432031373494E-2</v>
       </c>
       <c r="CG8" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.1201969170096179E-4</v>
       </c>
       <c r="CH8" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
@@ -49160,39 +49250,39 @@
         <v>0</v>
       </c>
       <c r="BX9" s="104">
-        <f>((AZ9^2)/(AZ9^2+BI9))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.32021801928313393</v>
       </c>
       <c r="BY9" s="104">
-        <f>0.5*LN((1+BX9)/(1-BX9))</f>
+        <f t="shared" si="1"/>
         <v>0.33189001894838011</v>
       </c>
       <c r="BZ9" s="104">
-        <f>((1-(BY9^2)^2)/(BI9-1))</f>
+        <f t="shared" si="2"/>
         <v>2.822476458784471E-2</v>
       </c>
       <c r="CA9" s="104">
-        <f>1/(BI9-3)</f>
+        <f t="shared" si="3"/>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="CC9">
-        <f>BI9-2</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="CE9" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.1459137182263048E-2</v>
       </c>
       <c r="CF9" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.1462432031373494E-2</v>
       </c>
       <c r="CG9" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.1201969170096179E-4</v>
       </c>
       <c r="CH9" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
@@ -49419,39 +49509,39 @@
         <v>0</v>
       </c>
       <c r="BX10" s="104">
-        <f>((AZ10^2)/(AZ10^2+BI10))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.5126110197955529</v>
       </c>
       <c r="BY10" s="104">
-        <f>0.5*LN((1+BX10)/(1-BX10))</f>
+        <f t="shared" si="1"/>
         <v>0.56626502857004413</v>
       </c>
       <c r="BZ10" s="104">
-        <f>((1-(BY10^2)^2)/(BI10-1))</f>
+        <f t="shared" si="2"/>
         <v>2.5633705048672264E-2</v>
       </c>
       <c r="CA10" s="104">
-        <f>1/(BI10-3)</f>
+        <f t="shared" si="3"/>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="CC10">
-        <f>BI10-2</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="CE10" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.788338276740591E-2</v>
       </c>
       <c r="CF10" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.7901521176417756E-2</v>
       </c>
       <c r="CG10" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.1201948430548235E-4</v>
       </c>
       <c r="CH10" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
@@ -49678,39 +49768,39 @@
         <v>0</v>
       </c>
       <c r="BX11" s="104">
-        <f>((AZ11^2)/(AZ11^2+BI11))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.5126110197955529</v>
       </c>
       <c r="BY11" s="104">
-        <f>0.5*LN((1+BX11)/(1-BX11))</f>
+        <f t="shared" si="1"/>
         <v>0.56626502857004413</v>
       </c>
       <c r="BZ11" s="104">
-        <f>((1-(BY11^2)^2)/(BI11-1))</f>
+        <f t="shared" si="2"/>
         <v>2.5633705048672264E-2</v>
       </c>
       <c r="CA11" s="104">
-        <f>1/(BI11-3)</f>
+        <f t="shared" si="3"/>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="CC11">
-        <f>BI11-2</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="CE11" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.788338276740591E-2</v>
       </c>
       <c r="CF11" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.7901521176417756E-2</v>
       </c>
       <c r="CG11" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.1201948430548235E-4</v>
       </c>
       <c r="CH11" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
@@ -49937,39 +50027,39 @@
         <v>0</v>
       </c>
       <c r="BX12" s="104">
-        <f>((AZ12^2)/(AZ12^2+BI12))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.5126110197955529</v>
       </c>
       <c r="BY12" s="104">
-        <f>0.5*LN((1+BX12)/(1-BX12))</f>
+        <f t="shared" si="1"/>
         <v>0.56626502857004413</v>
       </c>
       <c r="BZ12" s="104">
-        <f>((1-(BY12^2)^2)/(BI12-1))</f>
+        <f t="shared" si="2"/>
         <v>2.5633705048672264E-2</v>
       </c>
       <c r="CA12" s="104">
-        <f>1/(BI12-3)</f>
+        <f t="shared" si="3"/>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="CC12">
-        <f>BI12-2</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="CE12" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.788338276740591E-2</v>
       </c>
       <c r="CF12" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.7901521176417756E-2</v>
       </c>
       <c r="CG12" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.1201948430548235E-4</v>
       </c>
       <c r="CH12" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
@@ -50196,39 +50286,39 @@
         <v>0</v>
       </c>
       <c r="BX13" s="104">
-        <f>((AZ13^2)/(AZ13^2+BI13))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.5126110197955529</v>
       </c>
       <c r="BY13" s="104">
-        <f>0.5*LN((1+BX13)/(1-BX13))</f>
+        <f t="shared" si="1"/>
         <v>0.56626502857004413</v>
       </c>
       <c r="BZ13" s="104">
-        <f>((1-(BY13^2)^2)/(BI13-1))</f>
+        <f t="shared" si="2"/>
         <v>2.5633705048672264E-2</v>
       </c>
       <c r="CA13" s="104">
-        <f>1/(BI13-3)</f>
+        <f t="shared" si="3"/>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="CC13">
-        <f>BI13-2</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="CE13" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.788338276740591E-2</v>
       </c>
       <c r="CF13" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.7901521176417756E-2</v>
       </c>
       <c r="CG13" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.1201948430548235E-4</v>
       </c>
       <c r="CH13" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
@@ -50385,7 +50475,7 @@
         <v>1</v>
       </c>
       <c r="AZ14">
-        <f>TINV(AX14,CC14)</f>
+        <f t="shared" ref="AZ14:AZ23" si="9">TINV(AX14,CC14)</f>
         <v>3.3101701484367259</v>
       </c>
       <c r="BA14" s="99" t="s">
@@ -50456,39 +50546,39 @@
         <v>1</v>
       </c>
       <c r="BX14" s="30">
-        <f>((AZ14^2)/(AZ14^2+BI14))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.1464394351286451</v>
       </c>
       <c r="BY14" s="30">
-        <f>0.5*LN((1+BX14)/(1-BX14))</f>
+        <f t="shared" si="1"/>
         <v>0.14749988735332095</v>
       </c>
       <c r="BZ14" s="30">
-        <f>((1-(BY14^2)^2)/(BI14-1))</f>
+        <f t="shared" si="2"/>
         <v>2.0030594529697188E-3</v>
       </c>
       <c r="CA14" s="30">
-        <f>1/(BI14-3)</f>
+        <f t="shared" si="3"/>
         <v>2.012072434607646E-3</v>
       </c>
       <c r="CC14">
-        <f>BI14-2</f>
+        <f t="shared" si="8"/>
         <v>498</v>
       </c>
       <c r="CE14" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>7.3815726974840262E-2</v>
       </c>
       <c r="CF14" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>7.395023508930447E-2</v>
       </c>
       <c r="CG14" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>5.0023516458549868E-4</v>
       </c>
       <c r="CH14" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.00751126690035E-4</v>
       </c>
     </row>
@@ -50645,7 +50735,7 @@
         <v>3</v>
       </c>
       <c r="AZ15">
-        <f>TINV(AX15,CC15)</f>
+        <f t="shared" si="9"/>
         <v>2.5857376110802122</v>
       </c>
       <c r="BA15" s="99" t="s">
@@ -50716,39 +50806,39 @@
         <v>1</v>
       </c>
       <c r="BX15" s="30">
-        <f>((AZ15^2)/(AZ15^2+BI15))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.11487221186750445</v>
       </c>
       <c r="BY15" s="30">
-        <f>0.5*LN((1+BX15)/(1-BX15))</f>
+        <f t="shared" si="1"/>
         <v>0.11538152059067894</v>
       </c>
       <c r="BZ15" s="30">
-        <f>((1-(BY15^2)^2)/(BI15-1))</f>
+        <f t="shared" si="2"/>
         <v>2.0036528393164244E-3</v>
       </c>
       <c r="CA15" s="30">
-        <f>1/(BI15-3)</f>
+        <f t="shared" si="3"/>
         <v>2.012072434607646E-3</v>
       </c>
       <c r="CC15">
-        <f>BI15-2</f>
+        <f t="shared" si="8"/>
         <v>498</v>
       </c>
       <c r="CE15" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>5.7722447571881538E-2</v>
       </c>
       <c r="CF15" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>5.7786684145923431E-2</v>
       </c>
       <c r="CG15" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>5.00244546808272E-4</v>
       </c>
       <c r="CH15" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.00751126690035E-4</v>
       </c>
     </row>
@@ -50905,7 +50995,7 @@
         <v>1</v>
       </c>
       <c r="AZ16">
-        <f>TINV(AX16,CC16)</f>
+        <f t="shared" si="9"/>
         <v>1.9645365010317388</v>
       </c>
       <c r="BA16" t="s">
@@ -50975,39 +51065,39 @@
         <v>1</v>
       </c>
       <c r="BX16" s="30">
-        <f>((AZ16^2)/(AZ16^2+BI16))^(1/2)</f>
-        <v>8.5669312189989619E-2</v>
-      </c>
-      <c r="BY16" s="30">
-        <f>0.5*LN((1+BX16)/(1-BX16))</f>
-        <v>8.5879822251689428E-2</v>
-      </c>
-      <c r="BZ16" s="30">
-        <f>((1-(BY16^2)^2)/(BI16-1))</f>
-        <v>1.9192813902165059E-3</v>
-      </c>
-      <c r="CA16" s="30">
-        <f>1/(BI16-3)</f>
-        <v>1.9267822736030828E-3</v>
-      </c>
-      <c r="CC16">
-        <f>BI16-2</f>
-        <v>520</v>
-      </c>
-      <c r="CE16" s="30">
         <f t="shared" si="0"/>
         <v>8.5669312189989619E-2</v>
       </c>
-      <c r="CF16" s="30">
+      <c r="BY16" s="30">
         <f t="shared" si="1"/>
         <v>8.5879822251689428E-2</v>
       </c>
-      <c r="CG16" s="30">
+      <c r="BZ16" s="30">
         <f t="shared" si="2"/>
         <v>1.9192813902165059E-3</v>
       </c>
+      <c r="CA16" s="30">
+        <f t="shared" si="3"/>
+        <v>1.9267822736030828E-3</v>
+      </c>
+      <c r="CC16">
+        <f t="shared" si="8"/>
+        <v>520</v>
+      </c>
+      <c r="CE16" s="30">
+        <f t="shared" si="4"/>
+        <v>8.5669312189989619E-2</v>
+      </c>
+      <c r="CF16" s="30">
+        <f t="shared" si="5"/>
+        <v>8.5879822251689428E-2</v>
+      </c>
+      <c r="CG16" s="30">
+        <f t="shared" si="6"/>
+        <v>1.9192813902165059E-3</v>
+      </c>
       <c r="CH16" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -51164,7 +51254,7 @@
         <v>1</v>
       </c>
       <c r="AZ17">
-        <f>TINV(AX17,CC17)</f>
+        <f t="shared" si="9"/>
         <v>1.6477892114622541</v>
       </c>
       <c r="BA17" t="s">
@@ -51234,39 +51324,39 @@
         <v>1</v>
       </c>
       <c r="BX17" s="30">
-        <f>((AZ17^2)/(AZ17^2+BI17))^(1/2)</f>
-        <v>7.1934930559867688E-2</v>
-      </c>
-      <c r="BY17" s="30">
-        <f>0.5*LN((1+BX17)/(1-BX17))</f>
-        <v>7.2059396212325363E-2</v>
-      </c>
-      <c r="BZ17" s="30">
-        <f>((1-(BY17^2)^2)/(BI17-1))</f>
-        <v>1.919334044829439E-3</v>
-      </c>
-      <c r="CA17" s="30">
-        <f>1/(BI17-3)</f>
-        <v>1.9267822736030828E-3</v>
-      </c>
-      <c r="CC17">
-        <f>BI17-2</f>
-        <v>520</v>
-      </c>
-      <c r="CE17" s="30">
         <f t="shared" si="0"/>
         <v>7.1934930559867688E-2</v>
       </c>
-      <c r="CF17" s="30">
+      <c r="BY17" s="30">
         <f t="shared" si="1"/>
         <v>7.2059396212325363E-2</v>
       </c>
-      <c r="CG17" s="30">
+      <c r="BZ17" s="30">
         <f t="shared" si="2"/>
         <v>1.919334044829439E-3</v>
       </c>
+      <c r="CA17" s="30">
+        <f t="shared" si="3"/>
+        <v>1.9267822736030828E-3</v>
+      </c>
+      <c r="CC17">
+        <f t="shared" si="8"/>
+        <v>520</v>
+      </c>
+      <c r="CE17" s="30">
+        <f t="shared" si="4"/>
+        <v>7.1934930559867688E-2</v>
+      </c>
+      <c r="CF17" s="30">
+        <f t="shared" si="5"/>
+        <v>7.2059396212325363E-2</v>
+      </c>
+      <c r="CG17" s="30">
+        <f t="shared" si="6"/>
+        <v>1.919334044829439E-3</v>
+      </c>
       <c r="CH17" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -51423,7 +51513,7 @@
         <v>1</v>
       </c>
       <c r="AZ18">
-        <f>TINV(AX18,CC18)</f>
+        <f t="shared" si="9"/>
         <v>1.6477892114622541</v>
       </c>
       <c r="BA18" t="s">
@@ -51493,39 +51583,39 @@
         <v>1</v>
       </c>
       <c r="BX18" s="30">
-        <f>((AZ18^2)/(AZ18^2+BI18))^(1/2)</f>
-        <v>7.1934930559867688E-2</v>
-      </c>
-      <c r="BY18" s="30">
-        <f>0.5*LN((1+BX18)/(1-BX18))</f>
-        <v>7.2059396212325363E-2</v>
-      </c>
-      <c r="BZ18" s="30">
-        <f>((1-(BY18^2)^2)/(BI18-1))</f>
-        <v>1.919334044829439E-3</v>
-      </c>
-      <c r="CA18" s="30">
-        <f>1/(BI18-3)</f>
-        <v>1.9267822736030828E-3</v>
-      </c>
-      <c r="CC18">
-        <f>BI18-2</f>
-        <v>520</v>
-      </c>
-      <c r="CE18" s="30">
         <f t="shared" si="0"/>
         <v>7.1934930559867688E-2</v>
       </c>
-      <c r="CF18" s="30">
+      <c r="BY18" s="30">
         <f t="shared" si="1"/>
         <v>7.2059396212325363E-2</v>
       </c>
-      <c r="CG18" s="30">
+      <c r="BZ18" s="30">
         <f t="shared" si="2"/>
         <v>1.919334044829439E-3</v>
       </c>
+      <c r="CA18" s="30">
+        <f t="shared" si="3"/>
+        <v>1.9267822736030828E-3</v>
+      </c>
+      <c r="CC18">
+        <f t="shared" si="8"/>
+        <v>520</v>
+      </c>
+      <c r="CE18" s="30">
+        <f t="shared" si="4"/>
+        <v>7.1934930559867688E-2</v>
+      </c>
+      <c r="CF18" s="30">
+        <f t="shared" si="5"/>
+        <v>7.2059396212325363E-2</v>
+      </c>
+      <c r="CG18" s="30">
+        <f t="shared" si="6"/>
+        <v>1.919334044829439E-3</v>
+      </c>
       <c r="CH18" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -51682,7 +51772,7 @@
         <v>2</v>
       </c>
       <c r="AZ19">
-        <f>TINV(AX19,CC19)</f>
+        <f t="shared" si="9"/>
         <v>1.6477892114622541</v>
       </c>
       <c r="BA19" t="s">
@@ -51752,39 +51842,39 @@
         <v>1</v>
       </c>
       <c r="BX19" s="30">
-        <f>((AZ19^2)/(AZ19^2+BI19))^(1/2)</f>
-        <v>7.1934930559867688E-2</v>
-      </c>
-      <c r="BY19" s="30">
-        <f>0.5*LN((1+BX19)/(1-BX19))</f>
-        <v>7.2059396212325363E-2</v>
-      </c>
-      <c r="BZ19" s="30">
-        <f>((1-(BY19^2)^2)/(BI19-1))</f>
-        <v>1.919334044829439E-3</v>
-      </c>
-      <c r="CA19" s="30">
-        <f>1/(BI19-3)</f>
-        <v>1.9267822736030828E-3</v>
-      </c>
-      <c r="CC19">
-        <f>BI19-2</f>
-        <v>520</v>
-      </c>
-      <c r="CE19" s="30">
         <f t="shared" si="0"/>
         <v>7.1934930559867688E-2</v>
       </c>
-      <c r="CF19" s="30">
+      <c r="BY19" s="30">
         <f t="shared" si="1"/>
         <v>7.2059396212325363E-2</v>
       </c>
-      <c r="CG19" s="30">
+      <c r="BZ19" s="30">
         <f t="shared" si="2"/>
         <v>1.919334044829439E-3</v>
       </c>
+      <c r="CA19" s="30">
+        <f t="shared" si="3"/>
+        <v>1.9267822736030828E-3</v>
+      </c>
+      <c r="CC19">
+        <f t="shared" si="8"/>
+        <v>520</v>
+      </c>
+      <c r="CE19" s="30">
+        <f t="shared" si="4"/>
+        <v>7.1934930559867688E-2</v>
+      </c>
+      <c r="CF19" s="30">
+        <f t="shared" si="5"/>
+        <v>7.2059396212325363E-2</v>
+      </c>
+      <c r="CG19" s="30">
+        <f t="shared" si="6"/>
+        <v>1.919334044829439E-3</v>
+      </c>
       <c r="CH19" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -51941,7 +52031,7 @@
         <v>1</v>
       </c>
       <c r="AZ20">
-        <f>TINV(AX20,CC20)</f>
+        <f t="shared" si="9"/>
         <v>2.5853169622486396</v>
       </c>
       <c r="BA20" t="s">
@@ -52011,39 +52101,39 @@
         <v>1</v>
       </c>
       <c r="BX20" s="30">
-        <f>((AZ20^2)/(AZ20^2+BI20))^(1/2)</f>
-        <v>0.11243868763294575</v>
-      </c>
-      <c r="BY20" s="30">
-        <f>0.5*LN((1+BX20)/(1-BX20))</f>
-        <v>0.11291614848050519</v>
-      </c>
-      <c r="BZ20" s="30">
-        <f>((1-(BY20^2)^2)/(BI20-1))</f>
-        <v>1.9190737736219023E-3</v>
-      </c>
-      <c r="CA20" s="30">
-        <f>1/(BI20-3)</f>
-        <v>1.9267822736030828E-3</v>
-      </c>
-      <c r="CC20">
-        <f>BI20-2</f>
-        <v>520</v>
-      </c>
-      <c r="CE20" s="30">
         <f t="shared" si="0"/>
         <v>0.11243868763294575</v>
       </c>
-      <c r="CF20" s="30">
+      <c r="BY20" s="30">
         <f t="shared" si="1"/>
         <v>0.11291614848050519</v>
       </c>
-      <c r="CG20" s="30">
+      <c r="BZ20" s="30">
         <f t="shared" si="2"/>
         <v>1.9190737736219023E-3</v>
       </c>
+      <c r="CA20" s="30">
+        <f t="shared" si="3"/>
+        <v>1.9267822736030828E-3</v>
+      </c>
+      <c r="CC20">
+        <f t="shared" si="8"/>
+        <v>520</v>
+      </c>
+      <c r="CE20" s="30">
+        <f t="shared" si="4"/>
+        <v>0.11243868763294575</v>
+      </c>
+      <c r="CF20" s="30">
+        <f t="shared" si="5"/>
+        <v>0.11291614848050519</v>
+      </c>
+      <c r="CG20" s="30">
+        <f t="shared" si="6"/>
+        <v>1.9190737736219023E-3</v>
+      </c>
       <c r="CH20" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -52200,7 +52290,7 @@
         <v>1</v>
       </c>
       <c r="AZ21">
-        <f>TINV(AX21,CC21)</f>
+        <f t="shared" si="9"/>
         <v>2.5853169622486396</v>
       </c>
       <c r="BA21" t="s">
@@ -52271,41 +52361,41 @@
         <v>1</v>
       </c>
       <c r="BX21" s="30">
-        <f>((AZ21^2)/(AZ21^2+BI21))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.11243868763294575</v>
       </c>
       <c r="BY21" s="30">
-        <f>0.5*LN((1+BX21)/(1-BX21))</f>
+        <f t="shared" si="1"/>
         <v>0.11291614848050519</v>
       </c>
       <c r="BZ21" s="30">
-        <f>((1-(BY21^2)^2)/(BI21-1))</f>
+        <f t="shared" si="2"/>
         <v>1.9190737736219023E-3</v>
       </c>
       <c r="CA21" s="30">
-        <f>1/(BI21-3)</f>
+        <f t="shared" si="3"/>
         <v>1.9267822736030828E-3</v>
       </c>
       <c r="CB21"/>
       <c r="CC21">
-        <f>BI21-2</f>
+        <f t="shared" si="8"/>
         <v>520</v>
       </c>
       <c r="CD21"/>
       <c r="CE21" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0.11243868763294575</v>
       </c>
       <c r="CF21" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.11291614848050519</v>
       </c>
       <c r="CG21" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.9190737736219023E-3</v>
       </c>
       <c r="CH21" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -52462,7 +52552,7 @@
         <v>1</v>
       </c>
       <c r="AZ22">
-        <f>TINV(AX22,CC22)</f>
+        <f t="shared" si="9"/>
         <v>2.5853169622486396</v>
       </c>
       <c r="BA22" t="s">
@@ -52533,41 +52623,41 @@
         <v>1</v>
       </c>
       <c r="BX22" s="30">
-        <f>((AZ22^2)/(AZ22^2+BI22))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>0.11243868763294575</v>
       </c>
       <c r="BY22" s="30">
-        <f>0.5*LN((1+BX22)/(1-BX22))</f>
+        <f t="shared" si="1"/>
         <v>0.11291614848050519</v>
       </c>
       <c r="BZ22" s="30">
-        <f>((1-(BY22^2)^2)/(BI22-1))</f>
+        <f t="shared" si="2"/>
         <v>1.9190737736219023E-3</v>
       </c>
       <c r="CA22" s="30">
-        <f>1/(BI22-3)</f>
+        <f t="shared" si="3"/>
         <v>1.9267822736030828E-3</v>
       </c>
       <c r="CB22"/>
       <c r="CC22">
-        <f>BI22-2</f>
+        <f t="shared" si="8"/>
         <v>520</v>
       </c>
       <c r="CD22"/>
       <c r="CE22" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0.11243868763294575</v>
       </c>
       <c r="CF22" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.11291614848050519</v>
       </c>
       <c r="CG22" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.9190737736219023E-3</v>
       </c>
       <c r="CH22" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -52724,7 +52814,7 @@
         <v>1</v>
       </c>
       <c r="AZ23">
-        <f>TINV(AX23,CC23)</f>
+        <f t="shared" si="9"/>
         <v>1.9645365010317388</v>
       </c>
       <c r="BA23" t="s">
@@ -52795,41 +52885,41 @@
         <v>1</v>
       </c>
       <c r="BX23" s="30">
-        <f>((AZ23^2)/(AZ23^2+BI23))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>8.5669312189989619E-2</v>
       </c>
       <c r="BY23" s="30">
-        <f>0.5*LN((1+BX23)/(1-BX23))</f>
+        <f t="shared" si="1"/>
         <v>8.5879822251689428E-2</v>
       </c>
       <c r="BZ23" s="30">
-        <f>((1-(BY23^2)^2)/(BI23-1))</f>
+        <f t="shared" si="2"/>
         <v>1.9192813902165059E-3</v>
       </c>
       <c r="CA23" s="30">
-        <f>1/(BI23-3)</f>
+        <f t="shared" si="3"/>
         <v>1.9267822736030828E-3</v>
       </c>
       <c r="CB23"/>
       <c r="CC23">
-        <f>BI23-2</f>
+        <f t="shared" si="8"/>
         <v>520</v>
       </c>
       <c r="CD23"/>
       <c r="CE23" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>8.5669312189989619E-2</v>
       </c>
       <c r="CF23" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>8.5879822251689428E-2</v>
       </c>
       <c r="CG23" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.9192813902165059E-3</v>
       </c>
       <c r="CH23" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -52977,7 +53067,7 @@
         <v>80</v>
       </c>
       <c r="AW24">
-        <f>AU24/AZ24</f>
+        <f t="shared" ref="AW24:AW30" si="10">AU24/AZ24</f>
         <v>9.8591549295774641E-2</v>
       </c>
       <c r="AX24">
@@ -53056,39 +53146,39 @@
         <v>1</v>
       </c>
       <c r="BX24" s="30">
-        <f>((AZ24^2)/(AZ24^2+BI24))^(1/2)</f>
-        <v>0.2020824660717096</v>
-      </c>
-      <c r="BY24" s="30">
-        <f>0.5*LN((1+BX24)/(1-BX24))</f>
-        <v>0.20490273447739515</v>
-      </c>
-      <c r="BZ24" s="30">
-        <f>((1-(BY24^2)^2)/(BI24-1))</f>
-        <v>8.4381846898462422E-4</v>
-      </c>
-      <c r="CA24" s="30">
-        <f>1/(BI24-3)</f>
-        <v>8.4674005080440302E-4</v>
-      </c>
-      <c r="CC24">
-        <f>BI24-2</f>
-        <v>1182</v>
-      </c>
-      <c r="CE24" s="30">
         <f t="shared" si="0"/>
         <v>0.2020824660717096</v>
       </c>
-      <c r="CF24" s="30">
+      <c r="BY24" s="30">
         <f t="shared" si="1"/>
         <v>0.20490273447739515</v>
       </c>
-      <c r="CG24" s="30">
+      <c r="BZ24" s="30">
         <f t="shared" si="2"/>
         <v>8.4381846898462422E-4</v>
       </c>
+      <c r="CA24" s="30">
+        <f t="shared" si="3"/>
+        <v>8.4674005080440302E-4</v>
+      </c>
+      <c r="CC24">
+        <f t="shared" si="8"/>
+        <v>1182</v>
+      </c>
+      <c r="CE24" s="30">
+        <f t="shared" si="4"/>
+        <v>0.2020824660717096</v>
+      </c>
+      <c r="CF24" s="30">
+        <f t="shared" si="5"/>
+        <v>0.20490273447739515</v>
+      </c>
+      <c r="CG24" s="30">
+        <f t="shared" si="6"/>
+        <v>8.4381846898462422E-4</v>
+      </c>
       <c r="CH24" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -53236,7 +53326,7 @@
         <v>80</v>
       </c>
       <c r="AW25">
-        <f>AU25/AZ25</f>
+        <f t="shared" si="10"/>
         <v>0.15416666666666667</v>
       </c>
       <c r="AX25">
@@ -53315,39 +53405,39 @@
         <v>1</v>
       </c>
       <c r="BX25" s="30">
-        <f>((AZ25^2)/(AZ25^2+BI25))^(1/2)</f>
-        <v>2.0919995692237577E-2</v>
-      </c>
-      <c r="BY25" s="30">
-        <f>0.5*LN((1+BX25)/(1-BX25))</f>
-        <v>2.0923048346211292E-2</v>
-      </c>
-      <c r="BZ25" s="30">
-        <f>((1-(BY25^2)^2)/(BI25-1))</f>
-        <v>8.453083756162019E-4</v>
-      </c>
-      <c r="CA25" s="30">
-        <f>1/(BI25-3)</f>
-        <v>8.4674005080440302E-4</v>
-      </c>
-      <c r="CC25">
-        <f>BI25-2</f>
-        <v>1182</v>
-      </c>
-      <c r="CE25" s="30">
         <f t="shared" si="0"/>
         <v>2.0919995692237577E-2</v>
       </c>
-      <c r="CF25" s="30">
+      <c r="BY25" s="30">
         <f t="shared" si="1"/>
         <v>2.0923048346211292E-2</v>
       </c>
-      <c r="CG25" s="30">
+      <c r="BZ25" s="30">
         <f t="shared" si="2"/>
         <v>8.453083756162019E-4</v>
       </c>
+      <c r="CA25" s="30">
+        <f t="shared" si="3"/>
+        <v>8.4674005080440302E-4</v>
+      </c>
+      <c r="CC25">
+        <f t="shared" si="8"/>
+        <v>1182</v>
+      </c>
+      <c r="CE25" s="30">
+        <f t="shared" si="4"/>
+        <v>2.0919995692237577E-2</v>
+      </c>
+      <c r="CF25" s="30">
+        <f t="shared" si="5"/>
+        <v>2.0923048346211292E-2</v>
+      </c>
+      <c r="CG25" s="30">
+        <f t="shared" si="6"/>
+        <v>8.453083756162019E-4</v>
+      </c>
       <c r="CH25" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -53495,7 +53585,7 @@
         <v>86</v>
       </c>
       <c r="AW26">
-        <f>AU26/AZ26</f>
+        <f t="shared" si="10"/>
         <v>0.11478260869565218</v>
       </c>
       <c r="AX26">
@@ -53574,39 +53664,39 @@
         <v>1</v>
       </c>
       <c r="BX26" s="30">
-        <f>((AZ26^2)/(AZ26^2+BI26))^(1/2)</f>
-        <v>3.3402546418006968E-2</v>
-      </c>
-      <c r="BY26" s="30">
-        <f>0.5*LN((1+BX26)/(1-BX26))</f>
-        <v>3.341497748312889E-2</v>
-      </c>
-      <c r="BZ26" s="30">
-        <f>((1-(BY26^2)^2)/(BI26-1))</f>
-        <v>8.4530748376344727E-4</v>
-      </c>
-      <c r="CA26" s="30">
-        <f>1/(BI26-3)</f>
-        <v>8.4674005080440302E-4</v>
-      </c>
-      <c r="CC26">
-        <f>BI26-2</f>
-        <v>1182</v>
-      </c>
-      <c r="CE26" s="30">
         <f t="shared" si="0"/>
         <v>3.3402546418006968E-2</v>
       </c>
-      <c r="CF26" s="30">
+      <c r="BY26" s="30">
         <f t="shared" si="1"/>
         <v>3.341497748312889E-2</v>
       </c>
-      <c r="CG26" s="30">
+      <c r="BZ26" s="30">
         <f t="shared" si="2"/>
         <v>8.4530748376344727E-4</v>
       </c>
+      <c r="CA26" s="30">
+        <f t="shared" si="3"/>
+        <v>8.4674005080440302E-4</v>
+      </c>
+      <c r="CC26">
+        <f t="shared" si="8"/>
+        <v>1182</v>
+      </c>
+      <c r="CE26" s="30">
+        <f t="shared" si="4"/>
+        <v>3.3402546418006968E-2</v>
+      </c>
+      <c r="CF26" s="30">
+        <f t="shared" si="5"/>
+        <v>3.341497748312889E-2</v>
+      </c>
+      <c r="CG26" s="30">
+        <f t="shared" si="6"/>
+        <v>8.4530748376344727E-4</v>
+      </c>
       <c r="CH26" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -53754,7 +53844,7 @@
         <v>86</v>
       </c>
       <c r="AW27">
-        <f>AU27/AZ27</f>
+        <f t="shared" si="10"/>
         <v>0.14476190476190476</v>
       </c>
       <c r="AX27">
@@ -53833,39 +53923,39 @@
         <v>1</v>
       </c>
       <c r="BX27" s="30">
-        <f>((AZ27^2)/(AZ27^2+BI27))^(1/2)</f>
-        <v>3.050080782390133E-2</v>
-      </c>
-      <c r="BY27" s="30">
-        <f>0.5*LN((1+BX27)/(1-BX27))</f>
-        <v>3.0510271400002755E-2</v>
-      </c>
-      <c r="BZ27" s="30">
-        <f>((1-(BY27^2)^2)/(BI27-1))</f>
-        <v>8.453078051298751E-4</v>
-      </c>
-      <c r="CA27" s="30">
-        <f>1/(BI27-3)</f>
-        <v>8.4674005080440302E-4</v>
-      </c>
-      <c r="CC27">
-        <f>BI27-2</f>
-        <v>1182</v>
-      </c>
-      <c r="CE27" s="30">
         <f t="shared" si="0"/>
         <v>3.050080782390133E-2</v>
       </c>
-      <c r="CF27" s="30">
+      <c r="BY27" s="30">
         <f t="shared" si="1"/>
         <v>3.0510271400002755E-2</v>
       </c>
-      <c r="CG27" s="30">
+      <c r="BZ27" s="30">
         <f t="shared" si="2"/>
         <v>8.453078051298751E-4</v>
       </c>
+      <c r="CA27" s="30">
+        <f t="shared" si="3"/>
+        <v>8.4674005080440302E-4</v>
+      </c>
+      <c r="CC27">
+        <f t="shared" si="8"/>
+        <v>1182</v>
+      </c>
+      <c r="CE27" s="30">
+        <f t="shared" si="4"/>
+        <v>3.050080782390133E-2</v>
+      </c>
+      <c r="CF27" s="30">
+        <f t="shared" si="5"/>
+        <v>3.0510271400002755E-2</v>
+      </c>
+      <c r="CG27" s="30">
+        <f t="shared" si="6"/>
+        <v>8.453078051298751E-4</v>
+      </c>
       <c r="CH27" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -54013,7 +54103,7 @@
         <v>80</v>
       </c>
       <c r="AW28">
-        <f>AU28/AZ28</f>
+        <f t="shared" si="10"/>
         <v>0.15044247787610621</v>
       </c>
       <c r="AX28">
@@ -54093,41 +54183,41 @@
         <v>1</v>
       </c>
       <c r="BX28" s="30">
-        <f>((AZ28^2)/(AZ28^2+BI28))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>6.5538705898597463E-2</v>
       </c>
       <c r="BY28" s="30">
-        <f>0.5*LN((1+BX28)/(1-BX28))</f>
+        <f t="shared" si="1"/>
         <v>6.563278509260187E-2</v>
       </c>
       <c r="BZ28" s="30">
-        <f>((1-(BY28^2)^2)/(BI28-1))</f>
+        <f t="shared" si="2"/>
         <v>8.4529285210817155E-4</v>
       </c>
       <c r="CA28" s="30">
-        <f>1/(BI28-3)</f>
+        <f t="shared" si="3"/>
         <v>8.4674005080440302E-4</v>
       </c>
       <c r="CB28"/>
       <c r="CC28">
-        <f>BI28-2</f>
+        <f t="shared" si="8"/>
         <v>1182</v>
       </c>
       <c r="CD28"/>
       <c r="CE28" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>6.5538705898597463E-2</v>
       </c>
       <c r="CF28" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6.563278509260187E-2</v>
       </c>
       <c r="CG28" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>8.4529285210817155E-4</v>
       </c>
       <c r="CH28" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -54275,7 +54365,7 @@
         <v>80</v>
       </c>
       <c r="AW29">
-        <f>AU29/AZ29</f>
+        <f t="shared" si="10"/>
         <v>0.13387096774193546</v>
       </c>
       <c r="AX29">
@@ -54355,41 +54445,41 @@
         <v>1</v>
       </c>
       <c r="BX29" s="30">
-        <f>((AZ29^2)/(AZ29^2+BI29))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>5.3976351182136464E-2</v>
       </c>
       <c r="BY29" s="30">
-        <f>0.5*LN((1+BX29)/(1-BX29))</f>
+        <f t="shared" si="1"/>
         <v>5.402886207559579E-2</v>
       </c>
       <c r="BZ29" s="30">
-        <f>((1-(BY29^2)^2)/(BI29-1))</f>
+        <f t="shared" si="2"/>
         <v>8.4530133453125005E-4</v>
       </c>
       <c r="CA29" s="30">
-        <f>1/(BI29-3)</f>
+        <f t="shared" si="3"/>
         <v>8.4674005080440302E-4</v>
       </c>
       <c r="CB29"/>
       <c r="CC29">
-        <f>BI29-2</f>
+        <f t="shared" si="8"/>
         <v>1182</v>
       </c>
       <c r="CD29"/>
       <c r="CE29" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>5.3976351182136464E-2</v>
       </c>
       <c r="CF29" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>5.402886207559579E-2</v>
       </c>
       <c r="CG29" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>8.4530133453125005E-4</v>
       </c>
       <c r="CH29" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -54537,7 +54627,7 @@
         <v>80</v>
       </c>
       <c r="AW30">
-        <f>AU30/AZ30</f>
+        <f t="shared" si="10"/>
         <v>0.19337349397590362</v>
       </c>
       <c r="AX30">
@@ -54617,41 +54707,41 @@
         <v>1</v>
       </c>
       <c r="BX30" s="30">
-        <f>((AZ30^2)/(AZ30^2+BI30))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>9.6039537672003544E-2</v>
       </c>
       <c r="BY30" s="30">
-        <f>0.5*LN((1+BX30)/(1-BX30))</f>
+        <f t="shared" si="1"/>
         <v>9.633645915133221E-2</v>
       </c>
       <c r="BZ30" s="30">
-        <f>((1-(BY30^2)^2)/(BI30-1))</f>
+        <f t="shared" si="2"/>
         <v>8.4523572980515279E-4</v>
       </c>
       <c r="CA30" s="30">
-        <f>1/(BI30-3)</f>
+        <f t="shared" si="3"/>
         <v>8.4674005080440302E-4</v>
       </c>
       <c r="CB30"/>
       <c r="CC30">
-        <f>BI30-2</f>
+        <f t="shared" si="8"/>
         <v>1182</v>
       </c>
       <c r="CD30"/>
       <c r="CE30" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>9.6039537672003544E-2</v>
       </c>
       <c r="CF30" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>9.633645915133221E-2</v>
       </c>
       <c r="CG30" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>8.4523572980515279E-4</v>
       </c>
       <c r="CH30" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -54869,41 +54959,41 @@
         <v>1</v>
       </c>
       <c r="BX31" s="104">
-        <f>((AZ31^2)/(AZ31^2+BI31))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>6.7103465160314887E-2</v>
       </c>
       <c r="BY31" s="104">
-        <f>0.5*LN((1+BX31)/(1-BX31))</f>
+        <f t="shared" si="1"/>
         <v>6.7204457661064573E-2</v>
       </c>
       <c r="BZ31" s="104">
-        <f>((1-(BY31^2)^2)/(BI31-1))</f>
+        <f t="shared" si="2"/>
         <v>1.6694150280093312E-3</v>
       </c>
       <c r="CA31" s="104">
-        <f>1/(BI31-3)</f>
+        <f t="shared" si="3"/>
         <v>1.6750418760469012E-3</v>
       </c>
       <c r="CB31"/>
       <c r="CC31">
-        <f>BI31-2</f>
+        <f t="shared" si="8"/>
         <v>598</v>
       </c>
       <c r="CD31"/>
       <c r="CE31" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.7446418247225011E-2</v>
       </c>
       <c r="CF31" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.7453313213271935E-2</v>
       </c>
       <c r="CG31" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>2.7785480187824828E-4</v>
       </c>
       <c r="CH31" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
@@ -55115,39 +55205,39 @@
         <v>1</v>
       </c>
       <c r="BX32" s="104">
-        <f>((AZ32^2)/(AZ32^2+BI32))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>6.7103465160314887E-2</v>
       </c>
       <c r="BY32" s="104">
-        <f>0.5*LN((1+BX32)/(1-BX32))</f>
+        <f t="shared" si="1"/>
         <v>6.7204457661064573E-2</v>
       </c>
       <c r="BZ32" s="104">
-        <f>((1-(BY32^2)^2)/(BI32-1))</f>
+        <f t="shared" si="2"/>
         <v>1.6694150280093312E-3</v>
       </c>
       <c r="CA32" s="104">
-        <f>1/(BI32-3)</f>
+        <f t="shared" si="3"/>
         <v>1.6750418760469012E-3</v>
       </c>
       <c r="CC32">
-        <f>BI32-2</f>
+        <f t="shared" si="8"/>
         <v>598</v>
       </c>
       <c r="CE32" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.7446418247225011E-2</v>
       </c>
       <c r="CF32" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.7453313213271935E-2</v>
       </c>
       <c r="CG32" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>2.7785480187824828E-4</v>
       </c>
       <c r="CH32" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
@@ -55359,39 +55449,39 @@
         <v>1</v>
       </c>
       <c r="BX33" s="104">
-        <f>((AZ33^2)/(AZ33^2+BI33))^(1/2)</f>
+        <f t="shared" si="0"/>
         <v>6.7103465160314887E-2</v>
       </c>
       <c r="BY33" s="104">
-        <f>0.5*LN((1+BX33)/(1-BX33))</f>
+        <f t="shared" si="1"/>
         <v>6.7204457661064573E-2</v>
       </c>
       <c r="BZ33" s="104">
-        <f>((1-(BY33^2)^2)/(BI33-1))</f>
+        <f t="shared" si="2"/>
         <v>1.6694150280093312E-3</v>
       </c>
       <c r="CA33" s="104">
-        <f>1/(BI33-3)</f>
+        <f t="shared" si="3"/>
         <v>1.6750418760469012E-3</v>
       </c>
       <c r="CC33">
-        <f>BI33-2</f>
+        <f t="shared" si="8"/>
         <v>598</v>
       </c>
       <c r="CE33" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.7446418247225011E-2</v>
       </c>
       <c r="CF33" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.7453313213271935E-2</v>
       </c>
       <c r="CG33" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>2.7785480187824828E-4</v>
       </c>
       <c r="CH33" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
@@ -55603,39 +55693,39 @@
         <v>1</v>
       </c>
       <c r="BX34" s="104">
-        <f>((AZ34^2)/(AZ34^2+BI34))^(1/2)</f>
+        <f t="shared" ref="BX34:BX62" si="11">((AZ34^2)/(AZ34^2+BI34))^(1/2)</f>
         <v>7.9920998150068992E-2</v>
       </c>
       <c r="BY34" s="104">
-        <f>0.5*LN((1+BX34)/(1-BX34))</f>
+        <f t="shared" ref="BY34:BY62" si="12">0.5*LN((1+BX34)/(1-BX34))</f>
         <v>8.0091814824645752E-2</v>
       </c>
       <c r="BZ34" s="104">
-        <f>((1-(BY34^2)^2)/(BI34-1))</f>
+        <f t="shared" ref="BZ34:BZ62" si="13">((1-(BY34^2)^2)/(BI34-1))</f>
         <v>1.6693803867099848E-3</v>
       </c>
       <c r="CA34" s="104">
-        <f>1/(BI34-3)</f>
+        <f t="shared" ref="CA34:CA62" si="14">1/(BI34-3)</f>
         <v>1.6750418760469012E-3</v>
       </c>
       <c r="CC34">
-        <f>BI34-2</f>
+        <f t="shared" si="8"/>
         <v>598</v>
       </c>
       <c r="CE34" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.2714794271304103E-2</v>
       </c>
       <c r="CF34" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.2726472859206039E-2</v>
       </c>
       <c r="CG34" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>2.7785464098689086E-4</v>
       </c>
       <c r="CH34" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
@@ -55650,7 +55740,7 @@
       <c r="D35" s="98">
         <v>144</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="127" t="s">
         <v>304</v>
       </c>
       <c r="F35" s="97">
@@ -55862,39 +55952,39 @@
         <v>1</v>
       </c>
       <c r="BX35" s="30">
-        <f>((AZ35^2)/(AZ35^2+BI35))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>0.43424883131426489</v>
       </c>
       <c r="BY35" s="30">
-        <f>0.5*LN((1+BX35)/(1-BX35))</f>
+        <f t="shared" si="12"/>
         <v>0.46512108920045175</v>
       </c>
       <c r="BZ35" s="30">
-        <f>((1-(BY35^2)^2)/(BI35-1))</f>
+        <f t="shared" si="13"/>
         <v>2.6926498047349623E-3</v>
       </c>
       <c r="CA35" s="30">
-        <f>1/(BI35-3)</f>
+        <f t="shared" si="14"/>
         <v>2.840909090909091E-3</v>
       </c>
       <c r="CC35">
-        <f>BI35-2</f>
+        <f t="shared" si="8"/>
         <v>353</v>
       </c>
       <c r="CE35" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>6.4318817101316442E-2</v>
       </c>
       <c r="CF35" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6.4407731628953774E-2</v>
       </c>
       <c r="CG35" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>5.0354136217502399E-5</v>
       </c>
       <c r="CH35" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -55909,7 +55999,7 @@
       <c r="D36" s="98">
         <v>144</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E36" s="127" t="s">
         <v>304</v>
       </c>
       <c r="F36" s="97">
@@ -56121,39 +56211,39 @@
         <v>1</v>
       </c>
       <c r="BX36" s="30">
-        <f>((AZ36^2)/(AZ36^2+BI36))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>0.57835709203923469</v>
       </c>
       <c r="BY36" s="30">
-        <f>0.5*LN((1+BX36)/(1-BX36))</f>
+        <f t="shared" si="12"/>
         <v>0.65999050186206398</v>
       </c>
       <c r="BZ36" s="30">
-        <f>((1-(BY36^2)^2)/(BI36-1))</f>
+        <f t="shared" si="13"/>
         <v>2.3283435703186023E-3</v>
       </c>
       <c r="CA36" s="30">
-        <f>1/(BI36-3)</f>
+        <f t="shared" si="14"/>
         <v>2.8901734104046241E-3</v>
       </c>
       <c r="CC36">
-        <f>BI36-2</f>
+        <f t="shared" si="8"/>
         <v>347</v>
       </c>
       <c r="CE36" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>9.4537081297198303E-2</v>
       </c>
       <c r="CF36" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>9.4820235378343692E-2</v>
       </c>
       <c r="CG36" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>5.1407082624548965E-5</v>
       </c>
       <c r="CH36" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.1416525271222172E-5</v>
       </c>
     </row>
@@ -56366,19 +56456,19 @@
         <v>1</v>
       </c>
       <c r="BX37" s="30" t="e">
-        <f>((AZ37^2)/(AZ37^2+BI37))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
       <c r="BY37" s="30" t="e">
-        <f>0.5*LN((1+BX37)/(1-BX37))</f>
+        <f t="shared" si="12"/>
         <v>#VALUE!</v>
       </c>
       <c r="BZ37" s="30" t="e">
-        <f>((1-(BY37^2)^2)/(BI37-1))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="CA37" s="30" t="e">
-        <f>1/(BI37-3)</f>
+        <f t="shared" si="14"/>
         <v>#VALUE!</v>
       </c>
       <c r="CB37" s="96"/>
@@ -56388,19 +56478,19 @@
       </c>
       <c r="CD37" s="96"/>
       <c r="CE37" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="CF37" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="CG37" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.5035333032626674E-4</v>
       </c>
       <c r="CH37" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.5039855617386073E-4</v>
       </c>
     </row>
@@ -56629,40 +56719,40 @@
         <v>0</v>
       </c>
       <c r="BX38" s="30">
-        <f>((AZ38^2)/(AZ38^2+BI38))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>9.8016085482412224E-2</v>
       </c>
       <c r="BY38" s="30">
-        <f>0.5*LN((1+BX38)/(1-BX38))</f>
+        <f t="shared" si="12"/>
         <v>9.8331792494724915E-2</v>
       </c>
       <c r="BZ38" s="30">
-        <f>((1-(BY38^2)^2)/(BI38-1))</f>
+        <f t="shared" si="13"/>
         <v>3.1542792041144869E-3</v>
       </c>
       <c r="CA38" s="30">
-        <f>1/(BI38-3)</f>
+        <f t="shared" si="14"/>
         <v>3.1746031746031746E-3</v>
       </c>
       <c r="CB38" s="100"/>
       <c r="CC38">
-        <f>BI38-2</f>
+        <f t="shared" ref="CC38:CC62" si="15">BI38-2</f>
         <v>316</v>
       </c>
       <c r="CE38" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>9.8016085482412224E-2</v>
       </c>
       <c r="CF38" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>9.8331792494724915E-2</v>
       </c>
       <c r="CG38" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>3.1542792041144869E-3</v>
       </c>
       <c r="CH38" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.1746031746031746E-3</v>
       </c>
     </row>
@@ -56791,16 +56881,16 @@
       <c r="AP39">
         <v>0</v>
       </c>
-      <c r="AQ39" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR39" t="s">
+      <c r="AQ39" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR39" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="AS39" t="s">
+      <c r="AS39" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="AT39" t="s">
+      <c r="AT39" s="41" t="s">
         <v>73</v>
       </c>
       <c r="AU39" s="21">
@@ -56889,40 +56979,40 @@
         <v>0</v>
       </c>
       <c r="BX39" s="104">
-        <f>((AZ39^2)/(AZ39^2+BI39))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>6.8895720725096588E-2</v>
       </c>
       <c r="BY39" s="104">
-        <f>0.5*LN((1+BX39)/(1-BX39))</f>
+        <f t="shared" si="12"/>
         <v>6.900503950756405E-2</v>
       </c>
       <c r="BZ39" s="104">
-        <f>((1-(BY39^2)^2)/(BI39-1))</f>
+        <f t="shared" si="13"/>
         <v>7.1734384953814931E-4</v>
       </c>
       <c r="CA39" s="104">
-        <f>1/(BI39-3)</f>
+        <f t="shared" si="14"/>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB39" s="100"/>
       <c r="CC39">
-        <f>BI39-2</f>
+        <f t="shared" si="15"/>
         <v>1393</v>
       </c>
       <c r="CE39" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1.8299961101675508E-2</v>
       </c>
       <c r="CF39" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>1.8302004328216499E-2</v>
       </c>
       <c r="CG39" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>5.035499711967097E-5</v>
       </c>
       <c r="CH39" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -57051,16 +57141,16 @@
       <c r="AP40">
         <v>0</v>
       </c>
-      <c r="AQ40" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR40" t="s">
+      <c r="AQ40" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR40" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="AS40" t="s">
+      <c r="AS40" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="AT40" t="s">
+      <c r="AT40" s="41" t="s">
         <v>73</v>
       </c>
       <c r="AU40" s="21">
@@ -57149,40 +57239,40 @@
         <v>1</v>
       </c>
       <c r="BX40" s="104">
-        <f>((AZ40^2)/(AZ40^2+BI40))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>6.8895720725096588E-2</v>
       </c>
       <c r="BY40" s="104">
-        <f>0.5*LN((1+BX40)/(1-BX40))</f>
+        <f t="shared" si="12"/>
         <v>6.900503950756405E-2</v>
       </c>
       <c r="BZ40" s="104">
-        <f>((1-(BY40^2)^2)/(BI40-1))</f>
+        <f t="shared" si="13"/>
         <v>7.1734384953814931E-4</v>
       </c>
       <c r="CA40" s="104">
-        <f>1/(BI40-3)</f>
+        <f t="shared" si="14"/>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB40" s="100"/>
       <c r="CC40">
-        <f>BI40-2</f>
+        <f t="shared" si="15"/>
         <v>1393</v>
       </c>
       <c r="CE40" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1.8299961101675508E-2</v>
       </c>
       <c r="CF40" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>1.8302004328216499E-2</v>
       </c>
       <c r="CG40" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>5.035499711967097E-5</v>
       </c>
       <c r="CH40" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -57311,16 +57401,16 @@
       <c r="AP41">
         <v>0</v>
       </c>
-      <c r="AQ41" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR41" t="s">
+      <c r="AQ41" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR41" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="AS41" t="s">
+      <c r="AS41" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="AT41" t="s">
+      <c r="AT41" s="41" t="s">
         <v>73</v>
       </c>
       <c r="AU41" s="21">
@@ -57409,40 +57499,40 @@
         <v>0</v>
       </c>
       <c r="BX41" s="104">
-        <f>((AZ41^2)/(AZ41^2+BI41))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>6.8895720725096588E-2</v>
       </c>
       <c r="BY41" s="104">
-        <f>0.5*LN((1+BX41)/(1-BX41))</f>
+        <f t="shared" si="12"/>
         <v>6.900503950756405E-2</v>
       </c>
       <c r="BZ41" s="104">
-        <f>((1-(BY41^2)^2)/(BI41-1))</f>
+        <f t="shared" si="13"/>
         <v>7.1734384953814931E-4</v>
       </c>
       <c r="CA41" s="104">
-        <f>1/(BI41-3)</f>
+        <f t="shared" si="14"/>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB41" s="100"/>
       <c r="CC41">
-        <f>BI41-2</f>
+        <f t="shared" si="15"/>
         <v>1393</v>
       </c>
       <c r="CE41" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1.8299961101675508E-2</v>
       </c>
       <c r="CF41" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>1.8302004328216499E-2</v>
       </c>
       <c r="CG41" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>5.035499711967097E-5</v>
       </c>
       <c r="CH41" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -57571,16 +57661,16 @@
       <c r="AP42">
         <v>0</v>
       </c>
-      <c r="AQ42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR42" t="s">
+      <c r="AQ42" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR42" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="AS42" t="s">
+      <c r="AS42" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="AT42" t="s">
+      <c r="AT42" s="41" t="s">
         <v>73</v>
       </c>
       <c r="AU42" s="21">
@@ -57669,40 +57759,40 @@
         <v>1</v>
       </c>
       <c r="BX42" s="104">
-        <f>((AZ42^2)/(AZ42^2+BI42))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>5.2449375133439773E-2</v>
       </c>
       <c r="BY42" s="104">
-        <f>0.5*LN((1+BX42)/(1-BX42))</f>
+        <f t="shared" si="12"/>
         <v>5.2497549648224964E-2</v>
       </c>
       <c r="BZ42" s="104">
-        <f>((1-(BY42^2)^2)/(BI42-1))</f>
+        <f t="shared" si="13"/>
         <v>7.1735466607183095E-4</v>
       </c>
       <c r="CA42" s="104">
-        <f>1/(BI42-3)</f>
+        <f t="shared" si="14"/>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB42" s="100"/>
       <c r="CC42">
-        <f>BI42-2</f>
+        <f t="shared" si="15"/>
         <v>1393</v>
       </c>
       <c r="CE42" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1.3918547330727849E-2</v>
       </c>
       <c r="CF42" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>1.3919446229861089E-2</v>
       </c>
       <c r="CG42" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>5.0355000879226367E-5</v>
       </c>
       <c r="CH42" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -57841,7 +57931,7 @@
         <v>331</v>
       </c>
       <c r="AT43" t="s">
-        <v>73</v>
+        <v>236</v>
       </c>
       <c r="AU43" s="21">
         <v>1.0760000000000001</v>
@@ -57928,40 +58018,40 @@
         <v>0</v>
       </c>
       <c r="BX43" s="104">
-        <f>((AZ43^2)/(AZ43^2+BI43))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>0.47242735990047685</v>
       </c>
       <c r="BY43" s="104">
-        <f>0.5*LN((1+BX43)/(1-BX43))</f>
+        <f t="shared" si="12"/>
         <v>0.51319051047617226</v>
       </c>
       <c r="BZ43" s="104">
-        <f>((1-(BY43^2)^2)/(BI43-1))</f>
+        <f t="shared" si="13"/>
         <v>6.6760340037102519E-4</v>
       </c>
       <c r="CA43" s="104">
-        <f>1/(BI43-3)</f>
+        <f t="shared" si="14"/>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB43" s="100"/>
       <c r="CC43">
-        <f>BI43-2</f>
+        <f t="shared" si="15"/>
         <v>1393</v>
       </c>
       <c r="CE43" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0.14064871674533846</v>
       </c>
       <c r="CF43" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.14158732325545795</v>
       </c>
       <c r="CG43" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>5.0334766050130579E-5</v>
       </c>
       <c r="CH43" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -58100,7 +58190,7 @@
         <v>332</v>
       </c>
       <c r="AT44" t="s">
-        <v>73</v>
+        <v>236</v>
       </c>
       <c r="AU44" s="21">
         <v>2.1459999999999999</v>
@@ -58187,40 +58277,40 @@
         <v>0</v>
       </c>
       <c r="BX44" s="104">
-        <f>((AZ44^2)/(AZ44^2+BI44))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>0.29473516954008327</v>
       </c>
       <c r="BY44" s="104">
-        <f>0.5*LN((1+BX44)/(1-BX44))</f>
+        <f t="shared" si="12"/>
         <v>0.3037440363085756</v>
       </c>
       <c r="BZ44" s="104">
-        <f>((1-(BY44^2)^2)/(BI44-1))</f>
+        <f t="shared" si="13"/>
         <v>7.1125395357683058E-4</v>
       </c>
       <c r="CA44" s="104">
-        <f>1/(BI44-3)</f>
+        <f t="shared" si="14"/>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB44" s="100"/>
       <c r="CC44">
-        <f>BI44-2</f>
+        <f t="shared" si="15"/>
         <v>1393</v>
       </c>
       <c r="CE44" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>8.1473550285666996E-2</v>
       </c>
       <c r="CF44" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>8.165454385204271E-2</v>
       </c>
       <c r="CG44" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>5.0352764233683405E-5</v>
       </c>
       <c r="CH44" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -58349,35 +58439,35 @@
       <c r="AP45" s="18">
         <v>0</v>
       </c>
-      <c r="AQ45" t="s">
+      <c r="AQ45" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AR45" t="s">
+      <c r="AR45" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS45" t="s">
+      <c r="AS45" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AT45" t="s">
+      <c r="AT45" s="122" t="s">
         <v>338</v>
       </c>
-      <c r="AU45" s="21">
+      <c r="AU45" s="124">
         <v>0.55700000000000005</v>
       </c>
-      <c r="AV45" s="7" t="s">
+      <c r="AV45" s="125" t="s">
         <v>80</v>
       </c>
-      <c r="AW45" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX45" s="41">
+      <c r="AW45" s="122" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX45" s="122">
         <v>1E-3</v>
       </c>
       <c r="AY45">
         <v>3</v>
       </c>
       <c r="AZ45">
-        <f>TINV(AX45,CC45)</f>
+        <f t="shared" ref="AZ45:AZ62" si="16">TINV(AX45,CC45)</f>
         <v>3.2994178866117148</v>
       </c>
       <c r="BA45" s="18" t="s">
@@ -58448,40 +58538,40 @@
         <v>0</v>
       </c>
       <c r="BX45" s="30">
-        <f>((AZ45^2)/(AZ45^2+BI45))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>9.9037143771440309E-2</v>
       </c>
       <c r="BY45" s="30">
-        <f>0.5*LN((1+BX45)/(1-BX45))</f>
+        <f t="shared" si="12"/>
         <v>9.9362859957839736E-2</v>
       </c>
       <c r="BZ45" s="30">
-        <f>((1-(BY45^2)^2)/(BI45-1))</f>
+        <f t="shared" si="13"/>
         <v>9.1065803670912202E-4</v>
       </c>
       <c r="CA45" s="30">
-        <f>1/(BI45-3)</f>
+        <f t="shared" si="14"/>
         <v>9.1240875912408756E-4</v>
       </c>
       <c r="CB45" s="100"/>
       <c r="CC45">
-        <f>BI45-2</f>
+        <f t="shared" si="15"/>
         <v>1097</v>
       </c>
       <c r="CE45" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.8718958292254938E-2</v>
       </c>
       <c r="CF45" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.8726857795568102E-2</v>
       </c>
       <c r="CG45" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>7.5832207400588011E-5</v>
       </c>
       <c r="CH45" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
@@ -58610,35 +58700,35 @@
       <c r="AP46" s="18">
         <v>0</v>
       </c>
-      <c r="AQ46" t="s">
+      <c r="AQ46" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AR46" t="s">
+      <c r="AR46" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS46" t="s">
+      <c r="AS46" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AT46" t="s">
+      <c r="AT46" s="122" t="s">
         <v>338</v>
       </c>
-      <c r="AU46" s="21">
+      <c r="AU46" s="124">
         <v>1.58</v>
       </c>
-      <c r="AV46" s="7" t="s">
+      <c r="AV46" s="125" t="s">
         <v>80</v>
       </c>
-      <c r="AW46" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX46" s="41">
+      <c r="AW46" s="122" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX46" s="122">
         <v>1E-3</v>
       </c>
       <c r="AY46">
         <v>3</v>
       </c>
       <c r="AZ46">
-        <f>TINV(AX46,CC46)</f>
+        <f t="shared" si="16"/>
         <v>3.2994178866117148</v>
       </c>
       <c r="BA46" s="18" t="s">
@@ -58709,40 +58799,40 @@
         <v>0</v>
       </c>
       <c r="BX46" s="30">
-        <f>((AZ46^2)/(AZ46^2+BI46))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>9.9037143771440309E-2</v>
       </c>
       <c r="BY46" s="30">
-        <f>0.5*LN((1+BX46)/(1-BX46))</f>
+        <f t="shared" si="12"/>
         <v>9.9362859957839736E-2</v>
       </c>
       <c r="BZ46" s="30">
-        <f>((1-(BY46^2)^2)/(BI46-1))</f>
+        <f t="shared" si="13"/>
         <v>9.1065803670912202E-4</v>
       </c>
       <c r="CA46" s="30">
-        <f>1/(BI46-3)</f>
+        <f t="shared" si="14"/>
         <v>9.1240875912408756E-4</v>
       </c>
       <c r="CB46" s="100"/>
       <c r="CC46">
-        <f>BI46-2</f>
+        <f t="shared" si="15"/>
         <v>1097</v>
       </c>
       <c r="CE46" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.8718958292254938E-2</v>
       </c>
       <c r="CF46" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.8726857795568102E-2</v>
       </c>
       <c r="CG46" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>7.5832207400588011E-5</v>
       </c>
       <c r="CH46" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
@@ -58871,35 +58961,35 @@
       <c r="AP47" s="18">
         <v>0</v>
       </c>
-      <c r="AQ47" t="s">
+      <c r="AQ47" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AR47" t="s">
+      <c r="AR47" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS47" t="s">
+      <c r="AS47" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AT47" t="s">
+      <c r="AT47" s="122" t="s">
         <v>338</v>
       </c>
-      <c r="AU47" s="21">
+      <c r="AU47" s="124">
         <v>0.17</v>
       </c>
-      <c r="AV47" s="7" t="s">
+      <c r="AV47" s="125" t="s">
         <v>80</v>
       </c>
-      <c r="AW47" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX47">
+      <c r="AW47" s="122" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX47" s="122">
         <v>0.311</v>
       </c>
       <c r="AY47">
         <v>3</v>
       </c>
       <c r="AZ47">
-        <f>TINV(AX47,CC47)</f>
+        <f t="shared" si="16"/>
         <v>1.0135940485180941</v>
       </c>
       <c r="BA47" s="18" t="s">
@@ -58970,40 +59060,40 @@
         <v>0</v>
       </c>
       <c r="BX47" s="30">
-        <f>((AZ47^2)/(AZ47^2+BI47))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>3.056063020259667E-2</v>
       </c>
       <c r="BY47" s="30">
-        <f>0.5*LN((1+BX47)/(1-BX47))</f>
+        <f t="shared" si="12"/>
         <v>3.0570149592664689E-2</v>
       </c>
       <c r="BZ47" s="30">
-        <f>((1-(BY47^2)^2)/(BI47-1))</f>
+        <f t="shared" si="13"/>
         <v>9.107460169818913E-4</v>
       </c>
       <c r="CA47" s="30">
-        <f>1/(BI47-3)</f>
+        <f t="shared" si="14"/>
         <v>9.1240875912408756E-4</v>
       </c>
       <c r="CB47" s="100"/>
       <c r="CC47">
-        <f>BI47-2</f>
+        <f t="shared" si="15"/>
         <v>1097</v>
       </c>
       <c r="CE47" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>8.8258728613782138E-3</v>
       </c>
       <c r="CF47" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>8.826102038913812E-3</v>
       </c>
       <c r="CG47" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>7.5832258582814749E-5</v>
       </c>
       <c r="CH47" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
@@ -59132,35 +59222,35 @@
       <c r="AP48" s="18">
         <v>0</v>
       </c>
-      <c r="AQ48" t="s">
+      <c r="AQ48" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AR48" t="s">
+      <c r="AR48" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS48" t="s">
+      <c r="AS48" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AT48" t="s">
+      <c r="AT48" s="122" t="s">
         <v>338</v>
       </c>
-      <c r="AU48" s="21">
+      <c r="AU48" s="124">
         <v>1.1140000000000001</v>
       </c>
-      <c r="AV48" s="7" t="s">
+      <c r="AV48" s="125" t="s">
         <v>80</v>
       </c>
-      <c r="AW48" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX48" s="41">
+      <c r="AW48" s="122" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX48" s="122">
         <v>1E-3</v>
       </c>
       <c r="AY48">
         <v>3</v>
       </c>
       <c r="AZ48">
-        <f>TINV(AX48,CC48)</f>
+        <f t="shared" si="16"/>
         <v>3.2994178866117148</v>
       </c>
       <c r="BA48" s="18" t="s">
@@ -59231,40 +59321,40 @@
         <v>0</v>
       </c>
       <c r="BX48" s="30">
-        <f>((AZ48^2)/(AZ48^2+BI48))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>9.9037143771440309E-2</v>
       </c>
       <c r="BY48" s="30">
-        <f>0.5*LN((1+BX48)/(1-BX48))</f>
+        <f t="shared" si="12"/>
         <v>9.9362859957839736E-2</v>
       </c>
       <c r="BZ48" s="30">
-        <f>((1-(BY48^2)^2)/(BI48-1))</f>
+        <f t="shared" si="13"/>
         <v>9.1065803670912202E-4</v>
       </c>
       <c r="CA48" s="30">
-        <f>1/(BI48-3)</f>
+        <f t="shared" si="14"/>
         <v>9.1240875912408756E-4</v>
       </c>
       <c r="CB48" s="100"/>
       <c r="CC48">
-        <f>BI48-2</f>
+        <f t="shared" si="15"/>
         <v>1097</v>
       </c>
       <c r="CE48" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>2.8718958292254938E-2</v>
       </c>
       <c r="CF48" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.8726857795568102E-2</v>
       </c>
       <c r="CG48" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>7.5832207400588011E-5</v>
       </c>
       <c r="CH48" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
@@ -59393,35 +59483,35 @@
       <c r="AP49" s="18">
         <v>0</v>
       </c>
-      <c r="AQ49" t="s">
+      <c r="AQ49" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AR49" t="s">
+      <c r="AR49" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS49" t="s">
+      <c r="AS49" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AT49" t="s">
+      <c r="AT49" s="122" t="s">
         <v>338</v>
       </c>
-      <c r="AU49" s="21">
+      <c r="AU49" s="124">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="AV49" s="7" t="s">
+      <c r="AV49" s="125" t="s">
         <v>86</v>
       </c>
-      <c r="AW49" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX49">
+      <c r="AW49" s="122" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX49" s="122">
         <v>0.71299999999999997</v>
       </c>
       <c r="AY49">
         <v>3</v>
       </c>
       <c r="AZ49">
-        <f>TINV(AX49,CC49)</f>
+        <f t="shared" si="16"/>
         <v>0.36792518213176223</v>
       </c>
       <c r="BA49" s="18" t="s">
@@ -59492,40 +59582,40 @@
         <v>0</v>
       </c>
       <c r="BX49" s="30">
-        <f>((AZ49^2)/(AZ49^2+BI49))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>1.1097724056507073E-2</v>
       </c>
       <c r="BY49" s="30">
-        <f>0.5*LN((1+BX49)/(1-BX49))</f>
+        <f t="shared" si="12"/>
         <v>1.1098179686815215E-2</v>
       </c>
       <c r="BZ49" s="30">
-        <f>((1-(BY49^2)^2)/(BI49-1))</f>
+        <f t="shared" si="13"/>
         <v>9.1074679856944585E-4</v>
       </c>
       <c r="CA49" s="30">
-        <f>1/(BI49-3)</f>
+        <f t="shared" si="14"/>
         <v>9.1240875912408756E-4</v>
       </c>
       <c r="CB49" s="100"/>
       <c r="CC49">
-        <f>BI49-2</f>
+        <f t="shared" si="15"/>
         <v>1097</v>
       </c>
       <c r="CE49" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.2038178402255461E-3</v>
       </c>
       <c r="CF49" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.2038288021011105E-3</v>
       </c>
       <c r="CG49" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>7.5832259035007177E-5</v>
       </c>
       <c r="CH49" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
@@ -59654,35 +59744,35 @@
       <c r="AP50" s="18">
         <v>0</v>
       </c>
-      <c r="AQ50" t="s">
+      <c r="AQ50" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AR50" t="s">
+      <c r="AR50" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS50" t="s">
+      <c r="AS50" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AT50" t="s">
+      <c r="AT50" s="122" t="s">
         <v>338</v>
       </c>
-      <c r="AU50" s="21">
+      <c r="AU50" s="124">
         <v>2E-3</v>
       </c>
-      <c r="AV50" s="7" t="s">
+      <c r="AV50" s="125" t="s">
         <v>86</v>
       </c>
-      <c r="AW50" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX50">
+      <c r="AW50" s="122" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX50" s="122">
         <v>0.99199999999999999</v>
       </c>
       <c r="AY50">
         <v>3</v>
       </c>
       <c r="AZ50">
-        <f>TINV(AX50,CC50)</f>
+        <f t="shared" si="16"/>
         <v>1.0028966613252909E-2</v>
       </c>
       <c r="BA50" s="18" t="s">
@@ -59753,41 +59843,41 @@
         <v>0</v>
       </c>
       <c r="BX50" s="30">
-        <f>((AZ50^2)/(AZ50^2+BI50))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>3.0252224837106504E-4</v>
       </c>
       <c r="BY50" s="30">
-        <f>0.5*LN((1+BX50)/(1-BX50))</f>
+        <f t="shared" si="12"/>
         <v>3.0252225759992615E-4</v>
       </c>
       <c r="BZ50" s="30">
-        <f>((1-(BY50^2)^2)/(BI50-1))</f>
+        <f t="shared" si="13"/>
         <v>9.1074681238614906E-4</v>
       </c>
       <c r="CA50" s="30">
-        <f>1/(BI50-3)</f>
+        <f t="shared" si="14"/>
         <v>9.1240875912408756E-4</v>
       </c>
       <c r="CB50" s="100"/>
       <c r="CC50">
-        <f>BI50-2</f>
+        <f t="shared" si="15"/>
         <v>1097</v>
       </c>
       <c r="CD50"/>
       <c r="CE50" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>8.7330654429660967E-5</v>
       </c>
       <c r="CF50" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>8.7330654651614581E-5</v>
       </c>
       <c r="CG50" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>7.583225904299688E-5</v>
       </c>
       <c r="CH50" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
@@ -59916,16 +60006,16 @@
       <c r="AP51" s="18">
         <v>0</v>
       </c>
-      <c r="AQ51" s="41" t="s">
+      <c r="AQ51" s="122" t="s">
         <v>346</v>
       </c>
-      <c r="AR51" t="s">
+      <c r="AR51" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS51" s="94" t="s">
+      <c r="AS51" s="123" t="s">
         <v>347</v>
       </c>
-      <c r="AT51" t="s">
+      <c r="AT51" s="122" t="s">
         <v>73</v>
       </c>
       <c r="AU51" s="21">
@@ -59944,7 +60034,7 @@
         <v>1</v>
       </c>
       <c r="AZ51">
-        <f>TINV(AX51,CC51)</f>
+        <f t="shared" si="16"/>
         <v>1.6519717481243639</v>
       </c>
       <c r="BA51" s="18" t="s">
@@ -59975,8 +60065,8 @@
       <c r="BJ51">
         <v>868</v>
       </c>
-      <c r="BK51" s="18" t="s">
-        <v>73</v>
+      <c r="BK51" s="21">
+        <v>25.879000000000001</v>
       </c>
       <c r="BL51" s="18" t="s">
         <v>73</v>
@@ -60015,41 +60105,41 @@
         <v>1</v>
       </c>
       <c r="BX51" s="30">
-        <f>((AZ51^2)/(AZ51^2+BI51))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>0.111444570712238</v>
       </c>
       <c r="BY51" s="30">
-        <f>0.5*LN((1+BX51)/(1-BX51))</f>
+        <f t="shared" si="12"/>
         <v>0.11190941618239179</v>
       </c>
       <c r="BZ51" s="30">
-        <f>((1-(BY51^2)^2)/(BI51-1))</f>
+        <f t="shared" si="13"/>
         <v>4.6289035023228077E-3</v>
       </c>
       <c r="CA51" s="30">
-        <f>1/(BI51-3)</f>
+        <f t="shared" si="14"/>
         <v>4.6728971962616819E-3</v>
       </c>
       <c r="CB51"/>
       <c r="CC51">
-        <f>BI51-2</f>
+        <f t="shared" si="15"/>
         <v>215</v>
       </c>
       <c r="CD51"/>
       <c r="CE51" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>5.5983636926066289E-2</v>
       </c>
       <c r="CF51" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>5.6042234525477685E-2</v>
       </c>
       <c r="CG51" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.1533911600947939E-3</v>
       </c>
       <c r="CH51" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
@@ -60178,16 +60268,16 @@
       <c r="AP52" s="18">
         <v>0</v>
       </c>
-      <c r="AQ52" s="41" t="s">
+      <c r="AQ52" s="122" t="s">
         <v>346</v>
       </c>
-      <c r="AR52" t="s">
+      <c r="AR52" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS52" s="94" t="s">
+      <c r="AS52" s="123" t="s">
         <v>347</v>
       </c>
-      <c r="AT52" t="s">
+      <c r="AT52" s="122" t="s">
         <v>73</v>
       </c>
       <c r="AU52" s="21">
@@ -60206,11 +60296,11 @@
         <v>1</v>
       </c>
       <c r="AZ52">
-        <f>TINV(AX52,CC52)</f>
+        <f t="shared" si="16"/>
         <v>1.9710591221336478</v>
       </c>
       <c r="BA52" s="18" t="s">
-        <v>73</v>
+        <v>648</v>
       </c>
       <c r="BB52" s="18"/>
       <c r="BC52" s="18" t="s">
@@ -60237,8 +60327,8 @@
       <c r="BJ52">
         <v>868</v>
       </c>
-      <c r="BK52" s="18" t="s">
-        <v>73</v>
+      <c r="BK52" s="21">
+        <v>45.747</v>
       </c>
       <c r="BL52" s="18" t="s">
         <v>73</v>
@@ -60277,41 +60367,41 @@
         <v>1</v>
       </c>
       <c r="BX52" s="30">
-        <f>((AZ52^2)/(AZ52^2+BI52))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>0.13262227273834529</v>
       </c>
       <c r="BY52" s="30">
-        <f>0.5*LN((1+BX52)/(1-BX52))</f>
+        <f t="shared" si="12"/>
         <v>0.13340813257086698</v>
       </c>
       <c r="BZ52" s="30">
-        <f>((1-(BY52^2)^2)/(BI52-1))</f>
+        <f t="shared" si="13"/>
         <v>4.6281631519105703E-3</v>
       </c>
       <c r="CA52" s="30">
-        <f>1/(BI52-3)</f>
+        <f t="shared" si="14"/>
         <v>4.6728971962616819E-3</v>
       </c>
       <c r="CB52"/>
       <c r="CC52">
-        <f>BI52-2</f>
+        <f t="shared" si="15"/>
         <v>215</v>
       </c>
       <c r="CD52"/>
       <c r="CE52" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>6.6752883376554634E-2</v>
       </c>
       <c r="CF52" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6.6852298418384234E-2</v>
       </c>
       <c r="CG52" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.1533794994059523E-3</v>
       </c>
       <c r="CH52" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
@@ -60439,16 +60529,16 @@
       <c r="AP53" s="18">
         <v>0</v>
       </c>
-      <c r="AQ53" s="41" t="s">
+      <c r="AQ53" s="122" t="s">
         <v>346</v>
       </c>
-      <c r="AR53" t="s">
+      <c r="AR53" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS53" s="94" t="s">
+      <c r="AS53" s="123" t="s">
         <v>347</v>
       </c>
-      <c r="AT53" t="s">
+      <c r="AT53" s="122" t="s">
         <v>73</v>
       </c>
       <c r="AU53" s="21">
@@ -60467,11 +60557,11 @@
         <v>1</v>
       </c>
       <c r="AZ53">
-        <f>TINV(AX53,CC53)</f>
+        <f t="shared" si="16"/>
         <v>1.6519717481243639</v>
       </c>
       <c r="BA53" s="18" t="s">
-        <v>73</v>
+        <v>649</v>
       </c>
       <c r="BB53" s="18"/>
       <c r="BC53" s="18" t="s">
@@ -60498,8 +60588,8 @@
       <c r="BJ53">
         <v>868</v>
       </c>
-      <c r="BK53" s="18" t="s">
-        <v>73</v>
+      <c r="BK53" s="21">
+        <v>33.076000000000001</v>
       </c>
       <c r="BL53" s="18" t="s">
         <v>73</v>
@@ -60538,39 +60628,39 @@
         <v>1</v>
       </c>
       <c r="BX53" s="30">
-        <f>((AZ53^2)/(AZ53^2+BI53))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>0.111444570712238</v>
       </c>
       <c r="BY53" s="30">
-        <f>0.5*LN((1+BX53)/(1-BX53))</f>
+        <f t="shared" si="12"/>
         <v>0.11190941618239179</v>
       </c>
       <c r="BZ53" s="30">
-        <f>((1-(BY53^2)^2)/(BI53-1))</f>
+        <f t="shared" si="13"/>
         <v>4.6289035023228077E-3</v>
       </c>
       <c r="CA53" s="30">
-        <f>1/(BI53-3)</f>
+        <f t="shared" si="14"/>
         <v>4.6728971962616819E-3</v>
       </c>
       <c r="CC53">
-        <f>BI53-2</f>
+        <f t="shared" si="15"/>
         <v>215</v>
       </c>
       <c r="CE53" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>5.5983636926066289E-2</v>
       </c>
       <c r="CF53" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>5.6042234525477685E-2</v>
       </c>
       <c r="CG53" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.1533911600947939E-3</v>
       </c>
       <c r="CH53" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
@@ -60608,7 +60698,7 @@
       <c r="L54">
         <v>9</v>
       </c>
-      <c r="M54" s="18" t="s">
+      <c r="M54" s="126" t="s">
         <v>352</v>
       </c>
       <c r="N54" t="s">
@@ -60698,16 +60788,16 @@
       <c r="AP54" s="18">
         <v>0</v>
       </c>
-      <c r="AQ54" t="s">
+      <c r="AQ54" s="122" t="s">
         <v>355</v>
       </c>
-      <c r="AR54" t="s">
+      <c r="AR54" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS54" s="94" t="s">
+      <c r="AS54" s="123" t="s">
         <v>355</v>
       </c>
-      <c r="AT54" t="s">
+      <c r="AT54" s="122" t="s">
         <v>73</v>
       </c>
       <c r="AU54" s="21">
@@ -60726,7 +60816,7 @@
         <v>2</v>
       </c>
       <c r="AZ54">
-        <f>TINV(AX54,CC54)</f>
+        <f t="shared" si="16"/>
         <v>1.647384517634447</v>
       </c>
       <c r="BA54" s="18" t="s">
@@ -60797,39 +60887,39 @@
         <v>0</v>
       </c>
       <c r="BX54" s="30">
-        <f>((AZ54^2)/(AZ54^2+BI54))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>6.6825990375612127E-2</v>
       </c>
       <c r="BY54" s="30">
-        <f>0.5*LN((1+BX54)/(1-BX54))</f>
+        <f t="shared" si="12"/>
         <v>6.692573299656196E-2</v>
       </c>
       <c r="BZ54" s="30">
-        <f>((1-(BY54^2)^2)/(BI54-1))</f>
+        <f t="shared" si="13"/>
         <v>1.6555959239695694E-3</v>
       </c>
       <c r="CA54" s="30">
-        <f>1/(BI54-3)</f>
+        <f t="shared" si="14"/>
         <v>1.6611295681063123E-3</v>
       </c>
       <c r="CC54">
-        <f>BI54-2</f>
+        <f t="shared" si="15"/>
         <v>603</v>
       </c>
       <c r="CE54" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>6.6825990375612127E-2</v>
       </c>
       <c r="CF54" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6.692573299656196E-2</v>
       </c>
       <c r="CG54" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.6555959239695694E-3</v>
       </c>
       <c r="CH54" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
@@ -60867,7 +60957,7 @@
       <c r="L55">
         <v>9</v>
       </c>
-      <c r="M55" s="18" t="s">
+      <c r="M55" s="126" t="s">
         <v>352</v>
       </c>
       <c r="N55" t="s">
@@ -60957,16 +61047,16 @@
       <c r="AP55" s="18">
         <v>0</v>
       </c>
-      <c r="AQ55" t="s">
+      <c r="AQ55" s="122" t="s">
         <v>355</v>
       </c>
-      <c r="AR55" t="s">
+      <c r="AR55" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS55" s="94" t="s">
+      <c r="AS55" s="123" t="s">
         <v>355</v>
       </c>
-      <c r="AT55" t="s">
+      <c r="AT55" s="122" t="s">
         <v>73</v>
       </c>
       <c r="AU55" s="21">
@@ -60985,7 +61075,7 @@
         <v>1</v>
       </c>
       <c r="AZ55">
-        <f>TINV(AX55,CC55)</f>
+        <f t="shared" si="16"/>
         <v>1.9639058734740764</v>
       </c>
       <c r="BA55" s="18" t="s">
@@ -61056,39 +61146,39 @@
         <v>0</v>
       </c>
       <c r="BX55" s="30">
-        <f>((AZ55^2)/(AZ55^2+BI55))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>7.959083180520346E-2</v>
       </c>
       <c r="BY55" s="30">
-        <f>0.5*LN((1+BX55)/(1-BX55))</f>
+        <f t="shared" si="12"/>
         <v>7.9759534841727944E-2</v>
       </c>
       <c r="BZ55" s="30">
-        <f>((1-(BY55^2)^2)/(BI55-1))</f>
+        <f t="shared" si="13"/>
         <v>1.6555621361865366E-3</v>
       </c>
       <c r="CA55" s="30">
-        <f>1/(BI55-3)</f>
+        <f t="shared" si="14"/>
         <v>1.6611295681063123E-3</v>
       </c>
       <c r="CC55">
-        <f>BI55-2</f>
+        <f t="shared" si="15"/>
         <v>603</v>
       </c>
       <c r="CE55" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>7.959083180520346E-2</v>
       </c>
       <c r="CF55" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>7.9759534841727944E-2</v>
       </c>
       <c r="CG55" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.6555621361865366E-3</v>
       </c>
       <c r="CH55" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
@@ -61126,7 +61216,7 @@
       <c r="L56">
         <v>9</v>
       </c>
-      <c r="M56" s="18" t="s">
+      <c r="M56" s="126" t="s">
         <v>352</v>
       </c>
       <c r="N56" t="s">
@@ -61216,16 +61306,16 @@
       <c r="AP56" s="18">
         <v>1</v>
       </c>
-      <c r="AQ56" t="s">
+      <c r="AQ56" s="122" t="s">
         <v>355</v>
       </c>
-      <c r="AR56" t="s">
+      <c r="AR56" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS56" s="94" t="s">
+      <c r="AS56" s="123" t="s">
         <v>355</v>
       </c>
-      <c r="AT56" t="s">
+      <c r="AT56" s="122" t="s">
         <v>73</v>
       </c>
       <c r="AU56" s="21">
@@ -61244,7 +61334,7 @@
         <v>2</v>
       </c>
       <c r="AZ56">
-        <f>TINV(AX56,CC56)</f>
+        <f t="shared" si="16"/>
         <v>1.647384517634447</v>
       </c>
       <c r="BA56" s="18" t="s">
@@ -61315,39 +61405,39 @@
         <v>0</v>
       </c>
       <c r="BX56" s="30">
-        <f>((AZ56^2)/(AZ56^2+BI56))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>6.6825990375612127E-2</v>
       </c>
       <c r="BY56" s="30">
-        <f>0.5*LN((1+BX56)/(1-BX56))</f>
+        <f t="shared" si="12"/>
         <v>6.692573299656196E-2</v>
       </c>
       <c r="BZ56" s="30">
-        <f>((1-(BY56^2)^2)/(BI56-1))</f>
+        <f t="shared" si="13"/>
         <v>1.6555959239695694E-3</v>
       </c>
       <c r="CA56" s="30">
-        <f>1/(BI56-3)</f>
+        <f t="shared" si="14"/>
         <v>1.6611295681063123E-3</v>
       </c>
       <c r="CC56">
-        <f>BI56-2</f>
+        <f t="shared" si="15"/>
         <v>603</v>
       </c>
       <c r="CE56" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>6.6825990375612127E-2</v>
       </c>
       <c r="CF56" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6.692573299656196E-2</v>
       </c>
       <c r="CG56" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.6555959239695694E-3</v>
       </c>
       <c r="CH56" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
@@ -61385,7 +61475,7 @@
       <c r="L57">
         <v>9</v>
       </c>
-      <c r="M57" s="18" t="s">
+      <c r="M57" s="126" t="s">
         <v>352</v>
       </c>
       <c r="N57" t="s">
@@ -61475,16 +61565,16 @@
       <c r="AP57" s="18">
         <v>0</v>
       </c>
-      <c r="AQ57" t="s">
+      <c r="AQ57" s="122" t="s">
         <v>355</v>
       </c>
-      <c r="AR57" t="s">
+      <c r="AR57" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS57" s="94" t="s">
+      <c r="AS57" s="123" t="s">
         <v>355</v>
       </c>
-      <c r="AT57" t="s">
+      <c r="AT57" s="122" t="s">
         <v>73</v>
       </c>
       <c r="AU57" s="21">
@@ -61503,7 +61593,7 @@
         <v>1</v>
       </c>
       <c r="AZ57">
-        <f>TINV(AX57,CC57)</f>
+        <f t="shared" si="16"/>
         <v>2.5840071350575324</v>
       </c>
       <c r="BA57" s="18" t="s">
@@ -61574,39 +61664,39 @@
         <v>0</v>
       </c>
       <c r="BX57" s="30">
-        <f>((AZ57^2)/(AZ57^2+BI57))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>0.10447986438429385</v>
       </c>
       <c r="BY57" s="30">
-        <f>0.5*LN((1+BX57)/(1-BX57))</f>
+        <f t="shared" si="12"/>
         <v>0.10486254279362485</v>
       </c>
       <c r="BZ57" s="30">
-        <f>((1-(BY57^2)^2)/(BI57-1))</f>
+        <f t="shared" si="13"/>
         <v>1.6554289480493617E-3</v>
       </c>
       <c r="CA57" s="30">
-        <f>1/(BI57-3)</f>
+        <f t="shared" si="14"/>
         <v>1.6611295681063123E-3</v>
       </c>
       <c r="CC57">
-        <f>BI57-2</f>
+        <f t="shared" si="15"/>
         <v>603</v>
       </c>
       <c r="CE57" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0.10447986438429385</v>
       </c>
       <c r="CF57" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0.10486254279362485</v>
       </c>
       <c r="CG57" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.6554289480493617E-3</v>
       </c>
       <c r="CH57" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
@@ -61644,7 +61734,7 @@
       <c r="L58">
         <v>9</v>
       </c>
-      <c r="M58" s="18" t="s">
+      <c r="M58" s="126" t="s">
         <v>352</v>
       </c>
       <c r="N58" t="s">
@@ -61734,16 +61824,16 @@
       <c r="AP58" s="18">
         <v>0</v>
       </c>
-      <c r="AQ58" t="s">
+      <c r="AQ58" s="122" t="s">
         <v>355</v>
       </c>
-      <c r="AR58" t="s">
+      <c r="AR58" s="122" t="s">
         <v>234</v>
       </c>
-      <c r="AS58" s="94" t="s">
+      <c r="AS58" s="123" t="s">
         <v>355</v>
       </c>
-      <c r="AT58" t="s">
+      <c r="AT58" s="122" t="s">
         <v>73</v>
       </c>
       <c r="AU58" s="21">
@@ -61762,7 +61852,7 @@
         <v>2</v>
       </c>
       <c r="AZ58">
-        <f>TINV(AX58,CC58)</f>
+        <f t="shared" si="16"/>
         <v>1.647384517634447</v>
       </c>
       <c r="BA58" s="18" t="s">
@@ -61833,39 +61923,39 @@
         <v>0</v>
       </c>
       <c r="BX58" s="30">
-        <f>((AZ58^2)/(AZ58^2+BI58))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>6.6825990375612127E-2</v>
       </c>
       <c r="BY58" s="30">
-        <f>0.5*LN((1+BX58)/(1-BX58))</f>
+        <f t="shared" si="12"/>
         <v>6.692573299656196E-2</v>
       </c>
       <c r="BZ58" s="30">
-        <f>((1-(BY58^2)^2)/(BI58-1))</f>
+        <f t="shared" si="13"/>
         <v>1.6555959239695694E-3</v>
       </c>
       <c r="CA58" s="30">
-        <f>1/(BI58-3)</f>
+        <f t="shared" si="14"/>
         <v>1.6611295681063123E-3</v>
       </c>
       <c r="CC58">
-        <f>BI58-2</f>
+        <f t="shared" si="15"/>
         <v>603</v>
       </c>
       <c r="CE58" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>6.6825990375612127E-2</v>
       </c>
       <c r="CF58" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6.692573299656196E-2</v>
       </c>
       <c r="CG58" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1.6555959239695694E-3</v>
       </c>
       <c r="CH58" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
@@ -61993,16 +62083,16 @@
       <c r="AP59" s="18">
         <v>0</v>
       </c>
-      <c r="AQ59" t="s">
+      <c r="AQ59" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AR59" s="94" t="s">
+      <c r="AR59" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="AS59" s="94" t="s">
+      <c r="AS59" s="123" t="s">
         <v>337</v>
       </c>
-      <c r="AT59" s="94" t="s">
+      <c r="AT59" s="123" t="s">
         <v>338</v>
       </c>
       <c r="AU59" s="21">
@@ -62021,7 +62111,7 @@
         <v>1</v>
       </c>
       <c r="AZ59">
-        <f>TINV(AX59,CC59)</f>
+        <f t="shared" si="16"/>
         <v>2.6063275150437986</v>
       </c>
       <c r="BA59" s="18" t="s">
@@ -62092,39 +62182,39 @@
         <v>0</v>
       </c>
       <c r="BX59" s="104">
-        <f>((AZ59^2)/(AZ59^2+BI59))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>0.19885033588999154</v>
       </c>
       <c r="BY59" s="104">
-        <f>0.5*LN((1+BX59)/(1-BX59))</f>
+        <f t="shared" si="12"/>
         <v>0.20153527346528599</v>
       </c>
       <c r="BZ59" s="104">
-        <f>((1-(BY59^2)^2)/(BI59-1))</f>
+        <f t="shared" si="13"/>
         <v>6.0875018454454692E-3</v>
       </c>
       <c r="CA59" s="95">
-        <f>1/(BI59-3)</f>
+        <f t="shared" si="14"/>
         <v>6.1728395061728392E-3</v>
       </c>
       <c r="CC59">
-        <f>BI59-2</f>
+        <f t="shared" si="15"/>
         <v>163</v>
       </c>
       <c r="CE59" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>5.0347553184348748E-2</v>
       </c>
       <c r="CF59" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>5.0390159607631088E-2</v>
       </c>
       <c r="CG59" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>3.7424908406621514E-4</v>
       </c>
       <c r="CH59" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
@@ -62252,16 +62342,16 @@
       <c r="AP60" s="18">
         <v>0</v>
       </c>
-      <c r="AQ60" t="s">
+      <c r="AQ60" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AR60" s="94" t="s">
+      <c r="AR60" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="AS60" s="94" t="s">
+      <c r="AS60" s="123" t="s">
         <v>337</v>
       </c>
-      <c r="AT60" s="94" t="s">
+      <c r="AT60" s="123" t="s">
         <v>338</v>
       </c>
       <c r="AU60" s="21">
@@ -62280,7 +62370,7 @@
         <v>1</v>
       </c>
       <c r="AZ60">
-        <f>TINV(AX60,CC60)</f>
+        <f t="shared" si="16"/>
         <v>1.974624620966356</v>
       </c>
       <c r="BA60" s="18" t="s">
@@ -62351,39 +62441,39 @@
         <v>0</v>
       </c>
       <c r="BX60" s="104">
-        <f>((AZ60^2)/(AZ60^2+BI60))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>0.15193954642337751</v>
       </c>
       <c r="BY60" s="104">
-        <f>0.5*LN((1+BX60)/(1-BX60))</f>
+        <f t="shared" si="12"/>
         <v>0.15312521998491627</v>
       </c>
       <c r="BZ60" s="104">
-        <f>((1-(BY60^2)^2)/(BI60-1))</f>
+        <f t="shared" si="13"/>
         <v>6.0942086742402533E-3</v>
       </c>
       <c r="CA60" s="95">
-        <f>1/(BI60-3)</f>
+        <f t="shared" si="14"/>
         <v>6.1728395061728392E-3</v>
       </c>
       <c r="CC60">
-        <f>BI60-2</f>
+        <f t="shared" si="15"/>
         <v>163</v>
       </c>
       <c r="CE60" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.1759803179979682E-2</v>
       </c>
       <c r="CF60" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>4.1784103322347603E-2</v>
       </c>
       <c r="CG60" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>4.4822812720473595E-4</v>
       </c>
       <c r="CH60" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
@@ -62511,16 +62601,16 @@
       <c r="AP61" s="18">
         <v>0</v>
       </c>
-      <c r="AQ61" t="s">
+      <c r="AQ61" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AR61" s="94" t="s">
+      <c r="AR61" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="AS61" s="94" t="s">
+      <c r="AS61" s="123" t="s">
         <v>337</v>
       </c>
-      <c r="AT61" s="94" t="s">
+      <c r="AT61" s="123" t="s">
         <v>338</v>
       </c>
       <c r="AU61" s="21">
@@ -62539,7 +62629,7 @@
         <v>1</v>
       </c>
       <c r="AZ61">
-        <f>TINV(AX61,CC61)</f>
+        <f t="shared" si="16"/>
         <v>2.6063275150437986</v>
       </c>
       <c r="BA61" s="18" t="s">
@@ -62610,39 +62700,39 @@
         <v>0</v>
       </c>
       <c r="BX61" s="104">
-        <f>((AZ61^2)/(AZ61^2+BI61))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>0.19885033588999154</v>
       </c>
       <c r="BY61" s="104">
-        <f>0.5*LN((1+BX61)/(1-BX61))</f>
+        <f t="shared" si="12"/>
         <v>0.20153527346528599</v>
       </c>
       <c r="BZ61" s="104">
-        <f>((1-(BY61^2)^2)/(BI61-1))</f>
+        <f t="shared" si="13"/>
         <v>6.0875018454454692E-3</v>
       </c>
       <c r="CA61" s="95">
-        <f>1/(BI61-3)</f>
+        <f t="shared" si="14"/>
         <v>6.1728395061728392E-3</v>
       </c>
       <c r="CC61">
-        <f>BI61-2</f>
+        <f t="shared" si="15"/>
         <v>163</v>
       </c>
       <c r="CE61" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>5.0347553184348748E-2</v>
       </c>
       <c r="CF61" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>5.0390159607631088E-2</v>
       </c>
       <c r="CG61" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>3.7424908406621514E-4</v>
       </c>
       <c r="CH61" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
@@ -62770,16 +62860,16 @@
       <c r="AP62" s="18">
         <v>0</v>
       </c>
-      <c r="AQ62" t="s">
+      <c r="AQ62" s="122" t="s">
         <v>337</v>
       </c>
-      <c r="AR62" s="94" t="s">
+      <c r="AR62" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="AS62" s="94" t="s">
+      <c r="AS62" s="123" t="s">
         <v>337</v>
       </c>
-      <c r="AT62" s="94" t="s">
+      <c r="AT62" s="123" t="s">
         <v>338</v>
       </c>
       <c r="AU62" s="21">
@@ -62798,7 +62888,7 @@
         <v>1</v>
       </c>
       <c r="AZ62">
-        <f>TINV(AX62,CC62)</f>
+        <f t="shared" si="16"/>
         <v>1.974624620966356</v>
       </c>
       <c r="BA62" s="18" t="s">
@@ -62869,39 +62959,39 @@
         <v>0</v>
       </c>
       <c r="BX62" s="104">
-        <f>((AZ62^2)/(AZ62^2+BI62))^(1/2)</f>
+        <f t="shared" si="11"/>
         <v>0.15193954642337751</v>
       </c>
       <c r="BY62" s="104">
-        <f>0.5*LN((1+BX62)/(1-BX62))</f>
+        <f t="shared" si="12"/>
         <v>0.15312521998491627</v>
       </c>
       <c r="BZ62" s="104">
-        <f>((1-(BY62^2)^2)/(BI62-1))</f>
+        <f t="shared" si="13"/>
         <v>6.0942086742402533E-3</v>
       </c>
       <c r="CA62" s="95">
-        <f>1/(BI62-3)</f>
+        <f t="shared" si="14"/>
         <v>6.1728395061728392E-3</v>
       </c>
       <c r="CC62">
-        <f>BI62-2</f>
+        <f t="shared" si="15"/>
         <v>163</v>
       </c>
       <c r="CE62" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.1759803179979682E-2</v>
       </c>
       <c r="CF62" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>4.1784103322347603E-2</v>
       </c>
       <c r="CG62" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>4.4822812720473595E-4</v>
       </c>
       <c r="CH62" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
@@ -62955,37 +63045,42 @@
       <c r="BB76" s="116"/>
     </row>
   </sheetData>
-  <autoFilter ref="AR1:AR71" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CD76">
+  <autoFilter ref="AR1:AR71"/>
+  <sortState ref="A2:CD76">
     <sortCondition ref="C2:C76"/>
   </sortState>
   <dataConsolidate/>
   <phoneticPr fontId="24" type="noConversion"/>
   <conditionalFormatting sqref="AU1:AU1048576">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BK51:BK53">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="603" yWindow="1085" count="7">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH1:AP1 AH32:AP43 AH7:AH8 AJ7:AP8 S15:S31 AH15:AP26 AH56:AP1048576 AL28 AH27:AK28 AL27:AP27 AH29:AL31 AN28:AQ31 S1 U1 AH44:AQ55 U40:U1048576 S35:S1048576 U15:U36" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH1:AP1 AH32:AP43 AH7:AH8 AJ7:AP8 S15:S31 AH15:AP26 AH56:AP1048576 AL28 AH27:AK28 AL27:AP27 AH29:AL31 AN28:AQ31 S1 U1 AH44:AQ55 U40:U1048576 S35:S1048576 U15:U36">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I15:I29 I31:I1048576" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I15:I29 I31:I1048576">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AD40:AF62 AG7:AG8 AD15:AF27 AG21:AG31 AD29:AF34 AD28:AE28 AD35:AE39 AG35:AG39 AH62 AD1:AG1 AD63:AG1048576" xr:uid="{00000000-0002-0000-0100-000002000000}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y1:AC1 AI7:AI8 Y7:Y8 AA7:AE8 Y15:AC1048576" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AD40:AF62 AG7:AG8 AD15:AF27 AG21:AG31 AD29:AF34 AD28:AE28 AD35:AE39 AG35:AG39 AH62 AD1:AG1 AD63:AG1048576"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y1:AC1 AI7:AI8 Y7:Y8 AA7:AE8 Y15:AC1048576">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN1 BO28:BO31 BO44:BO55 BN63:BN1048576" xr:uid="{00000000-0002-0000-0100-000004000000}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AY56:AY62" xr:uid="{00000000-0002-0000-0100-000005000000}">
+    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN1 BO28:BO31 BO44:BO55 BN63:BN1048576"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AY56:AY62">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY15:AY26 AY32:AY43" xr:uid="{00000000-0002-0000-0100-000006000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY15:AY26 AY32:AY43">
       <formula1>1</formula1>
       <formula2>3</formula2>
     </dataValidation>
@@ -62996,127 +63091,127 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="603" yWindow="1085" count="21">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000007000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>U1 U63:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000008000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>BU56:BW1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000009000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$C$2:$C$4</xm:f>
           </x14:formula1>
           <xm:sqref>BO1 BO56:BO1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$I$2:$I$3</xm:f>
           </x14:formula1>
           <xm:sqref>AV1 AV63:AV1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$9</xm:f>
           </x14:formula1>
           <xm:sqref>U1 S1 S56:S1048576 U63:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$K$2:$K$3</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1 S1 S56:S1048576 U63:W1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000D000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N$2:$N$7</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1 S1 S56:S1048576 U63:W1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000F000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$J$2:$J$12</xm:f>
           </x14:formula1>
           <xm:sqref>K1 K63:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000010000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$O:$O</xm:f>
           </x14:formula1>
           <xm:sqref>BT1 BT63:BT1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000011000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$S:$S</xm:f>
           </x14:formula1>
           <xm:sqref>G1 G63:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000012000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G:$G</xm:f>
           </x14:formula1>
           <xm:sqref>AR1 AR56:AR1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000013000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F:$F</xm:f>
           </x14:formula1>
           <xm:sqref>M77:M1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000014000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$P:$P</xm:f>
           </x14:formula1>
           <xm:sqref>AT1 AT56:AT1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000015000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D:$D</xm:f>
           </x14:formula1>
           <xm:sqref>U63:W1048576 S1 U1:W1 S56:S1048576 N56:N1048576 N1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000016000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N:$N</xm:f>
           </x14:formula1>
           <xm:sqref>O1 O56:O1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000017000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B:$B</xm:f>
           </x14:formula1>
           <xm:sqref>T1 T56:T1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000018000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$R:$R</xm:f>
           </x14:formula1>
           <xm:sqref>E1 E56:E1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000019000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H:$H</xm:f>
           </x14:formula1>
           <xm:sqref>U63:U1048576 U1 S1 S56:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00001A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$M:$M</xm:f>
           </x14:formula1>
           <xm:sqref>S1 P28:P31 P1 U1 S56:S1048576 P56:P1048576 U63:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00001B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$10</xm:f>
           </x14:formula1>
           <xm:sqref>R1:R1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00001C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H$1:$H$7</xm:f>
           </x14:formula1>
@@ -63129,9 +63224,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4103C6B8-D66D-FF4D-BFD0-320CD520D889}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BJ18"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
@@ -66034,9 +66129,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S99"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
     <col min="5" max="5" width="19.625" customWidth="1"/>
@@ -66047,7 +66142,7 @@
     <col min="10" max="10" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.100000000000001">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>432</v>
       </c>
@@ -66103,7 +66198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="33.950000000000003">
+    <row r="2" spans="1:19" ht="31.5">
       <c r="A2">
         <v>0</v>
       </c>
@@ -66159,7 +66254,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="33.950000000000003">
+    <row r="3" spans="1:19" ht="31.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -66215,7 +66310,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="51">
+    <row r="4" spans="1:19" ht="47.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -66265,7 +66360,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="51">
+    <row r="5" spans="1:19" ht="47.25">
       <c r="D5" t="s">
         <v>453</v>
       </c>
@@ -67266,7 +67361,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="R2:S91">
+  <sortState ref="R2:S91">
     <sortCondition ref="R2:R91"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/appliances_wtp.xlsx
+++ b/appliances_wtp.xlsx
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4072" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4072" uniqueCount="646">
   <si>
     <t>Coder</t>
   </si>
@@ -2552,6 +2552,9 @@
   <si>
     <t>1,83</t>
   </si>
+  <si>
+    <t>dishwasher</t>
+  </si>
 </sst>
 </file>
 
@@ -35040,7 +35043,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -47011,7 +47014,7 @@
         <v>195</v>
       </c>
       <c r="AJ1" s="75" t="s">
-        <v>18</v>
+        <v>645</v>
       </c>
       <c r="AK1" s="75" t="s">
         <v>19</v>
@@ -47388,39 +47391,39 @@
         <v>1</v>
       </c>
       <c r="BX2" s="103">
-        <f t="shared" ref="BX2:BX33" si="0">((AZ2^2)/(AZ2^2+BI2))^(1/2)</f>
+        <f>((AZ2^2)/(AZ2^2+BI2))^(1/2)</f>
         <v>2.4066942415906588E-2</v>
       </c>
       <c r="BY2" s="103">
-        <f t="shared" ref="BY2:BY33" si="1">0.5*LN((1+BX2)/(1-BX2))</f>
+        <f>0.5*LN((1+BX2)/(1-BX2))</f>
         <v>2.4071590697916326E-2</v>
       </c>
       <c r="BZ2" s="103">
-        <f t="shared" ref="BZ2:BZ33" si="2">((1-(BY2^2)^2)/(BI2-1))</f>
+        <f>((1-(BY2^2)^2)/(BI2-1))</f>
         <v>2.9940109708011158E-3</v>
       </c>
       <c r="CA2" s="95">
-        <f t="shared" ref="CA2:CA33" si="3">1/(BI2-3)</f>
+        <f>1/(BI2-3)</f>
         <v>3.0120481927710845E-3</v>
       </c>
       <c r="CC2">
-        <f t="shared" ref="CC2:CC45" si="4">BI2-2</f>
+        <f>BI2-2</f>
         <v>333</v>
       </c>
       <c r="CE2" s="30">
-        <f t="shared" ref="CE2:CE33" si="5">((AZ2^2)/(AZ2^2+BJ2))^(1/2)</f>
+        <f>((AZ2^2)/(AZ2^2+BJ2))^(1/2)</f>
         <v>2.4066942415906588E-2</v>
       </c>
       <c r="CF2" s="30">
-        <f t="shared" ref="CF2:CF33" si="6">0.5*LN((1+CE2)/(1-CE2))</f>
+        <f>0.5*LN((1+CE2)/(1-CE2))</f>
         <v>2.4071590697916326E-2</v>
       </c>
       <c r="CG2" s="30">
-        <f t="shared" ref="CG2:CG33" si="7">((1-(CF2^2)^2)/(BJ2-1))</f>
+        <f>((1-(CF2^2)^2)/(BJ2-1))</f>
         <v>2.9940109708011158E-3</v>
       </c>
       <c r="CH2" s="30">
-        <f t="shared" ref="CH2:CH33" si="8">1/(BJ2-3)</f>
+        <f>1/(BJ2-3)</f>
         <v>3.0120481927710845E-3</v>
       </c>
     </row>
@@ -47649,39 +47652,39 @@
         <v>1</v>
       </c>
       <c r="BX3" s="103">
-        <f t="shared" si="0"/>
+        <f>((AZ3^2)/(AZ3^2+BI3))^(1/2)</f>
         <v>0.18088754235543161</v>
       </c>
       <c r="BY3" s="103">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX3)/(1-BX3))</f>
         <v>0.18290010196181533</v>
       </c>
       <c r="BZ3" s="103">
-        <f t="shared" si="2"/>
+        <f>((1-(BY3^2)^2)/(BI3-1))</f>
         <v>2.2753552022091081E-3</v>
       </c>
       <c r="CA3" s="95">
-        <f t="shared" si="3"/>
+        <f>1/(BI3-3)</f>
         <v>2.2883295194508009E-3</v>
       </c>
       <c r="CC3">
-        <f t="shared" si="4"/>
+        <f>BI3-2</f>
         <v>438</v>
       </c>
       <c r="CE3" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ3^2)/(AZ3^2+BJ3))^(1/2)</f>
         <v>0.18088754235543161</v>
       </c>
       <c r="CF3" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE3)/(1-CE3))</f>
         <v>0.18290010196181533</v>
       </c>
       <c r="CG3" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF3^2)^2)/(BJ3-1))</f>
         <v>2.2753552022091081E-3</v>
       </c>
       <c r="CH3" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ3-3)</f>
         <v>2.2883295194508009E-3</v>
       </c>
     </row>
@@ -47789,10 +47792,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL4" s="18">
         <v>0</v>
@@ -47908,39 +47911,39 @@
         <v>0</v>
       </c>
       <c r="BX4" s="103">
-        <f t="shared" si="0"/>
+        <f>((AZ4^2)/(AZ4^2+BI4))^(1/2)</f>
         <v>0.19885033588999154</v>
       </c>
       <c r="BY4" s="103">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX4)/(1-BX4))</f>
         <v>0.20153527346528599</v>
       </c>
       <c r="BZ4" s="103">
-        <f t="shared" si="2"/>
+        <f>((1-(BY4^2)^2)/(BI4-1))</f>
         <v>6.0875018454454692E-3</v>
       </c>
       <c r="CA4" s="95">
-        <f t="shared" si="3"/>
+        <f>1/(BI4-3)</f>
         <v>6.1728395061728392E-3</v>
       </c>
       <c r="CC4">
-        <f t="shared" si="4"/>
+        <f>BI4-2</f>
         <v>163</v>
       </c>
       <c r="CE4" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ4^2)/(AZ4^2+BJ4))^(1/2)</f>
         <v>5.0347553184348748E-2</v>
       </c>
       <c r="CF4" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE4)/(1-CE4))</f>
         <v>5.0390159607631088E-2</v>
       </c>
       <c r="CG4" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF4^2)^2)/(BJ4-1))</f>
         <v>3.7424908406621514E-4</v>
       </c>
       <c r="CH4" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ4-3)</f>
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
@@ -48049,10 +48052,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL5" s="18">
         <v>0</v>
@@ -48168,41 +48171,41 @@
         <v>0</v>
       </c>
       <c r="BX5" s="103">
-        <f t="shared" si="0"/>
+        <f>((AZ5^2)/(AZ5^2+BI5))^(1/2)</f>
         <v>0.15193954642337751</v>
       </c>
       <c r="BY5" s="103">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX5)/(1-BX5))</f>
         <v>0.15312521998491627</v>
       </c>
       <c r="BZ5" s="103">
-        <f t="shared" si="2"/>
+        <f>((1-(BY5^2)^2)/(BI5-1))</f>
         <v>6.0942086742402533E-3</v>
       </c>
       <c r="CA5" s="95">
-        <f t="shared" si="3"/>
+        <f>1/(BI5-3)</f>
         <v>6.1728395061728392E-3</v>
       </c>
       <c r="CB5"/>
       <c r="CC5">
-        <f t="shared" si="4"/>
+        <f>BI5-2</f>
         <v>163</v>
       </c>
       <c r="CD5"/>
       <c r="CE5" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ5^2)/(AZ5^2+BJ5))^(1/2)</f>
         <v>4.1759803179979682E-2</v>
       </c>
       <c r="CF5" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE5)/(1-CE5))</f>
         <v>4.1784103322347603E-2</v>
       </c>
       <c r="CG5" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF5^2)^2)/(BJ5-1))</f>
         <v>4.4822812720473595E-4</v>
       </c>
       <c r="CH5" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ5-3)</f>
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
@@ -48310,10 +48313,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL6" s="18">
         <v>0</v>
@@ -48429,39 +48432,39 @@
         <v>0</v>
       </c>
       <c r="BX6" s="103">
-        <f t="shared" si="0"/>
+        <f>((AZ6^2)/(AZ6^2+BI6))^(1/2)</f>
         <v>0.19885033588999154</v>
       </c>
       <c r="BY6" s="103">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX6)/(1-BX6))</f>
         <v>0.20153527346528599</v>
       </c>
       <c r="BZ6" s="103">
-        <f t="shared" si="2"/>
+        <f>((1-(BY6^2)^2)/(BI6-1))</f>
         <v>6.0875018454454692E-3</v>
       </c>
       <c r="CA6" s="95">
-        <f t="shared" si="3"/>
+        <f>1/(BI6-3)</f>
         <v>6.1728395061728392E-3</v>
       </c>
       <c r="CC6">
-        <f t="shared" si="4"/>
+        <f>BI6-2</f>
         <v>163</v>
       </c>
       <c r="CE6" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ6^2)/(AZ6^2+BJ6))^(1/2)</f>
         <v>5.0347553184348748E-2</v>
       </c>
       <c r="CF6" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE6)/(1-CE6))</f>
         <v>5.0390159607631088E-2</v>
       </c>
       <c r="CG6" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF6^2)^2)/(BJ6-1))</f>
         <v>3.7424908406621514E-4</v>
       </c>
       <c r="CH6" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ6-3)</f>
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
@@ -48570,10 +48573,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL7" s="18">
         <v>0</v>
@@ -48689,41 +48692,41 @@
         <v>0</v>
       </c>
       <c r="BX7" s="103">
-        <f t="shared" si="0"/>
+        <f>((AZ7^2)/(AZ7^2+BI7))^(1/2)</f>
         <v>0.15193954642337751</v>
       </c>
       <c r="BY7" s="103">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX7)/(1-BX7))</f>
         <v>0.15312521998491627</v>
       </c>
       <c r="BZ7" s="103">
-        <f t="shared" si="2"/>
+        <f>((1-(BY7^2)^2)/(BI7-1))</f>
         <v>6.0942086742402533E-3</v>
       </c>
       <c r="CA7" s="95">
-        <f t="shared" si="3"/>
+        <f>1/(BI7-3)</f>
         <v>6.1728395061728392E-3</v>
       </c>
       <c r="CB7"/>
       <c r="CC7">
-        <f t="shared" si="4"/>
+        <f>BI7-2</f>
         <v>163</v>
       </c>
       <c r="CD7"/>
       <c r="CE7" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ7^2)/(AZ7^2+BJ7))^(1/2)</f>
         <v>4.1759803179979682E-2</v>
       </c>
       <c r="CF7" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE7)/(1-CE7))</f>
         <v>4.1784103322347603E-2</v>
       </c>
       <c r="CG7" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF7^2)^2)/(BJ7-1))</f>
         <v>4.4822812720473595E-4</v>
       </c>
       <c r="CH7" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ7-3)</f>
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
@@ -48951,41 +48954,41 @@
         <v>1</v>
       </c>
       <c r="BX8" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ8^2)/(AZ8^2+BI8))^(1/2)</f>
         <v>1.3921746511164878E-2</v>
       </c>
       <c r="BY8" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX8)/(1-BX8))</f>
         <v>1.3922646030325031E-2</v>
       </c>
       <c r="BZ8" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY8^2)^2)/(BI8-1))</f>
         <v>4.1000408463551713E-4</v>
       </c>
       <c r="CA8" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI8-3)</f>
         <v>4.103405826836274E-4</v>
       </c>
       <c r="CB8"/>
       <c r="CC8">
-        <f t="shared" si="4"/>
+        <f>BI8-2</f>
         <v>2438</v>
       </c>
       <c r="CD8"/>
       <c r="CE8" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ8^2)/(AZ8^2+BJ8))^(1/2)</f>
         <v>8.0630640330570883E-3</v>
       </c>
       <c r="CF8" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE8)/(1-CE8))</f>
         <v>8.0632387745383748E-3</v>
       </c>
       <c r="CG8" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF8^2)^2)/(BJ8-1))</f>
         <v>1.374759411290821E-4</v>
       </c>
       <c r="CH8" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ8-3)</f>
         <v>1.3751375137513751E-4</v>
       </c>
     </row>
@@ -49142,7 +49145,7 @@
         <v>3</v>
       </c>
       <c r="AZ9">
-        <f t="shared" ref="AZ9:AZ15" si="9">TINV(AX9,CC9)</f>
+        <f>TINV(AX9,CC9)</f>
         <v>3.2994178866117148</v>
       </c>
       <c r="BA9" s="18" t="s">
@@ -49213,40 +49216,40 @@
         <v>0</v>
       </c>
       <c r="BX9" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ9^2)/(AZ9^2+BI9))^(1/2)</f>
         <v>9.9037143771440309E-2</v>
       </c>
       <c r="BY9" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX9)/(1-BX9))</f>
         <v>9.9362859957839736E-2</v>
       </c>
       <c r="BZ9" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY9^2)^2)/(BI9-1))</f>
         <v>9.1065803670912202E-4</v>
       </c>
       <c r="CA9" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI9-3)</f>
         <v>9.1240875912408756E-4</v>
       </c>
       <c r="CB9" s="99"/>
       <c r="CC9">
-        <f t="shared" si="4"/>
+        <f>BI9-2</f>
         <v>1097</v>
       </c>
       <c r="CE9" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ9^2)/(AZ9^2+BJ9))^(1/2)</f>
         <v>2.8718958292254938E-2</v>
       </c>
       <c r="CF9" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE9)/(1-CE9))</f>
         <v>2.8726857795568102E-2</v>
       </c>
       <c r="CG9" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF9^2)^2)/(BJ9-1))</f>
         <v>7.5832207400588011E-5</v>
       </c>
       <c r="CH9" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ9-3)</f>
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
@@ -49403,7 +49406,7 @@
         <v>3</v>
       </c>
       <c r="AZ10">
-        <f t="shared" si="9"/>
+        <f>TINV(AX10,CC10)</f>
         <v>3.2994178866117148</v>
       </c>
       <c r="BA10" s="18" t="s">
@@ -49474,40 +49477,40 @@
         <v>0</v>
       </c>
       <c r="BX10" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ10^2)/(AZ10^2+BI10))^(1/2)</f>
         <v>9.9037143771440309E-2</v>
       </c>
       <c r="BY10" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX10)/(1-BX10))</f>
         <v>9.9362859957839736E-2</v>
       </c>
       <c r="BZ10" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY10^2)^2)/(BI10-1))</f>
         <v>9.1065803670912202E-4</v>
       </c>
       <c r="CA10" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI10-3)</f>
         <v>9.1240875912408756E-4</v>
       </c>
       <c r="CB10" s="99"/>
       <c r="CC10">
-        <f t="shared" si="4"/>
+        <f>BI10-2</f>
         <v>1097</v>
       </c>
       <c r="CE10" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ10^2)/(AZ10^2+BJ10))^(1/2)</f>
         <v>2.8718958292254938E-2</v>
       </c>
       <c r="CF10" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE10)/(1-CE10))</f>
         <v>2.8726857795568102E-2</v>
       </c>
       <c r="CG10" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF10^2)^2)/(BJ10-1))</f>
         <v>7.5832207400588011E-5</v>
       </c>
       <c r="CH10" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ10-3)</f>
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
@@ -49664,7 +49667,7 @@
         <v>3</v>
       </c>
       <c r="AZ11">
-        <f t="shared" si="9"/>
+        <f>TINV(AX11,CC11)</f>
         <v>1.0135940485180941</v>
       </c>
       <c r="BA11" s="18" t="s">
@@ -49735,40 +49738,40 @@
         <v>0</v>
       </c>
       <c r="BX11" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ11^2)/(AZ11^2+BI11))^(1/2)</f>
         <v>3.056063020259667E-2</v>
       </c>
       <c r="BY11" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX11)/(1-BX11))</f>
         <v>3.0570149592664689E-2</v>
       </c>
       <c r="BZ11" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY11^2)^2)/(BI11-1))</f>
         <v>9.107460169818913E-4</v>
       </c>
       <c r="CA11" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI11-3)</f>
         <v>9.1240875912408756E-4</v>
       </c>
       <c r="CB11" s="99"/>
       <c r="CC11">
-        <f t="shared" si="4"/>
+        <f>BI11-2</f>
         <v>1097</v>
       </c>
       <c r="CE11" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ11^2)/(AZ11^2+BJ11))^(1/2)</f>
         <v>8.8258728613782138E-3</v>
       </c>
       <c r="CF11" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE11)/(1-CE11))</f>
         <v>8.826102038913812E-3</v>
       </c>
       <c r="CG11" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF11^2)^2)/(BJ11-1))</f>
         <v>7.5832258582814749E-5</v>
       </c>
       <c r="CH11" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ11-3)</f>
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
@@ -49925,7 +49928,7 @@
         <v>3</v>
       </c>
       <c r="AZ12">
-        <f t="shared" si="9"/>
+        <f>TINV(AX12,CC12)</f>
         <v>3.2994178866117148</v>
       </c>
       <c r="BA12" s="18" t="s">
@@ -49996,40 +49999,40 @@
         <v>0</v>
       </c>
       <c r="BX12" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ12^2)/(AZ12^2+BI12))^(1/2)</f>
         <v>9.9037143771440309E-2</v>
       </c>
       <c r="BY12" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX12)/(1-BX12))</f>
         <v>9.9362859957839736E-2</v>
       </c>
       <c r="BZ12" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY12^2)^2)/(BI12-1))</f>
         <v>9.1065803670912202E-4</v>
       </c>
       <c r="CA12" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI12-3)</f>
         <v>9.1240875912408756E-4</v>
       </c>
       <c r="CB12" s="99"/>
       <c r="CC12">
-        <f t="shared" si="4"/>
+        <f>BI12-2</f>
         <v>1097</v>
       </c>
       <c r="CE12" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ12^2)/(AZ12^2+BJ12))^(1/2)</f>
         <v>2.8718958292254938E-2</v>
       </c>
       <c r="CF12" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE12)/(1-CE12))</f>
         <v>2.8726857795568102E-2</v>
       </c>
       <c r="CG12" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF12^2)^2)/(BJ12-1))</f>
         <v>7.5832207400588011E-5</v>
       </c>
       <c r="CH12" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ12-3)</f>
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
@@ -50186,7 +50189,7 @@
         <v>3</v>
       </c>
       <c r="AZ13">
-        <f t="shared" si="9"/>
+        <f>TINV(AX13,CC13)</f>
         <v>0.36792518213176223</v>
       </c>
       <c r="BA13" s="18" t="s">
@@ -50257,40 +50260,40 @@
         <v>0</v>
       </c>
       <c r="BX13" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ13^2)/(AZ13^2+BI13))^(1/2)</f>
         <v>1.1097724056507073E-2</v>
       </c>
       <c r="BY13" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX13)/(1-BX13))</f>
         <v>1.1098179686815215E-2</v>
       </c>
       <c r="BZ13" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY13^2)^2)/(BI13-1))</f>
         <v>9.1074679856944585E-4</v>
       </c>
       <c r="CA13" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI13-3)</f>
         <v>9.1240875912408756E-4</v>
       </c>
       <c r="CB13" s="99"/>
       <c r="CC13">
-        <f t="shared" si="4"/>
+        <f>BI13-2</f>
         <v>1097</v>
       </c>
       <c r="CE13" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ13^2)/(AZ13^2+BJ13))^(1/2)</f>
         <v>3.2038178402255461E-3</v>
       </c>
       <c r="CF13" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE13)/(1-CE13))</f>
         <v>3.2038288021011105E-3</v>
       </c>
       <c r="CG13" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF13^2)^2)/(BJ13-1))</f>
         <v>7.5832259035007177E-5</v>
       </c>
       <c r="CH13" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ13-3)</f>
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
@@ -50447,7 +50450,7 @@
         <v>3</v>
       </c>
       <c r="AZ14">
-        <f t="shared" si="9"/>
+        <f>TINV(AX14,CC14)</f>
         <v>1.0028966613252909E-2</v>
       </c>
       <c r="BA14" s="18" t="s">
@@ -50518,40 +50521,40 @@
         <v>0</v>
       </c>
       <c r="BX14" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ14^2)/(AZ14^2+BI14))^(1/2)</f>
         <v>3.0252224837106504E-4</v>
       </c>
       <c r="BY14" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX14)/(1-BX14))</f>
         <v>3.0252225759992615E-4</v>
       </c>
       <c r="BZ14" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY14^2)^2)/(BI14-1))</f>
         <v>9.1074681238614906E-4</v>
       </c>
       <c r="CA14" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI14-3)</f>
         <v>9.1240875912408756E-4</v>
       </c>
       <c r="CB14" s="99"/>
       <c r="CC14">
-        <f t="shared" si="4"/>
+        <f>BI14-2</f>
         <v>1097</v>
       </c>
       <c r="CE14" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ14^2)/(AZ14^2+BJ14))^(1/2)</f>
         <v>8.7330654429660967E-5</v>
       </c>
       <c r="CF14" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE14)/(1-CE14))</f>
         <v>8.7330654651614581E-5</v>
       </c>
       <c r="CG14" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF14^2)^2)/(BJ14-1))</f>
         <v>7.583225904299688E-5</v>
       </c>
       <c r="CH14" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ14-3)</f>
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
@@ -50709,7 +50712,7 @@
         <v>3</v>
       </c>
       <c r="AZ15">
-        <f t="shared" si="9"/>
+        <f>TINV(AX15,CC15)</f>
         <v>1.75633423317142</v>
       </c>
       <c r="BA15" s="10" t="s">
@@ -50780,40 +50783,40 @@
         <v>0</v>
       </c>
       <c r="BX15" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ15^2)/(AZ15^2+BI15))^(1/2)</f>
         <v>9.8016085482412224E-2</v>
       </c>
       <c r="BY15" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX15)/(1-BX15))</f>
         <v>9.8331792494724915E-2</v>
       </c>
       <c r="BZ15" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY15^2)^2)/(BI15-1))</f>
         <v>3.1542792041144869E-3</v>
       </c>
       <c r="CA15" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI15-3)</f>
         <v>3.1746031746031746E-3</v>
       </c>
       <c r="CB15" s="99"/>
       <c r="CC15">
-        <f t="shared" si="4"/>
+        <f>BI15-2</f>
         <v>316</v>
       </c>
       <c r="CE15" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ15^2)/(AZ15^2+BJ15))^(1/2)</f>
         <v>9.8016085482412224E-2</v>
       </c>
       <c r="CF15" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE15)/(1-CE15))</f>
         <v>9.8331792494724915E-2</v>
       </c>
       <c r="CG15" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF15^2)^2)/(BJ15-1))</f>
         <v>3.1542792041144869E-3</v>
       </c>
       <c r="CH15" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ15-3)</f>
         <v>3.1746031746031746E-3</v>
       </c>
     </row>
@@ -51041,39 +51044,39 @@
         <v>0</v>
       </c>
       <c r="BX16" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ16^2)/(AZ16^2+BI16))^(1/2)</f>
         <v>0.15374448735583945</v>
       </c>
       <c r="BY16" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX16)/(1-BX16))</f>
         <v>0.15497333468721167</v>
       </c>
       <c r="BZ16" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY16^2)^2)/(BI16-1))</f>
         <v>1.4806269577269365E-3</v>
       </c>
       <c r="CA16" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI16-3)</f>
         <v>1.4858841010401188E-3</v>
       </c>
       <c r="CC16">
-        <f t="shared" si="4"/>
+        <f>BI16-2</f>
         <v>674</v>
       </c>
       <c r="CE16" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ16^2)/(AZ16^2+BJ16))^(1/2)</f>
         <v>0.15374448735583945</v>
       </c>
       <c r="CF16" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE16)/(1-CE16))</f>
         <v>0.15497333468721167</v>
       </c>
       <c r="CG16" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF16^2)^2)/(BJ16-1))</f>
         <v>1.4806269577269365E-3</v>
       </c>
       <c r="CH16" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ16-3)</f>
         <v>1.4858841010401188E-3</v>
       </c>
     </row>
@@ -51229,7 +51232,7 @@
         <v>2</v>
       </c>
       <c r="AZ17">
-        <f t="shared" ref="AZ17:AZ23" si="10">TINV(AX17,CC17)</f>
+        <f>TINV(AX17,CC17)</f>
         <v>1.647384517634447</v>
       </c>
       <c r="BA17" s="18" t="s">
@@ -51300,39 +51303,39 @@
         <v>0</v>
       </c>
       <c r="BX17" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ17^2)/(AZ17^2+BI17))^(1/2)</f>
         <v>6.6825990375612127E-2</v>
       </c>
       <c r="BY17" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX17)/(1-BX17))</f>
         <v>6.692573299656196E-2</v>
       </c>
       <c r="BZ17" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY17^2)^2)/(BI17-1))</f>
         <v>1.6555959239695694E-3</v>
       </c>
       <c r="CA17" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI17-3)</f>
         <v>1.6611295681063123E-3</v>
       </c>
       <c r="CC17">
-        <f t="shared" si="4"/>
+        <f>BI17-2</f>
         <v>603</v>
       </c>
       <c r="CE17" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ17^2)/(AZ17^2+BJ17))^(1/2)</f>
         <v>6.6825990375612127E-2</v>
       </c>
       <c r="CF17" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE17)/(1-CE17))</f>
         <v>6.692573299656196E-2</v>
       </c>
       <c r="CG17" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF17^2)^2)/(BJ17-1))</f>
         <v>1.6555959239695694E-3</v>
       </c>
       <c r="CH17" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ17-3)</f>
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
@@ -51488,7 +51491,7 @@
         <v>1</v>
       </c>
       <c r="AZ18">
-        <f t="shared" si="10"/>
+        <f>TINV(AX18,CC18)</f>
         <v>1.9639058734740764</v>
       </c>
       <c r="BA18" s="18" t="s">
@@ -51559,39 +51562,39 @@
         <v>0</v>
       </c>
       <c r="BX18" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ18^2)/(AZ18^2+BI18))^(1/2)</f>
         <v>7.959083180520346E-2</v>
       </c>
       <c r="BY18" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX18)/(1-BX18))</f>
         <v>7.9759534841727944E-2</v>
       </c>
       <c r="BZ18" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY18^2)^2)/(BI18-1))</f>
         <v>1.6555621361865366E-3</v>
       </c>
       <c r="CA18" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI18-3)</f>
         <v>1.6611295681063123E-3</v>
       </c>
       <c r="CC18">
-        <f t="shared" si="4"/>
+        <f>BI18-2</f>
         <v>603</v>
       </c>
       <c r="CE18" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ18^2)/(AZ18^2+BJ18))^(1/2)</f>
         <v>7.959083180520346E-2</v>
       </c>
       <c r="CF18" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE18)/(1-CE18))</f>
         <v>7.9759534841727944E-2</v>
       </c>
       <c r="CG18" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF18^2)^2)/(BJ18-1))</f>
         <v>1.6555621361865366E-3</v>
       </c>
       <c r="CH18" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ18-3)</f>
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
@@ -51747,7 +51750,7 @@
         <v>2</v>
       </c>
       <c r="AZ19">
-        <f t="shared" si="10"/>
+        <f>TINV(AX19,CC19)</f>
         <v>1.647384517634447</v>
       </c>
       <c r="BA19" s="18" t="s">
@@ -51818,39 +51821,39 @@
         <v>0</v>
       </c>
       <c r="BX19" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ19^2)/(AZ19^2+BI19))^(1/2)</f>
         <v>6.6825990375612127E-2</v>
       </c>
       <c r="BY19" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX19)/(1-BX19))</f>
         <v>6.692573299656196E-2</v>
       </c>
       <c r="BZ19" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY19^2)^2)/(BI19-1))</f>
         <v>1.6555959239695694E-3</v>
       </c>
       <c r="CA19" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI19-3)</f>
         <v>1.6611295681063123E-3</v>
       </c>
       <c r="CC19">
-        <f t="shared" si="4"/>
+        <f>BI19-2</f>
         <v>603</v>
       </c>
       <c r="CE19" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ19^2)/(AZ19^2+BJ19))^(1/2)</f>
         <v>6.6825990375612127E-2</v>
       </c>
       <c r="CF19" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE19)/(1-CE19))</f>
         <v>6.692573299656196E-2</v>
       </c>
       <c r="CG19" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF19^2)^2)/(BJ19-1))</f>
         <v>1.6555959239695694E-3</v>
       </c>
       <c r="CH19" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ19-3)</f>
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
@@ -52007,7 +52010,7 @@
         <v>1</v>
       </c>
       <c r="AZ20">
-        <f t="shared" si="10"/>
+        <f>TINV(AX20,CC20)</f>
         <v>2.5840071350575324</v>
       </c>
       <c r="BA20" s="18" t="s">
@@ -52078,41 +52081,41 @@
         <v>0</v>
       </c>
       <c r="BX20" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ20^2)/(AZ20^2+BI20))^(1/2)</f>
         <v>0.10447986438429385</v>
       </c>
       <c r="BY20" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX20)/(1-BX20))</f>
         <v>0.10486254279362485</v>
       </c>
       <c r="BZ20" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY20^2)^2)/(BI20-1))</f>
         <v>1.6554289480493617E-3</v>
       </c>
       <c r="CA20" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI20-3)</f>
         <v>1.6611295681063123E-3</v>
       </c>
       <c r="CB20"/>
       <c r="CC20">
-        <f t="shared" si="4"/>
+        <f>BI20-2</f>
         <v>603</v>
       </c>
       <c r="CD20"/>
       <c r="CE20" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ20^2)/(AZ20^2+BJ20))^(1/2)</f>
         <v>0.10447986438429385</v>
       </c>
       <c r="CF20" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE20)/(1-CE20))</f>
         <v>0.10486254279362485</v>
       </c>
       <c r="CG20" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF20^2)^2)/(BJ20-1))</f>
         <v>1.6554289480493617E-3</v>
       </c>
       <c r="CH20" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ20-3)</f>
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
@@ -52269,7 +52272,7 @@
         <v>2</v>
       </c>
       <c r="AZ21">
-        <f t="shared" si="10"/>
+        <f>TINV(AX21,CC21)</f>
         <v>1.647384517634447</v>
       </c>
       <c r="BA21" s="18" t="s">
@@ -52340,41 +52343,41 @@
         <v>0</v>
       </c>
       <c r="BX21" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ21^2)/(AZ21^2+BI21))^(1/2)</f>
         <v>6.6825990375612127E-2</v>
       </c>
       <c r="BY21" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX21)/(1-BX21))</f>
         <v>6.692573299656196E-2</v>
       </c>
       <c r="BZ21" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY21^2)^2)/(BI21-1))</f>
         <v>1.6555959239695694E-3</v>
       </c>
       <c r="CA21" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI21-3)</f>
         <v>1.6611295681063123E-3</v>
       </c>
       <c r="CB21"/>
       <c r="CC21">
-        <f t="shared" si="4"/>
+        <f>BI21-2</f>
         <v>603</v>
       </c>
       <c r="CD21"/>
       <c r="CE21" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ21^2)/(AZ21^2+BJ21))^(1/2)</f>
         <v>6.6825990375612127E-2</v>
       </c>
       <c r="CF21" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE21)/(1-CE21))</f>
         <v>6.692573299656196E-2</v>
       </c>
       <c r="CG21" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF21^2)^2)/(BJ21-1))</f>
         <v>1.6555959239695694E-3</v>
       </c>
       <c r="CH21" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ21-3)</f>
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
@@ -52531,7 +52534,7 @@
         <v>1</v>
       </c>
       <c r="AZ22">
-        <f t="shared" si="10"/>
+        <f>TINV(AX22,CC22)</f>
         <v>3.3101701484367259</v>
       </c>
       <c r="BA22" s="98" t="s">
@@ -52602,41 +52605,41 @@
         <v>1</v>
       </c>
       <c r="BX22" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ22^2)/(AZ22^2+BI22))^(1/2)</f>
         <v>0.1464394351286451</v>
       </c>
       <c r="BY22" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX22)/(1-BX22))</f>
         <v>0.14749988735332095</v>
       </c>
       <c r="BZ22" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY22^2)^2)/(BI22-1))</f>
         <v>2.0030594529697188E-3</v>
       </c>
       <c r="CA22" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI22-3)</f>
         <v>2.012072434607646E-3</v>
       </c>
       <c r="CB22"/>
       <c r="CC22">
-        <f t="shared" si="4"/>
+        <f>BI22-2</f>
         <v>498</v>
       </c>
       <c r="CD22"/>
       <c r="CE22" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ22^2)/(AZ22^2+BJ22))^(1/2)</f>
         <v>7.3815726974840262E-2</v>
       </c>
       <c r="CF22" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE22)/(1-CE22))</f>
         <v>7.395023508930447E-2</v>
       </c>
       <c r="CG22" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF22^2)^2)/(BJ22-1))</f>
         <v>5.0023516458549868E-4</v>
       </c>
       <c r="CH22" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ22-3)</f>
         <v>5.00751126690035E-4</v>
       </c>
     </row>
@@ -52793,7 +52796,7 @@
         <v>3</v>
       </c>
       <c r="AZ23">
-        <f t="shared" si="10"/>
+        <f>TINV(AX23,CC23)</f>
         <v>2.5857376110802122</v>
       </c>
       <c r="BA23" s="98" t="s">
@@ -52864,39 +52867,39 @@
         <v>1</v>
       </c>
       <c r="BX23" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ23^2)/(AZ23^2+BI23))^(1/2)</f>
         <v>0.11487221186750445</v>
       </c>
       <c r="BY23" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX23)/(1-BX23))</f>
         <v>0.11538152059067894</v>
       </c>
       <c r="BZ23" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY23^2)^2)/(BI23-1))</f>
         <v>2.0036528393164244E-3</v>
       </c>
       <c r="CA23" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI23-3)</f>
         <v>2.012072434607646E-3</v>
       </c>
       <c r="CC23">
-        <f t="shared" si="4"/>
+        <f>BI23-2</f>
         <v>498</v>
       </c>
       <c r="CE23" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ23^2)/(AZ23^2+BJ23))^(1/2)</f>
         <v>5.7722447571881538E-2</v>
       </c>
       <c r="CF23" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE23)/(1-CE23))</f>
         <v>5.7786684145923431E-2</v>
       </c>
       <c r="CG23" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF23^2)^2)/(BJ23-1))</f>
         <v>5.00244546808272E-4</v>
       </c>
       <c r="CH23" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ23-3)</f>
         <v>5.00751126690035E-4</v>
       </c>
     </row>
@@ -53123,39 +53126,39 @@
         <v>1</v>
       </c>
       <c r="BX24" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ24^2)/(AZ24^2+BI24))^(1/2)</f>
         <v>0.43424883131426489</v>
       </c>
       <c r="BY24" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX24)/(1-BX24))</f>
         <v>0.46512108920045175</v>
       </c>
       <c r="BZ24" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY24^2)^2)/(BI24-1))</f>
         <v>2.6926498047349623E-3</v>
       </c>
       <c r="CA24" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI24-3)</f>
         <v>2.840909090909091E-3</v>
       </c>
       <c r="CC24">
-        <f t="shared" si="4"/>
+        <f>BI24-2</f>
         <v>353</v>
       </c>
       <c r="CE24" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ24^2)/(AZ24^2+BJ24))^(1/2)</f>
         <v>6.4318817101316442E-2</v>
       </c>
       <c r="CF24" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE24)/(1-CE24))</f>
         <v>6.4407731628953774E-2</v>
       </c>
       <c r="CG24" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF24^2)^2)/(BJ24-1))</f>
         <v>5.0354136217502399E-5</v>
       </c>
       <c r="CH24" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ24-3)</f>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -53382,39 +53385,39 @@
         <v>1</v>
       </c>
       <c r="BX25" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ25^2)/(AZ25^2+BI25))^(1/2)</f>
         <v>0.57835709203923469</v>
       </c>
       <c r="BY25" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX25)/(1-BX25))</f>
         <v>0.65999050186206398</v>
       </c>
       <c r="BZ25" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY25^2)^2)/(BI25-1))</f>
         <v>2.3283435703186023E-3</v>
       </c>
       <c r="CA25" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI25-3)</f>
         <v>2.8901734104046241E-3</v>
       </c>
       <c r="CC25">
-        <f t="shared" si="4"/>
+        <f>BI25-2</f>
         <v>347</v>
       </c>
       <c r="CE25" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ25^2)/(AZ25^2+BJ25))^(1/2)</f>
         <v>9.4537081297198303E-2</v>
       </c>
       <c r="CF25" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE25)/(1-CE25))</f>
         <v>9.4820235378343692E-2</v>
       </c>
       <c r="CG25" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF25^2)^2)/(BJ25-1))</f>
         <v>5.1407082624548965E-5</v>
       </c>
       <c r="CH25" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ25-3)</f>
         <v>5.1416525271222172E-5</v>
       </c>
     </row>
@@ -53562,7 +53565,7 @@
         <v>80</v>
       </c>
       <c r="AW26">
-        <f t="shared" ref="AW26:AW32" si="11">AU26/AZ26</f>
+        <f>AU26/AZ26</f>
         <v>9.8591549295774641E-2</v>
       </c>
       <c r="AX26">
@@ -53641,39 +53644,39 @@
         <v>1</v>
       </c>
       <c r="BX26" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ26^2)/(AZ26^2+BI26))^(1/2)</f>
         <v>0.2020824660717096</v>
       </c>
       <c r="BY26" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX26)/(1-BX26))</f>
         <v>0.20490273447739515</v>
       </c>
       <c r="BZ26" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY26^2)^2)/(BI26-1))</f>
         <v>8.4381846898462422E-4</v>
       </c>
       <c r="CA26" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI26-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
       <c r="CC26">
-        <f t="shared" si="4"/>
+        <f>BI26-2</f>
         <v>1182</v>
       </c>
       <c r="CE26" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ26^2)/(AZ26^2+BJ26))^(1/2)</f>
         <v>0.2020824660717096</v>
       </c>
       <c r="CF26" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE26)/(1-CE26))</f>
         <v>0.20490273447739515</v>
       </c>
       <c r="CG26" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF26^2)^2)/(BJ26-1))</f>
         <v>8.4381846898462422E-4</v>
       </c>
       <c r="CH26" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ26-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -53821,7 +53824,7 @@
         <v>80</v>
       </c>
       <c r="AW27">
-        <f t="shared" si="11"/>
+        <f>AU27/AZ27</f>
         <v>0.15416666666666667</v>
       </c>
       <c r="AX27">
@@ -53901,41 +53904,41 @@
         <v>1</v>
       </c>
       <c r="BX27" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ27^2)/(AZ27^2+BI27))^(1/2)</f>
         <v>2.0919995692237577E-2</v>
       </c>
       <c r="BY27" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX27)/(1-BX27))</f>
         <v>2.0923048346211292E-2</v>
       </c>
       <c r="BZ27" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY27^2)^2)/(BI27-1))</f>
         <v>8.453083756162019E-4</v>
       </c>
       <c r="CA27" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI27-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
       <c r="CB27"/>
       <c r="CC27">
-        <f t="shared" si="4"/>
+        <f>BI27-2</f>
         <v>1182</v>
       </c>
       <c r="CD27"/>
       <c r="CE27" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ27^2)/(AZ27^2+BJ27))^(1/2)</f>
         <v>2.0919995692237577E-2</v>
       </c>
       <c r="CF27" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE27)/(1-CE27))</f>
         <v>2.0923048346211292E-2</v>
       </c>
       <c r="CG27" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF27^2)^2)/(BJ27-1))</f>
         <v>8.453083756162019E-4</v>
       </c>
       <c r="CH27" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ27-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -54083,7 +54086,7 @@
         <v>86</v>
       </c>
       <c r="AW28">
-        <f t="shared" si="11"/>
+        <f>AU28/AZ28</f>
         <v>0.11478260869565218</v>
       </c>
       <c r="AX28">
@@ -54163,41 +54166,41 @@
         <v>1</v>
       </c>
       <c r="BX28" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ28^2)/(AZ28^2+BI28))^(1/2)</f>
         <v>3.3402546418006968E-2</v>
       </c>
       <c r="BY28" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX28)/(1-BX28))</f>
         <v>3.341497748312889E-2</v>
       </c>
       <c r="BZ28" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY28^2)^2)/(BI28-1))</f>
         <v>8.4530748376344727E-4</v>
       </c>
       <c r="CA28" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI28-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
       <c r="CB28"/>
       <c r="CC28">
-        <f t="shared" si="4"/>
+        <f>BI28-2</f>
         <v>1182</v>
       </c>
       <c r="CD28"/>
       <c r="CE28" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ28^2)/(AZ28^2+BJ28))^(1/2)</f>
         <v>3.3402546418006968E-2</v>
       </c>
       <c r="CF28" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE28)/(1-CE28))</f>
         <v>3.341497748312889E-2</v>
       </c>
       <c r="CG28" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF28^2)^2)/(BJ28-1))</f>
         <v>8.4530748376344727E-4</v>
       </c>
       <c r="CH28" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ28-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -54345,7 +54348,7 @@
         <v>86</v>
       </c>
       <c r="AW29">
-        <f t="shared" si="11"/>
+        <f>AU29/AZ29</f>
         <v>0.14476190476190476</v>
       </c>
       <c r="AX29">
@@ -54425,41 +54428,41 @@
         <v>1</v>
       </c>
       <c r="BX29" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ29^2)/(AZ29^2+BI29))^(1/2)</f>
         <v>3.050080782390133E-2</v>
       </c>
       <c r="BY29" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX29)/(1-BX29))</f>
         <v>3.0510271400002755E-2</v>
       </c>
       <c r="BZ29" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY29^2)^2)/(BI29-1))</f>
         <v>8.453078051298751E-4</v>
       </c>
       <c r="CA29" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI29-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
       <c r="CB29"/>
       <c r="CC29">
-        <f t="shared" si="4"/>
+        <f>BI29-2</f>
         <v>1182</v>
       </c>
       <c r="CD29"/>
       <c r="CE29" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ29^2)/(AZ29^2+BJ29))^(1/2)</f>
         <v>3.050080782390133E-2</v>
       </c>
       <c r="CF29" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE29)/(1-CE29))</f>
         <v>3.0510271400002755E-2</v>
       </c>
       <c r="CG29" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF29^2)^2)/(BJ29-1))</f>
         <v>8.453078051298751E-4</v>
       </c>
       <c r="CH29" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ29-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -54607,7 +54610,7 @@
         <v>80</v>
       </c>
       <c r="AW30">
-        <f t="shared" si="11"/>
+        <f>AU30/AZ30</f>
         <v>0.15044247787610621</v>
       </c>
       <c r="AX30">
@@ -54687,41 +54690,41 @@
         <v>1</v>
       </c>
       <c r="BX30" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ30^2)/(AZ30^2+BI30))^(1/2)</f>
         <v>6.5538705898597463E-2</v>
       </c>
       <c r="BY30" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX30)/(1-BX30))</f>
         <v>6.563278509260187E-2</v>
       </c>
       <c r="BZ30" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY30^2)^2)/(BI30-1))</f>
         <v>8.4529285210817155E-4</v>
       </c>
       <c r="CA30" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI30-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
       <c r="CB30"/>
       <c r="CC30">
-        <f t="shared" si="4"/>
+        <f>BI30-2</f>
         <v>1182</v>
       </c>
       <c r="CD30"/>
       <c r="CE30" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ30^2)/(AZ30^2+BJ30))^(1/2)</f>
         <v>6.5538705898597463E-2</v>
       </c>
       <c r="CF30" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE30)/(1-CE30))</f>
         <v>6.563278509260187E-2</v>
       </c>
       <c r="CG30" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF30^2)^2)/(BJ30-1))</f>
         <v>8.4529285210817155E-4</v>
       </c>
       <c r="CH30" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ30-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -54869,7 +54872,7 @@
         <v>80</v>
       </c>
       <c r="AW31">
-        <f t="shared" si="11"/>
+        <f>AU31/AZ31</f>
         <v>0.13387096774193546</v>
       </c>
       <c r="AX31">
@@ -54948,39 +54951,39 @@
         <v>1</v>
       </c>
       <c r="BX31" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ31^2)/(AZ31^2+BI31))^(1/2)</f>
         <v>5.3976351182136464E-2</v>
       </c>
       <c r="BY31" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX31)/(1-BX31))</f>
         <v>5.402886207559579E-2</v>
       </c>
       <c r="BZ31" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY31^2)^2)/(BI31-1))</f>
         <v>8.4530133453125005E-4</v>
       </c>
       <c r="CA31" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI31-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
       <c r="CC31">
-        <f t="shared" si="4"/>
+        <f>BI31-2</f>
         <v>1182</v>
       </c>
       <c r="CE31" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ31^2)/(AZ31^2+BJ31))^(1/2)</f>
         <v>5.3976351182136464E-2</v>
       </c>
       <c r="CF31" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE31)/(1-CE31))</f>
         <v>5.402886207559579E-2</v>
       </c>
       <c r="CG31" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF31^2)^2)/(BJ31-1))</f>
         <v>8.4530133453125005E-4</v>
       </c>
       <c r="CH31" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ31-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -55128,7 +55131,7 @@
         <v>80</v>
       </c>
       <c r="AW32">
-        <f t="shared" si="11"/>
+        <f>AU32/AZ32</f>
         <v>0.19337349397590362</v>
       </c>
       <c r="AX32">
@@ -55207,39 +55210,39 @@
         <v>1</v>
       </c>
       <c r="BX32" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ32^2)/(AZ32^2+BI32))^(1/2)</f>
         <v>9.6039537672003544E-2</v>
       </c>
       <c r="BY32" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX32)/(1-BX32))</f>
         <v>9.633645915133221E-2</v>
       </c>
       <c r="BZ32" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY32^2)^2)/(BI32-1))</f>
         <v>8.4523572980515279E-4</v>
       </c>
       <c r="CA32" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI32-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
       <c r="CC32">
-        <f t="shared" si="4"/>
+        <f>BI32-2</f>
         <v>1182</v>
       </c>
       <c r="CE32" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ32^2)/(AZ32^2+BJ32))^(1/2)</f>
         <v>9.6039537672003544E-2</v>
       </c>
       <c r="CF32" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE32)/(1-CE32))</f>
         <v>9.633645915133221E-2</v>
       </c>
       <c r="CG32" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF32^2)^2)/(BJ32-1))</f>
         <v>8.4523572980515279E-4</v>
       </c>
       <c r="CH32" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ32-3)</f>
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
@@ -55395,7 +55398,7 @@
         <v>1</v>
       </c>
       <c r="AZ33">
-        <f t="shared" ref="AZ33:AZ39" si="12">TINV(AX33,CC33)</f>
+        <f>TINV(AX33,CC33)</f>
         <v>1.6519717481243639</v>
       </c>
       <c r="BA33" s="18" t="s">
@@ -55466,39 +55469,39 @@
         <v>1</v>
       </c>
       <c r="BX33" s="30">
-        <f t="shared" si="0"/>
+        <f>((AZ33^2)/(AZ33^2+BI33))^(1/2)</f>
         <v>0.111444570712238</v>
       </c>
       <c r="BY33" s="30">
-        <f t="shared" si="1"/>
+        <f>0.5*LN((1+BX33)/(1-BX33))</f>
         <v>0.11190941618239179</v>
       </c>
       <c r="BZ33" s="30">
-        <f t="shared" si="2"/>
+        <f>((1-(BY33^2)^2)/(BI33-1))</f>
         <v>4.6289035023228077E-3</v>
       </c>
       <c r="CA33" s="30">
-        <f t="shared" si="3"/>
+        <f>1/(BI33-3)</f>
         <v>4.6728971962616819E-3</v>
       </c>
       <c r="CC33">
-        <f t="shared" si="4"/>
+        <f>BI33-2</f>
         <v>215</v>
       </c>
       <c r="CE33" s="30">
-        <f t="shared" si="5"/>
+        <f>((AZ33^2)/(AZ33^2+BJ33))^(1/2)</f>
         <v>5.5983636926066289E-2</v>
       </c>
       <c r="CF33" s="30">
-        <f t="shared" si="6"/>
+        <f>0.5*LN((1+CE33)/(1-CE33))</f>
         <v>5.6042234525477685E-2</v>
       </c>
       <c r="CG33" s="30">
-        <f t="shared" si="7"/>
+        <f>((1-(CF33^2)^2)/(BJ33-1))</f>
         <v>1.1533911600947939E-3</v>
       </c>
       <c r="CH33" s="30">
-        <f t="shared" si="8"/>
+        <f>1/(BJ33-3)</f>
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
@@ -55654,7 +55657,7 @@
         <v>1</v>
       </c>
       <c r="AZ34">
-        <f t="shared" si="12"/>
+        <f>TINV(AX34,CC34)</f>
         <v>1.9710591221336478</v>
       </c>
       <c r="BA34" s="18" t="s">
@@ -55725,39 +55728,39 @@
         <v>1</v>
       </c>
       <c r="BX34" s="30">
-        <f t="shared" ref="BX34:BX61" si="13">((AZ34^2)/(AZ34^2+BI34))^(1/2)</f>
+        <f>((AZ34^2)/(AZ34^2+BI34))^(1/2)</f>
         <v>0.13262227273834529</v>
       </c>
       <c r="BY34" s="30">
-        <f t="shared" ref="BY34:BY65" si="14">0.5*LN((1+BX34)/(1-BX34))</f>
+        <f>0.5*LN((1+BX34)/(1-BX34))</f>
         <v>0.13340813257086698</v>
       </c>
       <c r="BZ34" s="30">
-        <f t="shared" ref="BZ34:BZ65" si="15">((1-(BY34^2)^2)/(BI34-1))</f>
+        <f>((1-(BY34^2)^2)/(BI34-1))</f>
         <v>4.6281631519105703E-3</v>
       </c>
       <c r="CA34" s="30">
-        <f t="shared" ref="CA34:CA61" si="16">1/(BI34-3)</f>
+        <f>1/(BI34-3)</f>
         <v>4.6728971962616819E-3</v>
       </c>
       <c r="CC34">
-        <f t="shared" si="4"/>
+        <f>BI34-2</f>
         <v>215</v>
       </c>
       <c r="CE34" s="30">
-        <f t="shared" ref="CE34:CE61" si="17">((AZ34^2)/(AZ34^2+BJ34))^(1/2)</f>
+        <f>((AZ34^2)/(AZ34^2+BJ34))^(1/2)</f>
         <v>6.6752883376554634E-2</v>
       </c>
       <c r="CF34" s="30">
-        <f t="shared" ref="CF34:CF65" si="18">0.5*LN((1+CE34)/(1-CE34))</f>
+        <f>0.5*LN((1+CE34)/(1-CE34))</f>
         <v>6.6852298418384234E-2</v>
       </c>
       <c r="CG34" s="30">
-        <f t="shared" ref="CG34:CG65" si="19">((1-(CF34^2)^2)/(BJ34-1))</f>
+        <f>((1-(CF34^2)^2)/(BJ34-1))</f>
         <v>1.1533794994059523E-3</v>
       </c>
       <c r="CH34" s="30">
-        <f t="shared" ref="CH34:CH61" si="20">1/(BJ34-3)</f>
+        <f>1/(BJ34-3)</f>
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
@@ -55913,7 +55916,7 @@
         <v>1</v>
       </c>
       <c r="AZ35">
-        <f t="shared" si="12"/>
+        <f>TINV(AX35,CC35)</f>
         <v>1.6519717481243639</v>
       </c>
       <c r="BA35" s="18" t="s">
@@ -55984,39 +55987,39 @@
         <v>1</v>
       </c>
       <c r="BX35" s="30">
-        <f t="shared" si="13"/>
+        <f>((AZ35^2)/(AZ35^2+BI35))^(1/2)</f>
         <v>0.111444570712238</v>
       </c>
       <c r="BY35" s="30">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX35)/(1-BX35))</f>
         <v>0.11190941618239179</v>
       </c>
       <c r="BZ35" s="30">
-        <f t="shared" si="15"/>
+        <f>((1-(BY35^2)^2)/(BI35-1))</f>
         <v>4.6289035023228077E-3</v>
       </c>
       <c r="CA35" s="30">
-        <f t="shared" si="16"/>
+        <f>1/(BI35-3)</f>
         <v>4.6728971962616819E-3</v>
       </c>
       <c r="CC35">
-        <f t="shared" si="4"/>
+        <f>BI35-2</f>
         <v>215</v>
       </c>
       <c r="CE35" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ35^2)/(AZ35^2+BJ35))^(1/2)</f>
         <v>5.5983636926066289E-2</v>
       </c>
       <c r="CF35" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE35)/(1-CE35))</f>
         <v>5.6042234525477685E-2</v>
       </c>
       <c r="CG35" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF35^2)^2)/(BJ35-1))</f>
         <v>1.1533911600947939E-3</v>
       </c>
       <c r="CH35" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ35-3)</f>
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
@@ -56173,7 +56176,7 @@
         <v>1</v>
       </c>
       <c r="AZ36">
-        <f t="shared" si="12"/>
+        <f>TINV(AX36,CC36)</f>
         <v>1.6474057119344734</v>
       </c>
       <c r="BA36" t="s">
@@ -56228,39 +56231,39 @@
         <v>1</v>
       </c>
       <c r="BX36" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ36^2)/(AZ36^2+BI36))^(1/2)</f>
         <v>6.7103465160314887E-2</v>
       </c>
       <c r="BY36" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX36)/(1-BX36))</f>
         <v>6.7204457661064573E-2</v>
       </c>
       <c r="BZ36" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY36^2)^2)/(BI36-1))</f>
         <v>1.6694150280093312E-3</v>
       </c>
       <c r="CA36" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI36-3)</f>
         <v>1.6750418760469012E-3</v>
       </c>
       <c r="CC36">
-        <f t="shared" si="4"/>
+        <f>BI36-2</f>
         <v>598</v>
       </c>
       <c r="CE36" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ36^2)/(AZ36^2+BJ36))^(1/2)</f>
         <v>2.7446418247225011E-2</v>
       </c>
       <c r="CF36" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE36)/(1-CE36))</f>
         <v>2.7453313213271935E-2</v>
       </c>
       <c r="CG36" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF36^2)^2)/(BJ36-1))</f>
         <v>2.7785480187824828E-4</v>
       </c>
       <c r="CH36" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ36-3)</f>
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
@@ -56417,7 +56420,7 @@
         <v>1</v>
       </c>
       <c r="AZ37">
-        <f t="shared" si="12"/>
+        <f>TINV(AX37,CC37)</f>
         <v>1.9639388980555066</v>
       </c>
       <c r="BA37" t="s">
@@ -56472,39 +56475,39 @@
         <v>1</v>
       </c>
       <c r="BX37" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ37^2)/(AZ37^2+BI37))^(1/2)</f>
         <v>7.9920998150068992E-2</v>
       </c>
       <c r="BY37" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX37)/(1-BX37))</f>
         <v>8.0091814824645752E-2</v>
       </c>
       <c r="BZ37" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY37^2)^2)/(BI37-1))</f>
         <v>1.6693803867099848E-3</v>
       </c>
       <c r="CA37" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI37-3)</f>
         <v>1.6750418760469012E-3</v>
       </c>
       <c r="CC37">
-        <f t="shared" si="4"/>
+        <f>BI37-2</f>
         <v>598</v>
       </c>
       <c r="CE37" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ37^2)/(AZ37^2+BJ37))^(1/2)</f>
         <v>3.2714794271304103E-2</v>
       </c>
       <c r="CF37" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE37)/(1-CE37))</f>
         <v>3.2726472859206039E-2</v>
       </c>
       <c r="CG37" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF37^2)^2)/(BJ37-1))</f>
         <v>2.7785464098689086E-4</v>
       </c>
       <c r="CH37" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ37-3)</f>
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
@@ -56661,7 +56664,7 @@
         <v>1</v>
       </c>
       <c r="AZ38">
-        <f t="shared" si="12"/>
+        <f>TINV(AX38,CC38)</f>
         <v>1.6474057119344734</v>
       </c>
       <c r="BA38" t="s">
@@ -56716,39 +56719,39 @@
         <v>1</v>
       </c>
       <c r="BX38" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ38^2)/(AZ38^2+BI38))^(1/2)</f>
         <v>6.7103465160314887E-2</v>
       </c>
       <c r="BY38" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX38)/(1-BX38))</f>
         <v>6.7204457661064573E-2</v>
       </c>
       <c r="BZ38" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY38^2)^2)/(BI38-1))</f>
         <v>1.6694150280093312E-3</v>
       </c>
       <c r="CA38" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI38-3)</f>
         <v>1.6750418760469012E-3</v>
       </c>
       <c r="CC38">
-        <f t="shared" si="4"/>
+        <f>BI38-2</f>
         <v>598</v>
       </c>
       <c r="CE38" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ38^2)/(AZ38^2+BJ38))^(1/2)</f>
         <v>2.7446418247225011E-2</v>
       </c>
       <c r="CF38" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE38)/(1-CE38))</f>
         <v>2.7453313213271935E-2</v>
       </c>
       <c r="CG38" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF38^2)^2)/(BJ38-1))</f>
         <v>2.7785480187824828E-4</v>
       </c>
       <c r="CH38" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ38-3)</f>
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
@@ -56905,7 +56908,7 @@
         <v>1</v>
       </c>
       <c r="AZ39">
-        <f t="shared" si="12"/>
+        <f>TINV(AX39,CC39)</f>
         <v>1.6474057119344734</v>
       </c>
       <c r="BA39" t="s">
@@ -56960,39 +56963,39 @@
         <v>1</v>
       </c>
       <c r="BX39" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ39^2)/(AZ39^2+BI39))^(1/2)</f>
         <v>6.7103465160314887E-2</v>
       </c>
       <c r="BY39" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX39)/(1-BX39))</f>
         <v>6.7204457661064573E-2</v>
       </c>
       <c r="BZ39" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY39^2)^2)/(BI39-1))</f>
         <v>1.6694150280093312E-3</v>
       </c>
       <c r="CA39" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI39-3)</f>
         <v>1.6750418760469012E-3</v>
       </c>
       <c r="CC39">
-        <f t="shared" si="4"/>
+        <f>BI39-2</f>
         <v>598</v>
       </c>
       <c r="CE39" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ39^2)/(AZ39^2+BJ39))^(1/2)</f>
         <v>2.7446418247225011E-2</v>
       </c>
       <c r="CF39" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE39)/(1-CE39))</f>
         <v>2.7453313213271935E-2</v>
       </c>
       <c r="CG39" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF39^2)^2)/(BJ39-1))</f>
         <v>2.7785480187824828E-4</v>
       </c>
       <c r="CH39" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ39-3)</f>
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
@@ -57219,39 +57222,39 @@
         <v>0</v>
       </c>
       <c r="BX40" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ40^2)/(AZ40^2+BI40))^(1/2)</f>
         <v>0.32021801928313393</v>
       </c>
       <c r="BY40" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX40)/(1-BX40))</f>
         <v>0.33189001894838011</v>
       </c>
       <c r="BZ40" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY40^2)^2)/(BI40-1))</f>
         <v>2.822476458784471E-2</v>
       </c>
       <c r="CA40" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI40-3)</f>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="CC40">
-        <f t="shared" si="4"/>
+        <f>BI40-2</f>
         <v>34</v>
       </c>
       <c r="CE40" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ40^2)/(AZ40^2+BJ40))^(1/2)</f>
         <v>2.1459137182263048E-2</v>
       </c>
       <c r="CF40" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE40)/(1-CE40))</f>
         <v>2.1462432031373494E-2</v>
       </c>
       <c r="CG40" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF40^2)^2)/(BJ40-1))</f>
         <v>1.1201969170096179E-4</v>
       </c>
       <c r="CH40" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ40-3)</f>
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
@@ -57478,39 +57481,39 @@
         <v>0</v>
       </c>
       <c r="BX41" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ41^2)/(AZ41^2+BI41))^(1/2)</f>
         <v>0.32021801928313393</v>
       </c>
       <c r="BY41" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX41)/(1-BX41))</f>
         <v>0.33189001894838011</v>
       </c>
       <c r="BZ41" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY41^2)^2)/(BI41-1))</f>
         <v>2.822476458784471E-2</v>
       </c>
       <c r="CA41" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI41-3)</f>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="CC41">
-        <f t="shared" si="4"/>
+        <f>BI41-2</f>
         <v>34</v>
       </c>
       <c r="CE41" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ41^2)/(AZ41^2+BJ41))^(1/2)</f>
         <v>2.1459137182263048E-2</v>
       </c>
       <c r="CF41" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE41)/(1-CE41))</f>
         <v>2.1462432031373494E-2</v>
       </c>
       <c r="CG41" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF41^2)^2)/(BJ41-1))</f>
         <v>1.1201969170096179E-4</v>
       </c>
       <c r="CH41" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ41-3)</f>
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
@@ -57737,39 +57740,39 @@
         <v>0</v>
       </c>
       <c r="BX42" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ42^2)/(AZ42^2+BI42))^(1/2)</f>
         <v>0.5126110197955529</v>
       </c>
       <c r="BY42" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX42)/(1-BX42))</f>
         <v>0.56626502857004413</v>
       </c>
       <c r="BZ42" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY42^2)^2)/(BI42-1))</f>
         <v>2.5633705048672264E-2</v>
       </c>
       <c r="CA42" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI42-3)</f>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="CC42">
-        <f t="shared" si="4"/>
+        <f>BI42-2</f>
         <v>34</v>
       </c>
       <c r="CE42" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ42^2)/(AZ42^2+BJ42))^(1/2)</f>
         <v>3.788338276740591E-2</v>
       </c>
       <c r="CF42" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE42)/(1-CE42))</f>
         <v>3.7901521176417756E-2</v>
       </c>
       <c r="CG42" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF42^2)^2)/(BJ42-1))</f>
         <v>1.1201948430548235E-4</v>
       </c>
       <c r="CH42" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ42-3)</f>
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
@@ -57996,39 +57999,39 @@
         <v>0</v>
       </c>
       <c r="BX43" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ43^2)/(AZ43^2+BI43))^(1/2)</f>
         <v>0.5126110197955529</v>
       </c>
       <c r="BY43" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX43)/(1-BX43))</f>
         <v>0.56626502857004413</v>
       </c>
       <c r="BZ43" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY43^2)^2)/(BI43-1))</f>
         <v>2.5633705048672264E-2</v>
       </c>
       <c r="CA43" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI43-3)</f>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="CC43">
-        <f t="shared" si="4"/>
+        <f>BI43-2</f>
         <v>34</v>
       </c>
       <c r="CE43" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ43^2)/(AZ43^2+BJ43))^(1/2)</f>
         <v>3.788338276740591E-2</v>
       </c>
       <c r="CF43" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE43)/(1-CE43))</f>
         <v>3.7901521176417756E-2</v>
       </c>
       <c r="CG43" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF43^2)^2)/(BJ43-1))</f>
         <v>1.1201948430548235E-4</v>
       </c>
       <c r="CH43" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ43-3)</f>
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
@@ -58255,39 +58258,39 @@
         <v>0</v>
       </c>
       <c r="BX44" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ44^2)/(AZ44^2+BI44))^(1/2)</f>
         <v>0.5126110197955529</v>
       </c>
       <c r="BY44" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX44)/(1-BX44))</f>
         <v>0.56626502857004413</v>
       </c>
       <c r="BZ44" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY44^2)^2)/(BI44-1))</f>
         <v>2.5633705048672264E-2</v>
       </c>
       <c r="CA44" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI44-3)</f>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="CC44">
-        <f t="shared" si="4"/>
+        <f>BI44-2</f>
         <v>34</v>
       </c>
       <c r="CE44" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ44^2)/(AZ44^2+BJ44))^(1/2)</f>
         <v>3.788338276740591E-2</v>
       </c>
       <c r="CF44" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE44)/(1-CE44))</f>
         <v>3.7901521176417756E-2</v>
       </c>
       <c r="CG44" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF44^2)^2)/(BJ44-1))</f>
         <v>1.1201948430548235E-4</v>
       </c>
       <c r="CH44" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ44-3)</f>
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
@@ -58514,39 +58517,39 @@
         <v>0</v>
       </c>
       <c r="BX45" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ45^2)/(AZ45^2+BI45))^(1/2)</f>
         <v>0.5126110197955529</v>
       </c>
       <c r="BY45" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX45)/(1-BX45))</f>
         <v>0.56626502857004413</v>
       </c>
       <c r="BZ45" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY45^2)^2)/(BI45-1))</f>
         <v>2.5633705048672264E-2</v>
       </c>
       <c r="CA45" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI45-3)</f>
         <v>3.0303030303030304E-2</v>
       </c>
       <c r="CC45">
-        <f t="shared" si="4"/>
+        <f>BI45-2</f>
         <v>34</v>
       </c>
       <c r="CE45" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ45^2)/(AZ45^2+BJ45))^(1/2)</f>
         <v>3.788338276740591E-2</v>
       </c>
       <c r="CF45" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE45)/(1-CE45))</f>
         <v>3.7901521176417756E-2</v>
       </c>
       <c r="CG45" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF45^2)^2)/(BJ45-1))</f>
         <v>1.1201948430548235E-4</v>
       </c>
       <c r="CH45" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ45-3)</f>
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
@@ -58773,19 +58776,19 @@
         <v>1</v>
       </c>
       <c r="BX46" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ46^2)/(AZ46^2+BI46))^(1/2)</f>
         <v>0.47242735990047685</v>
       </c>
       <c r="BY46" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX46)/(1-BX46))</f>
         <v>0.51319051047617226</v>
       </c>
       <c r="BZ46" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY46^2)^2)/(BI46-1))</f>
         <v>6.6760340037102519E-4</v>
       </c>
       <c r="CA46" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI46-3)</f>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CC46">
@@ -58793,19 +58796,19 @@
         <v>1394</v>
       </c>
       <c r="CE46" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ46^2)/(AZ46^2+BJ46))^(1/2)</f>
         <v>0.47242735990047685</v>
       </c>
       <c r="CF46" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE46)/(1-CE46))</f>
         <v>0.51319051047617226</v>
       </c>
       <c r="CG46" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF46^2)^2)/(BJ46-1))</f>
         <v>6.6760340037102519E-4</v>
       </c>
       <c r="CH46" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ46-3)</f>
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
@@ -59032,19 +59035,19 @@
         <v>1</v>
       </c>
       <c r="BX47" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ47^2)/(AZ47^2+BI47))^(1/2)</f>
         <v>0.29473516954008327</v>
       </c>
       <c r="BY47" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX47)/(1-BX47))</f>
         <v>0.3037440363085756</v>
       </c>
       <c r="BZ47" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY47^2)^2)/(BI47-1))</f>
         <v>7.1125395357683058E-4</v>
       </c>
       <c r="CA47" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI47-3)</f>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CC47">
@@ -59052,19 +59055,19 @@
         <v>1394</v>
       </c>
       <c r="CE47" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ47^2)/(AZ47^2+BJ47))^(1/2)</f>
         <v>0.29473516954008327</v>
       </c>
       <c r="CF47" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE47)/(1-CE47))</f>
         <v>0.3037440363085756</v>
       </c>
       <c r="CG47" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF47^2)^2)/(BJ47-1))</f>
         <v>7.1125395357683058E-4</v>
       </c>
       <c r="CH47" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ47-3)</f>
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
@@ -59291,40 +59294,40 @@
         <v>0</v>
       </c>
       <c r="BX48" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ48^2)/(AZ48^2+BI48))^(1/2)</f>
         <v>6.8895720725096588E-2</v>
       </c>
       <c r="BY48" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX48)/(1-BX48))</f>
         <v>6.900503950756405E-2</v>
       </c>
       <c r="BZ48" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY48^2)^2)/(BI48-1))</f>
         <v>7.1734384953814931E-4</v>
       </c>
       <c r="CA48" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI48-3)</f>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB48" s="99"/>
       <c r="CC48">
-        <f t="shared" ref="CC48:CC61" si="21">BI48-2</f>
+        <f>BI48-2</f>
         <v>1393</v>
       </c>
       <c r="CE48" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ48^2)/(AZ48^2+BJ48))^(1/2)</f>
         <v>1.8299961101675508E-2</v>
       </c>
       <c r="CF48" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE48)/(1-CE48))</f>
         <v>1.8302004328216499E-2</v>
       </c>
       <c r="CG48" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF48^2)^2)/(BJ48-1))</f>
         <v>5.035499711967097E-5</v>
       </c>
       <c r="CH48" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ48-3)</f>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -59552,41 +59555,41 @@
         <v>1</v>
       </c>
       <c r="BX49" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ49^2)/(AZ49^2+BI49))^(1/2)</f>
         <v>6.8895720725096588E-2</v>
       </c>
       <c r="BY49" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX49)/(1-BX49))</f>
         <v>6.900503950756405E-2</v>
       </c>
       <c r="BZ49" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY49^2)^2)/(BI49-1))</f>
         <v>7.1734384953814931E-4</v>
       </c>
       <c r="CA49" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI49-3)</f>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB49" s="99"/>
       <c r="CC49">
-        <f t="shared" si="21"/>
+        <f>BI49-2</f>
         <v>1393</v>
       </c>
       <c r="CD49"/>
       <c r="CE49" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ49^2)/(AZ49^2+BJ49))^(1/2)</f>
         <v>1.8299961101675508E-2</v>
       </c>
       <c r="CF49" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE49)/(1-CE49))</f>
         <v>1.8302004328216499E-2</v>
       </c>
       <c r="CG49" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF49^2)^2)/(BJ49-1))</f>
         <v>5.035499711967097E-5</v>
       </c>
       <c r="CH49" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ49-3)</f>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -59814,41 +59817,41 @@
         <v>0</v>
       </c>
       <c r="BX50" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ50^2)/(AZ50^2+BI50))^(1/2)</f>
         <v>6.8895720725096588E-2</v>
       </c>
       <c r="BY50" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX50)/(1-BX50))</f>
         <v>6.900503950756405E-2</v>
       </c>
       <c r="BZ50" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY50^2)^2)/(BI50-1))</f>
         <v>7.1734384953814931E-4</v>
       </c>
       <c r="CA50" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI50-3)</f>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB50" s="99"/>
       <c r="CC50">
-        <f t="shared" si="21"/>
+        <f>BI50-2</f>
         <v>1393</v>
       </c>
       <c r="CD50"/>
       <c r="CE50" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ50^2)/(AZ50^2+BJ50))^(1/2)</f>
         <v>1.8299961101675508E-2</v>
       </c>
       <c r="CF50" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE50)/(1-CE50))</f>
         <v>1.8302004328216499E-2</v>
       </c>
       <c r="CG50" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF50^2)^2)/(BJ50-1))</f>
         <v>5.035499711967097E-5</v>
       </c>
       <c r="CH50" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ50-3)</f>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -60076,41 +60079,41 @@
         <v>1</v>
       </c>
       <c r="BX51" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ51^2)/(AZ51^2+BI51))^(1/2)</f>
         <v>5.2449375133439773E-2</v>
       </c>
       <c r="BY51" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX51)/(1-BX51))</f>
         <v>5.2497549648224964E-2</v>
       </c>
       <c r="BZ51" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY51^2)^2)/(BI51-1))</f>
         <v>7.1735466607183095E-4</v>
       </c>
       <c r="CA51" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI51-3)</f>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB51" s="99"/>
       <c r="CC51">
-        <f t="shared" si="21"/>
+        <f>BI51-2</f>
         <v>1393</v>
       </c>
       <c r="CD51"/>
       <c r="CE51" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ51^2)/(AZ51^2+BJ51))^(1/2)</f>
         <v>1.3918547330727849E-2</v>
       </c>
       <c r="CF51" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE51)/(1-CE51))</f>
         <v>1.3919446229861089E-2</v>
       </c>
       <c r="CG51" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF51^2)^2)/(BJ51-1))</f>
         <v>5.0355000879226367E-5</v>
       </c>
       <c r="CH51" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ51-3)</f>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -60336,40 +60339,40 @@
         <v>0</v>
       </c>
       <c r="BX52" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ52^2)/(AZ52^2+BI52))^(1/2)</f>
         <v>0.47242735990047685</v>
       </c>
       <c r="BY52" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX52)/(1-BX52))</f>
         <v>0.51319051047617226</v>
       </c>
       <c r="BZ52" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY52^2)^2)/(BI52-1))</f>
         <v>6.6760340037102519E-4</v>
       </c>
       <c r="CA52" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI52-3)</f>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB52" s="99"/>
       <c r="CC52">
-        <f t="shared" si="21"/>
+        <f>BI52-2</f>
         <v>1393</v>
       </c>
       <c r="CE52" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ52^2)/(AZ52^2+BJ52))^(1/2)</f>
         <v>0.14064871674533846</v>
       </c>
       <c r="CF52" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE52)/(1-CE52))</f>
         <v>0.14158732325545795</v>
       </c>
       <c r="CG52" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF52^2)^2)/(BJ52-1))</f>
         <v>5.0334766050130579E-5</v>
       </c>
       <c r="CH52" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ52-3)</f>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -60595,40 +60598,40 @@
         <v>0</v>
       </c>
       <c r="BX53" s="103">
-        <f t="shared" si="13"/>
+        <f>((AZ53^2)/(AZ53^2+BI53))^(1/2)</f>
         <v>0.29473516954008327</v>
       </c>
       <c r="BY53" s="103">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX53)/(1-BX53))</f>
         <v>0.3037440363085756</v>
       </c>
       <c r="BZ53" s="103">
-        <f t="shared" si="15"/>
+        <f>((1-(BY53^2)^2)/(BI53-1))</f>
         <v>7.1125395357683058E-4</v>
       </c>
       <c r="CA53" s="103">
-        <f t="shared" si="16"/>
+        <f>1/(BI53-3)</f>
         <v>7.1839080459770114E-4</v>
       </c>
       <c r="CB53" s="99"/>
       <c r="CC53">
-        <f t="shared" si="21"/>
+        <f>BI53-2</f>
         <v>1393</v>
       </c>
       <c r="CE53" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ53^2)/(AZ53^2+BJ53))^(1/2)</f>
         <v>8.1473550285666996E-2</v>
       </c>
       <c r="CF53" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE53)/(1-CE53))</f>
         <v>8.165454385204271E-2</v>
       </c>
       <c r="CG53" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF53^2)^2)/(BJ53-1))</f>
         <v>5.0352764233683405E-5</v>
       </c>
       <c r="CH53" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ53-3)</f>
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
@@ -60785,7 +60788,7 @@
         <v>1</v>
       </c>
       <c r="AZ54">
-        <f t="shared" ref="AZ54:AZ61" si="22">TINV(AX54,CC54)</f>
+        <f>TINV(AX54,CC54)</f>
         <v>1.9645365010317388</v>
       </c>
       <c r="BA54" t="s">
@@ -60855,39 +60858,39 @@
         <v>1</v>
       </c>
       <c r="BX54" s="30">
-        <f t="shared" si="13"/>
+        <f>((AZ54^2)/(AZ54^2+BI54))^(1/2)</f>
         <v>8.5669312189989619E-2</v>
       </c>
       <c r="BY54" s="30">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX54)/(1-BX54))</f>
         <v>8.5879822251689428E-2</v>
       </c>
       <c r="BZ54" s="30">
-        <f t="shared" si="15"/>
+        <f>((1-(BY54^2)^2)/(BI54-1))</f>
         <v>1.9192813902165059E-3</v>
       </c>
       <c r="CA54" s="30">
-        <f t="shared" si="16"/>
+        <f>1/(BI54-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
       <c r="CC54">
-        <f t="shared" si="21"/>
+        <f>BI54-2</f>
         <v>520</v>
       </c>
       <c r="CE54" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ54^2)/(AZ54^2+BJ54))^(1/2)</f>
         <v>8.5669312189989619E-2</v>
       </c>
       <c r="CF54" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE54)/(1-CE54))</f>
         <v>8.5879822251689428E-2</v>
       </c>
       <c r="CG54" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF54^2)^2)/(BJ54-1))</f>
         <v>1.9192813902165059E-3</v>
       </c>
       <c r="CH54" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ54-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -61044,7 +61047,7 @@
         <v>1</v>
       </c>
       <c r="AZ55">
-        <f t="shared" si="22"/>
+        <f>TINV(AX55,CC55)</f>
         <v>1.6477892114622541</v>
       </c>
       <c r="BA55" t="s">
@@ -61114,39 +61117,39 @@
         <v>1</v>
       </c>
       <c r="BX55" s="30">
-        <f t="shared" si="13"/>
+        <f>((AZ55^2)/(AZ55^2+BI55))^(1/2)</f>
         <v>7.1934930559867688E-2</v>
       </c>
       <c r="BY55" s="30">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX55)/(1-BX55))</f>
         <v>7.2059396212325363E-2</v>
       </c>
       <c r="BZ55" s="30">
-        <f t="shared" si="15"/>
+        <f>((1-(BY55^2)^2)/(BI55-1))</f>
         <v>1.919334044829439E-3</v>
       </c>
       <c r="CA55" s="30">
-        <f t="shared" si="16"/>
+        <f>1/(BI55-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
       <c r="CC55">
-        <f t="shared" si="21"/>
+        <f>BI55-2</f>
         <v>520</v>
       </c>
       <c r="CE55" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ55^2)/(AZ55^2+BJ55))^(1/2)</f>
         <v>7.1934930559867688E-2</v>
       </c>
       <c r="CF55" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE55)/(1-CE55))</f>
         <v>7.2059396212325363E-2</v>
       </c>
       <c r="CG55" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF55^2)^2)/(BJ55-1))</f>
         <v>1.919334044829439E-3</v>
       </c>
       <c r="CH55" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ55-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -61303,7 +61306,7 @@
         <v>1</v>
       </c>
       <c r="AZ56">
-        <f t="shared" si="22"/>
+        <f>TINV(AX56,CC56)</f>
         <v>1.6477892114622541</v>
       </c>
       <c r="BA56" t="s">
@@ -61373,39 +61376,39 @@
         <v>1</v>
       </c>
       <c r="BX56" s="30">
-        <f t="shared" si="13"/>
+        <f>((AZ56^2)/(AZ56^2+BI56))^(1/2)</f>
         <v>7.1934930559867688E-2</v>
       </c>
       <c r="BY56" s="30">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX56)/(1-BX56))</f>
         <v>7.2059396212325363E-2</v>
       </c>
       <c r="BZ56" s="30">
-        <f t="shared" si="15"/>
+        <f>((1-(BY56^2)^2)/(BI56-1))</f>
         <v>1.919334044829439E-3</v>
       </c>
       <c r="CA56" s="30">
-        <f t="shared" si="16"/>
+        <f>1/(BI56-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
       <c r="CC56">
-        <f t="shared" si="21"/>
+        <f>BI56-2</f>
         <v>520</v>
       </c>
       <c r="CE56" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ56^2)/(AZ56^2+BJ56))^(1/2)</f>
         <v>7.1934930559867688E-2</v>
       </c>
       <c r="CF56" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE56)/(1-CE56))</f>
         <v>7.2059396212325363E-2</v>
       </c>
       <c r="CG56" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF56^2)^2)/(BJ56-1))</f>
         <v>1.919334044829439E-3</v>
       </c>
       <c r="CH56" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ56-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -61562,7 +61565,7 @@
         <v>2</v>
       </c>
       <c r="AZ57">
-        <f t="shared" si="22"/>
+        <f>TINV(AX57,CC57)</f>
         <v>1.6477892114622541</v>
       </c>
       <c r="BA57" t="s">
@@ -61632,39 +61635,39 @@
         <v>1</v>
       </c>
       <c r="BX57" s="30">
-        <f t="shared" si="13"/>
+        <f>((AZ57^2)/(AZ57^2+BI57))^(1/2)</f>
         <v>7.1934930559867688E-2</v>
       </c>
       <c r="BY57" s="30">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX57)/(1-BX57))</f>
         <v>7.2059396212325363E-2</v>
       </c>
       <c r="BZ57" s="30">
-        <f t="shared" si="15"/>
+        <f>((1-(BY57^2)^2)/(BI57-1))</f>
         <v>1.919334044829439E-3</v>
       </c>
       <c r="CA57" s="30">
-        <f t="shared" si="16"/>
+        <f>1/(BI57-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
       <c r="CC57">
-        <f t="shared" si="21"/>
+        <f>BI57-2</f>
         <v>520</v>
       </c>
       <c r="CE57" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ57^2)/(AZ57^2+BJ57))^(1/2)</f>
         <v>7.1934930559867688E-2</v>
       </c>
       <c r="CF57" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE57)/(1-CE57))</f>
         <v>7.2059396212325363E-2</v>
       </c>
       <c r="CG57" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF57^2)^2)/(BJ57-1))</f>
         <v>1.919334044829439E-3</v>
       </c>
       <c r="CH57" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ57-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -61821,7 +61824,7 @@
         <v>1</v>
       </c>
       <c r="AZ58">
-        <f t="shared" si="22"/>
+        <f>TINV(AX58,CC58)</f>
         <v>2.5853169622486396</v>
       </c>
       <c r="BA58" t="s">
@@ -61891,39 +61894,39 @@
         <v>1</v>
       </c>
       <c r="BX58" s="30">
-        <f t="shared" si="13"/>
+        <f>((AZ58^2)/(AZ58^2+BI58))^(1/2)</f>
         <v>0.11243868763294575</v>
       </c>
       <c r="BY58" s="30">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX58)/(1-BX58))</f>
         <v>0.11291614848050519</v>
       </c>
       <c r="BZ58" s="30">
-        <f t="shared" si="15"/>
+        <f>((1-(BY58^2)^2)/(BI58-1))</f>
         <v>1.9190737736219023E-3</v>
       </c>
       <c r="CA58" s="30">
-        <f t="shared" si="16"/>
+        <f>1/(BI58-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
       <c r="CC58">
-        <f t="shared" si="21"/>
+        <f>BI58-2</f>
         <v>520</v>
       </c>
       <c r="CE58" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ58^2)/(AZ58^2+BJ58))^(1/2)</f>
         <v>0.11243868763294575</v>
       </c>
       <c r="CF58" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE58)/(1-CE58))</f>
         <v>0.11291614848050519</v>
       </c>
       <c r="CG58" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF58^2)^2)/(BJ58-1))</f>
         <v>1.9190737736219023E-3</v>
       </c>
       <c r="CH58" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ58-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -62080,7 +62083,7 @@
         <v>1</v>
       </c>
       <c r="AZ59">
-        <f t="shared" si="22"/>
+        <f>TINV(AX59,CC59)</f>
         <v>2.5853169622486396</v>
       </c>
       <c r="BA59" t="s">
@@ -62150,39 +62153,39 @@
         <v>1</v>
       </c>
       <c r="BX59" s="30">
-        <f t="shared" si="13"/>
+        <f>((AZ59^2)/(AZ59^2+BI59))^(1/2)</f>
         <v>0.11243868763294575</v>
       </c>
       <c r="BY59" s="30">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX59)/(1-BX59))</f>
         <v>0.11291614848050519</v>
       </c>
       <c r="BZ59" s="30">
-        <f t="shared" si="15"/>
+        <f>((1-(BY59^2)^2)/(BI59-1))</f>
         <v>1.9190737736219023E-3</v>
       </c>
       <c r="CA59" s="30">
-        <f t="shared" si="16"/>
+        <f>1/(BI59-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
       <c r="CC59">
-        <f t="shared" si="21"/>
+        <f>BI59-2</f>
         <v>520</v>
       </c>
       <c r="CE59" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ59^2)/(AZ59^2+BJ59))^(1/2)</f>
         <v>0.11243868763294575</v>
       </c>
       <c r="CF59" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE59)/(1-CE59))</f>
         <v>0.11291614848050519</v>
       </c>
       <c r="CG59" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF59^2)^2)/(BJ59-1))</f>
         <v>1.9190737736219023E-3</v>
       </c>
       <c r="CH59" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ59-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -62339,7 +62342,7 @@
         <v>1</v>
       </c>
       <c r="AZ60">
-        <f t="shared" si="22"/>
+        <f>TINV(AX60,CC60)</f>
         <v>2.5853169622486396</v>
       </c>
       <c r="BA60" t="s">
@@ -62409,39 +62412,39 @@
         <v>1</v>
       </c>
       <c r="BX60" s="30">
-        <f t="shared" si="13"/>
+        <f>((AZ60^2)/(AZ60^2+BI60))^(1/2)</f>
         <v>0.11243868763294575</v>
       </c>
       <c r="BY60" s="30">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX60)/(1-BX60))</f>
         <v>0.11291614848050519</v>
       </c>
       <c r="BZ60" s="30">
-        <f t="shared" si="15"/>
+        <f>((1-(BY60^2)^2)/(BI60-1))</f>
         <v>1.9190737736219023E-3</v>
       </c>
       <c r="CA60" s="30">
-        <f t="shared" si="16"/>
+        <f>1/(BI60-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
       <c r="CC60">
-        <f t="shared" si="21"/>
+        <f>BI60-2</f>
         <v>520</v>
       </c>
       <c r="CE60" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ60^2)/(AZ60^2+BJ60))^(1/2)</f>
         <v>0.11243868763294575</v>
       </c>
       <c r="CF60" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE60)/(1-CE60))</f>
         <v>0.11291614848050519</v>
       </c>
       <c r="CG60" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF60^2)^2)/(BJ60-1))</f>
         <v>1.9190737736219023E-3</v>
       </c>
       <c r="CH60" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ60-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -62598,7 +62601,7 @@
         <v>1</v>
       </c>
       <c r="AZ61">
-        <f t="shared" si="22"/>
+        <f>TINV(AX61,CC61)</f>
         <v>1.9645365010317388</v>
       </c>
       <c r="BA61" t="s">
@@ -62668,39 +62671,39 @@
         <v>1</v>
       </c>
       <c r="BX61" s="30">
-        <f t="shared" si="13"/>
+        <f>((AZ61^2)/(AZ61^2+BI61))^(1/2)</f>
         <v>8.5669312189989619E-2</v>
       </c>
       <c r="BY61" s="30">
-        <f t="shared" si="14"/>
+        <f>0.5*LN((1+BX61)/(1-BX61))</f>
         <v>8.5879822251689428E-2</v>
       </c>
       <c r="BZ61" s="30">
-        <f t="shared" si="15"/>
+        <f>((1-(BY61^2)^2)/(BI61-1))</f>
         <v>1.9192813902165059E-3</v>
       </c>
       <c r="CA61" s="30">
-        <f t="shared" si="16"/>
+        <f>1/(BI61-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
       <c r="CC61">
-        <f t="shared" si="21"/>
+        <f>BI61-2</f>
         <v>520</v>
       </c>
       <c r="CE61" s="30">
-        <f t="shared" si="17"/>
+        <f>((AZ61^2)/(AZ61^2+BJ61))^(1/2)</f>
         <v>8.5669312189989619E-2</v>
       </c>
       <c r="CF61" s="30">
-        <f t="shared" si="18"/>
+        <f>0.5*LN((1+CE61)/(1-CE61))</f>
         <v>8.5879822251689428E-2</v>
       </c>
       <c r="CG61" s="30">
-        <f t="shared" si="19"/>
+        <f>((1-(CF61^2)^2)/(BJ61-1))</f>
         <v>1.9192813902165059E-3</v>
       </c>
       <c r="CH61" s="30">
-        <f t="shared" si="20"/>
+        <f>1/(BJ61-3)</f>
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
@@ -62771,7 +62774,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="603" yWindow="1085" count="7">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH1:AP1 AH31:AP42 AH7:AH8 AJ7:AP8 AH55:AP1048576 AL27 AH26:AK27 AL26:AP26 AH28:AL30 S15:S30 S1 U1 AH43:AQ54 U39:U1048576 S34:S1048576 U15:U35 AH15:AP25 AN27:AP30">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN27:AP30 AH31:AP42 AH7:AH8 AJ7:AP8 AH55:AP1048576 AL27 AH26:AK27 AL26:AP26 AH28:AL30 S15:S30 S1 U1 AH43:AQ54 U39:U1048576 S34:S1048576 U15:U35 AH15:AP25 AH1:AI1 AK1:AP1">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>

--- a/appliances_wtp.xlsx
+++ b/appliances_wtp.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dand\Documents\GitHub\appliances_interventions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianadanilenko/Desktop/appliances_interventions/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74253D57-879C-8B40-92CB-6ABB77712488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4476" yWindow="-21600" windowWidth="38400" windowHeight="21600" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="-5280" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -21,9 +22,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Appliances!$AR$1:$AR$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Usage!$A$1:$BN$53</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,62 +46,35 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={73C2226C-6106-4DC2-88CF-9C0A06F48311}</author>
     <author>tc={CEE78422-255C-40DC-AFED-5AA185CC03E1}</author>
     <author>tc={C7CEED71-5EFE-4791-84D8-7010C40A69F0}</author>
   </authors>
   <commentList>
-    <comment ref="AQ1" authorId="0" shapeId="0">
+    <comment ref="AQ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     is this supposed to capture mean difference between control and treatment or ?</t>
-        </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="1" shapeId="0">
+    <comment ref="AZ1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     daily kWh</t>
-        </r>
       </text>
     </comment>
-    <comment ref="AQ22" authorId="2" shapeId="0">
+    <comment ref="AQ22" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     in kWh</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -108,44 +82,26 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={1DD52412-77C6-1E43-B8CC-07AD562D2C6E}</author>
     <author>tc={52E723F4-9A55-1E46-88F7-D2164B4696BA}</author>
   </authors>
   <commentList>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     check label studies from srmt for label type</t>
-        </r>
       </text>
     </comment>
-    <comment ref="AR23" authorId="1" shapeId="0">
+    <comment ref="AR23" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
+        <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     can we code them as relative WTP? </t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -153,28 +109,19 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={CF36070F-7893-4948-8AB8-1CADF6EBBFD9}</author>
   </authors>
   <commentList>
-    <comment ref="D6" authorId="0" shapeId="0">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     a bit confused as of where it’s correlation and where - quasi-experimental
 Reply:
     the way i reassessed this was - market statistics - correlation, whereas hypothetical choice - quasi-experimental</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -2559,7 +2506,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
@@ -2799,6 +2746,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3044,7 +2992,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3191,18 +3139,14 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="36" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -3246,7 +3190,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:CD1048576" sheet="Appliances"/>
   </cacheSource>
@@ -35043,7 +34987,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -35880,7 +35824,7 @@
   <threadedComment ref="AA1" dT="2022-11-21T17:36:05.27" personId="{07E012BB-865F-6142-9A86-EDCC0A8503F7}" id="{1DD52412-77C6-1E43-B8CC-07AD562D2C6E}">
     <text>check label studies from srmt for label type</text>
   </threadedComment>
-  <threadedComment ref="AR15" dT="2022-12-14T13:27:58.05" personId="{07E012BB-865F-6142-9A86-EDCC0A8503F7}" id="{52E723F4-9A55-1E46-88F7-D2164B4696BA}">
+  <threadedComment ref="AR23" dT="2022-12-14T13:27:58.05" personId="{07E012BB-865F-6142-9A86-EDCC0A8503F7}" id="{52E723F4-9A55-1E46-88F7-D2164B4696BA}">
     <text xml:space="preserve">can we code them as relative WTP? </text>
   </threadedComment>
 </ThreadedComments>
@@ -35898,57 +35842,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BP53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="4" max="4" width="20.59765625" customWidth="1"/>
-    <col min="5" max="5" width="14.09765625" customWidth="1"/>
-    <col min="7" max="7" width="16.09765625" customWidth="1"/>
-    <col min="8" max="8" width="16.59765625" customWidth="1"/>
-    <col min="10" max="10" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" hidden="1" customWidth="1"/>
     <col min="12" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="16" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="12.09765625" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="12.1640625" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="0" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="0" style="12" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="18.59765625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.59765625" style="7" customWidth="1"/>
-    <col min="30" max="30" width="13.59765625" customWidth="1"/>
-    <col min="31" max="31" width="14.59765625" customWidth="1"/>
-    <col min="32" max="32" width="13.59765625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="19.09765625" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="10.59765625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="13.09765625" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="22.09765625" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="10.59765625" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="18.09765625" customWidth="1"/>
-    <col min="39" max="39" width="14.09765625" customWidth="1"/>
-    <col min="40" max="40" width="9.59765625" customWidth="1"/>
-    <col min="41" max="41" width="19.09765625" customWidth="1"/>
-    <col min="42" max="42" width="12.09765625" customWidth="1"/>
+    <col min="27" max="27" width="18.6640625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.6640625" style="7" customWidth="1"/>
+    <col min="30" max="30" width="13.6640625" customWidth="1"/>
+    <col min="31" max="31" width="14.6640625" customWidth="1"/>
+    <col min="32" max="32" width="13.6640625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="19.1640625" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="10.6640625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="13.1640625" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="22.1640625" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="10.6640625" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="18.1640625" customWidth="1"/>
+    <col min="39" max="39" width="14.1640625" customWidth="1"/>
+    <col min="40" max="40" width="9.6640625" customWidth="1"/>
+    <col min="41" max="41" width="19.1640625" customWidth="1"/>
+    <col min="42" max="42" width="12.1640625" customWidth="1"/>
     <col min="44" max="45" width="0" hidden="1" customWidth="1"/>
-    <col min="46" max="47" width="13.09765625" hidden="1" customWidth="1"/>
+    <col min="46" max="47" width="13.1640625" hidden="1" customWidth="1"/>
     <col min="48" max="51" width="0" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="13.59765625" style="17" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="13.6640625" style="17" hidden="1" customWidth="1"/>
     <col min="53" max="53" width="26.5" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="20.59765625" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="20.6640625" hidden="1" customWidth="1"/>
     <col min="55" max="55" width="0" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="17.59765625" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="16.09765625" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="15.09765625" hidden="1" customWidth="1"/>
-    <col min="59" max="59" width="20.59765625" hidden="1" customWidth="1"/>
-    <col min="60" max="60" width="24.59765625" hidden="1" customWidth="1"/>
-    <col min="61" max="61" width="19.59765625" style="30" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="24.09765625" style="30" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.6640625" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="16.1640625" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="15.1640625" hidden="1" customWidth="1"/>
+    <col min="59" max="59" width="20.6640625" hidden="1" customWidth="1"/>
+    <col min="60" max="60" width="24.6640625" hidden="1" customWidth="1"/>
+    <col min="61" max="61" width="19.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="24.1640625" style="30" bestFit="1" customWidth="1"/>
     <col min="63" max="65" width="11" style="30"/>
-    <col min="67" max="67" width="25.09765625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="43.2">
+    <row r="1" spans="1:68" ht="48">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -41492,11 +41436,11 @@
       </c>
       <c r="BI27" s="30">
         <f t="shared" si="14"/>
-        <v>6.4285714285714259E-3</v>
+        <v>6.4285714285714276E-3</v>
       </c>
       <c r="BJ27" s="30">
         <f t="shared" si="15"/>
-        <v>6.4285714285714259E-3</v>
+        <v>6.4285714285714276E-3</v>
       </c>
       <c r="BK27" s="30">
         <f t="shared" si="9"/>
@@ -43746,7 +43690,7 @@
         <v>6.7567567567567571E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.8">
+    <row r="39" spans="1:66" s="41" customFormat="1" ht="17">
       <c r="A39" s="45" t="s">
         <v>68</v>
       </c>
@@ -43951,7 +43895,7 @@
       </c>
       <c r="BN39" s="43"/>
     </row>
-    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.8">
+    <row r="40" spans="1:66" s="41" customFormat="1" ht="17">
       <c r="A40" s="45" t="s">
         <v>68</v>
       </c>
@@ -44156,7 +44100,7 @@
       </c>
       <c r="BN40" s="43"/>
     </row>
-    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.8">
+    <row r="41" spans="1:66" s="41" customFormat="1" ht="17">
       <c r="A41" s="45" t="s">
         <v>68</v>
       </c>
@@ -44365,7 +44309,7 @@
         <v>2.0421052631578922</v>
       </c>
     </row>
-    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.8">
+    <row r="42" spans="1:66" s="41" customFormat="1" ht="17">
       <c r="A42" s="45" t="s">
         <v>68</v>
       </c>
@@ -46762,34 +46706,34 @@
   </sheetData>
   <dataConsolidate/>
   <dataValidations count="10">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>$D$2:$D$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>$D$2:$D$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>$F$2:$F$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -46798,43 +46742,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_" xr:uid="{00000000-0002-0000-0000-00000A000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>BC23:BC28 BC54:BC1048576 BC33:BC38 BC1:BC12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$9</xm:f>
           </x14:formula1>
           <xm:sqref>J54:J1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>AS43:AX51 AS54:AX1048576 AS23:AX38 AS2:AX12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$10</xm:f>
           </x14:formula1>
           <xm:sqref>J38</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$E$2:$E$4</xm:f>
           </x14:formula1>
           <xm:sqref>AO43:AO51</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$6</xm:f>
           </x14:formula1>
           <xm:sqref>K54:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$7</xm:f>
           </x14:formula1>
@@ -46847,63 +46791,63 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CH75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="5" max="5" width="24.59765625" customWidth="1"/>
-    <col min="6" max="6" width="17.59765625" customWidth="1"/>
-    <col min="7" max="7" width="14.09765625" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" customWidth="1"/>
     <col min="8" max="8" width="16.5" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16.09765625" customWidth="1"/>
-    <col min="11" max="11" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.09765625" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" customWidth="1"/>
+    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.1640625" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="14.59765625" customWidth="1"/>
-    <col min="17" max="17" width="13.09765625" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" customWidth="1"/>
+    <col min="17" max="17" width="13.1640625" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="14.09765625" customWidth="1"/>
+    <col min="19" max="19" width="14.1640625" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="21.09765625" customWidth="1"/>
+    <col min="21" max="21" width="21.1640625" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.59765625" customWidth="1"/>
+    <col min="23" max="23" width="14.6640625" customWidth="1"/>
     <col min="24" max="24" width="12.5" customWidth="1"/>
     <col min="25" max="33" width="11" customWidth="1"/>
     <col min="34" max="35" width="16" customWidth="1"/>
     <col min="36" max="39" width="11" customWidth="1"/>
-    <col min="40" max="41" width="12.09765625" customWidth="1"/>
+    <col min="40" max="41" width="12.1640625" customWidth="1"/>
     <col min="42" max="42" width="11" customWidth="1"/>
-    <col min="43" max="43" width="27.59765625" customWidth="1"/>
-    <col min="44" max="44" width="41.09765625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="54.59765625" customWidth="1"/>
+    <col min="43" max="43" width="27.6640625" customWidth="1"/>
+    <col min="44" max="44" width="41.1640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="54.6640625" customWidth="1"/>
     <col min="46" max="46" width="21" customWidth="1"/>
-    <col min="47" max="47" width="26.59765625" style="7" customWidth="1"/>
-    <col min="48" max="48" width="14.09765625" style="7" customWidth="1"/>
-    <col min="49" max="49" width="13.09765625" customWidth="1"/>
-    <col min="50" max="50" width="9.59765625" customWidth="1"/>
+    <col min="47" max="47" width="26.6640625" style="7" customWidth="1"/>
+    <col min="48" max="48" width="14.1640625" style="7" customWidth="1"/>
+    <col min="49" max="49" width="13.1640625" customWidth="1"/>
+    <col min="50" max="50" width="9.6640625" customWidth="1"/>
     <col min="51" max="51" width="17" customWidth="1"/>
     <col min="52" max="52" width="9"/>
-    <col min="53" max="54" width="14.09765625" customWidth="1"/>
-    <col min="55" max="55" width="13.59765625" customWidth="1"/>
-    <col min="56" max="56" width="12.59765625" customWidth="1"/>
-    <col min="57" max="57" width="10.59765625" customWidth="1"/>
+    <col min="53" max="54" width="14.1640625" customWidth="1"/>
+    <col min="55" max="55" width="13.6640625" customWidth="1"/>
+    <col min="56" max="56" width="12.6640625" customWidth="1"/>
+    <col min="57" max="57" width="10.6640625" customWidth="1"/>
     <col min="58" max="58" width="13" customWidth="1"/>
-    <col min="59" max="60" width="10.59765625" customWidth="1"/>
-    <col min="61" max="62" width="11.09765625" customWidth="1"/>
+    <col min="59" max="60" width="10.6640625" customWidth="1"/>
+    <col min="61" max="62" width="11.1640625" customWidth="1"/>
     <col min="63" max="64" width="11" customWidth="1"/>
-    <col min="65" max="65" width="12.59765625" customWidth="1"/>
-    <col min="66" max="66" width="18.09765625" customWidth="1"/>
-    <col min="67" max="67" width="22.09765625" customWidth="1"/>
-    <col min="68" max="68" width="15.09765625" customWidth="1"/>
+    <col min="65" max="65" width="12.6640625" customWidth="1"/>
+    <col min="66" max="66" width="18.1640625" customWidth="1"/>
+    <col min="67" max="67" width="22.1640625" customWidth="1"/>
+    <col min="68" max="68" width="15.1640625" customWidth="1"/>
     <col min="69" max="69" width="18" customWidth="1"/>
-    <col min="70" max="70" width="17.09765625" customWidth="1"/>
-    <col min="71" max="71" width="21.09765625" customWidth="1"/>
-    <col min="72" max="72" width="10.09765625" customWidth="1"/>
+    <col min="70" max="70" width="17.1640625" customWidth="1"/>
+    <col min="71" max="71" width="21.1640625" customWidth="1"/>
+    <col min="72" max="72" width="10.1640625" customWidth="1"/>
     <col min="73" max="73" width="13" customWidth="1"/>
     <col min="74" max="74" width="14" customWidth="1"/>
-    <col min="75" max="75" width="13.09765625" customWidth="1"/>
+    <col min="75" max="75" width="13.1640625" customWidth="1"/>
     <col min="82" max="82" width="24" customWidth="1"/>
   </cols>
   <sheetData>
@@ -47167,7 +47111,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:86" ht="15.6">
+    <row r="2" spans="1:86" ht="16">
       <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
@@ -47427,7 +47371,7 @@
         <v>3.0120481927710845E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:86" ht="15.6">
+    <row r="3" spans="1:86" ht="16">
       <c r="A3" s="11" t="s">
         <v>68</v>
       </c>
@@ -47688,7 +47632,7 @@
         <v>2.2883295194508009E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:86" ht="15.6">
+    <row r="4" spans="1:86" ht="16">
       <c r="A4" t="s">
         <v>334</v>
       </c>
@@ -47812,16 +47756,16 @@
       <c r="AP4" s="18">
         <v>0</v>
       </c>
-      <c r="AQ4" s="118" t="s">
+      <c r="AQ4" t="s">
         <v>332</v>
       </c>
-      <c r="AR4" s="119" t="s">
+      <c r="AR4" s="94" t="s">
         <v>234</v>
       </c>
-      <c r="AS4" s="119" t="s">
+      <c r="AS4" s="94" t="s">
         <v>332</v>
       </c>
-      <c r="AT4" s="119" t="s">
+      <c r="AT4" s="94" t="s">
         <v>333</v>
       </c>
       <c r="AU4" s="21">
@@ -47947,7 +47891,7 @@
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:86" s="102" customFormat="1" ht="15.6">
+    <row r="5" spans="1:86" s="102" customFormat="1" ht="16">
       <c r="A5" t="s">
         <v>334</v>
       </c>
@@ -48072,16 +48016,16 @@
       <c r="AP5" s="18">
         <v>0</v>
       </c>
-      <c r="AQ5" s="118" t="s">
+      <c r="AQ5" t="s">
         <v>332</v>
       </c>
-      <c r="AR5" s="119" t="s">
+      <c r="AR5" s="94" t="s">
         <v>234</v>
       </c>
-      <c r="AS5" s="119" t="s">
+      <c r="AS5" s="94" t="s">
         <v>332</v>
       </c>
-      <c r="AT5" s="119" t="s">
+      <c r="AT5" s="94" t="s">
         <v>333</v>
       </c>
       <c r="AU5" s="21">
@@ -48209,7 +48153,7 @@
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:86" ht="15.6">
+    <row r="6" spans="1:86" ht="16">
       <c r="A6" t="s">
         <v>334</v>
       </c>
@@ -48333,16 +48277,16 @@
       <c r="AP6" s="18">
         <v>0</v>
       </c>
-      <c r="AQ6" s="118" t="s">
+      <c r="AQ6" t="s">
         <v>332</v>
       </c>
-      <c r="AR6" s="119" t="s">
+      <c r="AR6" s="94" t="s">
         <v>234</v>
       </c>
-      <c r="AS6" s="119" t="s">
+      <c r="AS6" s="94" t="s">
         <v>332</v>
       </c>
-      <c r="AT6" s="119" t="s">
+      <c r="AT6" s="94" t="s">
         <v>333</v>
       </c>
       <c r="AU6" s="21">
@@ -48468,7 +48412,7 @@
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:86" s="99" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="7" spans="1:86" s="99" customFormat="1" ht="17" customHeight="1">
       <c r="A7" t="s">
         <v>334</v>
       </c>
@@ -48593,16 +48537,16 @@
       <c r="AP7" s="18">
         <v>0</v>
       </c>
-      <c r="AQ7" s="118" t="s">
+      <c r="AQ7" t="s">
         <v>332</v>
       </c>
-      <c r="AR7" s="119" t="s">
+      <c r="AR7" s="94" t="s">
         <v>234</v>
       </c>
-      <c r="AS7" s="119" t="s">
+      <c r="AS7" s="94" t="s">
         <v>332</v>
       </c>
-      <c r="AT7" s="119" t="s">
+      <c r="AT7" s="94" t="s">
         <v>333</v>
       </c>
       <c r="AU7" s="21">
@@ -48730,7 +48674,7 @@
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:86" s="99" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="8" spans="1:86" s="99" customFormat="1" ht="17" customHeight="1">
       <c r="A8" s="100" t="s">
         <v>68</v>
       </c>
@@ -49117,28 +49061,28 @@
       <c r="AP9" s="18">
         <v>0</v>
       </c>
-      <c r="AQ9" s="118" t="s">
+      <c r="AQ9" t="s">
         <v>332</v>
       </c>
-      <c r="AR9" s="118" t="s">
+      <c r="AR9" t="s">
         <v>234</v>
       </c>
-      <c r="AS9" s="118" t="s">
+      <c r="AS9" t="s">
         <v>332</v>
       </c>
-      <c r="AT9" s="118" t="s">
+      <c r="AT9" t="s">
         <v>333</v>
       </c>
-      <c r="AU9" s="120">
+      <c r="AU9" s="21">
         <v>0.55700000000000005</v>
       </c>
-      <c r="AV9" s="121" t="s">
+      <c r="AV9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AW9" s="118" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX9" s="118">
+      <c r="AW9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX9">
         <v>1E-3</v>
       </c>
       <c r="AY9">
@@ -49378,28 +49322,28 @@
       <c r="AP10" s="18">
         <v>0</v>
       </c>
-      <c r="AQ10" s="118" t="s">
+      <c r="AQ10" t="s">
         <v>332</v>
       </c>
-      <c r="AR10" s="118" t="s">
+      <c r="AR10" t="s">
         <v>234</v>
       </c>
-      <c r="AS10" s="118" t="s">
+      <c r="AS10" t="s">
         <v>332</v>
       </c>
-      <c r="AT10" s="118" t="s">
+      <c r="AT10" t="s">
         <v>333</v>
       </c>
-      <c r="AU10" s="120">
+      <c r="AU10" s="21">
         <v>1.58</v>
       </c>
-      <c r="AV10" s="121" t="s">
+      <c r="AV10" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AW10" s="118" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX10" s="118">
+      <c r="AW10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX10">
         <v>1E-3</v>
       </c>
       <c r="AY10">
@@ -49514,7 +49458,7 @@
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:86" ht="15.6">
+    <row r="11" spans="1:86" ht="16">
       <c r="A11" s="11" t="s">
         <v>314</v>
       </c>
@@ -49639,28 +49583,28 @@
       <c r="AP11" s="18">
         <v>0</v>
       </c>
-      <c r="AQ11" s="118" t="s">
+      <c r="AQ11" t="s">
         <v>332</v>
       </c>
-      <c r="AR11" s="118" t="s">
+      <c r="AR11" t="s">
         <v>234</v>
       </c>
-      <c r="AS11" s="118" t="s">
+      <c r="AS11" t="s">
         <v>332</v>
       </c>
-      <c r="AT11" s="118" t="s">
+      <c r="AT11" t="s">
         <v>333</v>
       </c>
-      <c r="AU11" s="120">
+      <c r="AU11" s="21">
         <v>0.17</v>
       </c>
-      <c r="AV11" s="121" t="s">
+      <c r="AV11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AW11" s="118" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX11" s="118">
+      <c r="AW11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX11">
         <v>0.311</v>
       </c>
       <c r="AY11">
@@ -49900,28 +49844,28 @@
       <c r="AP12" s="18">
         <v>0</v>
       </c>
-      <c r="AQ12" s="118" t="s">
+      <c r="AQ12" t="s">
         <v>332</v>
       </c>
-      <c r="AR12" s="118" t="s">
+      <c r="AR12" t="s">
         <v>234</v>
       </c>
-      <c r="AS12" s="118" t="s">
+      <c r="AS12" t="s">
         <v>332</v>
       </c>
-      <c r="AT12" s="118" t="s">
+      <c r="AT12" t="s">
         <v>333</v>
       </c>
-      <c r="AU12" s="120">
+      <c r="AU12" s="21">
         <v>1.1140000000000001</v>
       </c>
-      <c r="AV12" s="121" t="s">
+      <c r="AV12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AW12" s="118" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX12" s="118">
+      <c r="AW12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX12">
         <v>1E-3</v>
       </c>
       <c r="AY12">
@@ -50161,28 +50105,28 @@
       <c r="AP13" s="18">
         <v>0</v>
       </c>
-      <c r="AQ13" s="118" t="s">
+      <c r="AQ13" t="s">
         <v>332</v>
       </c>
-      <c r="AR13" s="118" t="s">
+      <c r="AR13" t="s">
         <v>234</v>
       </c>
-      <c r="AS13" s="118" t="s">
+      <c r="AS13" t="s">
         <v>332</v>
       </c>
-      <c r="AT13" s="118" t="s">
+      <c r="AT13" t="s">
         <v>333</v>
       </c>
-      <c r="AU13" s="120">
+      <c r="AU13" s="21">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="AV13" s="121" t="s">
+      <c r="AV13" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="AW13" s="118" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX13" s="118">
+      <c r="AW13" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX13">
         <v>0.71299999999999997</v>
       </c>
       <c r="AY13">
@@ -50422,28 +50366,28 @@
       <c r="AP14" s="18">
         <v>0</v>
       </c>
-      <c r="AQ14" s="118" t="s">
+      <c r="AQ14" t="s">
         <v>332</v>
       </c>
-      <c r="AR14" s="118" t="s">
+      <c r="AR14" t="s">
         <v>234</v>
       </c>
-      <c r="AS14" s="118" t="s">
+      <c r="AS14" t="s">
         <v>332</v>
       </c>
-      <c r="AT14" s="118" t="s">
+      <c r="AT14" t="s">
         <v>333</v>
       </c>
-      <c r="AU14" s="120">
+      <c r="AU14" s="21">
         <v>2E-3</v>
       </c>
-      <c r="AV14" s="121" t="s">
+      <c r="AV14" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="AW14" s="118" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX14" s="118">
+      <c r="AW14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX14">
         <v>0.99199999999999999</v>
       </c>
       <c r="AY14">
@@ -50558,7 +50502,7 @@
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:86" ht="15.6">
+    <row r="15" spans="1:86" ht="16">
       <c r="A15" s="100" t="s">
         <v>314</v>
       </c>
@@ -50820,7 +50764,7 @@
         <v>3.1746031746031746E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:86" ht="15.6">
+    <row r="16" spans="1:86" ht="16">
       <c r="A16" s="11" t="s">
         <v>68</v>
       </c>
@@ -51080,7 +51024,7 @@
         <v>1.4858841010401188E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:86" ht="15.6">
+    <row r="17" spans="1:86" ht="16">
       <c r="A17" t="s">
         <v>334</v>
       </c>
@@ -51114,7 +51058,7 @@
       <c r="L17">
         <v>9</v>
       </c>
-      <c r="M17" s="122" t="s">
+      <c r="M17" s="118" t="s">
         <v>347</v>
       </c>
       <c r="N17" t="s">
@@ -51204,16 +51148,16 @@
       <c r="AP17" s="18">
         <v>0</v>
       </c>
-      <c r="AQ17" s="118" t="s">
+      <c r="AQ17" t="s">
         <v>350</v>
       </c>
-      <c r="AR17" s="118" t="s">
+      <c r="AR17" t="s">
         <v>234</v>
       </c>
-      <c r="AS17" s="119" t="s">
+      <c r="AS17" s="94" t="s">
         <v>350</v>
       </c>
-      <c r="AT17" s="118" t="s">
+      <c r="AT17" t="s">
         <v>73</v>
       </c>
       <c r="AU17" s="21">
@@ -51339,7 +51283,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:86" ht="15.6">
+    <row r="18" spans="1:86" ht="16">
       <c r="A18" t="s">
         <v>334</v>
       </c>
@@ -51373,7 +51317,7 @@
       <c r="L18">
         <v>9</v>
       </c>
-      <c r="M18" s="122" t="s">
+      <c r="M18" s="118" t="s">
         <v>347</v>
       </c>
       <c r="N18" t="s">
@@ -51463,16 +51407,16 @@
       <c r="AP18" s="18">
         <v>0</v>
       </c>
-      <c r="AQ18" s="118" t="s">
+      <c r="AQ18" t="s">
         <v>350</v>
       </c>
-      <c r="AR18" s="118" t="s">
+      <c r="AR18" t="s">
         <v>234</v>
       </c>
-      <c r="AS18" s="119" t="s">
+      <c r="AS18" s="94" t="s">
         <v>350</v>
       </c>
-      <c r="AT18" s="118" t="s">
+      <c r="AT18" t="s">
         <v>73</v>
       </c>
       <c r="AU18" s="21">
@@ -51598,7 +51542,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:86" ht="15.6">
+    <row r="19" spans="1:86" ht="16">
       <c r="A19" t="s">
         <v>334</v>
       </c>
@@ -51632,7 +51576,7 @@
       <c r="L19">
         <v>9</v>
       </c>
-      <c r="M19" s="122" t="s">
+      <c r="M19" s="118" t="s">
         <v>347</v>
       </c>
       <c r="N19" t="s">
@@ -51722,16 +51666,16 @@
       <c r="AP19" s="18">
         <v>1</v>
       </c>
-      <c r="AQ19" s="118" t="s">
+      <c r="AQ19" t="s">
         <v>350</v>
       </c>
-      <c r="AR19" s="118" t="s">
+      <c r="AR19" t="s">
         <v>234</v>
       </c>
-      <c r="AS19" s="119" t="s">
+      <c r="AS19" s="94" t="s">
         <v>350</v>
       </c>
-      <c r="AT19" s="118" t="s">
+      <c r="AT19" t="s">
         <v>73</v>
       </c>
       <c r="AU19" s="21">
@@ -51857,7 +51801,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:86" s="102" customFormat="1" ht="15.6">
+    <row r="20" spans="1:86" s="102" customFormat="1" ht="16">
       <c r="A20" t="s">
         <v>334</v>
       </c>
@@ -51892,7 +51836,7 @@
       <c r="L20">
         <v>9</v>
       </c>
-      <c r="M20" s="122" t="s">
+      <c r="M20" s="118" t="s">
         <v>347</v>
       </c>
       <c r="N20" t="s">
@@ -51982,16 +51926,16 @@
       <c r="AP20" s="18">
         <v>0</v>
       </c>
-      <c r="AQ20" s="118" t="s">
+      <c r="AQ20" t="s">
         <v>350</v>
       </c>
-      <c r="AR20" s="118" t="s">
+      <c r="AR20" t="s">
         <v>234</v>
       </c>
-      <c r="AS20" s="119" t="s">
+      <c r="AS20" s="94" t="s">
         <v>350</v>
       </c>
-      <c r="AT20" s="118" t="s">
+      <c r="AT20" t="s">
         <v>73</v>
       </c>
       <c r="AU20" s="21">
@@ -52119,7 +52063,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:86" s="102" customFormat="1" ht="15.6">
+    <row r="21" spans="1:86" s="102" customFormat="1" ht="16">
       <c r="A21" t="s">
         <v>334</v>
       </c>
@@ -52154,7 +52098,7 @@
       <c r="L21">
         <v>9</v>
       </c>
-      <c r="M21" s="122" t="s">
+      <c r="M21" s="118" t="s">
         <v>347</v>
       </c>
       <c r="N21" t="s">
@@ -52244,16 +52188,16 @@
       <c r="AP21" s="18">
         <v>0</v>
       </c>
-      <c r="AQ21" s="118" t="s">
+      <c r="AQ21" t="s">
         <v>350</v>
       </c>
-      <c r="AR21" s="118" t="s">
+      <c r="AR21" t="s">
         <v>234</v>
       </c>
-      <c r="AS21" s="119" t="s">
+      <c r="AS21" s="94" t="s">
         <v>350</v>
       </c>
-      <c r="AT21" s="118" t="s">
+      <c r="AT21" t="s">
         <v>73</v>
       </c>
       <c r="AU21" s="21">
@@ -52381,7 +52325,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:86" s="102" customFormat="1" ht="15.6">
+    <row r="22" spans="1:86" s="102" customFormat="1" ht="16">
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
@@ -52643,7 +52587,7 @@
         <v>5.00751126690035E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:86" ht="15.6">
+    <row r="23" spans="1:86" ht="16">
       <c r="A23" s="11" t="s">
         <v>68</v>
       </c>
@@ -52903,7 +52847,7 @@
         <v>5.00751126690035E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:86" ht="15.6">
+    <row r="24" spans="1:86" ht="16">
       <c r="A24" s="11" t="s">
         <v>68</v>
       </c>
@@ -52914,7 +52858,7 @@
       <c r="D24" s="97">
         <v>144</v>
       </c>
-      <c r="E24" s="123" t="s">
+      <c r="E24" s="119" t="s">
         <v>303</v>
       </c>
       <c r="F24" s="96">
@@ -53162,7 +53106,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="25" spans="1:86" ht="15.6">
+    <row r="25" spans="1:86" ht="16">
       <c r="A25" s="11" t="s">
         <v>68</v>
       </c>
@@ -53173,7 +53117,7 @@
       <c r="D25" s="97">
         <v>144</v>
       </c>
-      <c r="E25" s="123" t="s">
+      <c r="E25" s="119" t="s">
         <v>303</v>
       </c>
       <c r="F25" s="96">
@@ -53421,7 +53365,7 @@
         <v>5.1416525271222172E-5</v>
       </c>
     </row>
-    <row r="26" spans="1:86" ht="15.6">
+    <row r="26" spans="1:86" ht="16">
       <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
@@ -53680,7 +53624,7 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:86" s="104" customFormat="1" ht="15.6">
+    <row r="27" spans="1:86" s="104" customFormat="1" ht="16">
       <c r="A27" s="11" t="s">
         <v>68</v>
       </c>
@@ -53942,7 +53886,7 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:86" s="108" customFormat="1" ht="15.6">
+    <row r="28" spans="1:86" s="108" customFormat="1" ht="16">
       <c r="A28" s="11" t="s">
         <v>68</v>
       </c>
@@ -54204,7 +54148,7 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:86" s="108" customFormat="1" ht="15.6">
+    <row r="29" spans="1:86" s="108" customFormat="1" ht="16">
       <c r="A29" s="11" t="s">
         <v>68</v>
       </c>
@@ -54466,7 +54410,7 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:86" s="108" customFormat="1" ht="15.6">
+    <row r="30" spans="1:86" s="108" customFormat="1" ht="16">
       <c r="A30" s="11" t="s">
         <v>68</v>
       </c>
@@ -55370,16 +55314,16 @@
       <c r="AP33" s="18">
         <v>0</v>
       </c>
-      <c r="AQ33" s="118" t="s">
+      <c r="AQ33" t="s">
         <v>341</v>
       </c>
-      <c r="AR33" s="118" t="s">
+      <c r="AR33" t="s">
         <v>234</v>
       </c>
-      <c r="AS33" s="119" t="s">
+      <c r="AS33" s="94" t="s">
         <v>342</v>
       </c>
-      <c r="AT33" s="118" t="s">
+      <c r="AT33" t="s">
         <v>73</v>
       </c>
       <c r="AU33" s="21">
@@ -55505,7 +55449,7 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:86" ht="15.6">
+    <row r="34" spans="1:86" ht="16">
       <c r="A34" t="s">
         <v>334</v>
       </c>
@@ -55629,16 +55573,16 @@
       <c r="AP34" s="18">
         <v>0</v>
       </c>
-      <c r="AQ34" s="118" t="s">
+      <c r="AQ34" t="s">
         <v>341</v>
       </c>
-      <c r="AR34" s="118" t="s">
+      <c r="AR34" t="s">
         <v>234</v>
       </c>
-      <c r="AS34" s="119" t="s">
+      <c r="AS34" s="94" t="s">
         <v>342</v>
       </c>
-      <c r="AT34" s="118" t="s">
+      <c r="AT34" t="s">
         <v>73</v>
       </c>
       <c r="AU34" s="21">
@@ -55764,7 +55708,7 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:86" ht="15.6">
+    <row r="35" spans="1:86" ht="16">
       <c r="A35" t="s">
         <v>334</v>
       </c>
@@ -55888,16 +55832,16 @@
       <c r="AP35" s="18">
         <v>0</v>
       </c>
-      <c r="AQ35" s="118" t="s">
+      <c r="AQ35" t="s">
         <v>341</v>
       </c>
-      <c r="AR35" s="118" t="s">
+      <c r="AR35" t="s">
         <v>234</v>
       </c>
-      <c r="AS35" s="119" t="s">
+      <c r="AS35" s="94" t="s">
         <v>342</v>
       </c>
-      <c r="AT35" s="118" t="s">
+      <c r="AT35" t="s">
         <v>73</v>
       </c>
       <c r="AU35" s="21">
@@ -56023,7 +55967,7 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:86" ht="15.6">
+    <row r="36" spans="1:86" ht="16">
       <c r="A36" s="11" t="s">
         <v>68</v>
       </c>
@@ -56267,7 +56211,7 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:86" ht="15.6">
+    <row r="37" spans="1:86" ht="16">
       <c r="A37" s="11" t="s">
         <v>68</v>
       </c>
@@ -56511,7 +56455,7 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:86" ht="15.6">
+    <row r="38" spans="1:86" ht="16">
       <c r="A38" s="11" t="s">
         <v>68</v>
       </c>
@@ -56755,7 +56699,7 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:86" ht="15.6">
+    <row r="39" spans="1:86" ht="16">
       <c r="A39" s="11" t="s">
         <v>68</v>
       </c>
@@ -56999,7 +56943,7 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:86" ht="15.6">
+    <row r="40" spans="1:86" ht="16">
       <c r="A40" s="11" t="s">
         <v>68</v>
       </c>
@@ -57258,7 +57202,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:86" ht="15.6">
+    <row r="41" spans="1:86" ht="16">
       <c r="A41" s="11" t="s">
         <v>68</v>
       </c>
@@ -57517,7 +57461,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:86" ht="15.6">
+    <row r="42" spans="1:86" ht="16">
       <c r="A42" s="11" t="s">
         <v>68</v>
       </c>
@@ -57776,7 +57720,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="43" spans="1:86" ht="15.6">
+    <row r="43" spans="1:86" ht="16">
       <c r="A43" s="11" t="s">
         <v>68</v>
       </c>
@@ -58035,7 +57979,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:86" ht="15.6">
+    <row r="44" spans="1:86" ht="16">
       <c r="A44" s="11" t="s">
         <v>68</v>
       </c>
@@ -58294,7 +58238,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:86" ht="15.6">
+    <row r="45" spans="1:86" ht="16">
       <c r="A45" s="11" t="s">
         <v>68</v>
       </c>
@@ -58553,7 +58497,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:86" ht="15.6">
+    <row r="46" spans="1:86" ht="16">
       <c r="A46" s="11" t="s">
         <v>68</v>
       </c>
@@ -58812,7 +58756,7 @@
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:86" ht="15.6">
+    <row r="47" spans="1:86" ht="16">
       <c r="A47" s="11" t="s">
         <v>68</v>
       </c>
@@ -59071,7 +59015,7 @@
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:86" ht="15.6">
+    <row r="48" spans="1:86" ht="16">
       <c r="A48" s="11" t="s">
         <v>314</v>
       </c>
@@ -59331,7 +59275,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="49" spans="1:86" s="102" customFormat="1" ht="15.6">
+    <row r="49" spans="1:86" s="102" customFormat="1" ht="16">
       <c r="A49" s="11" t="s">
         <v>314</v>
       </c>
@@ -59593,7 +59537,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="50" spans="1:86" s="102" customFormat="1" ht="15.6">
+    <row r="50" spans="1:86" s="102" customFormat="1" ht="16">
       <c r="A50" s="11" t="s">
         <v>314</v>
       </c>
@@ -59855,7 +59799,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="51" spans="1:86" s="102" customFormat="1" ht="15.6">
+    <row r="51" spans="1:86" s="102" customFormat="1" ht="16">
       <c r="A51" s="11" t="s">
         <v>314</v>
       </c>
@@ -60117,7 +60061,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="52" spans="1:86" ht="15.6">
+    <row r="52" spans="1:86" ht="16">
       <c r="A52" s="11" t="s">
         <v>314</v>
       </c>
@@ -60376,7 +60320,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="53" spans="1:86" ht="15.6">
+    <row r="53" spans="1:86" ht="16">
       <c r="A53" s="11" t="s">
         <v>314</v>
       </c>
@@ -60635,7 +60579,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="54" spans="1:86" ht="15.6">
+    <row r="54" spans="1:86" ht="16">
       <c r="A54" s="11" t="s">
         <v>68</v>
       </c>
@@ -60894,7 +60838,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:86" ht="15.6">
+    <row r="55" spans="1:86" ht="16">
       <c r="A55" s="11" t="s">
         <v>68</v>
       </c>
@@ -61153,7 +61097,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:86" ht="15.6">
+    <row r="56" spans="1:86" ht="16">
       <c r="A56" s="11" t="s">
         <v>68</v>
       </c>
@@ -61412,7 +61356,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:86" ht="15.6">
+    <row r="57" spans="1:86" ht="16">
       <c r="A57" s="11" t="s">
         <v>68</v>
       </c>
@@ -61671,7 +61615,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:86" ht="15.6">
+    <row r="58" spans="1:86" ht="16">
       <c r="A58" s="11" t="s">
         <v>68</v>
       </c>
@@ -61930,7 +61874,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:86" ht="15.6">
+    <row r="59" spans="1:86" ht="16">
       <c r="A59" s="11" t="s">
         <v>68</v>
       </c>
@@ -62189,7 +62133,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:86" ht="15.6">
+    <row r="60" spans="1:86" ht="16">
       <c r="A60" s="11" t="s">
         <v>68</v>
       </c>
@@ -62448,7 +62392,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:86" ht="15.6">
+    <row r="61" spans="1:86" ht="16">
       <c r="A61" s="11" t="s">
         <v>68</v>
       </c>
@@ -62707,43 +62651,43 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:86" ht="15.6">
+    <row r="62" spans="1:86" ht="16">
       <c r="M62" s="18"/>
     </row>
-    <row r="63" spans="1:86" ht="15.6">
+    <row r="63" spans="1:86" ht="16">
       <c r="M63" s="18"/>
     </row>
-    <row r="64" spans="1:86" ht="15.6">
+    <row r="64" spans="1:86" ht="16">
       <c r="M64" s="18"/>
     </row>
-    <row r="65" spans="13:76" ht="15.6">
+    <row r="65" spans="13:76" ht="16">
       <c r="M65" s="18"/>
     </row>
-    <row r="66" spans="13:76" ht="15.6">
+    <row r="66" spans="13:76" ht="16">
       <c r="M66" s="18"/>
     </row>
-    <row r="67" spans="13:76" ht="15.6">
+    <row r="67" spans="13:76" ht="16">
       <c r="M67" s="18"/>
     </row>
-    <row r="68" spans="13:76" ht="15.6">
+    <row r="68" spans="13:76" ht="16">
       <c r="M68" s="18"/>
     </row>
-    <row r="69" spans="13:76" ht="15.6">
+    <row r="69" spans="13:76" ht="16">
       <c r="M69" s="18"/>
     </row>
-    <row r="70" spans="13:76" ht="15.6">
+    <row r="70" spans="13:76" ht="16">
       <c r="M70" s="18"/>
     </row>
     <row r="71" spans="13:76" ht="15.75" customHeight="1">
       <c r="M71" s="18"/>
       <c r="BX71" s="30"/>
     </row>
-    <row r="72" spans="13:76" ht="15.6">
+    <row r="72" spans="13:76" ht="16">
       <c r="M72" s="18"/>
       <c r="BA72" s="112"/>
       <c r="BB72" s="112"/>
     </row>
-    <row r="73" spans="13:76" ht="15.6">
+    <row r="73" spans="13:76" ht="16">
       <c r="M73" s="18"/>
       <c r="BA73" s="112"/>
       <c r="BB73" s="112"/>
@@ -62751,15 +62695,15 @@
     <row r="74" spans="13:76" ht="15.75" customHeight="1">
       <c r="M74" s="18"/>
     </row>
-    <row r="75" spans="13:76" ht="15.6">
+    <row r="75" spans="13:76" ht="16">
       <c r="M75" s="18"/>
       <c r="BA75" s="113"/>
       <c r="BB75" s="113"/>
     </row>
   </sheetData>
-  <autoFilter ref="AR1:AR70"/>
-  <sortState ref="A2:CH75">
-    <sortCondition ref="E1"/>
+  <autoFilter ref="AR1:AR70" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CH75">
+    <sortCondition ref="E1:E75"/>
   </sortState>
   <dataConsolidate/>
   <phoneticPr fontId="24" type="noConversion"/>
@@ -62774,25 +62718,25 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="603" yWindow="1085" count="7">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN27:AP30 AH31:AP42 AH7:AH8 AJ7:AP8 AH55:AP1048576 AL27 AH26:AK27 AL26:AP26 AH28:AL30 S15:S30 S1 U1 AH43:AQ54 U39:U1048576 S34:S1048576 U15:U35 AH15:AP25 AH1:AI1 AK1:AP1">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN27:AP30 AH31:AP42 AH7:AH8 AJ7:AP8 AH55:AP1048576 AL27 AH26:AK27 AL26:AP26 AH28:AL30 S15:S30 S1 U1 AH43:AQ54 U39:U1048576 S34:S1048576 U15:U35 AH15:AP25 AH1:AI1 AK1:AP1" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I30:I1048576 I15:I28">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I30:I1048576 I15:I28" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AD39:AF61 AG7:AG8 AG20:AG30 AD28:AF33 AD27:AE27 AD34:AE38 AG34:AG38 AH61 AD1:AG1 AD62:AG1048576 AD15:AF26"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y1:AC1 AI7:AI8 Y7:Y8 AA7:AE8 Y15:AC1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AD39:AF61 AG7:AG8 AG20:AG30 AD28:AF33 AD27:AE27 AD34:AE38 AG34:AG38 AH61 AD1:AG1 AD62:AG1048576 AD15:AF26" xr:uid="{00000000-0002-0000-0100-000002000000}"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y1:AC1 AI7:AI8 Y7:Y8 AA7:AE8 Y15:AC1048576" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN1 BO27:BO30 BO43:BO54 BN62:BN1048576"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AY55:AY61">
+    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN1 BO27:BO30 BO43:BO54 BN62:BN1048576" xr:uid="{00000000-0002-0000-0100-000004000000}"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AY55:AY61" xr:uid="{00000000-0002-0000-0100-000005000000}">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY31:AY42 AY15:AY25">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY31:AY42 AY15:AY25" xr:uid="{00000000-0002-0000-0100-000006000000}">
       <formula1>1</formula1>
       <formula2>3</formula2>
     </dataValidation>
@@ -62803,127 +62747,127 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="603" yWindow="1085" count="21">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000007000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>U1 U62:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000008000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>BU55:BW1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000009000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$C$2:$C$4</xm:f>
           </x14:formula1>
           <xm:sqref>BO1 BO55:BO1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000A000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$I$2:$I$3</xm:f>
           </x14:formula1>
           <xm:sqref>AV1 AV62:AV1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000B000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$9</xm:f>
           </x14:formula1>
           <xm:sqref>U1 S1 S55:S1048576 U62:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000C000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$K$2:$K$3</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1 S1 S55:S1048576 U62:W1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000D000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N$2:$N$7</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1 S1 S55:S1048576 U62:W1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000E000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$J$2:$J$12</xm:f>
           </x14:formula1>
           <xm:sqref>K1 K62:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000F000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$O:$O</xm:f>
           </x14:formula1>
           <xm:sqref>BT1 BT62:BT1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000010000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$S:$S</xm:f>
           </x14:formula1>
           <xm:sqref>G1 G62:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000011000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G:$G</xm:f>
           </x14:formula1>
           <xm:sqref>AR1 AR55:AR1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000012000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F:$F</xm:f>
           </x14:formula1>
           <xm:sqref>M76:M1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000013000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$P:$P</xm:f>
           </x14:formula1>
           <xm:sqref>AT1 AT55:AT1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000014000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D:$D</xm:f>
           </x14:formula1>
           <xm:sqref>U62:W1048576 S1 U1:W1 S55:S1048576 N55:N1048576 N1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000015000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N:$N</xm:f>
           </x14:formula1>
           <xm:sqref>O1 O55:O1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000016000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B:$B</xm:f>
           </x14:formula1>
           <xm:sqref>T1 T55:T1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000017000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$R:$R</xm:f>
           </x14:formula1>
           <xm:sqref>E1 E55:E1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000018000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H:$H</xm:f>
           </x14:formula1>
           <xm:sqref>U62:U1048576 U1 S1 S55:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000019000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$M:$M</xm:f>
           </x14:formula1>
           <xm:sqref>S1 P27:P30 P1 U1 S55:S1048576 P55:P1048576 U62:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00001A000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$10</xm:f>
           </x14:formula1>
           <xm:sqref>R1:R1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00001B000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H$1:$H$7</xm:f>
           </x14:formula1>
@@ -62936,72 +62880,72 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BJ18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.09765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.8984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.59765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.09765625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.09765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.09765625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.8984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.8984375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.8984375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.8984375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.59765625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.8984375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="17" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.8984375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="36.3984375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="36.33203125" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="29" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17.8984375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="21.8984375" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="20.09765625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="15" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.8984375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.83203125" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="23.8984375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.09765625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="33" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.8984375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.3984375" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17.8984375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="25.8984375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="35" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="26.3984375" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="63" max="64" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -65841,20 +65785,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:S99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="19.59765625" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18.09765625" style="26" customWidth="1"/>
+    <col min="7" max="7" width="18.1640625" style="26" customWidth="1"/>
     <col min="8" max="8" width="20.5" customWidth="1"/>
-    <col min="9" max="9" width="14.09765625" customWidth="1"/>
-    <col min="10" max="10" width="15.09765625" customWidth="1"/>
+    <col min="9" max="9" width="14.1640625" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" ht="17">
       <c r="A1" t="s">
         <v>427</v>
       </c>
@@ -65910,7 +65854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="31.2">
+    <row r="2" spans="1:19" ht="34">
       <c r="A2">
         <v>0</v>
       </c>
@@ -65966,7 +65910,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="31.2">
+    <row r="3" spans="1:19" ht="34">
       <c r="A3">
         <v>1</v>
       </c>
@@ -66022,7 +65966,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="46.8">
+    <row r="4" spans="1:19" ht="51">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -66072,7 +66016,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="46.8">
+    <row r="5" spans="1:19" ht="51">
       <c r="D5" t="s">
         <v>448</v>
       </c>
@@ -67073,7 +67017,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="R2:S91">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="R2:S91">
     <sortCondition ref="R2:R91"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/appliances_wtp.xlsx
+++ b/appliances_wtp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10709"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianadanilenko/Desktop/appliances_interventions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00474439-B32A-ED46-A70E-6F6448442B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01760F0C-6BB2-9C4B-8327-CB28535CB3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5280" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4086" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4106" uniqueCount="656">
   <si>
     <t>Coder</t>
   </si>
@@ -2520,6 +2520,18 @@
   <si>
     <t>WTP for top-rated appliance in presence of a label compared to no label</t>
   </si>
+  <si>
+    <t>WTP for efficient appliance compared to existing appliance</t>
+  </si>
+  <si>
+    <t>WTP for efficient appliance in presence of a label compared to no label</t>
+  </si>
+  <si>
+    <t>baseline is the current EnergyGuide label</t>
+  </si>
+  <si>
+    <t>label compared to no label</t>
+  </si>
 </sst>
 </file>
 
@@ -3010,7 +3022,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3158,7 +3170,11 @@
     <xf numFmtId="2" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="36" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -50823,13 +50839,13 @@
       <c r="D16" s="11">
         <v>104</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="54" t="s">
         <v>220</v>
       </c>
       <c r="F16" s="11">
         <v>2011</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="119" t="s">
         <v>221</v>
       </c>
       <c r="H16" t="s">
@@ -51076,6 +51092,9 @@
       <c r="A17" t="s">
         <v>332</v>
       </c>
+      <c r="B17" s="11" t="s">
+        <v>652</v>
+      </c>
       <c r="C17" s="94">
         <v>1261</v>
       </c>
@@ -51335,6 +51354,9 @@
       <c r="A18" t="s">
         <v>332</v>
       </c>
+      <c r="B18" s="11" t="s">
+        <v>652</v>
+      </c>
       <c r="C18" s="94">
         <v>1262</v>
       </c>
@@ -51594,6 +51616,9 @@
       <c r="A19" t="s">
         <v>332</v>
       </c>
+      <c r="B19" s="11" t="s">
+        <v>652</v>
+      </c>
       <c r="C19" s="94">
         <v>1263</v>
       </c>
@@ -51853,7 +51878,9 @@
       <c r="A20" t="s">
         <v>332</v>
       </c>
-      <c r="B20"/>
+      <c r="B20" s="11" t="s">
+        <v>652</v>
+      </c>
       <c r="C20" s="94">
         <v>1264</v>
       </c>
@@ -52115,7 +52142,9 @@
       <c r="A21" t="s">
         <v>332</v>
       </c>
-      <c r="B21"/>
+      <c r="B21" s="11" t="s">
+        <v>652</v>
+      </c>
       <c r="C21" s="94">
         <v>1265</v>
       </c>
@@ -52377,7 +52406,9 @@
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="11"/>
+      <c r="B22" s="11" t="s">
+        <v>653</v>
+      </c>
       <c r="C22" s="96">
         <v>1155</v>
       </c>
@@ -52639,7 +52670,9 @@
       <c r="A23" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="11"/>
+      <c r="B23" s="11" t="s">
+        <v>653</v>
+      </c>
       <c r="C23" s="96">
         <v>1156</v>
       </c>
@@ -52906,7 +52939,7 @@
       <c r="D24" s="97">
         <v>144</v>
       </c>
-      <c r="E24" s="119" t="s">
+      <c r="E24" s="120" t="s">
         <v>301</v>
       </c>
       <c r="F24" s="96">
@@ -53165,7 +53198,7 @@
       <c r="D25" s="97">
         <v>144</v>
       </c>
-      <c r="E25" s="119" t="s">
+      <c r="E25" s="120" t="s">
         <v>301</v>
       </c>
       <c r="F25" s="96">
@@ -53417,7 +53450,9 @@
       <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="11"/>
+      <c r="B26" s="11" t="s">
+        <v>654</v>
+      </c>
       <c r="C26" s="96">
         <v>1180</v>
       </c>
@@ -53676,7 +53711,9 @@
       <c r="A27" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="11"/>
+      <c r="B27" s="11" t="s">
+        <v>654</v>
+      </c>
       <c r="C27" s="96">
         <v>1181</v>
       </c>
@@ -53938,7 +53975,9 @@
       <c r="A28" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="11"/>
+      <c r="B28" s="11" t="s">
+        <v>654</v>
+      </c>
       <c r="C28" s="96">
         <v>1182</v>
       </c>
@@ -54200,7 +54239,9 @@
       <c r="A29" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="11"/>
+      <c r="B29" s="11" t="s">
+        <v>654</v>
+      </c>
       <c r="C29" s="96">
         <v>1183</v>
       </c>
@@ -54462,7 +54503,9 @@
       <c r="A30" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="11"/>
+      <c r="B30" s="11" t="s">
+        <v>654</v>
+      </c>
       <c r="C30" s="96">
         <v>1184</v>
       </c>
@@ -54724,7 +54767,9 @@
       <c r="A31" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="11"/>
+      <c r="B31" s="11" t="s">
+        <v>654</v>
+      </c>
       <c r="C31" s="96">
         <v>1185</v>
       </c>
@@ -54983,7 +55028,9 @@
       <c r="A32" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="11"/>
+      <c r="B32" s="11" t="s">
+        <v>654</v>
+      </c>
       <c r="C32" s="96">
         <v>1186</v>
       </c>
@@ -55248,7 +55295,7 @@
       <c r="D33" s="11">
         <v>404</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="41" t="s">
         <v>333</v>
       </c>
       <c r="F33" s="11">
@@ -55724,11 +55771,11 @@
         <v>0.13262227273834529</v>
       </c>
       <c r="BY34" s="30">
-        <f t="shared" ref="BY34:BY65" si="14">0.5*LN((1+BX34)/(1-BX34))</f>
+        <f t="shared" ref="BY34:BY61" si="14">0.5*LN((1+BX34)/(1-BX34))</f>
         <v>0.13340813257086698</v>
       </c>
       <c r="BZ34" s="30">
-        <f t="shared" ref="BZ34:BZ65" si="15">((1-(BY34^2)^2)/(BI34-1))</f>
+        <f t="shared" ref="BZ34:BZ61" si="15">((1-(BY34^2)^2)/(BI34-1))</f>
         <v>4.6281631519105703E-3</v>
       </c>
       <c r="CA34" s="30">
@@ -55744,11 +55791,11 @@
         <v>6.6752883376554634E-2</v>
       </c>
       <c r="CF34" s="30">
-        <f t="shared" ref="CF34:CF65" si="18">0.5*LN((1+CE34)/(1-CE34))</f>
+        <f t="shared" ref="CF34:CF61" si="18">0.5*LN((1+CE34)/(1-CE34))</f>
         <v>6.6852298418384234E-2</v>
       </c>
       <c r="CG34" s="30">
-        <f t="shared" ref="CG34:CG65" si="19">((1-(CF34^2)^2)/(BJ34-1))</f>
+        <f t="shared" ref="CG34:CG61" si="19">((1-(CF34^2)^2)/(BJ34-1))</f>
         <v>1.1533794994059523E-3</v>
       </c>
       <c r="CH34" s="30">
@@ -56026,7 +56073,7 @@
       <c r="D36" s="97">
         <v>143</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E36" s="121" t="s">
         <v>294</v>
       </c>
       <c r="F36" s="96">
@@ -56995,7 +57042,9 @@
       <c r="A40" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="11"/>
+      <c r="B40" s="11" t="s">
+        <v>655</v>
+      </c>
       <c r="C40" s="94">
         <v>1122</v>
       </c>
@@ -57254,7 +57303,9 @@
       <c r="A41" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B41" s="11"/>
+      <c r="B41" s="11" t="s">
+        <v>655</v>
+      </c>
       <c r="C41" s="94">
         <v>1123</v>
       </c>
@@ -57513,7 +57564,9 @@
       <c r="A42" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="11"/>
+      <c r="B42" s="11" t="s">
+        <v>655</v>
+      </c>
       <c r="C42" s="94">
         <v>1124</v>
       </c>
@@ -57772,7 +57825,9 @@
       <c r="A43" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B43" s="11"/>
+      <c r="B43" s="11" t="s">
+        <v>655</v>
+      </c>
       <c r="C43" s="94">
         <v>1125</v>
       </c>
@@ -58031,7 +58086,9 @@
       <c r="A44" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B44" s="11"/>
+      <c r="B44" s="11" t="s">
+        <v>655</v>
+      </c>
       <c r="C44" s="94">
         <v>1126</v>
       </c>
@@ -58290,7 +58347,9 @@
       <c r="A45" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B45" s="11"/>
+      <c r="B45" s="11" t="s">
+        <v>655</v>
+      </c>
       <c r="C45" s="94">
         <v>1127</v>
       </c>
@@ -58556,7 +58615,7 @@
       <c r="D46">
         <v>118</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="41" t="s">
         <v>254</v>
       </c>
       <c r="F46" s="11">
@@ -60638,7 +60697,7 @@
       <c r="D54" s="97">
         <v>141</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="41" t="s">
         <v>275</v>
       </c>
       <c r="F54" s="96">

--- a/appliances_wtp.xlsx
+++ b/appliances_wtp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianadanilenko/Desktop/appliances_interventions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01760F0C-6BB2-9C4B-8327-CB28535CB3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8BA5A3-9C91-C44C-985A-BE33BC056F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5280" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3022,7 +3022,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3170,7 +3170,6 @@
     <xf numFmtId="2" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="36" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -35021,7 +35020,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -50845,7 +50844,7 @@
       <c r="F16" s="11">
         <v>2011</v>
       </c>
-      <c r="G16" s="119" t="s">
+      <c r="G16" t="s">
         <v>221</v>
       </c>
       <c r="H16" t="s">
@@ -52939,7 +52938,7 @@
       <c r="D24" s="97">
         <v>144</v>
       </c>
-      <c r="E24" s="120" t="s">
+      <c r="E24" s="119" t="s">
         <v>301</v>
       </c>
       <c r="F24" s="96">
@@ -53198,7 +53197,7 @@
       <c r="D25" s="97">
         <v>144</v>
       </c>
-      <c r="E25" s="120" t="s">
+      <c r="E25" s="119" t="s">
         <v>301</v>
       </c>
       <c r="F25" s="96">
@@ -56073,7 +56072,7 @@
       <c r="D36" s="97">
         <v>143</v>
       </c>
-      <c r="E36" s="121" t="s">
+      <c r="E36" s="120" t="s">
         <v>294</v>
       </c>
       <c r="F36" s="96">

--- a/appliances_wtp.xlsx
+++ b/appliances_wtp.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10709"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianadanilenko/Desktop/appliances_interventions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dand\Documents\GitHub\appliances_interventions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8BA5A3-9C91-C44C-985A-BE33BC056F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5280" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5280" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -22,9 +21,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Appliances!$AR$1:$AR$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Usage!$A$1:$BN$53</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="3" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,35 +45,62 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={73C2226C-6106-4DC2-88CF-9C0A06F48311}</author>
     <author>tc={CEE78422-255C-40DC-AFED-5AA185CC03E1}</author>
     <author>tc={C7CEED71-5EFE-4791-84D8-7010C40A69F0}</author>
   </authors>
   <commentList>
-    <comment ref="AQ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="AQ1" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     is this supposed to capture mean difference between control and treatment or ?</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="AZ1" authorId="1" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     daily kWh</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AQ22" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="AQ22" authorId="2" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     in kWh</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -82,26 +108,44 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={1DD52412-77C6-1E43-B8CC-07AD562D2C6E}</author>
     <author>tc={52E723F4-9A55-1E46-88F7-D2164B4696BA}</author>
   </authors>
   <commentList>
-    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="AA1" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     check label studies from srmt for label type</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AR23" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="AR23" authorId="1" shapeId="0">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     can we code them as relative WTP? </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -109,19 +153,28 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={CF36070F-7893-4948-8AB8-1CADF6EBBFD9}</author>
   </authors>
   <commentList>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="D6" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     a bit confused as of where it’s correlation and where - quasi-experimental
 Reply:
     the way i reassessed this was - market statistics - correlation, whereas hypothetical choice - quasi-experimental</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -129,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4106" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4132" uniqueCount="662">
   <si>
     <t>Coder</t>
   </si>
@@ -2532,11 +2585,29 @@
   <si>
     <t>label compared to no label</t>
   </si>
+  <si>
+    <t>WTP for ENERGY STAR appliance compared to no label</t>
+  </si>
+  <si>
+    <t>WTP before and after an information message</t>
+  </si>
+  <si>
+    <t>WTP for ES appliance in presence of rebate compared to no rebate</t>
+  </si>
+  <si>
+    <t>WTP for A+ appliance in presence of a label compared to A</t>
+  </si>
+  <si>
+    <t>WTP for labelled compared to not labelled appliance</t>
+  </si>
+  <si>
+    <t>WTP for labelled appliance in presence compared to absence of information</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
@@ -3022,7 +3093,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3150,7 +3221,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
@@ -3170,16 +3240,19 @@
     <xf numFmtId="2" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="36" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -3223,7 +3296,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:CD1048576" sheet="Appliances"/>
   </cacheSource>
@@ -35020,7 +35093,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -35875,57 +35948,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BP53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.1640625" customWidth="1"/>
-    <col min="7" max="7" width="16.1640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="16.125" customWidth="1"/>
+    <col min="8" max="8" width="16.625" customWidth="1"/>
+    <col min="10" max="10" width="18.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" hidden="1" customWidth="1"/>
     <col min="12" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="16" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="12.1640625" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="12.125" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="0" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="0" style="12" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="18.6640625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.6640625" style="7" customWidth="1"/>
-    <col min="30" max="30" width="13.6640625" customWidth="1"/>
-    <col min="31" max="31" width="14.6640625" customWidth="1"/>
-    <col min="32" max="32" width="13.6640625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="19.1640625" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="10.6640625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="13.1640625" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="22.1640625" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="10.6640625" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="18.1640625" customWidth="1"/>
-    <col min="39" max="39" width="14.1640625" customWidth="1"/>
-    <col min="40" max="40" width="9.6640625" customWidth="1"/>
-    <col min="41" max="41" width="19.1640625" customWidth="1"/>
-    <col min="42" max="42" width="12.1640625" customWidth="1"/>
+    <col min="27" max="27" width="18.625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.625" style="7" customWidth="1"/>
+    <col min="30" max="30" width="13.625" customWidth="1"/>
+    <col min="31" max="31" width="14.625" customWidth="1"/>
+    <col min="32" max="32" width="13.625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="19.125" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="10.625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="13.125" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="22.125" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="10.625" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="18.125" customWidth="1"/>
+    <col min="39" max="39" width="14.125" customWidth="1"/>
+    <col min="40" max="40" width="9.625" customWidth="1"/>
+    <col min="41" max="41" width="19.125" customWidth="1"/>
+    <col min="42" max="42" width="12.125" customWidth="1"/>
     <col min="44" max="45" width="0" hidden="1" customWidth="1"/>
-    <col min="46" max="47" width="13.1640625" hidden="1" customWidth="1"/>
+    <col min="46" max="47" width="13.125" hidden="1" customWidth="1"/>
     <col min="48" max="51" width="0" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="13.6640625" style="17" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="13.625" style="17" hidden="1" customWidth="1"/>
     <col min="53" max="53" width="26.5" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="20.6640625" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="20.625" hidden="1" customWidth="1"/>
     <col min="55" max="55" width="0" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="17.6640625" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="16.1640625" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="15.1640625" hidden="1" customWidth="1"/>
-    <col min="59" max="59" width="20.6640625" hidden="1" customWidth="1"/>
-    <col min="60" max="60" width="24.6640625" hidden="1" customWidth="1"/>
-    <col min="61" max="61" width="19.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="24.1640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.625" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="16.125" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="15.125" hidden="1" customWidth="1"/>
+    <col min="59" max="59" width="20.625" hidden="1" customWidth="1"/>
+    <col min="60" max="60" width="24.625" hidden="1" customWidth="1"/>
+    <col min="61" max="61" width="19.625" style="30" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="24.125" style="30" bestFit="1" customWidth="1"/>
     <col min="63" max="65" width="11" style="30"/>
-    <col min="67" max="67" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="25.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="48">
+    <row r="1" spans="1:68" ht="45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -43723,7 +43796,7 @@
         <v>6.7567567567567571E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:66" s="41" customFormat="1" ht="17">
+    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A39" s="45" t="s">
         <v>68</v>
       </c>
@@ -43928,7 +44001,7 @@
       </c>
       <c r="BN39" s="43"/>
     </row>
-    <row r="40" spans="1:66" s="41" customFormat="1" ht="17">
+    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A40" s="45" t="s">
         <v>68</v>
       </c>
@@ -44133,7 +44206,7 @@
       </c>
       <c r="BN40" s="43"/>
     </row>
-    <row r="41" spans="1:66" s="41" customFormat="1" ht="17">
+    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A41" s="45" t="s">
         <v>68</v>
       </c>
@@ -44342,7 +44415,7 @@
         <v>2.0421052631578922</v>
       </c>
     </row>
-    <row r="42" spans="1:66" s="41" customFormat="1" ht="17">
+    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A42" s="45" t="s">
         <v>68</v>
       </c>
@@ -46739,34 +46812,34 @@
   </sheetData>
   <dataConsolidate/>
   <dataValidations count="10">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12">
       <formula1>$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12">
       <formula1>$D$2:$D$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51">
       <formula1>$D$2:$D$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51">
       <formula1>$F$2:$F$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -46775,43 +46848,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>BC23:BC28 BC54:BC1048576 BC33:BC38 BC1:BC12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$9</xm:f>
           </x14:formula1>
           <xm:sqref>J54:J1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>AS43:AX51 AS54:AX1048576 AS23:AX38 AS2:AX12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$10</xm:f>
           </x14:formula1>
           <xm:sqref>J38</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$E$2:$E$4</xm:f>
           </x14:formula1>
           <xm:sqref>AO43:AO51</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$6</xm:f>
           </x14:formula1>
           <xm:sqref>K54:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$7</xm:f>
           </x14:formula1>
@@ -46824,63 +46897,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CH75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="5" max="5" width="24.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" customWidth="1"/>
+    <col min="2" max="2" width="136" customWidth="1"/>
+    <col min="5" max="5" width="24.625" customWidth="1"/>
+    <col min="6" max="6" width="17.625" customWidth="1"/>
+    <col min="7" max="7" width="14.125" customWidth="1"/>
     <col min="8" max="8" width="16.5" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16.1640625" customWidth="1"/>
-    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.1640625" customWidth="1"/>
+    <col min="10" max="10" width="16.125" customWidth="1"/>
+    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.125" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="14.6640625" customWidth="1"/>
-    <col min="17" max="17" width="13.1640625" customWidth="1"/>
+    <col min="16" max="16" width="14.625" customWidth="1"/>
+    <col min="17" max="17" width="13.125" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="14.1640625" customWidth="1"/>
+    <col min="19" max="19" width="14.125" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="21.1640625" customWidth="1"/>
+    <col min="21" max="21" width="21.125" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.6640625" customWidth="1"/>
+    <col min="23" max="23" width="14.625" customWidth="1"/>
     <col min="24" max="24" width="12.5" customWidth="1"/>
     <col min="25" max="33" width="11" customWidth="1"/>
     <col min="34" max="35" width="16" customWidth="1"/>
     <col min="36" max="39" width="11" customWidth="1"/>
-    <col min="40" max="41" width="12.1640625" customWidth="1"/>
+    <col min="40" max="41" width="12.125" customWidth="1"/>
     <col min="42" max="42" width="11" customWidth="1"/>
-    <col min="43" max="43" width="27.6640625" customWidth="1"/>
-    <col min="44" max="44" width="41.1640625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="54.6640625" customWidth="1"/>
+    <col min="43" max="43" width="27.625" customWidth="1"/>
+    <col min="44" max="44" width="41.125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="54.625" customWidth="1"/>
     <col min="46" max="46" width="21" customWidth="1"/>
-    <col min="47" max="47" width="26.6640625" style="7" customWidth="1"/>
-    <col min="48" max="48" width="14.1640625" style="7" customWidth="1"/>
-    <col min="49" max="49" width="13.1640625" customWidth="1"/>
-    <col min="50" max="50" width="9.6640625" customWidth="1"/>
+    <col min="47" max="47" width="26.625" style="7" customWidth="1"/>
+    <col min="48" max="48" width="14.125" style="7" customWidth="1"/>
+    <col min="49" max="49" width="13.125" customWidth="1"/>
+    <col min="50" max="50" width="9.625" customWidth="1"/>
     <col min="51" max="51" width="17" customWidth="1"/>
     <col min="52" max="52" width="9"/>
-    <col min="53" max="54" width="14.1640625" customWidth="1"/>
-    <col min="55" max="55" width="13.6640625" customWidth="1"/>
-    <col min="56" max="56" width="12.6640625" customWidth="1"/>
-    <col min="57" max="57" width="10.6640625" customWidth="1"/>
+    <col min="53" max="54" width="14.125" customWidth="1"/>
+    <col min="55" max="55" width="13.625" customWidth="1"/>
+    <col min="56" max="56" width="12.625" customWidth="1"/>
+    <col min="57" max="57" width="10.625" customWidth="1"/>
     <col min="58" max="58" width="13" customWidth="1"/>
-    <col min="59" max="60" width="10.6640625" customWidth="1"/>
-    <col min="61" max="62" width="11.1640625" customWidth="1"/>
+    <col min="59" max="60" width="10.625" customWidth="1"/>
+    <col min="61" max="62" width="11.125" customWidth="1"/>
     <col min="63" max="64" width="11" customWidth="1"/>
-    <col min="65" max="65" width="12.6640625" customWidth="1"/>
-    <col min="66" max="66" width="18.1640625" customWidth="1"/>
-    <col min="67" max="67" width="22.1640625" customWidth="1"/>
-    <col min="68" max="68" width="15.1640625" customWidth="1"/>
+    <col min="65" max="65" width="12.625" customWidth="1"/>
+    <col min="66" max="66" width="18.125" customWidth="1"/>
+    <col min="67" max="67" width="22.125" customWidth="1"/>
+    <col min="68" max="68" width="15.125" customWidth="1"/>
     <col min="69" max="69" width="18" customWidth="1"/>
-    <col min="70" max="70" width="17.1640625" customWidth="1"/>
-    <col min="71" max="71" width="21.1640625" customWidth="1"/>
-    <col min="72" max="72" width="10.1640625" customWidth="1"/>
+    <col min="70" max="70" width="17.125" customWidth="1"/>
+    <col min="71" max="71" width="21.125" customWidth="1"/>
+    <col min="72" max="72" width="10.125" customWidth="1"/>
     <col min="73" max="73" width="13" customWidth="1"/>
     <col min="74" max="74" width="14" customWidth="1"/>
-    <col min="75" max="75" width="13.1640625" customWidth="1"/>
+    <col min="75" max="75" width="13.125" customWidth="1"/>
     <col min="82" max="82" width="24" customWidth="1"/>
   </cols>
   <sheetData>
@@ -46921,7 +46995,7 @@
       <c r="L1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="117" t="s">
+      <c r="M1" s="116" t="s">
         <v>9</v>
       </c>
       <c r="N1" s="64" t="s">
@@ -47144,7 +47218,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="2" spans="1:86" ht="16">
+    <row r="2" spans="1:86">
       <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
@@ -47289,7 +47363,7 @@
       <c r="AV2" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AW2" s="105">
+      <c r="AW2" s="104">
         <v>0.32</v>
       </c>
       <c r="AX2" s="18">
@@ -47369,15 +47443,15 @@
       <c r="BW2">
         <v>1</v>
       </c>
-      <c r="BX2" s="103">
+      <c r="BX2" s="102">
         <f t="shared" ref="BX2:BX33" si="0">((AZ2^2)/(AZ2^2+BI2))^(1/2)</f>
         <v>2.4066942415906588E-2</v>
       </c>
-      <c r="BY2" s="103">
+      <c r="BY2" s="102">
         <f t="shared" ref="BY2:BY33" si="1">0.5*LN((1+BX2)/(1-BX2))</f>
         <v>2.4071590697916326E-2</v>
       </c>
-      <c r="BZ2" s="103">
+      <c r="BZ2" s="102">
         <f t="shared" ref="BZ2:BZ33" si="2">((1-(BY2^2)^2)/(BI2-1))</f>
         <v>2.9940109708011158E-3</v>
       </c>
@@ -47406,7 +47480,7 @@
         <v>3.0120481927710845E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:86" ht="16">
+    <row r="3" spans="1:86">
       <c r="A3" s="11" t="s">
         <v>68</v>
       </c>
@@ -47551,7 +47625,7 @@
       <c r="AV3" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AW3" s="105">
+      <c r="AW3" s="104">
         <v>0.34499999999999997</v>
       </c>
       <c r="AX3" s="18">
@@ -47632,15 +47706,15 @@
       <c r="BW3">
         <v>1</v>
       </c>
-      <c r="BX3" s="103">
+      <c r="BX3" s="102">
         <f t="shared" si="0"/>
         <v>0.18088754235543161</v>
       </c>
-      <c r="BY3" s="103">
+      <c r="BY3" s="102">
         <f t="shared" si="1"/>
         <v>0.18290010196181533</v>
       </c>
-      <c r="BZ3" s="103">
+      <c r="BZ3" s="102">
         <f t="shared" si="2"/>
         <v>2.2753552022091081E-3</v>
       </c>
@@ -47669,7 +47743,7 @@
         <v>2.2883295194508009E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:86" ht="16">
+    <row r="4" spans="1:86">
       <c r="A4" t="s">
         <v>332</v>
       </c>
@@ -47894,15 +47968,15 @@
       <c r="BW4">
         <v>0</v>
       </c>
-      <c r="BX4" s="103">
+      <c r="BX4" s="102">
         <f t="shared" si="0"/>
         <v>0.19885033588999154</v>
       </c>
-      <c r="BY4" s="103">
+      <c r="BY4" s="102">
         <f t="shared" si="1"/>
         <v>0.20153527346528599</v>
       </c>
-      <c r="BZ4" s="103">
+      <c r="BZ4" s="102">
         <f t="shared" si="2"/>
         <v>6.0875018454454692E-3</v>
       </c>
@@ -47931,7 +48005,7 @@
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:86" s="102" customFormat="1" ht="16">
+    <row r="5" spans="1:86" s="101" customFormat="1">
       <c r="A5" t="s">
         <v>332</v>
       </c>
@@ -48156,15 +48230,15 @@
       <c r="BW5">
         <v>0</v>
       </c>
-      <c r="BX5" s="103">
+      <c r="BX5" s="102">
         <f t="shared" si="0"/>
         <v>0.15193954642337751</v>
       </c>
-      <c r="BY5" s="103">
+      <c r="BY5" s="102">
         <f t="shared" si="1"/>
         <v>0.15312521998491627</v>
       </c>
-      <c r="BZ5" s="103">
+      <c r="BZ5" s="102">
         <f t="shared" si="2"/>
         <v>6.0942086742402533E-3</v>
       </c>
@@ -48195,7 +48269,7 @@
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:86" ht="16">
+    <row r="6" spans="1:86">
       <c r="A6" t="s">
         <v>332</v>
       </c>
@@ -48420,15 +48494,15 @@
       <c r="BW6">
         <v>0</v>
       </c>
-      <c r="BX6" s="103">
+      <c r="BX6" s="102">
         <f t="shared" si="0"/>
         <v>0.19885033588999154</v>
       </c>
-      <c r="BY6" s="103">
+      <c r="BY6" s="102">
         <f t="shared" si="1"/>
         <v>0.20153527346528599</v>
       </c>
-      <c r="BZ6" s="103">
+      <c r="BZ6" s="102">
         <f t="shared" si="2"/>
         <v>6.0875018454454692E-3</v>
       </c>
@@ -48457,7 +48531,7 @@
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:86" s="99" customFormat="1" ht="17" customHeight="1">
+    <row r="7" spans="1:86" s="99" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A7" t="s">
         <v>332</v>
       </c>
@@ -48682,15 +48756,15 @@
       <c r="BW7">
         <v>0</v>
       </c>
-      <c r="BX7" s="103">
+      <c r="BX7" s="102">
         <f t="shared" si="0"/>
         <v>0.15193954642337751</v>
       </c>
-      <c r="BY7" s="103">
+      <c r="BY7" s="102">
         <f t="shared" si="1"/>
         <v>0.15312521998491627</v>
       </c>
-      <c r="BZ7" s="103">
+      <c r="BZ7" s="102">
         <f t="shared" si="2"/>
         <v>6.0942086742402533E-3</v>
       </c>
@@ -48721,7 +48795,7 @@
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:86" s="99" customFormat="1" ht="17" customHeight="1">
+    <row r="8" spans="1:86" s="99" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A8" s="100" t="s">
         <v>68</v>
       </c>
@@ -49511,7 +49585,7 @@
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:86" ht="16">
+    <row r="11" spans="1:86">
       <c r="A11" s="11" t="s">
         <v>312</v>
       </c>
@@ -50563,7 +50637,7 @@
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:86" ht="16">
+    <row r="15" spans="1:86">
       <c r="A15" s="100" t="s">
         <v>312</v>
       </c>
@@ -50702,13 +50776,13 @@
       <c r="AT15" s="100" t="s">
         <v>235</v>
       </c>
-      <c r="AU15" s="105">
+      <c r="AU15" s="104">
         <v>0.156</v>
       </c>
       <c r="AV15" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AW15" s="106">
+      <c r="AW15" s="105">
         <f>AZ15/ABS(_xlfn.T.INV.2T(AX15,CC15))</f>
         <v>1</v>
       </c>
@@ -50827,18 +50901,20 @@
         <v>3.1746031746031746E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:86" ht="16">
+    <row r="16" spans="1:86">
       <c r="A16" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="11"/>
+      <c r="B16" s="100" t="s">
+        <v>659</v>
+      </c>
       <c r="C16" s="11">
         <v>1013</v>
       </c>
       <c r="D16" s="11">
         <v>104</v>
       </c>
-      <c r="E16" s="54" t="s">
+      <c r="E16" s="118" t="s">
         <v>220</v>
       </c>
       <c r="F16" s="11">
@@ -50964,7 +51040,7 @@
       <c r="AT16" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="AU16" s="105">
+      <c r="AU16" s="104">
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="AV16" s="18" t="s">
@@ -51087,7 +51163,7 @@
         <v>1.4858841010401188E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:86" ht="16">
+    <row r="17" spans="1:86">
       <c r="A17" t="s">
         <v>332</v>
       </c>
@@ -51124,7 +51200,7 @@
       <c r="L17">
         <v>9</v>
       </c>
-      <c r="M17" s="118" t="s">
+      <c r="M17" s="117" t="s">
         <v>345</v>
       </c>
       <c r="N17" t="s">
@@ -51349,7 +51425,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:86" ht="16">
+    <row r="18" spans="1:86">
       <c r="A18" t="s">
         <v>332</v>
       </c>
@@ -51386,7 +51462,7 @@
       <c r="L18">
         <v>9</v>
       </c>
-      <c r="M18" s="118" t="s">
+      <c r="M18" s="117" t="s">
         <v>345</v>
       </c>
       <c r="N18" t="s">
@@ -51611,7 +51687,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:86" ht="16">
+    <row r="19" spans="1:86">
       <c r="A19" t="s">
         <v>332</v>
       </c>
@@ -51648,7 +51724,7 @@
       <c r="L19">
         <v>9</v>
       </c>
-      <c r="M19" s="118" t="s">
+      <c r="M19" s="117" t="s">
         <v>345</v>
       </c>
       <c r="N19" t="s">
@@ -51873,7 +51949,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:86" s="102" customFormat="1" ht="16">
+    <row r="20" spans="1:86" s="101" customFormat="1">
       <c r="A20" t="s">
         <v>332</v>
       </c>
@@ -51910,7 +51986,7 @@
       <c r="L20">
         <v>9</v>
       </c>
-      <c r="M20" s="118" t="s">
+      <c r="M20" s="117" t="s">
         <v>345</v>
       </c>
       <c r="N20" t="s">
@@ -52137,7 +52213,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:86" s="102" customFormat="1" ht="16">
+    <row r="21" spans="1:86" s="101" customFormat="1">
       <c r="A21" t="s">
         <v>332</v>
       </c>
@@ -52174,7 +52250,7 @@
       <c r="L21">
         <v>9</v>
       </c>
-      <c r="M21" s="118" t="s">
+      <c r="M21" s="117" t="s">
         <v>345</v>
       </c>
       <c r="N21" t="s">
@@ -52401,7 +52477,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:86" s="102" customFormat="1" ht="16">
+    <row r="22" spans="1:86" s="101" customFormat="1">
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
@@ -52549,7 +52625,7 @@
       <c r="AW22" t="s">
         <v>73</v>
       </c>
-      <c r="AX22" s="116">
+      <c r="AX22" s="115">
         <v>1E-3</v>
       </c>
       <c r="AY22">
@@ -52611,7 +52687,7 @@
       <c r="BR22">
         <v>1</v>
       </c>
-      <c r="BS22" s="109" t="s">
+      <c r="BS22" s="108" t="s">
         <v>73</v>
       </c>
       <c r="BT22" t="s">
@@ -52665,7 +52741,7 @@
         <v>5.00751126690035E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:86" ht="16">
+    <row r="23" spans="1:86">
       <c r="A23" s="11" t="s">
         <v>68</v>
       </c>
@@ -52875,7 +52951,7 @@
       <c r="BR23">
         <v>1</v>
       </c>
-      <c r="BS23" s="109" t="s">
+      <c r="BS23" s="108" t="s">
         <v>73</v>
       </c>
       <c r="BT23" t="s">
@@ -52927,11 +53003,13 @@
         <v>5.00751126690035E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:86" ht="16">
+    <row r="24" spans="1:86">
       <c r="A24" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="11"/>
+      <c r="B24" s="11" t="s">
+        <v>658</v>
+      </c>
       <c r="C24" s="96">
         <v>1191</v>
       </c>
@@ -53064,7 +53142,7 @@
       <c r="AT24" t="s">
         <v>235</v>
       </c>
-      <c r="AU24" s="105">
+      <c r="AU24" s="104">
         <v>2.08</v>
       </c>
       <c r="AV24" s="7" t="s">
@@ -53107,7 +53185,7 @@
       <c r="BI24">
         <v>355</v>
       </c>
-      <c r="BJ24" s="110">
+      <c r="BJ24" s="109">
         <v>19860</v>
       </c>
       <c r="BK24" t="s">
@@ -53134,7 +53212,7 @@
       <c r="BR24">
         <v>1</v>
       </c>
-      <c r="BS24" s="111">
+      <c r="BS24" s="110">
         <v>0.2</v>
       </c>
       <c r="BT24" t="s">
@@ -53186,11 +53264,13 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="25" spans="1:86" ht="16">
+    <row r="25" spans="1:86">
       <c r="A25" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="11"/>
+      <c r="B25" s="11" t="s">
+        <v>658</v>
+      </c>
       <c r="C25" s="96">
         <v>1192</v>
       </c>
@@ -53323,7 +53403,7 @@
       <c r="AT25" t="s">
         <v>235</v>
       </c>
-      <c r="AU25" s="105">
+      <c r="AU25" s="104">
         <v>2.3839999999999999</v>
       </c>
       <c r="AV25" s="7" t="s">
@@ -53366,7 +53446,7 @@
       <c r="BI25">
         <v>349</v>
       </c>
-      <c r="BJ25" s="110">
+      <c r="BJ25" s="109">
         <v>19452</v>
       </c>
       <c r="BK25" t="s">
@@ -53393,7 +53473,7 @@
       <c r="BR25">
         <v>1</v>
       </c>
-      <c r="BS25" s="111">
+      <c r="BS25" s="110">
         <v>0.2</v>
       </c>
       <c r="BT25" t="s">
@@ -53445,7 +53525,7 @@
         <v>5.1416525271222172E-5</v>
       </c>
     </row>
-    <row r="26" spans="1:86" ht="16">
+    <row r="26" spans="1:86">
       <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
@@ -53584,7 +53664,7 @@
       <c r="AT26" t="s">
         <v>73</v>
       </c>
-      <c r="AU26" s="105">
+      <c r="AU26" s="104">
         <v>0.7</v>
       </c>
       <c r="AV26" s="7" t="s">
@@ -53706,7 +53786,7 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:86" s="104" customFormat="1" ht="16">
+    <row r="27" spans="1:86" s="103" customFormat="1">
       <c r="A27" s="11" t="s">
         <v>68</v>
       </c>
@@ -53845,7 +53925,7 @@
       <c r="AT27" t="s">
         <v>73</v>
       </c>
-      <c r="AU27" s="105">
+      <c r="AU27" s="104">
         <v>0.111</v>
       </c>
       <c r="AV27" s="7" t="s">
@@ -53970,7 +54050,7 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:86" s="108" customFormat="1" ht="16">
+    <row r="28" spans="1:86" s="107" customFormat="1">
       <c r="A28" s="11" t="s">
         <v>68</v>
       </c>
@@ -54109,7 +54189,7 @@
       <c r="AT28" t="s">
         <v>73</v>
       </c>
-      <c r="AU28" s="105">
+      <c r="AU28" s="104">
         <v>0.13200000000000001</v>
       </c>
       <c r="AV28" s="7" t="s">
@@ -54234,7 +54314,7 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:86" s="108" customFormat="1" ht="16">
+    <row r="29" spans="1:86" s="107" customFormat="1">
       <c r="A29" s="11" t="s">
         <v>68</v>
       </c>
@@ -54373,7 +54453,7 @@
       <c r="AT29" t="s">
         <v>73</v>
       </c>
-      <c r="AU29" s="105">
+      <c r="AU29" s="104">
         <v>0.152</v>
       </c>
       <c r="AV29" s="7" t="s">
@@ -54498,7 +54578,7 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:86" s="108" customFormat="1" ht="16">
+    <row r="30" spans="1:86" s="107" customFormat="1">
       <c r="A30" s="11" t="s">
         <v>68</v>
       </c>
@@ -54637,7 +54717,7 @@
       <c r="AT30" t="s">
         <v>73</v>
       </c>
-      <c r="AU30" s="105">
+      <c r="AU30" s="104">
         <v>0.34</v>
       </c>
       <c r="AV30" s="7" t="s">
@@ -54901,7 +54981,7 @@
       <c r="AT31" t="s">
         <v>73</v>
       </c>
-      <c r="AU31" s="105">
+      <c r="AU31" s="104">
         <v>0.249</v>
       </c>
       <c r="AV31" s="7" t="s">
@@ -55162,7 +55242,7 @@
       <c r="AT32" t="s">
         <v>73</v>
       </c>
-      <c r="AU32" s="105">
+      <c r="AU32" s="104">
         <v>0.64200000000000002</v>
       </c>
       <c r="AV32" s="7" t="s">
@@ -55288,13 +55368,16 @@
       <c r="A33" t="s">
         <v>332</v>
       </c>
+      <c r="B33" s="11" t="s">
+        <v>657</v>
+      </c>
       <c r="C33" s="94">
         <v>1258</v>
       </c>
       <c r="D33" s="11">
         <v>404</v>
       </c>
-      <c r="E33" s="41" t="s">
+      <c r="E33" s="120" t="s">
         <v>333</v>
       </c>
       <c r="F33" s="11">
@@ -55543,9 +55626,12 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:86" ht="16">
+    <row r="34" spans="1:86">
       <c r="A34" t="s">
         <v>332</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>657</v>
       </c>
       <c r="C34" s="94">
         <v>1259</v>
@@ -55802,9 +55888,12 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:86" ht="16">
+    <row r="35" spans="1:86">
       <c r="A35" t="s">
         <v>332</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>657</v>
       </c>
       <c r="C35" s="94">
         <v>1260</v>
@@ -56061,18 +56150,20 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:86" ht="16">
+    <row r="36" spans="1:86">
       <c r="A36" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="11"/>
+      <c r="B36" s="11" t="s">
+        <v>660</v>
+      </c>
       <c r="C36" s="96">
         <v>1189</v>
       </c>
       <c r="D36" s="97">
         <v>143</v>
       </c>
-      <c r="E36" s="120" t="s">
+      <c r="E36" s="121" t="s">
         <v>294</v>
       </c>
       <c r="F36" s="96">
@@ -56268,19 +56359,19 @@
       <c r="BW36" s="97">
         <v>1</v>
       </c>
-      <c r="BX36" s="103">
+      <c r="BX36" s="102">
         <f t="shared" si="13"/>
         <v>6.7103465160314887E-2</v>
       </c>
-      <c r="BY36" s="103">
+      <c r="BY36" s="102">
         <f t="shared" si="14"/>
         <v>6.7204457661064573E-2</v>
       </c>
-      <c r="BZ36" s="103">
+      <c r="BZ36" s="102">
         <f t="shared" si="15"/>
         <v>1.6694150280093312E-3</v>
       </c>
-      <c r="CA36" s="103">
+      <c r="CA36" s="102">
         <f t="shared" si="16"/>
         <v>1.6750418760469012E-3</v>
       </c>
@@ -56305,18 +56396,20 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:86" ht="16">
+    <row r="37" spans="1:86">
       <c r="A37" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="11"/>
+      <c r="B37" s="11" t="s">
+        <v>660</v>
+      </c>
       <c r="C37" s="96">
         <v>1190</v>
       </c>
       <c r="D37" s="97">
         <v>143</v>
       </c>
-      <c r="E37" s="44" t="s">
+      <c r="E37" s="121" t="s">
         <v>294</v>
       </c>
       <c r="F37" s="96">
@@ -56512,19 +56605,19 @@
       <c r="BW37" s="97">
         <v>1</v>
       </c>
-      <c r="BX37" s="103">
+      <c r="BX37" s="102">
         <f t="shared" si="13"/>
         <v>7.9920998150068992E-2</v>
       </c>
-      <c r="BY37" s="103">
+      <c r="BY37" s="102">
         <f t="shared" si="14"/>
         <v>8.0091814824645752E-2</v>
       </c>
-      <c r="BZ37" s="103">
+      <c r="BZ37" s="102">
         <f t="shared" si="15"/>
         <v>1.6693803867099848E-3</v>
       </c>
-      <c r="CA37" s="103">
+      <c r="CA37" s="102">
         <f t="shared" si="16"/>
         <v>1.6750418760469012E-3</v>
       </c>
@@ -56549,18 +56642,20 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:86" ht="16">
+    <row r="38" spans="1:86">
       <c r="A38" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B38" s="11"/>
+      <c r="B38" s="11" t="s">
+        <v>660</v>
+      </c>
       <c r="C38" s="96">
         <v>1187</v>
       </c>
       <c r="D38" s="97">
         <v>143</v>
       </c>
-      <c r="E38" s="44" t="s">
+      <c r="E38" s="121" t="s">
         <v>294</v>
       </c>
       <c r="F38" s="96">
@@ -56756,19 +56851,19 @@
       <c r="BW38" s="97">
         <v>1</v>
       </c>
-      <c r="BX38" s="103">
+      <c r="BX38" s="102">
         <f t="shared" si="13"/>
         <v>6.7103465160314887E-2</v>
       </c>
-      <c r="BY38" s="103">
+      <c r="BY38" s="102">
         <f t="shared" si="14"/>
         <v>6.7204457661064573E-2</v>
       </c>
-      <c r="BZ38" s="103">
+      <c r="BZ38" s="102">
         <f t="shared" si="15"/>
         <v>1.6694150280093312E-3</v>
       </c>
-      <c r="CA38" s="103">
+      <c r="CA38" s="102">
         <f t="shared" si="16"/>
         <v>1.6750418760469012E-3</v>
       </c>
@@ -56793,18 +56888,20 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:86" ht="16">
+    <row r="39" spans="1:86">
       <c r="A39" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="11"/>
+      <c r="B39" s="11" t="s">
+        <v>660</v>
+      </c>
       <c r="C39" s="96">
         <v>1188</v>
       </c>
       <c r="D39" s="97">
         <v>143</v>
       </c>
-      <c r="E39" s="44" t="s">
+      <c r="E39" s="121" t="s">
         <v>294</v>
       </c>
       <c r="F39" s="96">
@@ -57000,19 +57097,19 @@
       <c r="BW39" s="97">
         <v>1</v>
       </c>
-      <c r="BX39" s="103">
+      <c r="BX39" s="102">
         <f t="shared" si="13"/>
         <v>6.7103465160314887E-2</v>
       </c>
-      <c r="BY39" s="103">
+      <c r="BY39" s="102">
         <f t="shared" si="14"/>
         <v>6.7204457661064573E-2</v>
       </c>
-      <c r="BZ39" s="103">
+      <c r="BZ39" s="102">
         <f t="shared" si="15"/>
         <v>1.6694150280093312E-3</v>
       </c>
-      <c r="CA39" s="103">
+      <c r="CA39" s="102">
         <f t="shared" si="16"/>
         <v>1.6750418760469012E-3</v>
       </c>
@@ -57037,7 +57134,7 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:86" ht="16">
+    <row r="40" spans="1:86">
       <c r="A40" s="11" t="s">
         <v>68</v>
       </c>
@@ -57050,7 +57147,7 @@
       <c r="D40" s="97">
         <v>127</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="120" t="s">
         <v>259</v>
       </c>
       <c r="F40" s="96">
@@ -57173,7 +57270,7 @@
       <c r="AS40" s="97" t="s">
         <v>265</v>
       </c>
-      <c r="AT40" s="109" t="s">
+      <c r="AT40" s="108" t="s">
         <v>73</v>
       </c>
       <c r="AU40" s="21">
@@ -57261,19 +57358,19 @@
       <c r="BW40" s="97">
         <v>0</v>
       </c>
-      <c r="BX40" s="103">
+      <c r="BX40" s="102">
         <f t="shared" si="13"/>
         <v>0.32021801928313393</v>
       </c>
-      <c r="BY40" s="103">
+      <c r="BY40" s="102">
         <f t="shared" si="14"/>
         <v>0.33189001894838011</v>
       </c>
-      <c r="BZ40" s="103">
+      <c r="BZ40" s="102">
         <f t="shared" si="15"/>
         <v>2.822476458784471E-2</v>
       </c>
-      <c r="CA40" s="103">
+      <c r="CA40" s="102">
         <f t="shared" si="16"/>
         <v>3.0303030303030304E-2</v>
       </c>
@@ -57298,7 +57395,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:86" ht="16">
+    <row r="41" spans="1:86">
       <c r="A41" s="11" t="s">
         <v>68</v>
       </c>
@@ -57311,7 +57408,7 @@
       <c r="D41" s="97">
         <v>127</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="120" t="s">
         <v>259</v>
       </c>
       <c r="F41" s="96">
@@ -57434,7 +57531,7 @@
       <c r="AS41" s="97" t="s">
         <v>265</v>
       </c>
-      <c r="AT41" s="109" t="s">
+      <c r="AT41" s="108" t="s">
         <v>73</v>
       </c>
       <c r="AU41" s="21">
@@ -57522,19 +57619,19 @@
       <c r="BW41" s="97">
         <v>0</v>
       </c>
-      <c r="BX41" s="103">
+      <c r="BX41" s="102">
         <f t="shared" si="13"/>
         <v>0.32021801928313393</v>
       </c>
-      <c r="BY41" s="103">
+      <c r="BY41" s="102">
         <f t="shared" si="14"/>
         <v>0.33189001894838011</v>
       </c>
-      <c r="BZ41" s="103">
+      <c r="BZ41" s="102">
         <f t="shared" si="15"/>
         <v>2.822476458784471E-2</v>
       </c>
-      <c r="CA41" s="103">
+      <c r="CA41" s="102">
         <f t="shared" si="16"/>
         <v>3.0303030303030304E-2</v>
       </c>
@@ -57559,7 +57656,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:86" ht="16">
+    <row r="42" spans="1:86">
       <c r="A42" s="11" t="s">
         <v>68</v>
       </c>
@@ -57572,7 +57669,7 @@
       <c r="D42" s="97">
         <v>127</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="120" t="s">
         <v>259</v>
       </c>
       <c r="F42" s="96">
@@ -57695,7 +57792,7 @@
       <c r="AS42" s="97" t="s">
         <v>265</v>
       </c>
-      <c r="AT42" s="109" t="s">
+      <c r="AT42" s="108" t="s">
         <v>73</v>
       </c>
       <c r="AU42" s="21">
@@ -57783,19 +57880,19 @@
       <c r="BW42" s="97">
         <v>0</v>
       </c>
-      <c r="BX42" s="103">
+      <c r="BX42" s="102">
         <f t="shared" si="13"/>
         <v>0.5126110197955529</v>
       </c>
-      <c r="BY42" s="103">
+      <c r="BY42" s="102">
         <f t="shared" si="14"/>
         <v>0.56626502857004413</v>
       </c>
-      <c r="BZ42" s="103">
+      <c r="BZ42" s="102">
         <f t="shared" si="15"/>
         <v>2.5633705048672264E-2</v>
       </c>
-      <c r="CA42" s="103">
+      <c r="CA42" s="102">
         <f t="shared" si="16"/>
         <v>3.0303030303030304E-2</v>
       </c>
@@ -57820,7 +57917,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="43" spans="1:86" ht="16">
+    <row r="43" spans="1:86">
       <c r="A43" s="11" t="s">
         <v>68</v>
       </c>
@@ -57833,7 +57930,7 @@
       <c r="D43" s="97">
         <v>127</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="120" t="s">
         <v>259</v>
       </c>
       <c r="F43" s="96">
@@ -57956,7 +58053,7 @@
       <c r="AS43" s="97" t="s">
         <v>265</v>
       </c>
-      <c r="AT43" s="109" t="s">
+      <c r="AT43" s="108" t="s">
         <v>73</v>
       </c>
       <c r="AU43" s="21">
@@ -58044,19 +58141,19 @@
       <c r="BW43" s="97">
         <v>0</v>
       </c>
-      <c r="BX43" s="103">
+      <c r="BX43" s="102">
         <f t="shared" si="13"/>
         <v>0.5126110197955529</v>
       </c>
-      <c r="BY43" s="103">
+      <c r="BY43" s="102">
         <f t="shared" si="14"/>
         <v>0.56626502857004413</v>
       </c>
-      <c r="BZ43" s="103">
+      <c r="BZ43" s="102">
         <f t="shared" si="15"/>
         <v>2.5633705048672264E-2</v>
       </c>
-      <c r="CA43" s="103">
+      <c r="CA43" s="102">
         <f t="shared" si="16"/>
         <v>3.0303030303030304E-2</v>
       </c>
@@ -58081,7 +58178,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:86" ht="16">
+    <row r="44" spans="1:86">
       <c r="A44" s="11" t="s">
         <v>68</v>
       </c>
@@ -58094,7 +58191,7 @@
       <c r="D44" s="97">
         <v>127</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="120" t="s">
         <v>259</v>
       </c>
       <c r="F44" s="96">
@@ -58217,7 +58314,7 @@
       <c r="AS44" s="97" t="s">
         <v>265</v>
       </c>
-      <c r="AT44" s="109" t="s">
+      <c r="AT44" s="108" t="s">
         <v>73</v>
       </c>
       <c r="AU44" s="21">
@@ -58305,19 +58402,19 @@
       <c r="BW44" s="97">
         <v>0</v>
       </c>
-      <c r="BX44" s="103">
+      <c r="BX44" s="102">
         <f t="shared" si="13"/>
         <v>0.5126110197955529</v>
       </c>
-      <c r="BY44" s="103">
+      <c r="BY44" s="102">
         <f t="shared" si="14"/>
         <v>0.56626502857004413</v>
       </c>
-      <c r="BZ44" s="103">
+      <c r="BZ44" s="102">
         <f t="shared" si="15"/>
         <v>2.5633705048672264E-2</v>
       </c>
-      <c r="CA44" s="103">
+      <c r="CA44" s="102">
         <f t="shared" si="16"/>
         <v>3.0303030303030304E-2</v>
       </c>
@@ -58342,7 +58439,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:86" ht="16">
+    <row r="45" spans="1:86">
       <c r="A45" s="11" t="s">
         <v>68</v>
       </c>
@@ -58355,7 +58452,7 @@
       <c r="D45" s="97">
         <v>127</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="120" t="s">
         <v>259</v>
       </c>
       <c r="F45" s="96">
@@ -58478,7 +58575,7 @@
       <c r="AS45" s="97" t="s">
         <v>265</v>
       </c>
-      <c r="AT45" s="109" t="s">
+      <c r="AT45" s="108" t="s">
         <v>73</v>
       </c>
       <c r="AU45" s="21">
@@ -58566,19 +58663,19 @@
       <c r="BW45" s="97">
         <v>0</v>
       </c>
-      <c r="BX45" s="103">
+      <c r="BX45" s="102">
         <f t="shared" si="13"/>
         <v>0.5126110197955529</v>
       </c>
-      <c r="BY45" s="103">
+      <c r="BY45" s="102">
         <f t="shared" si="14"/>
         <v>0.56626502857004413</v>
       </c>
-      <c r="BZ45" s="103">
+      <c r="BZ45" s="102">
         <f t="shared" si="15"/>
         <v>2.5633705048672264E-2</v>
       </c>
-      <c r="CA45" s="103">
+      <c r="CA45" s="102">
         <f t="shared" si="16"/>
         <v>3.0303030303030304E-2</v>
       </c>
@@ -58603,18 +58700,20 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:86" ht="16">
+    <row r="46" spans="1:86">
       <c r="A46" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B46" s="11"/>
+      <c r="B46" s="11" t="s">
+        <v>656</v>
+      </c>
       <c r="C46" s="11">
         <v>1099</v>
       </c>
       <c r="D46">
         <v>118</v>
       </c>
-      <c r="E46" s="41" t="s">
+      <c r="E46" s="120" t="s">
         <v>254</v>
       </c>
       <c r="F46" s="11">
@@ -58746,7 +58845,7 @@
       <c r="AV46" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AW46" s="107">
+      <c r="AW46" s="106">
         <f>AU46/AZ46</f>
         <v>5.3746253746253754E-2</v>
       </c>
@@ -58825,19 +58924,19 @@
       <c r="BW46">
         <v>1</v>
       </c>
-      <c r="BX46" s="103">
+      <c r="BX46" s="102">
         <f t="shared" si="13"/>
         <v>0.47242735990047685</v>
       </c>
-      <c r="BY46" s="103">
+      <c r="BY46" s="102">
         <f t="shared" si="14"/>
         <v>0.51319051047617226</v>
       </c>
-      <c r="BZ46" s="103">
+      <c r="BZ46" s="102">
         <f t="shared" si="15"/>
         <v>6.6760340037102519E-4</v>
       </c>
-      <c r="CA46" s="103">
+      <c r="CA46" s="102">
         <f t="shared" si="16"/>
         <v>7.1839080459770114E-4</v>
       </c>
@@ -58862,18 +58961,20 @@
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:86" ht="16">
+    <row r="47" spans="1:86">
       <c r="A47" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B47" s="11"/>
+      <c r="B47" s="11" t="s">
+        <v>656</v>
+      </c>
       <c r="C47" s="11">
         <v>1100</v>
       </c>
       <c r="D47">
         <v>118</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="120" t="s">
         <v>254</v>
       </c>
       <c r="F47" s="11">
@@ -59005,7 +59106,7 @@
       <c r="AV47" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AW47" s="107">
+      <c r="AW47" s="106">
         <f>AU47/AZ47</f>
         <v>0.18628472222222223</v>
       </c>
@@ -59084,19 +59185,19 @@
       <c r="BW47">
         <v>1</v>
       </c>
-      <c r="BX47" s="103">
+      <c r="BX47" s="102">
         <f t="shared" si="13"/>
         <v>0.29473516954008327</v>
       </c>
-      <c r="BY47" s="103">
+      <c r="BY47" s="102">
         <f t="shared" si="14"/>
         <v>0.3037440363085756</v>
       </c>
-      <c r="BZ47" s="103">
+      <c r="BZ47" s="102">
         <f t="shared" si="15"/>
         <v>7.1125395357683058E-4</v>
       </c>
-      <c r="CA47" s="103">
+      <c r="CA47" s="102">
         <f t="shared" si="16"/>
         <v>7.1839080459770114E-4</v>
       </c>
@@ -59121,18 +59222,20 @@
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:86" ht="16">
+    <row r="48" spans="1:86">
       <c r="A48" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="B48" s="11"/>
+      <c r="B48" s="11" t="s">
+        <v>656</v>
+      </c>
       <c r="C48" s="94">
         <v>1235</v>
       </c>
       <c r="D48">
         <v>118</v>
       </c>
-      <c r="E48" s="101" t="s">
+      <c r="E48" s="122" t="s">
         <v>254</v>
       </c>
       <c r="F48">
@@ -59343,19 +59446,19 @@
       <c r="BW48">
         <v>0</v>
       </c>
-      <c r="BX48" s="103">
+      <c r="BX48" s="102">
         <f t="shared" si="13"/>
         <v>6.8895720725096588E-2</v>
       </c>
-      <c r="BY48" s="103">
+      <c r="BY48" s="102">
         <f t="shared" si="14"/>
         <v>6.900503950756405E-2</v>
       </c>
-      <c r="BZ48" s="103">
+      <c r="BZ48" s="102">
         <f t="shared" si="15"/>
         <v>7.1734384953814931E-4</v>
       </c>
-      <c r="CA48" s="103">
+      <c r="CA48" s="102">
         <f t="shared" si="16"/>
         <v>7.1839080459770114E-4</v>
       </c>
@@ -59381,18 +59484,20 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="49" spans="1:86" s="102" customFormat="1" ht="16">
+    <row r="49" spans="1:86" s="101" customFormat="1">
       <c r="A49" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="B49" s="11"/>
+      <c r="B49" s="11" t="s">
+        <v>656</v>
+      </c>
       <c r="C49" s="94">
         <v>1236</v>
       </c>
       <c r="D49">
         <v>118</v>
       </c>
-      <c r="E49" s="101" t="s">
+      <c r="E49" s="122" t="s">
         <v>254</v>
       </c>
       <c r="F49">
@@ -59604,19 +59709,19 @@
       <c r="BW49">
         <v>1</v>
       </c>
-      <c r="BX49" s="103">
+      <c r="BX49" s="102">
         <f t="shared" si="13"/>
         <v>6.8895720725096588E-2</v>
       </c>
-      <c r="BY49" s="103">
+      <c r="BY49" s="102">
         <f t="shared" si="14"/>
         <v>6.900503950756405E-2</v>
       </c>
-      <c r="BZ49" s="103">
+      <c r="BZ49" s="102">
         <f t="shared" si="15"/>
         <v>7.1734384953814931E-4</v>
       </c>
-      <c r="CA49" s="103">
+      <c r="CA49" s="102">
         <f t="shared" si="16"/>
         <v>7.1839080459770114E-4</v>
       </c>
@@ -59643,18 +59748,20 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="50" spans="1:86" s="102" customFormat="1" ht="16">
+    <row r="50" spans="1:86" s="101" customFormat="1">
       <c r="A50" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="B50" s="11"/>
+      <c r="B50" s="11" t="s">
+        <v>656</v>
+      </c>
       <c r="C50" s="94">
         <v>1237</v>
       </c>
       <c r="D50">
         <v>118</v>
       </c>
-      <c r="E50" s="101" t="s">
+      <c r="E50" s="122" t="s">
         <v>254</v>
       </c>
       <c r="F50">
@@ -59866,19 +59973,19 @@
       <c r="BW50">
         <v>0</v>
       </c>
-      <c r="BX50" s="103">
+      <c r="BX50" s="102">
         <f t="shared" si="13"/>
         <v>6.8895720725096588E-2</v>
       </c>
-      <c r="BY50" s="103">
+      <c r="BY50" s="102">
         <f t="shared" si="14"/>
         <v>6.900503950756405E-2</v>
       </c>
-      <c r="BZ50" s="103">
+      <c r="BZ50" s="102">
         <f t="shared" si="15"/>
         <v>7.1734384953814931E-4</v>
       </c>
-      <c r="CA50" s="103">
+      <c r="CA50" s="102">
         <f t="shared" si="16"/>
         <v>7.1839080459770114E-4</v>
       </c>
@@ -59905,18 +60012,20 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="51" spans="1:86" s="102" customFormat="1" ht="16">
+    <row r="51" spans="1:86" s="101" customFormat="1">
       <c r="A51" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="B51" s="11"/>
+      <c r="B51" s="11" t="s">
+        <v>656</v>
+      </c>
       <c r="C51" s="94">
         <v>1238</v>
       </c>
       <c r="D51">
         <v>118</v>
       </c>
-      <c r="E51" s="101" t="s">
+      <c r="E51" s="122" t="s">
         <v>254</v>
       </c>
       <c r="F51">
@@ -60128,19 +60237,19 @@
       <c r="BW51">
         <v>1</v>
       </c>
-      <c r="BX51" s="103">
+      <c r="BX51" s="102">
         <f t="shared" si="13"/>
         <v>5.2449375133439773E-2</v>
       </c>
-      <c r="BY51" s="103">
+      <c r="BY51" s="102">
         <f t="shared" si="14"/>
         <v>5.2497549648224964E-2</v>
       </c>
-      <c r="BZ51" s="103">
+      <c r="BZ51" s="102">
         <f t="shared" si="15"/>
         <v>7.1735466607183095E-4</v>
       </c>
-      <c r="CA51" s="103">
+      <c r="CA51" s="102">
         <f t="shared" si="16"/>
         <v>7.1839080459770114E-4</v>
       </c>
@@ -60167,18 +60276,20 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="52" spans="1:86" ht="16">
+    <row r="52" spans="1:86">
       <c r="A52" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="B52" s="11"/>
+      <c r="B52" s="11" t="s">
+        <v>656</v>
+      </c>
       <c r="C52" s="94">
         <v>1239</v>
       </c>
       <c r="D52">
         <v>118</v>
       </c>
-      <c r="E52" s="101" t="s">
+      <c r="E52" s="122" t="s">
         <v>254</v>
       </c>
       <c r="F52">
@@ -60388,19 +60499,19 @@
       <c r="BW52">
         <v>0</v>
       </c>
-      <c r="BX52" s="103">
+      <c r="BX52" s="102">
         <f t="shared" si="13"/>
         <v>0.47242735990047685</v>
       </c>
-      <c r="BY52" s="103">
+      <c r="BY52" s="102">
         <f t="shared" si="14"/>
         <v>0.51319051047617226</v>
       </c>
-      <c r="BZ52" s="103">
+      <c r="BZ52" s="102">
         <f t="shared" si="15"/>
         <v>6.6760340037102519E-4</v>
       </c>
-      <c r="CA52" s="103">
+      <c r="CA52" s="102">
         <f t="shared" si="16"/>
         <v>7.1839080459770114E-4</v>
       </c>
@@ -60426,18 +60537,20 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="53" spans="1:86" ht="16">
+    <row r="53" spans="1:86">
       <c r="A53" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="B53" s="11"/>
+      <c r="B53" s="11" t="s">
+        <v>656</v>
+      </c>
       <c r="C53" s="94">
         <v>1240</v>
       </c>
       <c r="D53">
         <v>118</v>
       </c>
-      <c r="E53" s="101" t="s">
+      <c r="E53" s="122" t="s">
         <v>254</v>
       </c>
       <c r="F53">
@@ -60647,19 +60760,19 @@
       <c r="BW53">
         <v>0</v>
       </c>
-      <c r="BX53" s="103">
+      <c r="BX53" s="102">
         <f t="shared" si="13"/>
         <v>0.29473516954008327</v>
       </c>
-      <c r="BY53" s="103">
+      <c r="BY53" s="102">
         <f t="shared" si="14"/>
         <v>0.3037440363085756</v>
       </c>
-      <c r="BZ53" s="103">
+      <c r="BZ53" s="102">
         <f t="shared" si="15"/>
         <v>7.1125395357683058E-4</v>
       </c>
-      <c r="CA53" s="103">
+      <c r="CA53" s="102">
         <f t="shared" si="16"/>
         <v>7.1839080459770114E-4</v>
       </c>
@@ -60685,18 +60798,20 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="54" spans="1:86" ht="16">
+    <row r="54" spans="1:86">
       <c r="A54" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B54" s="11"/>
+      <c r="B54" s="11" t="s">
+        <v>661</v>
+      </c>
       <c r="C54" s="96">
         <v>1172</v>
       </c>
       <c r="D54" s="97">
         <v>141</v>
       </c>
-      <c r="E54" s="41" t="s">
+      <c r="E54" s="120" t="s">
         <v>275</v>
       </c>
       <c r="F54" s="96">
@@ -60822,7 +60937,7 @@
       <c r="AT54" t="s">
         <v>73</v>
       </c>
-      <c r="AU54" s="105">
+      <c r="AU54" s="104">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="AV54" s="7" t="s">
@@ -60944,11 +61059,13 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:86" ht="16">
+    <row r="55" spans="1:86">
       <c r="A55" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B55" s="11"/>
+      <c r="B55" s="11" t="s">
+        <v>661</v>
+      </c>
       <c r="C55" s="96">
         <v>1173</v>
       </c>
@@ -61081,7 +61198,7 @@
       <c r="AT55" t="s">
         <v>73</v>
       </c>
-      <c r="AU55" s="105">
+      <c r="AU55" s="104">
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="AV55" s="7" t="s">
@@ -61203,11 +61320,13 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:86" ht="16">
+    <row r="56" spans="1:86">
       <c r="A56" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B56" s="11"/>
+      <c r="B56" s="11" t="s">
+        <v>661</v>
+      </c>
       <c r="C56" s="96">
         <v>1174</v>
       </c>
@@ -61340,7 +61459,7 @@
       <c r="AT56" t="s">
         <v>73</v>
       </c>
-      <c r="AU56" s="105">
+      <c r="AU56" s="104">
         <v>0.13300000000000001</v>
       </c>
       <c r="AV56" s="7" t="s">
@@ -61462,11 +61581,13 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:86" ht="16">
+    <row r="57" spans="1:86">
       <c r="A57" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B57" s="11"/>
+      <c r="B57" s="11" t="s">
+        <v>661</v>
+      </c>
       <c r="C57" s="96">
         <v>1175</v>
       </c>
@@ -61599,7 +61720,7 @@
       <c r="AT57" t="s">
         <v>73</v>
       </c>
-      <c r="AU57" s="105">
+      <c r="AU57" s="104">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="AV57" s="7" t="s">
@@ -61721,11 +61842,13 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:86" ht="16">
+    <row r="58" spans="1:86">
       <c r="A58" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="11"/>
+      <c r="B58" s="11" t="s">
+        <v>661</v>
+      </c>
       <c r="C58" s="96">
         <v>1176</v>
       </c>
@@ -61858,7 +61981,7 @@
       <c r="AT58" t="s">
         <v>73</v>
       </c>
-      <c r="AU58" s="105">
+      <c r="AU58" s="104">
         <v>0.14000000000000001</v>
       </c>
       <c r="AV58" s="7" t="s">
@@ -61928,7 +62051,7 @@
       <c r="BR58">
         <v>1</v>
       </c>
-      <c r="BS58" s="109" t="s">
+      <c r="BS58" s="108" t="s">
         <v>73</v>
       </c>
       <c r="BT58" s="97" t="s">
@@ -61980,11 +62103,13 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:86" ht="16">
+    <row r="59" spans="1:86">
       <c r="A59" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B59" s="11"/>
+      <c r="B59" s="11" t="s">
+        <v>661</v>
+      </c>
       <c r="C59" s="96">
         <v>1177</v>
       </c>
@@ -62117,7 +62242,7 @@
       <c r="AT59" t="s">
         <v>73</v>
       </c>
-      <c r="AU59" s="105">
+      <c r="AU59" s="104">
         <v>0.14299999999999999</v>
       </c>
       <c r="AV59" s="7" t="s">
@@ -62187,7 +62312,7 @@
       <c r="BR59">
         <v>1</v>
       </c>
-      <c r="BS59" s="109" t="s">
+      <c r="BS59" s="108" t="s">
         <v>73</v>
       </c>
       <c r="BT59" s="97" t="s">
@@ -62239,11 +62364,13 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:86" ht="16">
+    <row r="60" spans="1:86">
       <c r="A60" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B60" s="11"/>
+      <c r="B60" s="11" t="s">
+        <v>661</v>
+      </c>
       <c r="C60" s="96">
         <v>1178</v>
       </c>
@@ -62376,7 +62503,7 @@
       <c r="AT60" t="s">
         <v>73</v>
       </c>
-      <c r="AU60" s="105">
+      <c r="AU60" s="104">
         <v>0.22</v>
       </c>
       <c r="AV60" s="7" t="s">
@@ -62446,7 +62573,7 @@
       <c r="BR60">
         <v>1</v>
       </c>
-      <c r="BS60" s="109" t="s">
+      <c r="BS60" s="108" t="s">
         <v>73</v>
       </c>
       <c r="BT60" s="97" t="s">
@@ -62498,11 +62625,13 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:86" ht="16">
+    <row r="61" spans="1:86">
       <c r="A61" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B61" s="11"/>
+      <c r="B61" s="11" t="s">
+        <v>661</v>
+      </c>
       <c r="C61" s="96">
         <v>1179</v>
       </c>
@@ -62635,7 +62764,7 @@
       <c r="AT61" t="s">
         <v>73</v>
       </c>
-      <c r="AU61" s="105">
+      <c r="AU61" s="104">
         <v>0.159</v>
       </c>
       <c r="AV61" s="7" t="s">
@@ -62705,7 +62834,7 @@
       <c r="BR61">
         <v>1</v>
       </c>
-      <c r="BS61" s="109" t="s">
+      <c r="BS61" s="108" t="s">
         <v>73</v>
       </c>
       <c r="BT61" s="97" t="s">
@@ -62757,58 +62886,58 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:86" ht="16">
+    <row r="62" spans="1:86">
       <c r="M62" s="18"/>
     </row>
-    <row r="63" spans="1:86" ht="16">
+    <row r="63" spans="1:86">
       <c r="M63" s="18"/>
     </row>
-    <row r="64" spans="1:86" ht="16">
+    <row r="64" spans="1:86">
       <c r="M64" s="18"/>
     </row>
-    <row r="65" spans="13:76" ht="16">
+    <row r="65" spans="13:76">
       <c r="M65" s="18"/>
     </row>
-    <row r="66" spans="13:76" ht="16">
+    <row r="66" spans="13:76">
       <c r="M66" s="18"/>
     </row>
-    <row r="67" spans="13:76" ht="16">
+    <row r="67" spans="13:76">
       <c r="M67" s="18"/>
     </row>
-    <row r="68" spans="13:76" ht="16">
+    <row r="68" spans="13:76">
       <c r="M68" s="18"/>
     </row>
-    <row r="69" spans="13:76" ht="16">
+    <row r="69" spans="13:76">
       <c r="M69" s="18"/>
     </row>
-    <row r="70" spans="13:76" ht="16">
+    <row r="70" spans="13:76">
       <c r="M70" s="18"/>
     </row>
     <row r="71" spans="13:76" ht="15.75" customHeight="1">
       <c r="M71" s="18"/>
       <c r="BX71" s="30"/>
     </row>
-    <row r="72" spans="13:76" ht="16">
+    <row r="72" spans="13:76">
       <c r="M72" s="18"/>
-      <c r="BA72" s="112"/>
-      <c r="BB72" s="112"/>
+      <c r="BA72" s="111"/>
+      <c r="BB72" s="111"/>
     </row>
-    <row r="73" spans="13:76" ht="16">
+    <row r="73" spans="13:76">
       <c r="M73" s="18"/>
-      <c r="BA73" s="112"/>
-      <c r="BB73" s="112"/>
+      <c r="BA73" s="111"/>
+      <c r="BB73" s="111"/>
     </row>
     <row r="74" spans="13:76" ht="15.75" customHeight="1">
       <c r="M74" s="18"/>
     </row>
-    <row r="75" spans="13:76" ht="16">
+    <row r="75" spans="13:76">
       <c r="M75" s="18"/>
-      <c r="BA75" s="113"/>
-      <c r="BB75" s="113"/>
+      <c r="BA75" s="112"/>
+      <c r="BB75" s="112"/>
     </row>
   </sheetData>
-  <autoFilter ref="AR1:AR70" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CH75">
+  <autoFilter ref="AR1:AR70"/>
+  <sortState ref="A2:CH75">
     <sortCondition ref="E1:E75"/>
   </sortState>
   <dataConsolidate/>
@@ -62824,25 +62953,25 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="603" yWindow="1085" count="7">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN27:AP30 AH31:AP42 AH7:AH8 AJ7:AP8 AH55:AP1048576 AL27 AH26:AK27 AL26:AP26 AH28:AL30 S15:S30 S1 U1 AH43:AQ54 U39:U1048576 S34:S1048576 U15:U35 AH15:AP25 AH1:AI1 AK1:AP1" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN27:AP30 AH31:AP42 AH7:AH8 AJ7:AP8 AH55:AP1048576 AL27 AH26:AK27 AL26:AP26 AH28:AL30 S15:S30 S1 U1 AH43:AQ54 U39:U1048576 S34:S1048576 U15:U35 AH15:AP25 AH1:AI1 AK1:AP1">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I30:I1048576 I15:I28" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I30:I1048576 I15:I28">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AD39:AF61 AG7:AG8 AG20:AG30 AD28:AF33 AD27:AE27 AD34:AE38 AG34:AG38 AH61 AD1:AG1 AD62:AG1048576 AD15:AF26" xr:uid="{00000000-0002-0000-0100-000002000000}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y1:AC1 AI7:AI8 Y7:Y8 AA7:AE8 Y15:AC1048576" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AD39:AF61 AG7:AG8 AG20:AG30 AD28:AF33 AD27:AE27 AD34:AE38 AG34:AG38 AH61 AD1:AG1 AD62:AG1048576 AD15:AF26"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y1:AC1 AI7:AI8 Y7:Y8 AA7:AE8 Y15:AC1048576">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN1 BO27:BO30 BO43:BO54 BN62:BN1048576" xr:uid="{00000000-0002-0000-0100-000004000000}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AY55:AY61" xr:uid="{00000000-0002-0000-0100-000005000000}">
+    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN1 BO27:BO30 BO43:BO54 BN62:BN1048576"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AY55:AY61">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY31:AY42 AY15:AY25" xr:uid="{00000000-0002-0000-0100-000006000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY31:AY42 AY15:AY25">
       <formula1>1</formula1>
       <formula2>3</formula2>
     </dataValidation>
@@ -62853,127 +62982,127 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="603" yWindow="1085" count="21">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000007000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>U1 U62:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000008000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>BU55:BW1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000009000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$C$2:$C$4</xm:f>
           </x14:formula1>
           <xm:sqref>BO1 BO55:BO1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$I$2:$I$3</xm:f>
           </x14:formula1>
           <xm:sqref>AV1 AV62:AV1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$9</xm:f>
           </x14:formula1>
           <xm:sqref>U1 S1 S55:S1048576 U62:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$K$2:$K$3</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1 S1 S55:S1048576 U62:W1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000D000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N$2:$N$7</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1 S1 S55:S1048576 U62:W1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000E000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$J$2:$J$12</xm:f>
           </x14:formula1>
           <xm:sqref>K1 K62:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000F000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$O:$O</xm:f>
           </x14:formula1>
           <xm:sqref>BT1 BT62:BT1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000010000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$S:$S</xm:f>
           </x14:formula1>
           <xm:sqref>G1 G62:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000011000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G:$G</xm:f>
           </x14:formula1>
           <xm:sqref>AR1 AR55:AR1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000012000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F:$F</xm:f>
           </x14:formula1>
           <xm:sqref>M76:M1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000013000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$P:$P</xm:f>
           </x14:formula1>
           <xm:sqref>AT1 AT55:AT1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000014000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D:$D</xm:f>
           </x14:formula1>
           <xm:sqref>U62:W1048576 S1 U1:W1 S55:S1048576 N55:N1048576 N1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000015000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N:$N</xm:f>
           </x14:formula1>
           <xm:sqref>O1 O55:O1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000016000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B:$B</xm:f>
           </x14:formula1>
           <xm:sqref>T1 T55:T1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000017000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$R:$R</xm:f>
           </x14:formula1>
           <xm:sqref>E1 E55:E1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000018000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H:$H</xm:f>
           </x14:formula1>
           <xm:sqref>U62:U1048576 U1 S1 S55:S1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000019000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$M:$M</xm:f>
           </x14:formula1>
           <xm:sqref>S1 P27:P30 P1 U1 S55:S1048576 P55:P1048576 U62:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00001A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$10</xm:f>
           </x14:formula1>
           <xm:sqref>R1:R1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00001B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H$1:$H$7</xm:f>
           </x14:formula1>
@@ -62986,77 +63115,77 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BJ18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="17" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="36.375" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="29" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="20.125" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="15" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.875" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="29.625" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="33" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="25.875" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="35" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.375" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="15.625" bestFit="1" customWidth="1"/>
     <col min="63" max="64" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="113" t="s">
         <v>7</v>
       </c>
       <c r="B1" t="s">
@@ -63064,7 +63193,7 @@
       </c>
     </row>
     <row r="2" spans="1:62">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="113" t="s">
         <v>197</v>
       </c>
       <c r="B2" t="s">
@@ -63072,7 +63201,7 @@
       </c>
     </row>
     <row r="4" spans="1:62">
-      <c r="A4" s="114" t="s">
+      <c r="A4" s="113" t="s">
         <v>355</v>
       </c>
       <c r="B4" t="s">
@@ -63260,7 +63389,7 @@
       </c>
     </row>
     <row r="5" spans="1:62">
-      <c r="A5" s="115" t="s">
+      <c r="A5" s="114" t="s">
         <v>417</v>
       </c>
       <c r="B5">
@@ -63445,7 +63574,7 @@
       </c>
     </row>
     <row r="6" spans="1:62">
-      <c r="A6" s="115" t="s">
+      <c r="A6" s="114" t="s">
         <v>107</v>
       </c>
       <c r="B6">
@@ -63630,7 +63759,7 @@
       </c>
     </row>
     <row r="7" spans="1:62">
-      <c r="A7" s="115" t="s">
+      <c r="A7" s="114" t="s">
         <v>418</v>
       </c>
       <c r="B7">
@@ -63818,7 +63947,7 @@
       </c>
     </row>
     <row r="8" spans="1:62">
-      <c r="A8" s="115" t="s">
+      <c r="A8" s="114" t="s">
         <v>93</v>
       </c>
       <c r="B8">
@@ -64006,7 +64135,7 @@
       </c>
     </row>
     <row r="9" spans="1:62">
-      <c r="A9" s="115" t="s">
+      <c r="A9" s="114" t="s">
         <v>155</v>
       </c>
       <c r="B9">
@@ -64194,7 +64323,7 @@
       </c>
     </row>
     <row r="10" spans="1:62">
-      <c r="A10" s="115" t="s">
+      <c r="A10" s="114" t="s">
         <v>274</v>
       </c>
       <c r="B10">
@@ -64382,7 +64511,7 @@
       </c>
     </row>
     <row r="11" spans="1:62">
-      <c r="A11" s="115" t="s">
+      <c r="A11" s="114" t="s">
         <v>269</v>
       </c>
       <c r="B11">
@@ -64570,7 +64699,7 @@
       </c>
     </row>
     <row r="12" spans="1:62">
-      <c r="A12" s="115" t="s">
+      <c r="A12" s="114" t="s">
         <v>419</v>
       </c>
       <c r="B12">
@@ -64758,7 +64887,7 @@
       </c>
     </row>
     <row r="13" spans="1:62">
-      <c r="A13" s="115" t="s">
+      <c r="A13" s="114" t="s">
         <v>420</v>
       </c>
       <c r="B13">
@@ -64946,7 +65075,7 @@
       </c>
     </row>
     <row r="14" spans="1:62">
-      <c r="A14" s="115" t="s">
+      <c r="A14" s="114" t="s">
         <v>421</v>
       </c>
       <c r="B14">
@@ -65134,7 +65263,7 @@
       </c>
     </row>
     <row r="15" spans="1:62">
-      <c r="A15" s="115" t="s">
+      <c r="A15" s="114" t="s">
         <v>422</v>
       </c>
       <c r="B15">
@@ -65322,7 +65451,7 @@
       </c>
     </row>
     <row r="16" spans="1:62">
-      <c r="A16" s="115" t="s">
+      <c r="A16" s="114" t="s">
         <v>423</v>
       </c>
       <c r="B16">
@@ -65510,7 +65639,7 @@
       </c>
     </row>
     <row r="17" spans="1:62">
-      <c r="A17" s="115" t="s">
+      <c r="A17" s="114" t="s">
         <v>172</v>
       </c>
       <c r="B17">
@@ -65698,7 +65827,7 @@
       </c>
     </row>
     <row r="18" spans="1:62">
-      <c r="A18" s="115" t="s">
+      <c r="A18" s="114" t="s">
         <v>424</v>
       </c>
       <c r="B18">
@@ -65891,20 +66020,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18.1640625" style="26" customWidth="1"/>
+    <col min="7" max="7" width="18.125" style="26" customWidth="1"/>
     <col min="8" max="8" width="20.5" customWidth="1"/>
-    <col min="9" max="9" width="14.1640625" customWidth="1"/>
-    <col min="10" max="10" width="15.1640625" customWidth="1"/>
+    <col min="9" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>425</v>
       </c>
@@ -65960,7 +66089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="34">
+    <row r="2" spans="1:19" ht="31.5">
       <c r="A2">
         <v>0</v>
       </c>
@@ -66016,7 +66145,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="34">
+    <row r="3" spans="1:19" ht="31.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -66072,7 +66201,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="51">
+    <row r="4" spans="1:19" ht="47.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -66122,7 +66251,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="51">
+    <row r="5" spans="1:19" ht="47.25">
       <c r="D5" t="s">
         <v>446</v>
       </c>
@@ -67123,7 +67252,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="R2:S91">
+  <sortState ref="R2:S91">
     <sortCondition ref="R2:R91"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/appliances_wtp.xlsx
+++ b/appliances_wtp.xlsx
@@ -18,12 +18,12 @@
     <sheet name="Lists for variables" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Appliances!$AR$1:$AR$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Appliances!$T$1:$T$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Usage!$A$1:$BN$53</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId5"/>
+    <pivotCache cacheId="5" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4132" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4135" uniqueCount="657">
   <si>
     <t>Coder</t>
   </si>
@@ -2568,22 +2568,10 @@
     <t>WTP for efficient appliance in a treatment group compared to control (where control is existing label and treatment is label including operating cost)</t>
   </si>
   <si>
-    <t>valuation of top-rated refrigerators in treatment (rescaled label) compared to control (existing label)</t>
-  </si>
-  <si>
     <t>WTP for top-rated appliance in presence of a label compared to no label</t>
   </si>
   <si>
     <t>WTP for efficient appliance compared to existing appliance</t>
-  </si>
-  <si>
-    <t>WTP for efficient appliance in presence of a label compared to no label</t>
-  </si>
-  <si>
-    <t>baseline is the current EnergyGuide label</t>
-  </si>
-  <si>
-    <t>label compared to no label</t>
   </si>
   <si>
     <t>WTP for ENERGY STAR appliance compared to no label</t>
@@ -2592,16 +2580,13 @@
     <t>WTP before and after an information message</t>
   </si>
   <si>
-    <t>WTP for ES appliance in presence of rebate compared to no rebate</t>
-  </si>
-  <si>
     <t>WTP for A+ appliance in presence of a label compared to A</t>
   </si>
   <si>
-    <t>WTP for labelled compared to not labelled appliance</t>
+    <t>no intervention</t>
   </si>
   <si>
-    <t>WTP for labelled appliance in presence compared to absence of information</t>
+    <t>basic intervention</t>
   </si>
 </sst>
 </file>
@@ -35093,7 +35078,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -46856,7 +46841,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$F$2:$F$9</xm:f>
+            <xm:f>'Lists for variables'!$G$2:$G$9</xm:f>
           </x14:formula1>
           <xm:sqref>J54:J1048576</xm:sqref>
         </x14:dataValidation>
@@ -46868,13 +46853,13 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$F$2:$F$10</xm:f>
+            <xm:f>'Lists for variables'!$G$2:$G$10</xm:f>
           </x14:formula1>
           <xm:sqref>J38</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$E$2:$E$4</xm:f>
+            <xm:f>'Lists for variables'!$F$2:$F$4</xm:f>
           </x14:formula1>
           <xm:sqref>AO43:AO51</xm:sqref>
         </x14:dataValidation>
@@ -46898,10 +46883,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:CH75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="136" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
     <col min="5" max="5" width="24.625" customWidth="1"/>
     <col min="6" max="6" width="17.625" customWidth="1"/>
     <col min="7" max="7" width="14.125" customWidth="1"/>
@@ -47218,7 +47204,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="2" spans="1:86">
+    <row r="2" spans="1:86" hidden="1">
       <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
@@ -47480,7 +47466,7 @@
         <v>3.0120481927710845E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:86">
+    <row r="3" spans="1:86" hidden="1">
       <c r="A3" s="11" t="s">
         <v>68</v>
       </c>
@@ -47743,7 +47729,7 @@
         <v>2.2883295194508009E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:86">
+    <row r="4" spans="1:86" hidden="1">
       <c r="A4" t="s">
         <v>332</v>
       </c>
@@ -48005,7 +47991,7 @@
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:86" s="101" customFormat="1">
+    <row r="5" spans="1:86" s="101" customFormat="1" hidden="1">
       <c r="A5" t="s">
         <v>332</v>
       </c>
@@ -48269,7 +48255,7 @@
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:86">
+    <row r="6" spans="1:86" hidden="1">
       <c r="A6" t="s">
         <v>332</v>
       </c>
@@ -48531,7 +48517,7 @@
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:86" s="99" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="7" spans="1:86" s="99" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1">
       <c r="A7" t="s">
         <v>332</v>
       </c>
@@ -48795,7 +48781,7 @@
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:86" s="99" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="8" spans="1:86" s="99" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1">
       <c r="A8" s="100" t="s">
         <v>68</v>
       </c>
@@ -49064,7 +49050,7 @@
         <v>312</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C9" s="94">
         <v>1241</v>
@@ -49118,7 +49104,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -49327,7 +49313,7 @@
         <v>312</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C10" s="94">
         <v>1242</v>
@@ -49381,7 +49367,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U10">
         <v>1</v>
@@ -49590,7 +49576,7 @@
         <v>312</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C11" s="94">
         <v>1243</v>
@@ -49644,7 +49630,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U11">
         <v>1</v>
@@ -49853,7 +49839,7 @@
         <v>312</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C12" s="94">
         <v>1244</v>
@@ -49907,7 +49893,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U12">
         <v>1</v>
@@ -50116,7 +50102,7 @@
         <v>312</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C13" s="94">
         <v>1245</v>
@@ -50170,7 +50156,7 @@
         <v>1</v>
       </c>
       <c r="T13" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U13">
         <v>1</v>
@@ -50379,7 +50365,7 @@
         <v>312</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C14" s="94">
         <v>1246</v>
@@ -50433,7 +50419,7 @@
         <v>1</v>
       </c>
       <c r="T14" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U14">
         <v>1</v>
@@ -50637,12 +50623,12 @@
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:86">
+    <row r="15" spans="1:86" hidden="1">
       <c r="A15" s="100" t="s">
         <v>312</v>
       </c>
       <c r="B15" s="100" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C15" s="94">
         <v>1232</v>
@@ -50901,12 +50887,12 @@
         <v>3.1746031746031746E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:86">
+    <row r="16" spans="1:86" hidden="1">
       <c r="A16" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B16" s="100" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="C16" s="11">
         <v>1013</v>
@@ -51163,12 +51149,12 @@
         <v>1.4858841010401188E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:86">
+    <row r="17" spans="1:86" hidden="1">
       <c r="A17" t="s">
         <v>332</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C17" s="94">
         <v>1261</v>
@@ -51425,12 +51411,12 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:86">
+    <row r="18" spans="1:86" hidden="1">
       <c r="A18" t="s">
         <v>332</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C18" s="94">
         <v>1262</v>
@@ -51687,12 +51673,12 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:86">
+    <row r="19" spans="1:86" hidden="1">
       <c r="A19" t="s">
         <v>332</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C19" s="94">
         <v>1263</v>
@@ -51949,12 +51935,12 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:86" s="101" customFormat="1">
+    <row r="20" spans="1:86" s="101" customFormat="1" hidden="1">
       <c r="A20" t="s">
         <v>332</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C20" s="94">
         <v>1264</v>
@@ -52213,12 +52199,12 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:86" s="101" customFormat="1">
+    <row r="21" spans="1:86" s="101" customFormat="1" hidden="1">
       <c r="A21" t="s">
         <v>332</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C21" s="94">
         <v>1265</v>
@@ -52482,7 +52468,7 @@
         <v>68</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C22" s="96">
         <v>1155</v>
@@ -52535,8 +52521,8 @@
       <c r="S22">
         <v>0</v>
       </c>
-      <c r="T22" s="32" t="s">
-        <v>263</v>
+      <c r="T22" t="s">
+        <v>228</v>
       </c>
       <c r="U22">
         <v>0</v>
@@ -52746,7 +52732,7 @@
         <v>68</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C23" s="96">
         <v>1156</v>
@@ -52799,8 +52785,8 @@
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23" s="32" t="s">
-        <v>263</v>
+      <c r="T23" t="s">
+        <v>228</v>
       </c>
       <c r="U23">
         <v>0</v>
@@ -53008,7 +52994,7 @@
         <v>68</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C24" s="96">
         <v>1191</v>
@@ -53061,8 +53047,8 @@
       <c r="S24">
         <v>1</v>
       </c>
-      <c r="T24" s="32" t="s">
-        <v>263</v>
+      <c r="T24" t="s">
+        <v>228</v>
       </c>
       <c r="U24">
         <v>1</v>
@@ -53269,7 +53255,7 @@
         <v>68</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C25" s="96">
         <v>1192</v>
@@ -53322,8 +53308,8 @@
       <c r="S25">
         <v>1</v>
       </c>
-      <c r="T25" s="32" t="s">
-        <v>263</v>
+      <c r="T25" t="s">
+        <v>228</v>
       </c>
       <c r="U25">
         <v>1</v>
@@ -53530,7 +53516,7 @@
         <v>68</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C26" s="96">
         <v>1180</v>
@@ -53583,8 +53569,8 @@
       <c r="S26">
         <v>1</v>
       </c>
-      <c r="T26" s="32" t="s">
-        <v>263</v>
+      <c r="T26" t="s">
+        <v>228</v>
       </c>
       <c r="U26">
         <v>1</v>
@@ -53791,7 +53777,7 @@
         <v>68</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C27" s="96">
         <v>1181</v>
@@ -53844,8 +53830,8 @@
       <c r="S27">
         <v>1</v>
       </c>
-      <c r="T27" s="32" t="s">
-        <v>263</v>
+      <c r="T27" t="s">
+        <v>228</v>
       </c>
       <c r="U27">
         <v>1</v>
@@ -54055,7 +54041,7 @@
         <v>68</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C28" s="96">
         <v>1182</v>
@@ -54108,8 +54094,8 @@
       <c r="S28">
         <v>1</v>
       </c>
-      <c r="T28" s="32" t="s">
-        <v>263</v>
+      <c r="T28" t="s">
+        <v>228</v>
       </c>
       <c r="U28">
         <v>1</v>
@@ -54319,7 +54305,7 @@
         <v>68</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C29" s="96">
         <v>1183</v>
@@ -54372,8 +54358,8 @@
       <c r="S29">
         <v>1</v>
       </c>
-      <c r="T29" s="32" t="s">
-        <v>263</v>
+      <c r="T29" t="s">
+        <v>228</v>
       </c>
       <c r="U29">
         <v>1</v>
@@ -54583,7 +54569,7 @@
         <v>68</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C30" s="96">
         <v>1184</v>
@@ -54636,8 +54622,8 @@
       <c r="S30">
         <v>1</v>
       </c>
-      <c r="T30" s="32" t="s">
-        <v>263</v>
+      <c r="T30" t="s">
+        <v>228</v>
       </c>
       <c r="U30">
         <v>1</v>
@@ -54847,7 +54833,7 @@
         <v>68</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C31" s="96">
         <v>1185</v>
@@ -54900,8 +54886,8 @@
       <c r="S31">
         <v>1</v>
       </c>
-      <c r="T31" s="32" t="s">
-        <v>263</v>
+      <c r="T31" t="s">
+        <v>228</v>
       </c>
       <c r="U31">
         <v>1</v>
@@ -55108,7 +55094,7 @@
         <v>68</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C32" s="96">
         <v>1186</v>
@@ -55161,8 +55147,8 @@
       <c r="S32">
         <v>1</v>
       </c>
-      <c r="T32" s="32" t="s">
-        <v>263</v>
+      <c r="T32" t="s">
+        <v>228</v>
       </c>
       <c r="U32">
         <v>1</v>
@@ -55364,12 +55350,12 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:86" ht="15.75" customHeight="1">
+    <row r="33" spans="1:86" ht="15.75" hidden="1" customHeight="1">
       <c r="A33" t="s">
         <v>332</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C33" s="94">
         <v>1258</v>
@@ -55626,12 +55612,12 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:86">
+    <row r="34" spans="1:86" hidden="1">
       <c r="A34" t="s">
         <v>332</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C34" s="94">
         <v>1259</v>
@@ -55888,12 +55874,12 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:86">
+    <row r="35" spans="1:86" hidden="1">
       <c r="A35" t="s">
         <v>332</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C35" s="94">
         <v>1260</v>
@@ -56155,7 +56141,7 @@
         <v>68</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C36" s="96">
         <v>1189</v>
@@ -56208,8 +56194,8 @@
       <c r="S36">
         <v>1</v>
       </c>
-      <c r="T36" s="32" t="s">
-        <v>263</v>
+      <c r="T36" t="s">
+        <v>228</v>
       </c>
       <c r="U36">
         <v>1</v>
@@ -56401,7 +56387,7 @@
         <v>68</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C37" s="96">
         <v>1190</v>
@@ -56454,8 +56440,8 @@
       <c r="S37">
         <v>1</v>
       </c>
-      <c r="T37" s="32" t="s">
-        <v>263</v>
+      <c r="T37" t="s">
+        <v>228</v>
       </c>
       <c r="U37">
         <v>1</v>
@@ -56647,7 +56633,7 @@
         <v>68</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C38" s="96">
         <v>1187</v>
@@ -56701,7 +56687,7 @@
         <v>1</v>
       </c>
       <c r="T38" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U38">
         <v>1</v>
@@ -56893,7 +56879,7 @@
         <v>68</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C39" s="96">
         <v>1188</v>
@@ -56946,8 +56932,8 @@
       <c r="S39">
         <v>1</v>
       </c>
-      <c r="T39" s="32" t="s">
-        <v>263</v>
+      <c r="T39" t="s">
+        <v>228</v>
       </c>
       <c r="U39">
         <v>1</v>
@@ -57193,7 +57179,7 @@
         <v>1</v>
       </c>
       <c r="T40" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U40">
         <v>1</v>
@@ -57454,7 +57440,7 @@
         <v>1</v>
       </c>
       <c r="T41" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U41">
         <v>1</v>
@@ -57715,7 +57701,7 @@
         <v>1</v>
       </c>
       <c r="T42" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U42">
         <v>1</v>
@@ -57976,7 +57962,7 @@
         <v>1</v>
       </c>
       <c r="T43" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U43">
         <v>1</v>
@@ -58237,7 +58223,7 @@
         <v>1</v>
       </c>
       <c r="T44" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U44">
         <v>1</v>
@@ -58498,7 +58484,7 @@
         <v>1</v>
       </c>
       <c r="T45" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="U45">
         <v>1</v>
@@ -58700,12 +58686,12 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:86">
+    <row r="46" spans="1:86" hidden="1">
       <c r="A46" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C46" s="11">
         <v>1099</v>
@@ -58961,12 +58947,12 @@
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:86">
+    <row r="47" spans="1:86" hidden="1">
       <c r="A47" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C47" s="11">
         <v>1100</v>
@@ -59222,12 +59208,12 @@
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:86">
+    <row r="48" spans="1:86" hidden="1">
       <c r="A48" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C48" s="94">
         <v>1235</v>
@@ -59484,12 +59470,12 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="49" spans="1:86" s="101" customFormat="1">
+    <row r="49" spans="1:86" s="101" customFormat="1" hidden="1">
       <c r="A49" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C49" s="94">
         <v>1236</v>
@@ -59748,12 +59734,12 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="50" spans="1:86" s="101" customFormat="1">
+    <row r="50" spans="1:86" s="101" customFormat="1" hidden="1">
       <c r="A50" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C50" s="94">
         <v>1237</v>
@@ -60012,12 +59998,12 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="51" spans="1:86" s="101" customFormat="1">
+    <row r="51" spans="1:86" s="101" customFormat="1" hidden="1">
       <c r="A51" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C51" s="94">
         <v>1238</v>
@@ -60276,12 +60262,12 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="52" spans="1:86">
+    <row r="52" spans="1:86" hidden="1">
       <c r="A52" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C52" s="94">
         <v>1239</v>
@@ -60537,12 +60523,12 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="53" spans="1:86">
+    <row r="53" spans="1:86" hidden="1">
       <c r="A53" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C53" s="94">
         <v>1240</v>
@@ -60803,7 +60789,7 @@
         <v>68</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C54" s="96">
         <v>1172</v>
@@ -60856,8 +60842,8 @@
       <c r="S54">
         <v>1</v>
       </c>
-      <c r="T54" s="32" t="s">
-        <v>263</v>
+      <c r="T54" t="s">
+        <v>228</v>
       </c>
       <c r="U54">
         <v>1</v>
@@ -61064,7 +61050,7 @@
         <v>68</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C55" s="96">
         <v>1173</v>
@@ -61117,8 +61103,8 @@
       <c r="S55">
         <v>1</v>
       </c>
-      <c r="T55" s="32" t="s">
-        <v>263</v>
+      <c r="T55" t="s">
+        <v>228</v>
       </c>
       <c r="U55">
         <v>1</v>
@@ -61325,7 +61311,7 @@
         <v>68</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C56" s="96">
         <v>1174</v>
@@ -61378,8 +61364,8 @@
       <c r="S56">
         <v>1</v>
       </c>
-      <c r="T56" s="32" t="s">
-        <v>263</v>
+      <c r="T56" t="s">
+        <v>228</v>
       </c>
       <c r="U56">
         <v>1</v>
@@ -61586,7 +61572,7 @@
         <v>68</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C57" s="96">
         <v>1175</v>
@@ -61639,8 +61625,8 @@
       <c r="S57">
         <v>1</v>
       </c>
-      <c r="T57" s="32" t="s">
-        <v>263</v>
+      <c r="T57" t="s">
+        <v>228</v>
       </c>
       <c r="U57">
         <v>1</v>
@@ -61847,7 +61833,7 @@
         <v>68</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C58" s="96">
         <v>1176</v>
@@ -61900,8 +61886,8 @@
       <c r="S58">
         <v>1</v>
       </c>
-      <c r="T58" s="32" t="s">
-        <v>263</v>
+      <c r="T58" t="s">
+        <v>228</v>
       </c>
       <c r="U58">
         <v>1</v>
@@ -62108,7 +62094,7 @@
         <v>68</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C59" s="96">
         <v>1177</v>
@@ -62161,8 +62147,8 @@
       <c r="S59">
         <v>1</v>
       </c>
-      <c r="T59" s="32" t="s">
-        <v>263</v>
+      <c r="T59" t="s">
+        <v>228</v>
       </c>
       <c r="U59">
         <v>1</v>
@@ -62369,7 +62355,7 @@
         <v>68</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C60" s="96">
         <v>1178</v>
@@ -62422,8 +62408,8 @@
       <c r="S60">
         <v>1</v>
       </c>
-      <c r="T60" s="32" t="s">
-        <v>263</v>
+      <c r="T60" t="s">
+        <v>228</v>
       </c>
       <c r="U60">
         <v>1</v>
@@ -62630,7 +62616,7 @@
         <v>68</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C61" s="96">
         <v>1179</v>
@@ -62683,8 +62669,8 @@
       <c r="S61">
         <v>1</v>
       </c>
-      <c r="T61" s="32" t="s">
-        <v>263</v>
+      <c r="T61" t="s">
+        <v>228</v>
       </c>
       <c r="U61">
         <v>1</v>
@@ -62936,7 +62922,13 @@
       <c r="BB75" s="112"/>
     </row>
   </sheetData>
-  <autoFilter ref="AR1:AR70"/>
+  <autoFilter ref="T1:T75">
+    <filterColumn colId="0">
+      <filters blank="1">
+        <filter val="opt_out"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState ref="A2:CH75">
     <sortCondition ref="E1:E75"/>
   </sortState>
@@ -62952,7 +62944,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations xWindow="603" yWindow="1085" count="7">
+  <dataValidations xWindow="603" yWindow="1085" count="33">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN27:AP30 AH31:AP42 AH7:AH8 AJ7:AP8 AH55:AP1048576 AL27 AH26:AK27 AL26:AP26 AH28:AL30 S15:S30 S1 U1 AH43:AQ54 U39:U1048576 S34:S1048576 U15:U35 AH15:AP25 AH1:AI1 AK1:AP1">
       <formula1>0</formula1>
       <formula2>1</formula2>
@@ -62975,13 +62967,91 @@
       <formula1>1</formula1>
       <formula2>3</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV62:AV1048576">
+      <formula1>$J$2:$J$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1">
+      <formula1>$M$2:$M$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S55:S1048576">
+      <formula1>$M$2:$M$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U62:U1048576">
+      <formula1>$M$2:$M$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1">
+      <formula1>$L$2:$L$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S55:S1048576">
+      <formula1>$L$2:$L$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U62:W1048576">
+      <formula1>$L$2:$L$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1">
+      <formula1>$O$2:$O$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S55:S1048576">
+      <formula1>$O$2:$O$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U62:W1048576">
+      <formula1>$O$2:$O$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K62:K1048576">
+      <formula1>$K$2:$K$12</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BT62:BT1048576">
+      <formula1>$P:$P</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G62:G1048576">
+      <formula1>$T:$T</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR55:AR1048576">
+      <formula1>$H:$H</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT55:AT1048576">
+      <formula1>$Q:$Q</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O55:O1048576">
+      <formula1>$O:$O</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E55:E1048576">
+      <formula1>$S:$S</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1">
+      <formula1>$I:$I</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1">
+      <formula1>$I:$I</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S55:S1048576">
+      <formula1>$I:$I</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P27:P30">
+      <formula1>$N:$N</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P1">
+      <formula1>$N:$N</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1">
+      <formula1>$N:$N</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S55:S1048576">
+      <formula1>$N:$N</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P55:P1048576">
+      <formula1>$N:$N</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U62:U1048576">
+      <formula1>$N:$N</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="603" yWindow="1085" count="21">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="603" yWindow="1085" count="22">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
@@ -63002,63 +63072,63 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$I$2:$I$3</xm:f>
+            <xm:f>'Lists for variables'!$J$2:$J$3</xm:f>
           </x14:formula1>
-          <xm:sqref>AV1 AV62:AV1048576</xm:sqref>
+          <xm:sqref>AV1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$L$2:$L$9</xm:f>
+            <xm:f>'Lists for variables'!$M$2:$M$9</xm:f>
           </x14:formula1>
-          <xm:sqref>U1 S1 S55:S1048576 U62:U1048576</xm:sqref>
+          <xm:sqref>U1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$K$2:$K$3</xm:f>
+            <xm:f>'Lists for variables'!$L$2:$L$3</xm:f>
           </x14:formula1>
-          <xm:sqref>U1:W1 S1 S55:S1048576 U62:W1048576</xm:sqref>
+          <xm:sqref>U1:W1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$N$2:$N$7</xm:f>
+            <xm:f>'Lists for variables'!$O$2:$O$7</xm:f>
           </x14:formula1>
-          <xm:sqref>U1:W1 S1 S55:S1048576 U62:W1048576</xm:sqref>
+          <xm:sqref>U1:W1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$J$2:$J$12</xm:f>
+            <xm:f>'Lists for variables'!$K$2:$K$12</xm:f>
           </x14:formula1>
-          <xm:sqref>K1 K62:K1048576</xm:sqref>
+          <xm:sqref>K1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$O:$O</xm:f>
+            <xm:f>'Lists for variables'!$P:$P</xm:f>
           </x14:formula1>
-          <xm:sqref>BT1 BT62:BT1048576</xm:sqref>
+          <xm:sqref>BT1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$S:$S</xm:f>
+            <xm:f>'Lists for variables'!$T:$T</xm:f>
           </x14:formula1>
-          <xm:sqref>G1 G62:G1048576</xm:sqref>
+          <xm:sqref>G1</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'Lists for variables'!$H:$H</xm:f>
+          </x14:formula1>
+          <xm:sqref>AR1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G:$G</xm:f>
           </x14:formula1>
-          <xm:sqref>AR1 AR55:AR1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>'Lists for variables'!$F:$F</xm:f>
-          </x14:formula1>
           <xm:sqref>M76:M1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$P:$P</xm:f>
+            <xm:f>'Lists for variables'!$Q:$Q</xm:f>
           </x14:formula1>
-          <xm:sqref>AT1 AT55:AT1048576</xm:sqref>
+          <xm:sqref>AT1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -63068,45 +63138,51 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$N:$N</xm:f>
+            <xm:f>'Lists for variables'!$O:$O</xm:f>
           </x14:formula1>
-          <xm:sqref>O1 O55:O1048576</xm:sqref>
+          <xm:sqref>O1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B:$B</xm:f>
           </x14:formula1>
-          <xm:sqref>T1 T55:T1048576</xm:sqref>
+          <xm:sqref>T1 T62:T1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$R:$R</xm:f>
+            <xm:f>'Lists for variables'!$S:$S</xm:f>
           </x14:formula1>
-          <xm:sqref>E1 E55:E1048576</xm:sqref>
+          <xm:sqref>E1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$H:$H</xm:f>
+            <xm:f>'Lists for variables'!$I:$I</xm:f>
           </x14:formula1>
-          <xm:sqref>U62:U1048576 U1 S1 S55:S1048576</xm:sqref>
+          <xm:sqref>U62:U1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$M:$M</xm:f>
+            <xm:f>'Lists for variables'!$N:$N</xm:f>
           </x14:formula1>
-          <xm:sqref>S1 P27:P30 P1 U1 S55:S1048576 P55:P1048576 U62:U1048576</xm:sqref>
+          <xm:sqref>S1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$L$2:$L$10</xm:f>
+            <xm:f>'Lists for variables'!$M$2:$M$10</xm:f>
           </x14:formula1>
           <xm:sqref>R1:R1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>'Lists for variables'!$H$1:$H$7</xm:f>
+            <xm:f>'Lists for variables'!$I$1:$I$7</xm:f>
           </x14:formula1>
           <xm:sqref>Q1:Q1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'Lists for variables'!$E$2:$E$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>B1:B1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -66021,75 +66097,78 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S99"/>
+  <dimension ref="A1:T99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="19.625" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18.125" style="26" customWidth="1"/>
-    <col min="8" max="8" width="20.5" customWidth="1"/>
-    <col min="9" max="9" width="14.125" customWidth="1"/>
-    <col min="10" max="10" width="15.125" customWidth="1"/>
+    <col min="6" max="6" width="19.625" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="18.125" style="26" customWidth="1"/>
+    <col min="9" max="9" width="20.5" customWidth="1"/>
+    <col min="10" max="10" width="14.125" customWidth="1"/>
+    <col min="11" max="11" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" t="s">
+    <row r="1" spans="1:20" s="39" customFormat="1">
+      <c r="A1" s="39" t="s">
         <v>425</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="39" t="s">
         <v>188</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="39" t="s">
+        <v>644</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="H1" s="37" t="s">
         <v>427</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="I1" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="J1" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="K1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="L1" s="39" t="s">
         <v>428</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="M1" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="M1" s="39" t="s">
+      <c r="N1" s="39" t="s">
         <v>184</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="O1" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="O1" s="39" t="s">
+      <c r="P1" s="39" t="s">
         <v>210</v>
       </c>
-      <c r="P1" s="42" t="s">
+      <c r="Q1" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="R1" s="39" t="s">
+      <c r="S1" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="S1" s="39" t="s">
+      <c r="T1" s="39" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="31.5">
+    <row r="2" spans="1:20" ht="31.5">
       <c r="A2">
         <v>0</v>
       </c>
@@ -66102,50 +66181,53 @@
       <c r="D2" t="s">
         <v>112</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" t="s">
+        <v>655</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="H2" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>226</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>80</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>430</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>229</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>431</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>225</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>81</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>248</v>
       </c>
-      <c r="P2" s="41" t="s">
+      <c r="Q2" s="41" t="s">
         <v>331</v>
       </c>
-      <c r="R2" s="47" t="s">
+      <c r="S2" s="47" t="s">
         <v>432</v>
       </c>
-      <c r="S2" s="47" t="s">
+      <c r="T2" s="47" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="31.5">
+    <row r="3" spans="1:20" ht="31.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -66158,50 +66240,53 @@
       <c r="D3" t="s">
         <v>240</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="26" t="s">
+        <v>656</v>
+      </c>
+      <c r="F3">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>422</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>434</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>252</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>86</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>435</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>311</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>227</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>241</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>148</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>436</v>
       </c>
-      <c r="P3" s="41" t="s">
+      <c r="Q3" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>437</v>
       </c>
-      <c r="S3" s="46" t="s">
+      <c r="T3" s="46" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="47.25">
+    <row r="4" spans="1:20" ht="47.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -66214,1046 +66299,1047 @@
       <c r="D4" t="s">
         <v>223</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>3</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>439</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>354</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>310</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>440</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>253</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>441</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>442</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>236</v>
       </c>
-      <c r="P4" s="41" t="s">
+      <c r="Q4" s="41" t="s">
         <v>443</v>
       </c>
-      <c r="R4" s="44" t="s">
+      <c r="S4" s="44" t="s">
         <v>444</v>
       </c>
-      <c r="S4" s="44" t="s">
+      <c r="T4" s="44" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="47.25">
+    <row r="5" spans="1:20" ht="47.25">
       <c r="D5" t="s">
         <v>446</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>120</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="H5" s="40" t="s">
         <v>447</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>448</v>
       </c>
-      <c r="J5" s="41" t="s">
+      <c r="K5" s="41" t="s">
         <v>449</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>450</v>
       </c>
-      <c r="M5" t="s">
-        <v>73</v>
-      </c>
       <c r="N5" t="s">
+        <v>73</v>
+      </c>
+      <c r="O5" t="s">
         <v>124</v>
       </c>
-      <c r="O5" s="41" t="s">
+      <c r="P5" s="41" t="s">
         <v>319</v>
       </c>
-      <c r="P5" t="s">
-        <v>73</v>
-      </c>
-      <c r="R5" s="46" t="s">
+      <c r="Q5" t="s">
+        <v>73</v>
+      </c>
+      <c r="S5" s="46" t="s">
         <v>451</v>
       </c>
-      <c r="S5" s="46" t="s">
+      <c r="T5" s="46" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:20">
       <c r="D6" s="41" t="s">
         <v>317</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E6" s="41"/>
+      <c r="G6" t="s">
         <v>453</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>242</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>454</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>455</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>278</v>
       </c>
-      <c r="O6" t="s">
-        <v>73</v>
-      </c>
-      <c r="R6" s="46" t="s">
+      <c r="P6" t="s">
+        <v>73</v>
+      </c>
+      <c r="S6" s="46" t="s">
         <v>456</v>
       </c>
-      <c r="S6" s="46" t="s">
+      <c r="T6" s="46" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
-      <c r="F7" t="s">
+    <row r="7" spans="1:20">
+      <c r="G7" t="s">
         <v>458</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>459</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="K7" s="41" t="s">
         <v>460</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>243</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>461</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>462</v>
       </c>
-      <c r="R7" s="46" t="s">
+      <c r="S7" s="46" t="s">
         <v>463</v>
       </c>
-      <c r="S7" s="46" t="s">
+      <c r="T7" s="46" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
-      <c r="F8" t="s">
+    <row r="8" spans="1:20">
+      <c r="G8" t="s">
         <v>107</v>
       </c>
-      <c r="J8" s="41" t="s">
+      <c r="K8" s="41" t="s">
         <v>465</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>462</v>
       </c>
-      <c r="N8" t="s">
+      <c r="O8" t="s">
         <v>466</v>
       </c>
-      <c r="R8" s="46" t="s">
+      <c r="S8" s="46" t="s">
         <v>249</v>
       </c>
-      <c r="S8" s="46" t="s">
+      <c r="T8" s="46" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
-      <c r="F9" t="s">
+    <row r="9" spans="1:20">
+      <c r="G9" t="s">
         <v>417</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>462</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>467</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>468</v>
       </c>
-      <c r="R9" s="44" t="s">
+      <c r="S9" s="44" t="s">
         <v>349</v>
       </c>
-      <c r="S9" s="44" t="s">
+      <c r="T9" s="44" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
-      <c r="F10" t="s">
+    <row r="10" spans="1:20">
+      <c r="G10" t="s">
         <v>155</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>469</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>257</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>224</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>470</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="T10" s="44" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
-      <c r="F11" t="s">
+    <row r="11" spans="1:20">
+      <c r="G11" t="s">
         <v>472</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>473</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>474</v>
       </c>
-      <c r="R11" s="44" t="s">
+      <c r="S11" s="44" t="s">
         <v>475</v>
       </c>
-      <c r="S11" s="44" t="s">
+      <c r="T11" s="44" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
-      <c r="F12" t="s">
+    <row r="12" spans="1:20">
+      <c r="G12" t="s">
         <v>477</v>
       </c>
-      <c r="J12" t="s">
-        <v>73</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="K12" t="s">
+        <v>73</v>
+      </c>
+      <c r="O12" t="s">
         <v>478</v>
       </c>
-      <c r="R12" s="44" t="s">
+      <c r="S12" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="S12" s="44" t="s">
+      <c r="T12" s="44" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
-      <c r="F13" t="s">
+    <row r="13" spans="1:20">
+      <c r="G13" t="s">
         <v>418</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>96</v>
       </c>
-      <c r="R13" s="46" t="s">
+      <c r="S13" s="46" t="s">
         <v>481</v>
       </c>
-      <c r="S13" s="46" t="s">
+      <c r="T13" s="46" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
-      <c r="F14" s="41" t="s">
+    <row r="14" spans="1:20">
+      <c r="G14" s="41" t="s">
         <v>421</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>483</v>
       </c>
-      <c r="R14" s="44" t="s">
+      <c r="S14" s="44" t="s">
         <v>484</v>
       </c>
-      <c r="S14" s="44" t="s">
+      <c r="T14" s="44" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
-      <c r="F15" s="41" t="s">
+    <row r="15" spans="1:20">
+      <c r="G15" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>486</v>
       </c>
-      <c r="R15" s="46" t="s">
+      <c r="S15" s="46" t="s">
         <v>487</v>
       </c>
-      <c r="S15" s="46" t="s">
+      <c r="T15" s="46" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
-      <c r="F16" s="41" t="s">
+    <row r="16" spans="1:20">
+      <c r="G16" s="41" t="s">
         <v>489</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>156</v>
       </c>
-      <c r="R16" s="46" t="s">
+      <c r="S16" s="46" t="s">
         <v>490</v>
       </c>
-      <c r="S16" s="46" t="s">
+      <c r="T16" s="46" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="17" spans="6:19">
-      <c r="F17" s="41" t="s">
+    <row r="17" spans="7:20">
+      <c r="G17" s="41" t="s">
         <v>274</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>492</v>
       </c>
-      <c r="R17" s="44" t="s">
+      <c r="S17" s="44" t="s">
         <v>493</v>
       </c>
-      <c r="S17" s="44" t="s">
+      <c r="T17" s="44" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="18" spans="6:19">
-      <c r="F18" s="41" t="s">
+    <row r="18" spans="7:20">
+      <c r="G18" s="41" t="s">
         <v>420</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>262</v>
       </c>
-      <c r="R18" s="46" t="s">
+      <c r="S18" s="46" t="s">
         <v>495</v>
       </c>
-      <c r="S18" s="46" t="s">
+      <c r="T18" s="46" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="19" spans="6:19">
-      <c r="F19" s="41" t="s">
+    <row r="19" spans="7:20">
+      <c r="G19" s="41" t="s">
         <v>496</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>497</v>
       </c>
-      <c r="R19" s="44" t="s">
+      <c r="S19" s="44" t="s">
         <v>237</v>
       </c>
-      <c r="S19" t="s">
+      <c r="T19" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="20" spans="6:19">
-      <c r="F20" s="41" t="s">
+    <row r="20" spans="7:20">
+      <c r="G20" s="41" t="s">
         <v>498</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>499</v>
       </c>
-      <c r="R20" s="46" t="s">
+      <c r="S20" s="46" t="s">
         <v>500</v>
       </c>
-      <c r="S20" s="46" t="s">
+      <c r="T20" s="46" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="21" spans="6:19">
-      <c r="F21" s="41" t="s">
+    <row r="21" spans="7:20">
+      <c r="G21" s="41" t="s">
         <v>502</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>503</v>
       </c>
-      <c r="R21" s="44" t="s">
+      <c r="S21" s="44" t="s">
         <v>504</v>
       </c>
-      <c r="S21" s="44" t="s">
+      <c r="T21" s="44" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="22" spans="6:19">
-      <c r="F22" s="41" t="s">
+    <row r="22" spans="7:20">
+      <c r="G22" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>138</v>
       </c>
-      <c r="R22" s="46" t="s">
+      <c r="S22" s="46" t="s">
         <v>504</v>
       </c>
-      <c r="S22" s="46" t="s">
+      <c r="T22" s="46" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="23" spans="6:19">
-      <c r="F23" s="41" t="s">
+    <row r="23" spans="7:20">
+      <c r="G23" s="41" t="s">
         <v>423</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>507</v>
       </c>
-      <c r="R23" s="44" t="s">
+      <c r="S23" s="44" t="s">
         <v>508</v>
       </c>
-      <c r="S23" s="44" t="s">
+      <c r="T23" s="44" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="24" spans="6:19">
-      <c r="F24" s="41" t="s">
+    <row r="24" spans="7:20">
+      <c r="G24" s="41" t="s">
         <v>510</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>270</v>
       </c>
-      <c r="R24" s="44" t="s">
+      <c r="S24" s="44" t="s">
         <v>511</v>
       </c>
-      <c r="S24" s="44" t="s">
+      <c r="T24" s="44" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="25" spans="6:19">
-      <c r="F25" s="41" t="s">
+    <row r="25" spans="7:20">
+      <c r="G25" s="41" t="s">
         <v>419</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>513</v>
       </c>
-      <c r="R25" s="44" t="s">
+      <c r="S25" s="44" t="s">
         <v>326</v>
       </c>
-      <c r="S25" s="44" t="s">
+      <c r="T25" s="44" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="26" spans="6:19">
-      <c r="F26" s="41" t="s">
+    <row r="26" spans="7:20">
+      <c r="G26" s="41" t="s">
         <v>514</v>
       </c>
-      <c r="N26" t="s">
+      <c r="O26" t="s">
         <v>515</v>
       </c>
-      <c r="R26" s="44" t="s">
+      <c r="S26" s="44" t="s">
         <v>516</v>
       </c>
-      <c r="S26" s="44" t="s">
+      <c r="T26" s="44" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="27" spans="6:19">
-      <c r="F27" s="41" t="s">
+    <row r="27" spans="7:20">
+      <c r="G27" s="41" t="s">
         <v>297</v>
       </c>
-      <c r="N27" t="s">
+      <c r="O27" t="s">
         <v>336</v>
       </c>
-      <c r="R27" s="44" t="s">
+      <c r="S27" s="44" t="s">
         <v>518</v>
       </c>
-      <c r="S27" s="44" t="s">
+      <c r="T27" s="44" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="28" spans="6:19">
-      <c r="F28" s="41" t="s">
+    <row r="28" spans="7:20">
+      <c r="G28" s="41" t="s">
         <v>520</v>
       </c>
-      <c r="N28" t="s">
+      <c r="O28" t="s">
         <v>521</v>
       </c>
-      <c r="R28" s="44" t="s">
+      <c r="S28" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="S28" s="44" t="s">
+      <c r="T28" s="44" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="29" spans="6:19">
-      <c r="F29" s="41" t="s">
+    <row r="29" spans="7:20">
+      <c r="G29" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
         <v>522</v>
       </c>
-      <c r="R29" s="44" t="s">
+      <c r="S29" s="44" t="s">
         <v>523</v>
       </c>
-      <c r="S29" s="44" t="s">
+      <c r="T29" s="44" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="30" spans="6:19">
-      <c r="F30" s="41" t="s">
+    <row r="30" spans="7:20">
+      <c r="G30" s="41" t="s">
         <v>525</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
         <v>526</v>
       </c>
-      <c r="R30" s="44" t="s">
+      <c r="S30" s="44" t="s">
         <v>527</v>
       </c>
-      <c r="S30" s="44" t="s">
+      <c r="T30" s="44" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="31" spans="6:19">
-      <c r="N31" t="s">
+    <row r="31" spans="7:20">
+      <c r="O31" t="s">
         <v>174</v>
       </c>
-      <c r="R31" s="44" t="s">
+      <c r="S31" s="44" t="s">
         <v>529</v>
       </c>
-      <c r="S31" s="44" t="s">
+      <c r="T31" s="44" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="32" spans="6:19">
-      <c r="N32" t="s">
+    <row r="32" spans="7:20">
+      <c r="O32" t="s">
         <v>531</v>
       </c>
-      <c r="R32" s="44" t="s">
+      <c r="S32" s="44" t="s">
         <v>532</v>
       </c>
-      <c r="S32" s="44" t="s">
+      <c r="T32" s="44" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="33" spans="14:19">
-      <c r="N33" t="s">
+    <row r="33" spans="15:20">
+      <c r="O33" t="s">
         <v>131</v>
       </c>
-      <c r="R33" s="44" t="s">
+      <c r="S33" s="44" t="s">
         <v>534</v>
       </c>
-      <c r="S33" s="44" t="s">
+      <c r="T33" s="44" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="34" spans="14:19">
-      <c r="R34" s="44" t="s">
+    <row r="34" spans="15:20">
+      <c r="S34" s="44" t="s">
         <v>536</v>
       </c>
-      <c r="S34" s="44" t="s">
+      <c r="T34" s="44" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="35" spans="14:19">
-      <c r="R35" s="44" t="s">
+    <row r="35" spans="15:20">
+      <c r="S35" s="44" t="s">
         <v>341</v>
       </c>
-      <c r="S35" s="44" t="s">
+      <c r="T35" s="44" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="36" spans="14:19">
-      <c r="R36" s="44" t="s">
+    <row r="36" spans="15:20">
+      <c r="S36" s="44" t="s">
         <v>538</v>
       </c>
-      <c r="S36" s="44" t="s">
+      <c r="T36" s="44" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="37" spans="14:19">
-      <c r="R37" s="46" t="s">
+    <row r="37" spans="15:20">
+      <c r="S37" s="46" t="s">
         <v>540</v>
       </c>
-      <c r="S37" s="46" t="s">
+      <c r="T37" s="46" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="38" spans="14:19">
-      <c r="R38" s="46" t="s">
+    <row r="38" spans="15:20">
+      <c r="S38" s="46" t="s">
         <v>542</v>
       </c>
-      <c r="S38" s="46" t="s">
+      <c r="T38" s="46" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="39" spans="14:19">
-      <c r="R39" s="46" t="s">
+    <row r="39" spans="15:20">
+      <c r="S39" s="46" t="s">
         <v>542</v>
       </c>
-      <c r="S39" s="46" t="s">
+      <c r="T39" s="46" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="40" spans="14:19">
-      <c r="R40" s="44" t="s">
+    <row r="40" spans="15:20">
+      <c r="S40" s="44" t="s">
         <v>545</v>
       </c>
-      <c r="S40" s="44" t="s">
+      <c r="T40" s="44" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="41" spans="14:19">
-      <c r="R41" s="44" t="s">
+    <row r="41" spans="15:20">
+      <c r="S41" s="44" t="s">
         <v>547</v>
       </c>
-      <c r="S41" s="44" t="s">
+      <c r="T41" s="44" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="42" spans="14:19">
-      <c r="R42" s="46" t="s">
+    <row r="42" spans="15:20">
+      <c r="S42" s="46" t="s">
         <v>549</v>
       </c>
-      <c r="S42" s="46" t="s">
+      <c r="T42" s="46" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="43" spans="14:19">
-      <c r="R43" s="46" t="s">
+    <row r="43" spans="15:20">
+      <c r="S43" s="46" t="s">
         <v>549</v>
       </c>
-      <c r="S43" s="46" t="s">
+      <c r="T43" s="46" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="44" spans="14:19">
-      <c r="R44" s="44" t="s">
+    <row r="44" spans="15:20">
+      <c r="S44" s="44" t="s">
         <v>552</v>
       </c>
-      <c r="S44" s="17" t="s">
+      <c r="T44" s="17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="14:19">
-      <c r="R45" s="46" t="s">
+    <row r="45" spans="15:20">
+      <c r="S45" s="46" t="s">
         <v>553</v>
       </c>
-      <c r="S45" s="46" t="s">
+      <c r="T45" s="46" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="46" spans="14:19">
-      <c r="R46" s="44" t="s">
+    <row r="46" spans="15:20">
+      <c r="S46" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="S46" s="44" t="s">
+      <c r="T46" s="44" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="47" spans="14:19">
-      <c r="R47" s="46" t="s">
+    <row r="47" spans="15:20">
+      <c r="S47" s="46" t="s">
         <v>555</v>
       </c>
-      <c r="S47" s="46" t="s">
+      <c r="T47" s="46" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="48" spans="14:19">
-      <c r="R48" s="44" t="s">
+    <row r="48" spans="15:20">
+      <c r="S48" s="44" t="s">
         <v>557</v>
       </c>
-      <c r="S48" s="44" t="s">
+      <c r="T48" s="44" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="49" spans="18:19">
-      <c r="R49" s="44" t="s">
+    <row r="49" spans="19:20">
+      <c r="S49" s="44" t="s">
         <v>559</v>
       </c>
-      <c r="S49" s="44" t="s">
+      <c r="T49" s="44" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="50" spans="18:19">
-      <c r="R50" s="44" t="s">
+    <row r="50" spans="19:20">
+      <c r="S50" s="44" t="s">
         <v>561</v>
       </c>
-      <c r="S50" s="44" t="s">
+      <c r="T50" s="44" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="51" spans="18:19">
-      <c r="R51" s="44" t="s">
+    <row r="51" spans="19:20">
+      <c r="S51" s="44" t="s">
         <v>563</v>
       </c>
-      <c r="S51" s="44" t="s">
+      <c r="T51" s="44" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="52" spans="18:19">
-      <c r="R52" s="44" t="s">
+    <row r="52" spans="19:20">
+      <c r="S52" s="44" t="s">
         <v>565</v>
       </c>
-      <c r="S52" s="44" t="s">
+      <c r="T52" s="44" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="53" spans="18:19">
-      <c r="R53" s="44" t="s">
+    <row r="53" spans="19:20">
+      <c r="S53" s="44" t="s">
         <v>567</v>
       </c>
-      <c r="S53" s="17" t="s">
+      <c r="T53" s="17" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="54" spans="18:19">
-      <c r="R54" s="44" t="s">
+    <row r="54" spans="19:20">
+      <c r="S54" s="44" t="s">
         <v>569</v>
       </c>
-      <c r="S54" s="44" t="s">
+      <c r="T54" s="44" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="55" spans="18:19">
-      <c r="R55" s="44" t="s">
+    <row r="55" spans="19:20">
+      <c r="S55" s="44" t="s">
         <v>571</v>
       </c>
-      <c r="S55" s="44" t="s">
+      <c r="T55" s="44" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="56" spans="18:19">
-      <c r="R56" s="44" t="s">
+    <row r="56" spans="19:20">
+      <c r="S56" s="44" t="s">
         <v>573</v>
       </c>
-      <c r="S56" s="44" t="s">
+      <c r="T56" s="44" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="57" spans="18:19">
-      <c r="R57" s="44" t="s">
+    <row r="57" spans="19:20">
+      <c r="S57" s="44" t="s">
         <v>575</v>
       </c>
-      <c r="S57" s="44" t="s">
+      <c r="T57" s="44" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="58" spans="18:19">
-      <c r="R58" s="44" t="s">
+    <row r="58" spans="19:20">
+      <c r="S58" s="44" t="s">
         <v>308</v>
       </c>
-      <c r="S58" s="44" t="s">
+      <c r="T58" s="44" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="59" spans="18:19">
-      <c r="R59" s="44" t="s">
+    <row r="59" spans="19:20">
+      <c r="S59" s="44" t="s">
         <v>577</v>
       </c>
-      <c r="S59" s="44" t="s">
+      <c r="T59" s="44" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="60" spans="18:19">
-      <c r="R60" s="44" t="s">
+    <row r="60" spans="19:20">
+      <c r="S60" s="44" t="s">
         <v>579</v>
       </c>
-      <c r="S60" s="44" t="s">
+      <c r="T60" s="44" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="61" spans="18:19">
-      <c r="R61" s="44" t="s">
+    <row r="61" spans="19:20">
+      <c r="S61" s="44" t="s">
         <v>581</v>
       </c>
-      <c r="S61" s="44" t="s">
+      <c r="T61" s="44" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="62" spans="18:19">
-      <c r="R62" s="44" t="s">
+    <row r="62" spans="19:20">
+      <c r="S62" s="44" t="s">
         <v>583</v>
       </c>
-      <c r="S62" s="44" t="s">
+      <c r="T62" s="44" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="63" spans="18:19">
-      <c r="R63" s="44" t="s">
+    <row r="63" spans="19:20">
+      <c r="S63" s="44" t="s">
         <v>585</v>
       </c>
-      <c r="S63" s="44" t="s">
+      <c r="T63" s="44" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="64" spans="18:19">
-      <c r="R64" s="44" t="s">
+    <row r="64" spans="19:20">
+      <c r="S64" s="44" t="s">
         <v>587</v>
       </c>
-      <c r="S64" s="44" t="s">
+      <c r="T64" s="44" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="65" spans="18:19">
-      <c r="R65" s="44" t="s">
+    <row r="65" spans="19:20">
+      <c r="S65" s="44" t="s">
         <v>589</v>
       </c>
-      <c r="S65" s="44" t="s">
+      <c r="T65" s="44" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="66" spans="18:19">
-      <c r="R66" s="44" t="s">
+    <row r="66" spans="19:20">
+      <c r="S66" s="44" t="s">
         <v>591</v>
       </c>
-      <c r="S66" s="44" t="s">
+      <c r="T66" s="44" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="67" spans="18:19">
-      <c r="R67" s="44" t="s">
+    <row r="67" spans="19:20">
+      <c r="S67" s="44" t="s">
         <v>333</v>
       </c>
-      <c r="S67" s="44" t="s">
+      <c r="T67" s="44" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="68" spans="18:19">
-      <c r="R68" s="44" t="s">
+    <row r="68" spans="19:20">
+      <c r="S68" s="44" t="s">
         <v>593</v>
       </c>
-      <c r="S68" s="44" t="s">
+      <c r="T68" s="44" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="69" spans="18:19">
-      <c r="R69" s="44" t="s">
+    <row r="69" spans="19:20">
+      <c r="S69" s="44" t="s">
         <v>595</v>
       </c>
-      <c r="S69" s="44" t="s">
+      <c r="T69" s="44" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="70" spans="18:19">
-      <c r="R70" s="44" t="s">
+    <row r="70" spans="19:20">
+      <c r="S70" s="44" t="s">
         <v>597</v>
       </c>
-      <c r="S70" s="44" t="s">
+      <c r="T70" s="44" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="71" spans="18:19">
-      <c r="R71" s="44" t="s">
+    <row r="71" spans="19:20">
+      <c r="S71" s="44" t="s">
         <v>599</v>
       </c>
-      <c r="S71" s="44" t="s">
+      <c r="T71" s="44" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="72" spans="18:19">
-      <c r="R72" s="44" t="s">
+    <row r="72" spans="19:20">
+      <c r="S72" s="44" t="s">
         <v>601</v>
       </c>
-      <c r="S72" t="s">
+      <c r="T72" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="73" spans="18:19">
-      <c r="R73" s="46" t="s">
+    <row r="73" spans="19:20">
+      <c r="S73" s="46" t="s">
         <v>601</v>
       </c>
-      <c r="S73" s="46" t="s">
+      <c r="T73" s="46" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="74" spans="18:19">
-      <c r="R74" s="44" t="s">
+    <row r="74" spans="19:20">
+      <c r="S74" s="44" t="s">
         <v>604</v>
       </c>
-      <c r="S74" s="44" t="s">
+      <c r="T74" s="44" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="75" spans="18:19">
-      <c r="R75" s="46" t="s">
+    <row r="75" spans="19:20">
+      <c r="S75" s="46" t="s">
         <v>606</v>
       </c>
-      <c r="S75" s="46" t="s">
+      <c r="T75" s="46" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="76" spans="18:19">
-      <c r="R76" s="44" t="s">
+    <row r="76" spans="19:20">
+      <c r="S76" s="44" t="s">
         <v>608</v>
       </c>
-      <c r="S76" s="44" t="s">
+      <c r="T76" s="44" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="77" spans="18:19">
-      <c r="R77" s="44" t="s">
+    <row r="77" spans="19:20">
+      <c r="S77" s="44" t="s">
         <v>610</v>
       </c>
-      <c r="S77" s="44" t="s">
+      <c r="T77" s="44" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="78" spans="18:19">
-      <c r="R78" s="46" t="s">
+    <row r="78" spans="19:20">
+      <c r="S78" s="46" t="s">
         <v>259</v>
       </c>
-      <c r="S78" s="46" t="s">
+      <c r="T78" s="46" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="79" spans="18:19">
-      <c r="R79" s="46" t="s">
+    <row r="79" spans="19:20">
+      <c r="S79" s="46" t="s">
         <v>612</v>
       </c>
-      <c r="S79" s="46" t="s">
+      <c r="T79" s="46" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="80" spans="18:19">
-      <c r="R80" s="44" t="s">
+    <row r="80" spans="19:20">
+      <c r="S80" s="44" t="s">
         <v>614</v>
       </c>
-      <c r="S80" s="44" t="s">
+      <c r="T80" s="44" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="81" spans="18:19">
-      <c r="R81" s="44" t="s">
+    <row r="81" spans="19:20">
+      <c r="S81" s="44" t="s">
         <v>616</v>
       </c>
-      <c r="S81" s="44" t="s">
+      <c r="T81" s="44" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="82" spans="18:19">
-      <c r="R82" s="44" t="s">
+    <row r="82" spans="19:20">
+      <c r="S82" s="44" t="s">
         <v>618</v>
       </c>
-      <c r="S82" s="44" t="s">
+      <c r="T82" s="44" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="83" spans="18:19">
-      <c r="R83" s="46" t="s">
+    <row r="83" spans="19:20">
+      <c r="S83" s="46" t="s">
         <v>620</v>
       </c>
-      <c r="S83" s="46" t="s">
+      <c r="T83" s="46" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="84" spans="18:19">
-      <c r="R84" s="46" t="s">
+    <row r="84" spans="19:20">
+      <c r="S84" s="46" t="s">
         <v>620</v>
       </c>
-      <c r="S84" s="46" t="s">
+      <c r="T84" s="46" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="85" spans="18:19">
-      <c r="R85" s="44" t="s">
+    <row r="85" spans="19:20">
+      <c r="S85" s="44" t="s">
         <v>623</v>
       </c>
-      <c r="S85" s="44" t="s">
+      <c r="T85" s="44" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="86" spans="18:19">
-      <c r="R86" s="44" t="s">
+    <row r="86" spans="19:20">
+      <c r="S86" s="44" t="s">
         <v>625</v>
       </c>
-      <c r="S86" s="44" t="s">
+      <c r="T86" s="44" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="87" spans="18:19">
-      <c r="R87" s="44" t="s">
+    <row r="87" spans="19:20">
+      <c r="S87" s="44" t="s">
         <v>254</v>
       </c>
-      <c r="S87" s="44" t="s">
+      <c r="T87" s="44" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="88" spans="18:19">
-      <c r="R88" s="44" t="s">
+    <row r="88" spans="19:20">
+      <c r="S88" s="44" t="s">
         <v>627</v>
       </c>
-      <c r="S88" s="44" t="s">
+      <c r="T88" s="44" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="89" spans="18:19">
-      <c r="R89" s="44" t="s">
+    <row r="89" spans="19:20">
+      <c r="S89" s="44" t="s">
         <v>629</v>
       </c>
-      <c r="S89" s="44" t="s">
+      <c r="T89" s="44" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="90" spans="18:19">
-      <c r="R90" s="44" t="s">
+    <row r="90" spans="19:20">
+      <c r="S90" s="44" t="s">
         <v>631</v>
       </c>
-      <c r="S90" s="44" t="s">
+      <c r="T90" s="44" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="91" spans="18:19">
-      <c r="R91" s="44" t="s">
+    <row r="91" spans="19:20">
+      <c r="S91" s="44" t="s">
         <v>633</v>
       </c>
-      <c r="S91" s="44" t="s">
+      <c r="T91" s="44" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="92" spans="18:19">
-      <c r="R92" s="44" t="s">
+    <row r="92" spans="19:20">
+      <c r="S92" s="44" t="s">
         <v>635</v>
       </c>
-      <c r="S92" s="44" t="s">
+      <c r="T92" s="44" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="93" spans="18:19">
-      <c r="R93" s="44" t="s">
+    <row r="93" spans="19:20">
+      <c r="S93" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="S93" t="s">
+      <c r="T93" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="94" spans="18:19">
-      <c r="R94" s="44" t="s">
+    <row r="94" spans="19:20">
+      <c r="S94" s="44" t="s">
         <v>283</v>
       </c>
-      <c r="S94" s="44" t="s">
+      <c r="T94" s="44" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="95" spans="18:19">
-      <c r="R95" s="44" t="s">
+    <row r="95" spans="19:20">
+      <c r="S95" s="44" t="s">
         <v>294</v>
       </c>
-      <c r="S95" s="44" t="s">
+      <c r="T95" s="44" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="96" spans="18:19">
-      <c r="R96" s="44" t="s">
+    <row r="96" spans="19:20">
+      <c r="S96" s="44" t="s">
         <v>301</v>
       </c>
-      <c r="S96" t="s">
+      <c r="T96" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="97" spans="18:19">
-      <c r="R97" s="44" t="s">
+    <row r="97" spans="19:20">
+      <c r="S97" s="44" t="s">
         <v>637</v>
       </c>
-      <c r="S97" s="57" t="s">
+      <c r="T97" s="57" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="98" spans="18:19">
-      <c r="R98" s="57" t="s">
+    <row r="98" spans="19:20">
+      <c r="S98" s="57" t="s">
         <v>638</v>
       </c>
-      <c r="S98" s="32" t="s">
+      <c r="T98" s="32" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="99" spans="18:19">
-      <c r="R99" s="44" t="s">
+    <row r="99" spans="19:20">
+      <c r="S99" s="44" t="s">
         <v>639</v>
       </c>
-      <c r="S99" t="s">
+      <c r="T99" t="s">
         <v>640</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="R2:S91">
-    <sortCondition ref="R2:R91"/>
+  <sortState ref="S2:T91">
+    <sortCondition ref="S2:S91"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/appliances_wtp.xlsx
+++ b/appliances_wtp.xlsx
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId5"/>
+    <pivotCache cacheId="7" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35078,7 +35078,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>

--- a/appliances_wtp.xlsx
+++ b/appliances_wtp.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dand\Documents\GitHub\appliances_interventions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianadanilenko/Desktop/appliances_interventions/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5994130-FEC1-4949-8D65-D0E957BEBB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5280" yWindow="-21600" windowWidth="38400" windowHeight="21600" activeTab="1"/>
+    <workbookView xWindow="-5280" yWindow="-21100" windowWidth="38400" windowHeight="19340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -21,9 +22,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Appliances!$T$1:$T$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Usage!$A$1:$BN$53</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId5"/>
+    <pivotCache cacheId="4" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,62 +46,35 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={73C2226C-6106-4DC2-88CF-9C0A06F48311}</author>
     <author>tc={CEE78422-255C-40DC-AFED-5AA185CC03E1}</author>
     <author>tc={C7CEED71-5EFE-4791-84D8-7010C40A69F0}</author>
   </authors>
   <commentList>
-    <comment ref="AQ1" authorId="0" shapeId="0">
+    <comment ref="AQ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     is this supposed to capture mean difference between control and treatment or ?</t>
-        </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="1" shapeId="0">
+    <comment ref="AZ1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     daily kWh</t>
-        </r>
       </text>
     </comment>
-    <comment ref="AQ22" authorId="2" shapeId="0">
+    <comment ref="AQ22" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     in kWh</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -108,44 +82,26 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={1DD52412-77C6-1E43-B8CC-07AD562D2C6E}</author>
     <author>tc={52E723F4-9A55-1E46-88F7-D2164B4696BA}</author>
   </authors>
   <commentList>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     check label studies from srmt for label type</t>
-        </r>
       </text>
     </comment>
-    <comment ref="AR23" authorId="1" shapeId="0">
+    <comment ref="AR23" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
+        <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     can we code them as relative WTP? </t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -153,28 +109,19 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={CF36070F-7893-4948-8AB8-1CADF6EBBFD9}</author>
   </authors>
   <commentList>
-    <comment ref="D6" authorId="0" shapeId="0">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     a bit confused as of where it’s correlation and where - quasi-experimental
 Reply:
     the way i reassessed this was - market statistics - correlation, whereas hypothetical choice - quasi-experimental</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -182,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4135" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4135" uniqueCount="648">
   <si>
     <t>Coder</t>
   </si>
@@ -2553,34 +2500,7 @@
     <t>counterfactual</t>
   </si>
   <si>
-    <t>relative WTP for a more energy-efficient LED light bulb compared to a CFL bulb</t>
-  </si>
-  <si>
-    <t>relative WTP for a more energy-efficient LED light bulb compared to a CFL bulb (in treatment and in control)</t>
-  </si>
-  <si>
     <t>relative WTP for LED vs CFL (diff experimental conditions), ATE in euro</t>
-  </si>
-  <si>
-    <t>choice of a labelled refrigerator compared to a not-labelled refrigerator</t>
-  </si>
-  <si>
-    <t>WTP for efficient appliance in a treatment group compared to control (where control is existing label and treatment is label including operating cost)</t>
-  </si>
-  <si>
-    <t>WTP for top-rated appliance in presence of a label compared to no label</t>
-  </si>
-  <si>
-    <t>WTP for efficient appliance compared to existing appliance</t>
-  </si>
-  <si>
-    <t>WTP for ENERGY STAR appliance compared to no label</t>
-  </si>
-  <si>
-    <t>WTP before and after an information message</t>
-  </si>
-  <si>
-    <t>WTP for A+ appliance in presence of a label compared to A</t>
   </si>
   <si>
     <t>no intervention</t>
@@ -2592,7 +2512,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
@@ -3078,7 +2998,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3225,19 +3145,14 @@
     <xf numFmtId="2" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="36" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -3281,7 +3196,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334" xr:uid="{00000000-000A-0000-FFFF-FFFF07000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:CD1048576" sheet="Appliances"/>
   </cacheSource>
@@ -35078,7 +34993,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -35933,57 +35848,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BP53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="4" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="5" width="14.125" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="16.625" customWidth="1"/>
-    <col min="10" max="10" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="10" max="10" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" hidden="1" customWidth="1"/>
     <col min="12" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="16" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="12.125" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="12.1640625" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="0" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="0" style="12" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="18.625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.625" style="7" customWidth="1"/>
-    <col min="30" max="30" width="13.625" customWidth="1"/>
-    <col min="31" max="31" width="14.625" customWidth="1"/>
-    <col min="32" max="32" width="13.625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="19.125" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="10.625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="13.125" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="22.125" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="10.625" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="18.125" customWidth="1"/>
-    <col min="39" max="39" width="14.125" customWidth="1"/>
-    <col min="40" max="40" width="9.625" customWidth="1"/>
-    <col min="41" max="41" width="19.125" customWidth="1"/>
-    <col min="42" max="42" width="12.125" customWidth="1"/>
+    <col min="27" max="27" width="18.6640625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.6640625" style="7" customWidth="1"/>
+    <col min="30" max="30" width="13.6640625" customWidth="1"/>
+    <col min="31" max="31" width="14.6640625" customWidth="1"/>
+    <col min="32" max="32" width="13.6640625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="19.1640625" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="10.6640625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="13.1640625" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="22.1640625" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="10.6640625" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="18.1640625" customWidth="1"/>
+    <col min="39" max="39" width="14.1640625" customWidth="1"/>
+    <col min="40" max="40" width="9.6640625" customWidth="1"/>
+    <col min="41" max="41" width="19.1640625" customWidth="1"/>
+    <col min="42" max="42" width="12.1640625" customWidth="1"/>
     <col min="44" max="45" width="0" hidden="1" customWidth="1"/>
-    <col min="46" max="47" width="13.125" hidden="1" customWidth="1"/>
+    <col min="46" max="47" width="13.1640625" hidden="1" customWidth="1"/>
     <col min="48" max="51" width="0" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="13.625" style="17" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="13.6640625" style="17" hidden="1" customWidth="1"/>
     <col min="53" max="53" width="26.5" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="20.625" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="20.6640625" hidden="1" customWidth="1"/>
     <col min="55" max="55" width="0" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="17.625" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="16.125" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="15.125" hidden="1" customWidth="1"/>
-    <col min="59" max="59" width="20.625" hidden="1" customWidth="1"/>
-    <col min="60" max="60" width="24.625" hidden="1" customWidth="1"/>
-    <col min="61" max="61" width="19.625" style="30" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="24.125" style="30" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.6640625" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="16.1640625" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="15.1640625" hidden="1" customWidth="1"/>
+    <col min="59" max="59" width="20.6640625" hidden="1" customWidth="1"/>
+    <col min="60" max="60" width="24.6640625" hidden="1" customWidth="1"/>
+    <col min="61" max="61" width="19.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="24.1640625" style="30" bestFit="1" customWidth="1"/>
     <col min="63" max="65" width="11" style="30"/>
-    <col min="67" max="67" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="45">
+    <row r="1" spans="1:68" ht="48">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -43781,7 +43696,7 @@
         <v>6.7567567567567571E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="39" spans="1:66" s="41" customFormat="1" ht="17">
       <c r="A39" s="45" t="s">
         <v>68</v>
       </c>
@@ -43986,7 +43901,7 @@
       </c>
       <c r="BN39" s="43"/>
     </row>
-    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="40" spans="1:66" s="41" customFormat="1" ht="17">
       <c r="A40" s="45" t="s">
         <v>68</v>
       </c>
@@ -44191,7 +44106,7 @@
       </c>
       <c r="BN40" s="43"/>
     </row>
-    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="41" spans="1:66" s="41" customFormat="1" ht="17">
       <c r="A41" s="45" t="s">
         <v>68</v>
       </c>
@@ -44400,7 +44315,7 @@
         <v>2.0421052631578922</v>
       </c>
     </row>
-    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.5">
+    <row r="42" spans="1:66" s="41" customFormat="1" ht="17">
       <c r="A42" s="45" t="s">
         <v>68</v>
       </c>
@@ -46797,34 +46712,34 @@
   </sheetData>
   <dataConsolidate/>
   <dataValidations count="10">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>$D$2:$D$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>$D$2:$D$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>$F$2:$F$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -46833,43 +46748,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_" xr:uid="{00000000-0002-0000-0000-00000A000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>BC23:BC28 BC54:BC1048576 BC33:BC38 BC1:BC12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G$2:$G$9</xm:f>
           </x14:formula1>
           <xm:sqref>J54:J1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>AS43:AX51 AS54:AX1048576 AS23:AX38 AS2:AX12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G$2:$G$10</xm:f>
           </x14:formula1>
           <xm:sqref>J38</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$4</xm:f>
           </x14:formula1>
           <xm:sqref>AO43:AO51</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$6</xm:f>
           </x14:formula1>
           <xm:sqref>K54:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$7</xm:f>
           </x14:formula1>
@@ -46882,65 +46797,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CH75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="5" max="5" width="24.625" customWidth="1"/>
-    <col min="6" max="6" width="17.625" customWidth="1"/>
-    <col min="7" max="7" width="14.125" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" customWidth="1"/>
     <col min="8" max="8" width="16.5" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.125" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" customWidth="1"/>
+    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.1640625" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="14.625" customWidth="1"/>
-    <col min="17" max="17" width="13.125" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" customWidth="1"/>
+    <col min="17" max="17" width="13.1640625" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="14.125" customWidth="1"/>
+    <col min="19" max="19" width="14.1640625" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="21.125" customWidth="1"/>
+    <col min="21" max="21" width="21.1640625" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.625" customWidth="1"/>
+    <col min="23" max="23" width="14.6640625" customWidth="1"/>
     <col min="24" max="24" width="12.5" customWidth="1"/>
     <col min="25" max="33" width="11" customWidth="1"/>
     <col min="34" max="35" width="16" customWidth="1"/>
     <col min="36" max="39" width="11" customWidth="1"/>
-    <col min="40" max="41" width="12.125" customWidth="1"/>
+    <col min="40" max="41" width="12.1640625" customWidth="1"/>
     <col min="42" max="42" width="11" customWidth="1"/>
-    <col min="43" max="43" width="27.625" customWidth="1"/>
-    <col min="44" max="44" width="41.125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="54.625" customWidth="1"/>
+    <col min="43" max="43" width="27.6640625" customWidth="1"/>
+    <col min="44" max="44" width="41.1640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="54.6640625" customWidth="1"/>
     <col min="46" max="46" width="21" customWidth="1"/>
-    <col min="47" max="47" width="26.625" style="7" customWidth="1"/>
-    <col min="48" max="48" width="14.125" style="7" customWidth="1"/>
-    <col min="49" max="49" width="13.125" customWidth="1"/>
-    <col min="50" max="50" width="9.625" customWidth="1"/>
+    <col min="47" max="47" width="26.6640625" style="7" customWidth="1"/>
+    <col min="48" max="48" width="14.1640625" style="7" customWidth="1"/>
+    <col min="49" max="49" width="13.1640625" customWidth="1"/>
+    <col min="50" max="50" width="9.6640625" customWidth="1"/>
     <col min="51" max="51" width="17" customWidth="1"/>
     <col min="52" max="52" width="9"/>
-    <col min="53" max="54" width="14.125" customWidth="1"/>
-    <col min="55" max="55" width="13.625" customWidth="1"/>
-    <col min="56" max="56" width="12.625" customWidth="1"/>
-    <col min="57" max="57" width="10.625" customWidth="1"/>
+    <col min="53" max="54" width="14.1640625" customWidth="1"/>
+    <col min="55" max="55" width="13.6640625" customWidth="1"/>
+    <col min="56" max="56" width="12.6640625" customWidth="1"/>
+    <col min="57" max="57" width="10.6640625" customWidth="1"/>
     <col min="58" max="58" width="13" customWidth="1"/>
-    <col min="59" max="60" width="10.625" customWidth="1"/>
-    <col min="61" max="62" width="11.125" customWidth="1"/>
+    <col min="59" max="60" width="10.6640625" customWidth="1"/>
+    <col min="61" max="62" width="11.1640625" customWidth="1"/>
     <col min="63" max="64" width="11" customWidth="1"/>
-    <col min="65" max="65" width="12.625" customWidth="1"/>
-    <col min="66" max="66" width="18.125" customWidth="1"/>
-    <col min="67" max="67" width="22.125" customWidth="1"/>
-    <col min="68" max="68" width="15.125" customWidth="1"/>
+    <col min="65" max="65" width="12.6640625" customWidth="1"/>
+    <col min="66" max="66" width="18.1640625" customWidth="1"/>
+    <col min="67" max="67" width="22.1640625" customWidth="1"/>
+    <col min="68" max="68" width="15.1640625" customWidth="1"/>
     <col min="69" max="69" width="18" customWidth="1"/>
-    <col min="70" max="70" width="17.125" customWidth="1"/>
-    <col min="71" max="71" width="21.125" customWidth="1"/>
-    <col min="72" max="72" width="10.125" customWidth="1"/>
+    <col min="70" max="70" width="17.1640625" customWidth="1"/>
+    <col min="71" max="71" width="21.1640625" customWidth="1"/>
+    <col min="72" max="72" width="10.1640625" customWidth="1"/>
     <col min="73" max="73" width="13" customWidth="1"/>
     <col min="74" max="74" width="14" customWidth="1"/>
-    <col min="75" max="75" width="13.125" customWidth="1"/>
+    <col min="75" max="75" width="13.1640625" customWidth="1"/>
     <col min="82" max="82" width="24" customWidth="1"/>
   </cols>
   <sheetData>
@@ -47204,7 +47118,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="2" spans="1:86" hidden="1">
+    <row r="2" spans="1:86" ht="16">
       <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
@@ -47338,7 +47252,7 @@
         <v>233</v>
       </c>
       <c r="AS2" s="98" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AT2" t="s">
         <v>73</v>
@@ -47466,12 +47380,12 @@
         <v>3.0120481927710845E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:86" hidden="1">
+    <row r="3" spans="1:86" ht="16">
       <c r="A3" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C3" s="11">
         <v>1072</v>
@@ -47600,7 +47514,7 @@
         <v>233</v>
       </c>
       <c r="AS3" s="98" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AT3" t="s">
         <v>73</v>
@@ -47729,12 +47643,12 @@
         <v>2.2883295194508009E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:86" hidden="1">
+    <row r="4" spans="1:86" ht="16">
       <c r="A4" t="s">
         <v>332</v>
       </c>
       <c r="B4" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C4" s="94">
         <v>1266</v>
@@ -47991,12 +47905,12 @@
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:86" s="101" customFormat="1" hidden="1">
+    <row r="5" spans="1:86" s="101" customFormat="1" ht="16">
       <c r="A5" t="s">
         <v>332</v>
       </c>
       <c r="B5" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C5" s="94">
         <v>1267</v>
@@ -48255,12 +48169,12 @@
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:86" hidden="1">
+    <row r="6" spans="1:86" ht="16">
       <c r="A6" t="s">
         <v>332</v>
       </c>
       <c r="B6" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C6" s="94">
         <v>1268</v>
@@ -48517,12 +48431,12 @@
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:86" s="99" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1">
+    <row r="7" spans="1:86" s="99" customFormat="1" ht="17" customHeight="1">
       <c r="A7" t="s">
         <v>332</v>
       </c>
       <c r="B7" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C7" s="94">
         <v>1269</v>
@@ -48781,12 +48695,12 @@
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:86" s="99" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1">
+    <row r="8" spans="1:86" s="99" customFormat="1" ht="17" customHeight="1">
       <c r="A8" s="100" t="s">
         <v>68</v>
       </c>
       <c r="B8" s="100" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C8" s="100">
         <v>1059</v>
@@ -49050,7 +48964,7 @@
         <v>312</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C9" s="94">
         <v>1241</v>
@@ -49313,7 +49227,7 @@
         <v>312</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C10" s="94">
         <v>1242</v>
@@ -49571,12 +49485,12 @@
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:86">
+    <row r="11" spans="1:86" ht="16">
       <c r="A11" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C11" s="94">
         <v>1243</v>
@@ -49839,7 +49753,7 @@
         <v>312</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C12" s="94">
         <v>1244</v>
@@ -50102,7 +50016,7 @@
         <v>312</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C13" s="94">
         <v>1245</v>
@@ -50365,7 +50279,7 @@
         <v>312</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C14" s="94">
         <v>1246</v>
@@ -50623,12 +50537,12 @@
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:86" hidden="1">
+    <row r="15" spans="1:86" ht="16">
       <c r="A15" s="100" t="s">
         <v>312</v>
       </c>
       <c r="B15" s="100" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C15" s="94">
         <v>1232</v>
@@ -50887,12 +50801,12 @@
         <v>3.1746031746031746E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:86" hidden="1">
+    <row r="16" spans="1:86" ht="16">
       <c r="A16" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B16" s="100" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="C16" s="11">
         <v>1013</v>
@@ -50900,7 +50814,7 @@
       <c r="D16" s="11">
         <v>104</v>
       </c>
-      <c r="E16" s="118" t="s">
+      <c r="E16" s="11" t="s">
         <v>220</v>
       </c>
       <c r="F16" s="11">
@@ -51149,12 +51063,12 @@
         <v>1.4858841010401188E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:86" hidden="1">
+    <row r="17" spans="1:86" ht="16">
       <c r="A17" t="s">
         <v>332</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C17" s="94">
         <v>1261</v>
@@ -51411,12 +51325,12 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:86" hidden="1">
+    <row r="18" spans="1:86" ht="16">
       <c r="A18" t="s">
         <v>332</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C18" s="94">
         <v>1262</v>
@@ -51673,12 +51587,12 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:86" hidden="1">
+    <row r="19" spans="1:86" ht="16">
       <c r="A19" t="s">
         <v>332</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C19" s="94">
         <v>1263</v>
@@ -51935,12 +51849,12 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:86" s="101" customFormat="1" hidden="1">
+    <row r="20" spans="1:86" s="101" customFormat="1" ht="16">
       <c r="A20" t="s">
         <v>332</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C20" s="94">
         <v>1264</v>
@@ -52199,12 +52113,12 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:86" s="101" customFormat="1" hidden="1">
+    <row r="21" spans="1:86" s="101" customFormat="1" ht="16">
       <c r="A21" t="s">
         <v>332</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C21" s="94">
         <v>1265</v>
@@ -52463,12 +52377,12 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:86" s="101" customFormat="1">
+    <row r="22" spans="1:86" s="101" customFormat="1" ht="16">
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C22" s="96">
         <v>1155</v>
@@ -52727,12 +52641,12 @@
         <v>5.00751126690035E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:86">
+    <row r="23" spans="1:86" ht="16">
       <c r="A23" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C23" s="96">
         <v>1156</v>
@@ -52989,12 +52903,12 @@
         <v>5.00751126690035E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:86">
+    <row r="24" spans="1:86" ht="16">
       <c r="A24" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C24" s="96">
         <v>1191</v>
@@ -53002,7 +52916,7 @@
       <c r="D24" s="97">
         <v>144</v>
       </c>
-      <c r="E24" s="119" t="s">
+      <c r="E24" s="118" t="s">
         <v>301</v>
       </c>
       <c r="F24" s="96">
@@ -53250,12 +53164,12 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="25" spans="1:86">
+    <row r="25" spans="1:86" ht="16">
       <c r="A25" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C25" s="96">
         <v>1192</v>
@@ -53263,7 +53177,7 @@
       <c r="D25" s="97">
         <v>144</v>
       </c>
-      <c r="E25" s="119" t="s">
+      <c r="E25" s="118" t="s">
         <v>301</v>
       </c>
       <c r="F25" s="96">
@@ -53511,12 +53425,12 @@
         <v>5.1416525271222172E-5</v>
       </c>
     </row>
-    <row r="26" spans="1:86">
+    <row r="26" spans="1:86" ht="16">
       <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C26" s="96">
         <v>1180</v>
@@ -53772,12 +53686,12 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:86" s="103" customFormat="1">
+    <row r="27" spans="1:86" s="103" customFormat="1" ht="16">
       <c r="A27" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C27" s="96">
         <v>1181</v>
@@ -54036,12 +53950,12 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:86" s="107" customFormat="1">
+    <row r="28" spans="1:86" s="107" customFormat="1" ht="16">
       <c r="A28" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C28" s="96">
         <v>1182</v>
@@ -54300,12 +54214,12 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:86" s="107" customFormat="1">
+    <row r="29" spans="1:86" s="107" customFormat="1" ht="16">
       <c r="A29" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C29" s="96">
         <v>1183</v>
@@ -54564,12 +54478,12 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:86" s="107" customFormat="1">
+    <row r="30" spans="1:86" s="107" customFormat="1" ht="16">
       <c r="A30" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C30" s="96">
         <v>1184</v>
@@ -54833,7 +54747,7 @@
         <v>68</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C31" s="96">
         <v>1185</v>
@@ -55094,7 +55008,7 @@
         <v>68</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C32" s="96">
         <v>1186</v>
@@ -55350,12 +55264,12 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:86" ht="15.75" hidden="1" customHeight="1">
+    <row r="33" spans="1:86" ht="15.75" customHeight="1">
       <c r="A33" t="s">
         <v>332</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="C33" s="94">
         <v>1258</v>
@@ -55363,7 +55277,7 @@
       <c r="D33" s="11">
         <v>404</v>
       </c>
-      <c r="E33" s="120" t="s">
+      <c r="E33" t="s">
         <v>333</v>
       </c>
       <c r="F33" s="11">
@@ -55612,12 +55526,12 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:86" hidden="1">
+    <row r="34" spans="1:86" ht="16">
       <c r="A34" t="s">
         <v>332</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="C34" s="94">
         <v>1259</v>
@@ -55874,12 +55788,12 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:86" hidden="1">
+    <row r="35" spans="1:86" ht="16">
       <c r="A35" t="s">
         <v>332</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="C35" s="94">
         <v>1260</v>
@@ -56136,12 +56050,12 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:86">
+    <row r="36" spans="1:86" ht="16">
       <c r="A36" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C36" s="96">
         <v>1189</v>
@@ -56149,7 +56063,7 @@
       <c r="D36" s="97">
         <v>143</v>
       </c>
-      <c r="E36" s="121" t="s">
+      <c r="E36" s="44" t="s">
         <v>294</v>
       </c>
       <c r="F36" s="96">
@@ -56382,12 +56296,12 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:86">
+    <row r="37" spans="1:86" ht="16">
       <c r="A37" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C37" s="96">
         <v>1190</v>
@@ -56395,7 +56309,7 @@
       <c r="D37" s="97">
         <v>143</v>
       </c>
-      <c r="E37" s="121" t="s">
+      <c r="E37" s="44" t="s">
         <v>294</v>
       </c>
       <c r="F37" s="96">
@@ -56628,12 +56542,12 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:86">
+    <row r="38" spans="1:86" ht="16">
       <c r="A38" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C38" s="96">
         <v>1187</v>
@@ -56641,7 +56555,7 @@
       <c r="D38" s="97">
         <v>143</v>
       </c>
-      <c r="E38" s="121" t="s">
+      <c r="E38" s="44" t="s">
         <v>294</v>
       </c>
       <c r="F38" s="96">
@@ -56874,12 +56788,12 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:86">
+    <row r="39" spans="1:86" ht="16">
       <c r="A39" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C39" s="96">
         <v>1188</v>
@@ -56887,7 +56801,7 @@
       <c r="D39" s="97">
         <v>143</v>
       </c>
-      <c r="E39" s="121" t="s">
+      <c r="E39" s="44" t="s">
         <v>294</v>
       </c>
       <c r="F39" s="96">
@@ -57120,12 +57034,12 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:86">
+    <row r="40" spans="1:86" ht="16">
       <c r="A40" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C40" s="94">
         <v>1122</v>
@@ -57133,7 +57047,7 @@
       <c r="D40" s="97">
         <v>127</v>
       </c>
-      <c r="E40" s="120" t="s">
+      <c r="E40" t="s">
         <v>259</v>
       </c>
       <c r="F40" s="96">
@@ -57381,12 +57295,12 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:86">
+    <row r="41" spans="1:86" ht="16">
       <c r="A41" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C41" s="94">
         <v>1123</v>
@@ -57394,7 +57308,7 @@
       <c r="D41" s="97">
         <v>127</v>
       </c>
-      <c r="E41" s="120" t="s">
+      <c r="E41" t="s">
         <v>259</v>
       </c>
       <c r="F41" s="96">
@@ -57642,12 +57556,12 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:86">
+    <row r="42" spans="1:86" ht="16">
       <c r="A42" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C42" s="94">
         <v>1124</v>
@@ -57655,7 +57569,7 @@
       <c r="D42" s="97">
         <v>127</v>
       </c>
-      <c r="E42" s="120" t="s">
+      <c r="E42" t="s">
         <v>259</v>
       </c>
       <c r="F42" s="96">
@@ -57903,12 +57817,12 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="43" spans="1:86">
+    <row r="43" spans="1:86" ht="16">
       <c r="A43" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C43" s="94">
         <v>1125</v>
@@ -57916,7 +57830,7 @@
       <c r="D43" s="97">
         <v>127</v>
       </c>
-      <c r="E43" s="120" t="s">
+      <c r="E43" t="s">
         <v>259</v>
       </c>
       <c r="F43" s="96">
@@ -58164,12 +58078,12 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:86">
+    <row r="44" spans="1:86" ht="16">
       <c r="A44" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C44" s="94">
         <v>1126</v>
@@ -58177,7 +58091,7 @@
       <c r="D44" s="97">
         <v>127</v>
       </c>
-      <c r="E44" s="120" t="s">
+      <c r="E44" t="s">
         <v>259</v>
       </c>
       <c r="F44" s="96">
@@ -58425,12 +58339,12 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:86">
+    <row r="45" spans="1:86" ht="16">
       <c r="A45" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C45" s="94">
         <v>1127</v>
@@ -58438,7 +58352,7 @@
       <c r="D45" s="97">
         <v>127</v>
       </c>
-      <c r="E45" s="120" t="s">
+      <c r="E45" t="s">
         <v>259</v>
       </c>
       <c r="F45" s="96">
@@ -58686,12 +58600,12 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:86" hidden="1">
+    <row r="46" spans="1:86" ht="16">
       <c r="A46" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C46" s="11">
         <v>1099</v>
@@ -58699,7 +58613,7 @@
       <c r="D46">
         <v>118</v>
       </c>
-      <c r="E46" s="120" t="s">
+      <c r="E46" t="s">
         <v>254</v>
       </c>
       <c r="F46" s="11">
@@ -58947,12 +58861,12 @@
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:86" hidden="1">
+    <row r="47" spans="1:86" ht="16">
       <c r="A47" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C47" s="11">
         <v>1100</v>
@@ -58960,7 +58874,7 @@
       <c r="D47">
         <v>118</v>
       </c>
-      <c r="E47" s="120" t="s">
+      <c r="E47" t="s">
         <v>254</v>
       </c>
       <c r="F47" s="11">
@@ -59208,12 +59122,12 @@
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:86" hidden="1">
+    <row r="48" spans="1:86" ht="16">
       <c r="A48" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C48" s="94">
         <v>1235</v>
@@ -59221,7 +59135,7 @@
       <c r="D48">
         <v>118</v>
       </c>
-      <c r="E48" s="122" t="s">
+      <c r="E48" s="119" t="s">
         <v>254</v>
       </c>
       <c r="F48">
@@ -59470,12 +59384,12 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="49" spans="1:86" s="101" customFormat="1" hidden="1">
+    <row r="49" spans="1:86" s="101" customFormat="1" ht="16">
       <c r="A49" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C49" s="94">
         <v>1236</v>
@@ -59483,7 +59397,7 @@
       <c r="D49">
         <v>118</v>
       </c>
-      <c r="E49" s="122" t="s">
+      <c r="E49" s="119" t="s">
         <v>254</v>
       </c>
       <c r="F49">
@@ -59734,12 +59648,12 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="50" spans="1:86" s="101" customFormat="1" hidden="1">
+    <row r="50" spans="1:86" s="101" customFormat="1" ht="16">
       <c r="A50" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C50" s="94">
         <v>1237</v>
@@ -59747,7 +59661,7 @@
       <c r="D50">
         <v>118</v>
       </c>
-      <c r="E50" s="122" t="s">
+      <c r="E50" s="119" t="s">
         <v>254</v>
       </c>
       <c r="F50">
@@ -59998,12 +59912,12 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="51" spans="1:86" s="101" customFormat="1" hidden="1">
+    <row r="51" spans="1:86" s="101" customFormat="1" ht="16">
       <c r="A51" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C51" s="94">
         <v>1238</v>
@@ -60011,7 +59925,7 @@
       <c r="D51">
         <v>118</v>
       </c>
-      <c r="E51" s="122" t="s">
+      <c r="E51" s="119" t="s">
         <v>254</v>
       </c>
       <c r="F51">
@@ -60262,12 +60176,12 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="52" spans="1:86" hidden="1">
+    <row r="52" spans="1:86" ht="16">
       <c r="A52" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C52" s="94">
         <v>1239</v>
@@ -60275,7 +60189,7 @@
       <c r="D52">
         <v>118</v>
       </c>
-      <c r="E52" s="122" t="s">
+      <c r="E52" s="119" t="s">
         <v>254</v>
       </c>
       <c r="F52">
@@ -60523,12 +60437,12 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="53" spans="1:86" hidden="1">
+    <row r="53" spans="1:86" ht="16">
       <c r="A53" s="11" t="s">
         <v>312</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C53" s="94">
         <v>1240</v>
@@ -60536,7 +60450,7 @@
       <c r="D53">
         <v>118</v>
       </c>
-      <c r="E53" s="122" t="s">
+      <c r="E53" s="119" t="s">
         <v>254</v>
       </c>
       <c r="F53">
@@ -60784,12 +60698,12 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="54" spans="1:86">
+    <row r="54" spans="1:86" ht="16">
       <c r="A54" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C54" s="96">
         <v>1172</v>
@@ -60797,7 +60711,7 @@
       <c r="D54" s="97">
         <v>141</v>
       </c>
-      <c r="E54" s="120" t="s">
+      <c r="E54" t="s">
         <v>275</v>
       </c>
       <c r="F54" s="96">
@@ -61045,12 +60959,12 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:86">
+    <row r="55" spans="1:86" ht="16">
       <c r="A55" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C55" s="96">
         <v>1173</v>
@@ -61306,12 +61220,12 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:86">
+    <row r="56" spans="1:86" ht="16">
       <c r="A56" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C56" s="96">
         <v>1174</v>
@@ -61567,12 +61481,12 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:86">
+    <row r="57" spans="1:86" ht="16">
       <c r="A57" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C57" s="96">
         <v>1175</v>
@@ -61828,12 +61742,12 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:86">
+    <row r="58" spans="1:86" ht="16">
       <c r="A58" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C58" s="96">
         <v>1176</v>
@@ -62089,12 +62003,12 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:86">
+    <row r="59" spans="1:86" ht="16">
       <c r="A59" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C59" s="96">
         <v>1177</v>
@@ -62350,12 +62264,12 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:86">
+    <row r="60" spans="1:86" ht="16">
       <c r="A60" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C60" s="96">
         <v>1178</v>
@@ -62611,12 +62525,12 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:86">
+    <row r="61" spans="1:86" ht="16">
       <c r="A61" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C61" s="96">
         <v>1179</v>
@@ -62872,43 +62786,43 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:86">
+    <row r="62" spans="1:86" ht="16">
       <c r="M62" s="18"/>
     </row>
-    <row r="63" spans="1:86">
+    <row r="63" spans="1:86" ht="16">
       <c r="M63" s="18"/>
     </row>
-    <row r="64" spans="1:86">
+    <row r="64" spans="1:86" ht="16">
       <c r="M64" s="18"/>
     </row>
-    <row r="65" spans="13:76">
+    <row r="65" spans="13:76" ht="16">
       <c r="M65" s="18"/>
     </row>
-    <row r="66" spans="13:76">
+    <row r="66" spans="13:76" ht="16">
       <c r="M66" s="18"/>
     </row>
-    <row r="67" spans="13:76">
+    <row r="67" spans="13:76" ht="16">
       <c r="M67" s="18"/>
     </row>
-    <row r="68" spans="13:76">
+    <row r="68" spans="13:76" ht="16">
       <c r="M68" s="18"/>
     </row>
-    <row r="69" spans="13:76">
+    <row r="69" spans="13:76" ht="16">
       <c r="M69" s="18"/>
     </row>
-    <row r="70" spans="13:76">
+    <row r="70" spans="13:76" ht="16">
       <c r="M70" s="18"/>
     </row>
     <row r="71" spans="13:76" ht="15.75" customHeight="1">
       <c r="M71" s="18"/>
       <c r="BX71" s="30"/>
     </row>
-    <row r="72" spans="13:76">
+    <row r="72" spans="13:76" ht="16">
       <c r="M72" s="18"/>
       <c r="BA72" s="111"/>
       <c r="BB72" s="111"/>
     </row>
-    <row r="73" spans="13:76">
+    <row r="73" spans="13:76" ht="16">
       <c r="M73" s="18"/>
       <c r="BA73" s="111"/>
       <c r="BB73" s="111"/>
@@ -62916,20 +62830,14 @@
     <row r="74" spans="13:76" ht="15.75" customHeight="1">
       <c r="M74" s="18"/>
     </row>
-    <row r="75" spans="13:76">
+    <row r="75" spans="13:76" ht="16">
       <c r="M75" s="18"/>
       <c r="BA75" s="112"/>
       <c r="BB75" s="112"/>
     </row>
   </sheetData>
-  <autoFilter ref="T1:T75">
-    <filterColumn colId="0">
-      <filters blank="1">
-        <filter val="opt_out"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState ref="A2:CH75">
+  <autoFilter ref="T1:T75" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CH75">
     <sortCondition ref="E1:E75"/>
   </sortState>
   <dataConsolidate/>
@@ -62944,105 +62852,66 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations xWindow="603" yWindow="1085" count="33">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN27:AP30 AH31:AP42 AH7:AH8 AJ7:AP8 AH55:AP1048576 AL27 AH26:AK27 AL26:AP26 AH28:AL30 S15:S30 S1 U1 AH43:AQ54 U39:U1048576 S34:S1048576 U15:U35 AH15:AP25 AH1:AI1 AK1:AP1">
+  <dataValidations xWindow="603" yWindow="1085" count="20">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN27:AP30 AH31:AP42 AH7:AH8 AJ7:AP8 AH55:AP1048576 AL27 AH26:AK27 AL26:AP26 AH28:AL30 S15:S30 S1 U1 AH43:AQ54 U39:U1048576 S34:S1048576 U15:U35 AH15:AP25 AH1:AI1 AK1:AP1" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I30:I1048576 I15:I28">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I30:I1048576 I15:I28" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AD39:AF61 AG7:AG8 AG20:AG30 AD28:AF33 AD27:AE27 AD34:AE38 AG34:AG38 AH61 AD1:AG1 AD62:AG1048576 AD15:AF26"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y1:AC1 AI7:AI8 Y7:Y8 AA7:AE8 Y15:AC1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AD39:AF61 AG7:AG8 AG20:AG30 AD28:AF33 AD27:AE27 AD34:AE38 AG34:AG38 AH61 AD1:AG1 AD62:AG1048576 AD15:AF26" xr:uid="{00000000-0002-0000-0100-000002000000}"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y1:AC1 AI7:AI8 Y7:Y8 AA7:AE8 Y15:AC1048576" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN1 BO27:BO30 BO43:BO54 BN62:BN1048576"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AY55:AY61">
+    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN1 BO27:BO30 BO43:BO54 BN62:BN1048576" xr:uid="{00000000-0002-0000-0100-000004000000}"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AY55:AY61" xr:uid="{00000000-0002-0000-0100-000005000000}">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY31:AY42 AY15:AY25">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY31:AY42 AY15:AY25" xr:uid="{00000000-0002-0000-0100-000006000000}">
       <formula1>1</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV62:AV1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV62:AV1048576" xr:uid="{00000000-0002-0000-0100-000007000000}">
       <formula1>$J$2:$J$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1 U62:U1048576 S55:S1048576" xr:uid="{00000000-0002-0000-0100-000008000000}">
       <formula1>$M$2:$M$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S55:S1048576">
-      <formula1>$M$2:$M$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U62:U1048576">
-      <formula1>$M$2:$M$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1 U62:W1048576 S55:S1048576" xr:uid="{00000000-0002-0000-0100-00000B000000}">
       <formula1>$L$2:$L$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S55:S1048576">
-      <formula1>$L$2:$L$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U62:W1048576">
-      <formula1>$L$2:$L$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1 U62:W1048576 S55:S1048576" xr:uid="{00000000-0002-0000-0100-00000E000000}">
       <formula1>$O$2:$O$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S55:S1048576">
-      <formula1>$O$2:$O$7</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U62:W1048576">
-      <formula1>$O$2:$O$7</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K62:K1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K62:K1048576" xr:uid="{00000000-0002-0000-0100-000011000000}">
       <formula1>$K$2:$K$12</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BT62:BT1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BT62:BT1048576" xr:uid="{00000000-0002-0000-0100-000012000000}">
       <formula1>$P:$P</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G62:G1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G62:G1048576" xr:uid="{00000000-0002-0000-0100-000013000000}">
       <formula1>$T:$T</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR55:AR1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR55:AR1048576" xr:uid="{00000000-0002-0000-0100-000014000000}">
       <formula1>$H:$H</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT55:AT1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT55:AT1048576" xr:uid="{00000000-0002-0000-0100-000015000000}">
       <formula1>$Q:$Q</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O55:O1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O55:O1048576" xr:uid="{00000000-0002-0000-0100-000016000000}">
       <formula1>$O:$O</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E55:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E55:E1048576" xr:uid="{00000000-0002-0000-0100-000017000000}">
       <formula1>$S:$S</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1 S55:S1048576 S1" xr:uid="{00000000-0002-0000-0100-000018000000}">
       <formula1>$I:$I</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1">
-      <formula1>$I:$I</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S55:S1048576">
-      <formula1>$I:$I</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P27:P30">
-      <formula1>$N:$N</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P1">
-      <formula1>$N:$N</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1">
-      <formula1>$N:$N</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S55:S1048576">
-      <formula1>$N:$N</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P55:P1048576">
-      <formula1>$N:$N</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U62:U1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P27:P30 U62:U1048576 P55:P1048576 S55:S1048576 U1 P1" xr:uid="{00000000-0002-0000-0100-00001B000000}">
       <formula1>$N:$N</formula1>
     </dataValidation>
   </dataValidations>
@@ -63052,133 +62921,133 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="603" yWindow="1085" count="22">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000021000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>U1 U62:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000022000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>BU55:BW1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000023000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$C$2:$C$4</xm:f>
           </x14:formula1>
           <xm:sqref>BO1 BO55:BO1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000024000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$J$2:$J$3</xm:f>
           </x14:formula1>
           <xm:sqref>AV1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000025000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$M$2:$M$9</xm:f>
           </x14:formula1>
           <xm:sqref>U1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000026000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$3</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000027000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$O$2:$O$7</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000028000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$K$2:$K$12</xm:f>
           </x14:formula1>
           <xm:sqref>K1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000029000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$P:$P</xm:f>
           </x14:formula1>
           <xm:sqref>BT1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002A000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$T:$T</xm:f>
           </x14:formula1>
           <xm:sqref>G1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002B000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H:$H</xm:f>
           </x14:formula1>
           <xm:sqref>AR1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002C000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G:$G</xm:f>
           </x14:formula1>
           <xm:sqref>M76:M1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002D000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$Q:$Q</xm:f>
           </x14:formula1>
           <xm:sqref>AT1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002E000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D:$D</xm:f>
           </x14:formula1>
           <xm:sqref>U62:W1048576 S1 U1:W1 S55:S1048576 N55:N1048576 N1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002F000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$O:$O</xm:f>
           </x14:formula1>
           <xm:sqref>O1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000030000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B:$B</xm:f>
           </x14:formula1>
           <xm:sqref>T1 T62:T1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000031000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$S:$S</xm:f>
           </x14:formula1>
           <xm:sqref>E1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000032000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$I:$I</xm:f>
           </x14:formula1>
           <xm:sqref>U62:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000033000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N:$N</xm:f>
           </x14:formula1>
           <xm:sqref>S1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000034000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$M$2:$M$10</xm:f>
           </x14:formula1>
           <xm:sqref>R1:R1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000035000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$I$1:$I$7</xm:f>
           </x14:formula1>
           <xm:sqref>Q1:Q1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000036000000}">
           <x14:formula1>
             <xm:f>'Lists for variables'!$E$2:$E$3</xm:f>
           </x14:formula1>
@@ -63191,72 +63060,72 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BJ18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="17" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="36.33203125" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="29" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="15" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.83203125" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="33" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.375" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="35" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="26.375" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="63" max="64" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -66096,20 +65965,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:T99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="19.625" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18.125" style="26" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" style="26" customWidth="1"/>
     <col min="9" max="9" width="20.5" customWidth="1"/>
-    <col min="10" max="10" width="14.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col min="10" max="10" width="14.1640625" customWidth="1"/>
+    <col min="11" max="11" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="39" customFormat="1">
+    <row r="1" spans="1:20" s="39" customFormat="1" ht="17">
       <c r="A1" s="39" t="s">
         <v>425</v>
       </c>
@@ -66168,7 +66037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="31.5">
+    <row r="2" spans="1:20" ht="34">
       <c r="A2">
         <v>0</v>
       </c>
@@ -66182,7 +66051,7 @@
         <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -66227,7 +66096,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="31.5">
+    <row r="3" spans="1:20" ht="34">
       <c r="A3">
         <v>1</v>
       </c>
@@ -66241,7 +66110,7 @@
         <v>240</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -66286,7 +66155,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="47.25">
+    <row r="4" spans="1:20" ht="51">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -66336,7 +66205,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="47.25">
+    <row r="5" spans="1:20" ht="51">
       <c r="D5" t="s">
         <v>446</v>
       </c>
@@ -67338,7 +67207,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="S2:T91">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="S2:T91">
     <sortCondition ref="S2:S91"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/appliances_wtp.xlsx
+++ b/appliances_wtp.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dianadanilenko/Desktop/appliances_interventions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dand\Documents\GitHub\appliances_interventions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5994130-FEC1-4949-8D65-D0E957BEBB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5280" yWindow="-21100" windowWidth="38400" windowHeight="19340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5280" yWindow="-21105" windowWidth="38400" windowHeight="19335" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="5" state="hidden" r:id="rId1"/>
@@ -22,9 +21,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Appliances!$T$1:$T$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Usage!$A$1:$BN$53</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId5"/>
+    <pivotCache cacheId="5" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,35 +45,62 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={73C2226C-6106-4DC2-88CF-9C0A06F48311}</author>
     <author>tc={CEE78422-255C-40DC-AFED-5AA185CC03E1}</author>
     <author>tc={C7CEED71-5EFE-4791-84D8-7010C40A69F0}</author>
   </authors>
   <commentList>
-    <comment ref="AQ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="AQ1" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     is this supposed to capture mean difference between control and treatment or ?</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="AZ1" authorId="1" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     daily kWh</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AQ22" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="AQ22" authorId="2" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     in kWh</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -82,26 +108,44 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={1DD52412-77C6-1E43-B8CC-07AD562D2C6E}</author>
     <author>tc={52E723F4-9A55-1E46-88F7-D2164B4696BA}</author>
   </authors>
   <commentList>
-    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="AA1" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     check label studies from srmt for label type</t>
+        </r>
       </text>
     </comment>
-    <comment ref="AR23" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="AR23" authorId="1" shapeId="0">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     can we code them as relative WTP? </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -109,19 +153,28 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={CF36070F-7893-4948-8AB8-1CADF6EBBFD9}</author>
   </authors>
   <commentList>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="D6" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     a bit confused as of where it’s correlation and where - quasi-experimental
 Reply:
     the way i reassessed this was - market statistics - correlation, whereas hypothetical choice - quasi-experimental</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2512,7 +2565,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
@@ -3151,8 +3204,8 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -3196,7 +3249,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334" xr:uid="{00000000-000A-0000-FFFF-FFFF07000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Microsoft Office User" refreshedDate="45057.552441087966" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="334">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:CD1048576" sheet="Appliances"/>
   </cacheSource>
@@ -34993,7 +35046,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:BJ18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="92">
     <pivotField showAll="0"/>
@@ -35848,57 +35901,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BP53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.1640625" customWidth="1"/>
-    <col min="7" max="7" width="16.1640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="16.125" customWidth="1"/>
+    <col min="8" max="8" width="16.625" customWidth="1"/>
+    <col min="10" max="10" width="18.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" hidden="1" customWidth="1"/>
     <col min="12" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="16" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="12.1640625" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="12.125" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="0" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="0" style="12" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="18.6640625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.6640625" style="7" customWidth="1"/>
-    <col min="30" max="30" width="13.6640625" customWidth="1"/>
-    <col min="31" max="31" width="14.6640625" customWidth="1"/>
-    <col min="32" max="32" width="13.6640625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="19.1640625" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="10.6640625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="13.1640625" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="22.1640625" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="10.6640625" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="18.1640625" customWidth="1"/>
-    <col min="39" max="39" width="14.1640625" customWidth="1"/>
-    <col min="40" max="40" width="9.6640625" customWidth="1"/>
-    <col min="41" max="41" width="19.1640625" customWidth="1"/>
-    <col min="42" max="42" width="12.1640625" customWidth="1"/>
+    <col min="27" max="27" width="18.625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.625" style="7" customWidth="1"/>
+    <col min="30" max="30" width="13.625" customWidth="1"/>
+    <col min="31" max="31" width="14.625" customWidth="1"/>
+    <col min="32" max="32" width="13.625" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="19.125" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="10.625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="13.125" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="22.125" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="10.625" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="18.125" customWidth="1"/>
+    <col min="39" max="39" width="14.125" customWidth="1"/>
+    <col min="40" max="40" width="9.625" customWidth="1"/>
+    <col min="41" max="41" width="19.125" customWidth="1"/>
+    <col min="42" max="42" width="12.125" customWidth="1"/>
     <col min="44" max="45" width="0" hidden="1" customWidth="1"/>
-    <col min="46" max="47" width="13.1640625" hidden="1" customWidth="1"/>
+    <col min="46" max="47" width="13.125" hidden="1" customWidth="1"/>
     <col min="48" max="51" width="0" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="13.6640625" style="17" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="13.625" style="17" hidden="1" customWidth="1"/>
     <col min="53" max="53" width="26.5" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="20.6640625" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="20.625" hidden="1" customWidth="1"/>
     <col min="55" max="55" width="0" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="17.6640625" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="16.1640625" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="15.1640625" hidden="1" customWidth="1"/>
-    <col min="59" max="59" width="20.6640625" hidden="1" customWidth="1"/>
-    <col min="60" max="60" width="24.6640625" hidden="1" customWidth="1"/>
-    <col min="61" max="61" width="19.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="24.1640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.625" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="16.125" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="15.125" hidden="1" customWidth="1"/>
+    <col min="59" max="59" width="20.625" hidden="1" customWidth="1"/>
+    <col min="60" max="60" width="24.625" hidden="1" customWidth="1"/>
+    <col min="61" max="61" width="19.625" style="30" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="24.125" style="30" bestFit="1" customWidth="1"/>
     <col min="63" max="65" width="11" style="30"/>
-    <col min="67" max="67" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="25.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="48">
+    <row r="1" spans="1:68" ht="45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -43696,7 +43749,7 @@
         <v>6.7567567567567571E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:66" s="41" customFormat="1" ht="17">
+    <row r="39" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A39" s="45" t="s">
         <v>68</v>
       </c>
@@ -43901,7 +43954,7 @@
       </c>
       <c r="BN39" s="43"/>
     </row>
-    <row r="40" spans="1:66" s="41" customFormat="1" ht="17">
+    <row r="40" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A40" s="45" t="s">
         <v>68</v>
       </c>
@@ -44106,7 +44159,7 @@
       </c>
       <c r="BN40" s="43"/>
     </row>
-    <row r="41" spans="1:66" s="41" customFormat="1" ht="17">
+    <row r="41" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A41" s="45" t="s">
         <v>68</v>
       </c>
@@ -44315,7 +44368,7 @@
         <v>2.0421052631578922</v>
       </c>
     </row>
-    <row r="42" spans="1:66" s="41" customFormat="1" ht="17">
+    <row r="42" spans="1:66" s="41" customFormat="1" ht="16.5">
       <c r="A42" s="45" t="s">
         <v>68</v>
       </c>
@@ -46712,34 +46765,34 @@
   </sheetData>
   <dataConsolidate/>
   <dataValidations count="10">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="M11:M12 N29:N32 M14:M16 L1:L1048576">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="R1:W1 R2:Y9 X10:X12 BB43:BB52 BC29:BC32 S23:Y28 BB39:BC42 BC43:BC51 BC17:BC22 BB54:BB1048576 BB13:BC16 R33:Y1048576 BB17:BB38 BB1:BB12">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="M1:Q9 M10 Y10:Y12 N10:W12 O29:Y32 P23:R28 N17:O28 P17:Y22 M13 N13:Y16 M17:M32 M33:Q1048576">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AO54:AO1048576 AO43:AO52 AO1:AO38">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1" xr:uid="{00000000-0002-0000-0000-000004000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53" xr:uid="{00000000-0002-0000-0000-000005000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Yes - 1_x000a_No - 0_x000a_" sqref="X1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA53 AR53"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J37 J1:J12">
       <formula1>$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K23:K37 K1:K12">
       <formula1>$D$2:$D$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K43:K51">
       <formula1>$D$2:$D$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J43:J51">
       <formula1>$F$2:$F$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -46748,43 +46801,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Option to Opt/in - 1_x000a_No Option to Opt/in - 0_x000a_NA_x000a__x000a_">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>BC23:BC28 BC54:BC1048576 BC33:BC38 BC1:BC12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G$2:$G$9</xm:f>
           </x14:formula1>
           <xm:sqref>J54:J1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>AS43:AX51 AS54:AX1048576 AS23:AX38 AS2:AX12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G$2:$G$10</xm:f>
           </x14:formula1>
           <xm:sqref>J38</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$4</xm:f>
           </x14:formula1>
           <xm:sqref>AO43:AO51</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$6</xm:f>
           </x14:formula1>
           <xm:sqref>K54:K1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$7</xm:f>
           </x14:formula1>
@@ -46797,64 +46850,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CH75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" customWidth="1"/>
+    <col min="5" max="5" width="24.625" customWidth="1"/>
+    <col min="6" max="6" width="17.625" customWidth="1"/>
+    <col min="7" max="7" width="14.125" customWidth="1"/>
     <col min="8" max="8" width="16.5" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16.1640625" customWidth="1"/>
-    <col min="11" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.1640625" customWidth="1"/>
+    <col min="10" max="10" width="16.125" customWidth="1"/>
+    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.125" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="14.6640625" customWidth="1"/>
-    <col min="17" max="17" width="13.1640625" customWidth="1"/>
+    <col min="16" max="16" width="14.625" customWidth="1"/>
+    <col min="17" max="17" width="13.125" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="14.1640625" customWidth="1"/>
+    <col min="19" max="19" width="14.125" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="21.1640625" customWidth="1"/>
+    <col min="21" max="21" width="21.125" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.6640625" customWidth="1"/>
+    <col min="23" max="23" width="14.625" customWidth="1"/>
     <col min="24" max="24" width="12.5" customWidth="1"/>
     <col min="25" max="33" width="11" customWidth="1"/>
     <col min="34" max="35" width="16" customWidth="1"/>
     <col min="36" max="39" width="11" customWidth="1"/>
-    <col min="40" max="41" width="12.1640625" customWidth="1"/>
+    <col min="40" max="41" width="12.125" customWidth="1"/>
     <col min="42" max="42" width="11" customWidth="1"/>
-    <col min="43" max="43" width="27.6640625" customWidth="1"/>
-    <col min="44" max="44" width="41.1640625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="54.6640625" customWidth="1"/>
+    <col min="43" max="43" width="27.625" customWidth="1"/>
+    <col min="44" max="44" width="41.125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="54.625" customWidth="1"/>
     <col min="46" max="46" width="21" customWidth="1"/>
-    <col min="47" max="47" width="26.6640625" style="7" customWidth="1"/>
-    <col min="48" max="48" width="14.1640625" style="7" customWidth="1"/>
-    <col min="49" max="49" width="13.1640625" customWidth="1"/>
-    <col min="50" max="50" width="9.6640625" customWidth="1"/>
+    <col min="47" max="47" width="26.625" style="7" customWidth="1"/>
+    <col min="48" max="48" width="14.125" style="7" customWidth="1"/>
+    <col min="49" max="49" width="13.125" customWidth="1"/>
+    <col min="50" max="50" width="9.625" customWidth="1"/>
     <col min="51" max="51" width="17" customWidth="1"/>
     <col min="52" max="52" width="9"/>
-    <col min="53" max="54" width="14.1640625" customWidth="1"/>
-    <col min="55" max="55" width="13.6640625" customWidth="1"/>
-    <col min="56" max="56" width="12.6640625" customWidth="1"/>
-    <col min="57" max="57" width="10.6640625" customWidth="1"/>
+    <col min="53" max="54" width="14.125" customWidth="1"/>
+    <col min="55" max="55" width="13.625" customWidth="1"/>
+    <col min="56" max="56" width="12.625" customWidth="1"/>
+    <col min="57" max="57" width="10.625" customWidth="1"/>
     <col min="58" max="58" width="13" customWidth="1"/>
-    <col min="59" max="60" width="10.6640625" customWidth="1"/>
-    <col min="61" max="62" width="11.1640625" customWidth="1"/>
+    <col min="59" max="60" width="10.625" customWidth="1"/>
+    <col min="61" max="62" width="11.125" customWidth="1"/>
     <col min="63" max="64" width="11" customWidth="1"/>
-    <col min="65" max="65" width="12.6640625" customWidth="1"/>
-    <col min="66" max="66" width="18.1640625" customWidth="1"/>
-    <col min="67" max="67" width="22.1640625" customWidth="1"/>
-    <col min="68" max="68" width="15.1640625" customWidth="1"/>
+    <col min="65" max="65" width="12.625" customWidth="1"/>
+    <col min="66" max="66" width="18.125" customWidth="1"/>
+    <col min="67" max="67" width="22.125" customWidth="1"/>
+    <col min="68" max="68" width="15.125" customWidth="1"/>
     <col min="69" max="69" width="18" customWidth="1"/>
-    <col min="70" max="70" width="17.1640625" customWidth="1"/>
-    <col min="71" max="71" width="21.1640625" customWidth="1"/>
-    <col min="72" max="72" width="10.1640625" customWidth="1"/>
+    <col min="70" max="70" width="17.125" customWidth="1"/>
+    <col min="71" max="71" width="21.125" customWidth="1"/>
+    <col min="72" max="72" width="10.125" customWidth="1"/>
     <col min="73" max="73" width="13" customWidth="1"/>
     <col min="74" max="74" width="14" customWidth="1"/>
-    <col min="75" max="75" width="13.1640625" customWidth="1"/>
+    <col min="75" max="75" width="13.125" customWidth="1"/>
     <col min="82" max="82" width="24" customWidth="1"/>
   </cols>
   <sheetData>
@@ -47118,7 +47171,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="2" spans="1:86" ht="16">
+    <row r="2" spans="1:86">
       <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
@@ -47380,7 +47433,7 @@
         <v>3.0120481927710845E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:86" ht="16">
+    <row r="3" spans="1:86">
       <c r="A3" s="11" t="s">
         <v>68</v>
       </c>
@@ -47643,7 +47696,7 @@
         <v>2.2883295194508009E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:86" ht="16">
+    <row r="4" spans="1:86">
       <c r="A4" t="s">
         <v>332</v>
       </c>
@@ -47905,7 +47958,7 @@
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:86" s="101" customFormat="1" ht="16">
+    <row r="5" spans="1:86" s="101" customFormat="1">
       <c r="A5" t="s">
         <v>332</v>
       </c>
@@ -48169,7 +48222,7 @@
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:86" ht="16">
+    <row r="6" spans="1:86">
       <c r="A6" t="s">
         <v>332</v>
       </c>
@@ -48431,7 +48484,7 @@
         <v>3.7453183520599252E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:86" s="99" customFormat="1" ht="17" customHeight="1">
+    <row r="7" spans="1:86" s="99" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A7" t="s">
         <v>332</v>
       </c>
@@ -48695,7 +48748,7 @@
         <v>4.4863167339614175E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:86" s="99" customFormat="1" ht="17" customHeight="1">
+    <row r="8" spans="1:86" s="99" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A8" s="100" t="s">
         <v>68</v>
       </c>
@@ -49485,7 +49538,7 @@
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:86" ht="16">
+    <row r="11" spans="1:86">
       <c r="A11" s="11" t="s">
         <v>312</v>
       </c>
@@ -50537,7 +50590,7 @@
         <v>7.5843761850587782E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:86" ht="16">
+    <row r="15" spans="1:86">
       <c r="A15" s="100" t="s">
         <v>312</v>
       </c>
@@ -50578,7 +50631,7 @@
         <v>120</v>
       </c>
       <c r="N15" t="s">
-        <v>317</v>
+        <v>223</v>
       </c>
       <c r="O15" t="s">
         <v>224</v>
@@ -50801,7 +50854,7 @@
         <v>3.1746031746031746E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:86" ht="16">
+    <row r="16" spans="1:86">
       <c r="A16" s="11" t="s">
         <v>68</v>
       </c>
@@ -51063,7 +51116,7 @@
         <v>1.4858841010401188E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:86" ht="16">
+    <row r="17" spans="1:86">
       <c r="A17" t="s">
         <v>332</v>
       </c>
@@ -51325,7 +51378,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:86" ht="16">
+    <row r="18" spans="1:86">
       <c r="A18" t="s">
         <v>332</v>
       </c>
@@ -51587,7 +51640,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:86" ht="16">
+    <row r="19" spans="1:86">
       <c r="A19" t="s">
         <v>332</v>
       </c>
@@ -51849,7 +51902,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:86" s="101" customFormat="1" ht="16">
+    <row r="20" spans="1:86" s="101" customFormat="1">
       <c r="A20" t="s">
         <v>332</v>
       </c>
@@ -52113,7 +52166,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:86" s="101" customFormat="1" ht="16">
+    <row r="21" spans="1:86" s="101" customFormat="1">
       <c r="A21" t="s">
         <v>332</v>
       </c>
@@ -52377,7 +52430,7 @@
         <v>1.6611295681063123E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:86" s="101" customFormat="1" ht="16">
+    <row r="22" spans="1:86" s="101" customFormat="1">
       <c r="A22" s="11" t="s">
         <v>68</v>
       </c>
@@ -52641,7 +52694,7 @@
         <v>5.00751126690035E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:86" ht="16">
+    <row r="23" spans="1:86">
       <c r="A23" s="11" t="s">
         <v>68</v>
       </c>
@@ -52903,7 +52956,7 @@
         <v>5.00751126690035E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:86" ht="16">
+    <row r="24" spans="1:86">
       <c r="A24" s="11" t="s">
         <v>68</v>
       </c>
@@ -53164,7 +53217,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="25" spans="1:86" ht="16">
+    <row r="25" spans="1:86">
       <c r="A25" s="11" t="s">
         <v>68</v>
       </c>
@@ -53425,7 +53478,7 @@
         <v>5.1416525271222172E-5</v>
       </c>
     </row>
-    <row r="26" spans="1:86" ht="16">
+    <row r="26" spans="1:86">
       <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
@@ -53686,7 +53739,7 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:86" s="103" customFormat="1" ht="16">
+    <row r="27" spans="1:86" s="103" customFormat="1">
       <c r="A27" s="11" t="s">
         <v>68</v>
       </c>
@@ -53950,7 +54003,7 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:86" s="107" customFormat="1" ht="16">
+    <row r="28" spans="1:86" s="107" customFormat="1">
       <c r="A28" s="11" t="s">
         <v>68</v>
       </c>
@@ -54214,7 +54267,7 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:86" s="107" customFormat="1" ht="16">
+    <row r="29" spans="1:86" s="107" customFormat="1">
       <c r="A29" s="11" t="s">
         <v>68</v>
       </c>
@@ -54478,7 +54531,7 @@
         <v>8.4674005080440302E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:86" s="107" customFormat="1" ht="16">
+    <row r="30" spans="1:86" s="107" customFormat="1">
       <c r="A30" s="11" t="s">
         <v>68</v>
       </c>
@@ -55526,7 +55579,7 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:86" ht="16">
+    <row r="34" spans="1:86">
       <c r="A34" t="s">
         <v>332</v>
       </c>
@@ -55788,7 +55841,7 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:86" ht="16">
+    <row r="35" spans="1:86">
       <c r="A35" t="s">
         <v>332</v>
       </c>
@@ -56050,7 +56103,7 @@
         <v>1.1560693641618498E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:86" ht="16">
+    <row r="36" spans="1:86">
       <c r="A36" s="11" t="s">
         <v>68</v>
       </c>
@@ -56296,7 +56349,7 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:86" ht="16">
+    <row r="37" spans="1:86">
       <c r="A37" s="11" t="s">
         <v>68</v>
       </c>
@@ -56542,7 +56595,7 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:86" ht="16">
+    <row r="38" spans="1:86">
       <c r="A38" s="11" t="s">
         <v>68</v>
       </c>
@@ -56788,7 +56841,7 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:86" ht="16">
+    <row r="39" spans="1:86">
       <c r="A39" s="11" t="s">
         <v>68</v>
       </c>
@@ -57034,7 +57087,7 @@
         <v>2.7800945232137893E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:86" ht="16">
+    <row r="40" spans="1:86">
       <c r="A40" s="11" t="s">
         <v>68</v>
       </c>
@@ -57295,7 +57348,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:86" ht="16">
+    <row r="41" spans="1:86">
       <c r="A41" s="11" t="s">
         <v>68</v>
       </c>
@@ -57556,7 +57609,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:86" ht="16">
+    <row r="42" spans="1:86">
       <c r="A42" s="11" t="s">
         <v>68</v>
       </c>
@@ -57817,7 +57870,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="43" spans="1:86" ht="16">
+    <row r="43" spans="1:86">
       <c r="A43" s="11" t="s">
         <v>68</v>
       </c>
@@ -58078,7 +58131,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:86" ht="16">
+    <row r="44" spans="1:86">
       <c r="A44" s="11" t="s">
         <v>68</v>
       </c>
@@ -58339,7 +58392,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:86" ht="16">
+    <row r="45" spans="1:86">
       <c r="A45" s="11" t="s">
         <v>68</v>
       </c>
@@ -58600,7 +58653,7 @@
         <v>1.1204481792717087E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:86" ht="16">
+    <row r="46" spans="1:86">
       <c r="A46" s="11" t="s">
         <v>68</v>
       </c>
@@ -58861,7 +58914,7 @@
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:86" ht="16">
+    <row r="47" spans="1:86">
       <c r="A47" s="11" t="s">
         <v>68</v>
       </c>
@@ -59122,7 +59175,7 @@
         <v>7.1839080459770114E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:86" ht="16">
+    <row r="48" spans="1:86">
       <c r="A48" s="11" t="s">
         <v>312</v>
       </c>
@@ -59384,7 +59437,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="49" spans="1:86" s="101" customFormat="1" ht="16">
+    <row r="49" spans="1:86" s="101" customFormat="1">
       <c r="A49" s="11" t="s">
         <v>312</v>
       </c>
@@ -59648,7 +59701,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="50" spans="1:86" s="101" customFormat="1" ht="16">
+    <row r="50" spans="1:86" s="101" customFormat="1">
       <c r="A50" s="11" t="s">
         <v>312</v>
       </c>
@@ -59912,7 +59965,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="51" spans="1:86" s="101" customFormat="1" ht="16">
+    <row r="51" spans="1:86" s="101" customFormat="1">
       <c r="A51" s="11" t="s">
         <v>312</v>
       </c>
@@ -60176,7 +60229,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="52" spans="1:86" ht="16">
+    <row r="52" spans="1:86">
       <c r="A52" s="11" t="s">
         <v>312</v>
       </c>
@@ -60437,7 +60490,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="53" spans="1:86" ht="16">
+    <row r="53" spans="1:86">
       <c r="A53" s="11" t="s">
         <v>312</v>
       </c>
@@ -60698,7 +60751,7 @@
         <v>5.0360074532910306E-5</v>
       </c>
     </row>
-    <row r="54" spans="1:86" ht="16">
+    <row r="54" spans="1:86">
       <c r="A54" s="11" t="s">
         <v>68</v>
       </c>
@@ -60959,7 +61012,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:86" ht="16">
+    <row r="55" spans="1:86">
       <c r="A55" s="11" t="s">
         <v>68</v>
       </c>
@@ -61220,7 +61273,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:86" ht="16">
+    <row r="56" spans="1:86">
       <c r="A56" s="11" t="s">
         <v>68</v>
       </c>
@@ -61481,7 +61534,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:86" ht="16">
+    <row r="57" spans="1:86">
       <c r="A57" s="11" t="s">
         <v>68</v>
       </c>
@@ -61742,7 +61795,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:86" ht="16">
+    <row r="58" spans="1:86">
       <c r="A58" s="11" t="s">
         <v>68</v>
       </c>
@@ -62003,7 +62056,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:86" ht="16">
+    <row r="59" spans="1:86">
       <c r="A59" s="11" t="s">
         <v>68</v>
       </c>
@@ -62264,7 +62317,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:86" ht="16">
+    <row r="60" spans="1:86">
       <c r="A60" s="11" t="s">
         <v>68</v>
       </c>
@@ -62525,7 +62578,7 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:86" ht="16">
+    <row r="61" spans="1:86">
       <c r="A61" s="11" t="s">
         <v>68</v>
       </c>
@@ -62786,43 +62839,43 @@
         <v>1.9267822736030828E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:86" ht="16">
+    <row r="62" spans="1:86">
       <c r="M62" s="18"/>
     </row>
-    <row r="63" spans="1:86" ht="16">
+    <row r="63" spans="1:86">
       <c r="M63" s="18"/>
     </row>
-    <row r="64" spans="1:86" ht="16">
+    <row r="64" spans="1:86">
       <c r="M64" s="18"/>
     </row>
-    <row r="65" spans="13:76" ht="16">
+    <row r="65" spans="13:76">
       <c r="M65" s="18"/>
     </row>
-    <row r="66" spans="13:76" ht="16">
+    <row r="66" spans="13:76">
       <c r="M66" s="18"/>
     </row>
-    <row r="67" spans="13:76" ht="16">
+    <row r="67" spans="13:76">
       <c r="M67" s="18"/>
     </row>
-    <row r="68" spans="13:76" ht="16">
+    <row r="68" spans="13:76">
       <c r="M68" s="18"/>
     </row>
-    <row r="69" spans="13:76" ht="16">
+    <row r="69" spans="13:76">
       <c r="M69" s="18"/>
     </row>
-    <row r="70" spans="13:76" ht="16">
+    <row r="70" spans="13:76">
       <c r="M70" s="18"/>
     </row>
     <row r="71" spans="13:76" ht="15.75" customHeight="1">
       <c r="M71" s="18"/>
       <c r="BX71" s="30"/>
     </row>
-    <row r="72" spans="13:76" ht="16">
+    <row r="72" spans="13:76">
       <c r="M72" s="18"/>
       <c r="BA72" s="111"/>
       <c r="BB72" s="111"/>
     </row>
-    <row r="73" spans="13:76" ht="16">
+    <row r="73" spans="13:76">
       <c r="M73" s="18"/>
       <c r="BA73" s="111"/>
       <c r="BB73" s="111"/>
@@ -62830,14 +62883,14 @@
     <row r="74" spans="13:76" ht="15.75" customHeight="1">
       <c r="M74" s="18"/>
     </row>
-    <row r="75" spans="13:76" ht="16">
+    <row r="75" spans="13:76">
       <c r="M75" s="18"/>
       <c r="BA75" s="112"/>
       <c r="BB75" s="112"/>
     </row>
   </sheetData>
-  <autoFilter ref="T1:T75" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CH75">
+  <autoFilter ref="T1:T75"/>
+  <sortState ref="A2:CH75">
     <sortCondition ref="E1:E75"/>
   </sortState>
   <dataConsolidate/>
@@ -62853,65 +62906,65 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="603" yWindow="1085" count="20">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN27:AP30 AH31:AP42 AH7:AH8 AJ7:AP8 AH55:AP1048576 AL27 AH26:AK27 AL26:AP26 AH28:AL30 S15:S30 S1 U1 AH43:AQ54 U39:U1048576 S34:S1048576 U15:U35 AH15:AP25 AH1:AI1 AK1:AP1" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN27:AP30 AH31:AP42 AH7:AH8 AJ7:AP8 AH55:AP1048576 AL27 AH26:AK27 AL26:AP26 AH28:AL30 S15:S30 S1 U1 AH43:AQ54 U39:U1048576 S34:S1048576 U15:U35 AH15:AP25 AH1:AI1 AK1:AP1">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I30:I1048576 I15:I28" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I1 I30:I1048576 I15:I28">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AD39:AF61 AG7:AG8 AG20:AG30 AD28:AF33 AD27:AE27 AD34:AE38 AG34:AG38 AH61 AD1:AG1 AD62:AG1048576 AD15:AF26" xr:uid="{00000000-0002-0000-0100-000002000000}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y1:AC1 AI7:AI8 Y7:Y8 AA7:AE8 Y15:AC1048576" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AD39:AF61 AG7:AG8 AG20:AG30 AD28:AF33 AD27:AE27 AD34:AE38 AG34:AG38 AH61 AD1:AG1 AD62:AG1048576 AD15:AF26"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y1:AC1 AI7:AI8 Y7:Y8 AA7:AE8 Y15:AC1048576">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN1 BO27:BO30 BO43:BO54 BN62:BN1048576" xr:uid="{00000000-0002-0000-0100-000004000000}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AY55:AY61" xr:uid="{00000000-0002-0000-0100-000005000000}">
+    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN1 BO27:BO30 BO43:BO54 BN62:BN1048576"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1- lower bound_x000a_2 - upper bound_x000a_3- actual" sqref="AY55:AY61">
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY31:AY42 AY15:AY25" xr:uid="{00000000-0002-0000-0100-000006000000}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY31:AY42 AY15:AY25">
       <formula1>1</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV62:AV1048576" xr:uid="{00000000-0002-0000-0100-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV62:AV1048576">
       <formula1>$J$2:$J$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1 U62:U1048576 S55:S1048576" xr:uid="{00000000-0002-0000-0100-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1 U62:U1048576 S55:S1048576">
       <formula1>$M$2:$M$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1 U62:W1048576 S55:S1048576" xr:uid="{00000000-0002-0000-0100-00000B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1 U62:W1048576 S55:S1048576">
       <formula1>$L$2:$L$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1 U62:W1048576 S55:S1048576" xr:uid="{00000000-0002-0000-0100-00000E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1 U62:W1048576 S55:S1048576">
       <formula1>$O$2:$O$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K62:K1048576" xr:uid="{00000000-0002-0000-0100-000011000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K62:K1048576">
       <formula1>$K$2:$K$12</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BT62:BT1048576" xr:uid="{00000000-0002-0000-0100-000012000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BT62:BT1048576">
       <formula1>$P:$P</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G62:G1048576" xr:uid="{00000000-0002-0000-0100-000013000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G62:G1048576">
       <formula1>$T:$T</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR55:AR1048576" xr:uid="{00000000-0002-0000-0100-000014000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR55:AR1048576">
       <formula1>$H:$H</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT55:AT1048576" xr:uid="{00000000-0002-0000-0100-000015000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT55:AT1048576">
       <formula1>$Q:$Q</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O55:O1048576" xr:uid="{00000000-0002-0000-0100-000016000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O55:O1048576">
       <formula1>$O:$O</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E55:E1048576" xr:uid="{00000000-0002-0000-0100-000017000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E55:E1048576">
       <formula1>$S:$S</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1 S55:S1048576 S1" xr:uid="{00000000-0002-0000-0100-000018000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1 S55:S1048576 S1">
       <formula1>$I:$I</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P27:P30 U62:U1048576 P55:P1048576 S55:S1048576 U1 P1" xr:uid="{00000000-0002-0000-0100-00001B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P27:P30 U62:U1048576 P55:P1048576 S55:S1048576 U1 P1">
       <formula1>$N:$N</formula1>
     </dataValidation>
   </dataValidations>
@@ -62921,133 +62974,133 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="603" yWindow="1085" count="22">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000021000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>U1 U62:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000022000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$A$2:$A$4</xm:f>
           </x14:formula1>
           <xm:sqref>BU55:BW1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000023000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$C$2:$C$4</xm:f>
           </x14:formula1>
           <xm:sqref>BO1 BO55:BO1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000024000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$J$2:$J$3</xm:f>
           </x14:formula1>
           <xm:sqref>AV1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000025000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$M$2:$M$9</xm:f>
           </x14:formula1>
           <xm:sqref>U1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000026000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$3</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000027000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$O$2:$O$7</xm:f>
           </x14:formula1>
           <xm:sqref>U1:W1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000028000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$K$2:$K$12</xm:f>
           </x14:formula1>
           <xm:sqref>K1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000029000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$P:$P</xm:f>
           </x14:formula1>
           <xm:sqref>BT1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$T:$T</xm:f>
           </x14:formula1>
           <xm:sqref>G1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H:$H</xm:f>
           </x14:formula1>
           <xm:sqref>AR1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$G:$G</xm:f>
           </x14:formula1>
           <xm:sqref>M76:M1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002D000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$Q:$Q</xm:f>
           </x14:formula1>
           <xm:sqref>AT1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002E000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D:$D</xm:f>
           </x14:formula1>
           <xm:sqref>U62:W1048576 S1 U1:W1 S55:S1048576 N55:N1048576 N1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00002F000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$O:$O</xm:f>
           </x14:formula1>
           <xm:sqref>O1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000030000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$B:$B</xm:f>
           </x14:formula1>
           <xm:sqref>T1 T62:T1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000031000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$S:$S</xm:f>
           </x14:formula1>
           <xm:sqref>E1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000032000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$I:$I</xm:f>
           </x14:formula1>
           <xm:sqref>U62:U1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000033000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$N:$N</xm:f>
           </x14:formula1>
           <xm:sqref>S1</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000034000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$M$2:$M$10</xm:f>
           </x14:formula1>
           <xm:sqref>R1:R1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000035000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$I$1:$I$7</xm:f>
           </x14:formula1>
           <xm:sqref>Q1:Q1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000036000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$E$2:$E$3</xm:f>
           </x14:formula1>
@@ -63060,72 +63113,72 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BJ18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="17" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="36.375" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="29" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="20.125" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="15" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.875" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="29.625" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="33" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="25.875" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="35" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.375" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="15.625" bestFit="1" customWidth="1"/>
     <col min="63" max="64" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -65965,20 +66018,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18.1640625" style="26" customWidth="1"/>
+    <col min="8" max="8" width="18.125" style="26" customWidth="1"/>
     <col min="9" max="9" width="20.5" customWidth="1"/>
-    <col min="10" max="10" width="14.1640625" customWidth="1"/>
-    <col min="11" max="11" width="15.1640625" customWidth="1"/>
+    <col min="10" max="10" width="14.125" customWidth="1"/>
+    <col min="11" max="11" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="39" customFormat="1" ht="17">
+    <row r="1" spans="1:20" s="39" customFormat="1">
       <c r="A1" s="39" t="s">
         <v>425</v>
       </c>
@@ -66037,7 +66090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="34">
+    <row r="2" spans="1:20" ht="31.5">
       <c r="A2">
         <v>0</v>
       </c>
@@ -66096,7 +66149,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="34">
+    <row r="3" spans="1:20" ht="31.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -66155,7 +66208,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="51">
+    <row r="4" spans="1:20" ht="47.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -66205,7 +66258,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="51">
+    <row r="5" spans="1:20" ht="47.25">
       <c r="D5" t="s">
         <v>446</v>
       </c>
@@ -67207,7 +67260,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="S2:T91">
+  <sortState ref="S2:T91">
     <sortCondition ref="S2:S91"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
